--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7828235D-159C-4789-B94D-48E7FE57DE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E760BC-E0DE-4EC7-BE2B-89173D0677FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6693" uniqueCount="6689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6743" uniqueCount="6738">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -20103,18 +20103,173 @@
   </si>
   <si>
     <t>41.338705, 69.206301</t>
+  </si>
+  <si>
+    <t>Xo'jaabot sh., Fayzobod MFY, Egamberdiobod ko‘chasi, 31 uy: г. Ходжаабат, МФЙ Файзобод, улица Эгамбердиобод, дом 31</t>
+  </si>
+  <si>
+    <t>FrХЖА-6</t>
+  </si>
+  <si>
+    <t>998 99 044 45 47</t>
+  </si>
+  <si>
+    <t>@frXja6</t>
+  </si>
+  <si>
+    <t>40.626832, 72.637292</t>
+  </si>
+  <si>
+    <t>Qibray sh., Ulug‘bek MFI, Yoshlik ko‘chasi, 21а uy: г. Кибрай, Улугбек МФИ, улица Ёшлик, дом 21 а</t>
+  </si>
+  <si>
+    <t>FrКИБ-4</t>
+  </si>
+  <si>
+    <t>998 50 872 38 07</t>
+  </si>
+  <si>
+    <t>@Frkib4</t>
+  </si>
+  <si>
+    <t>41.417739, 69.505758</t>
+  </si>
+  <si>
+    <t>Mindonobod sh., Istiqlol ko'chasi, 23 uy: г. Минданабад, улица Истиклол, дом 23</t>
+  </si>
+  <si>
+    <t>FrМНБ-3</t>
+  </si>
+  <si>
+    <t>998 95 096 79 06</t>
+  </si>
+  <si>
+    <t>@fr_mnb_3</t>
+  </si>
+  <si>
+    <t>40.306300, 71.765700</t>
+  </si>
+  <si>
+    <t>Jondor sh., Pochchoyi qishlog'i ko'chasi, 5 а uy: г. Жондор, улица кишлака Поччойи, дом 5 а</t>
+  </si>
+  <si>
+    <t>FrЖНД-3</t>
+  </si>
+  <si>
+    <t>998 97 632 33 03</t>
+  </si>
+  <si>
+    <t>@FrJND3</t>
+  </si>
+  <si>
+    <t>39.738918, 64.115774</t>
+  </si>
+  <si>
+    <t>Jizzax sh., Zargarlik mavzesi, 44 uy: г. Джизак, массив Заргарлик, дом 44</t>
+  </si>
+  <si>
+    <t>FrДЗК-20</t>
+  </si>
+  <si>
+    <t>998 50 791 29 00</t>
+  </si>
+  <si>
+    <t>@FrDZK_20</t>
+  </si>
+  <si>
+    <t>40.134718, 67.831794</t>
+  </si>
+  <si>
+    <t>Eshonguzar sh., Movarounnahr ko'chasi, 17 uy: г. Эшангузар, улица Мовароуннахр, дом 17</t>
+  </si>
+  <si>
+    <t>FrЭШН-2</t>
+  </si>
+  <si>
+    <t>998 70 190 91 50</t>
+  </si>
+  <si>
+    <t>@uzumfreshn_2</t>
+  </si>
+  <si>
+    <t>41.275785, 69.143696</t>
+  </si>
+  <si>
+    <t>Po‘latdarxon sh., Qirqdarxon qishlog'i ko'chasi, 90 uy: г. Пулатдархон, улица кишлак Киркдархон, дом 90</t>
+  </si>
+  <si>
+    <t>FrПТН-2</t>
+  </si>
+  <si>
+    <t>998 50 077 11 88</t>
+  </si>
+  <si>
+    <t>@fr_ptn_2</t>
+  </si>
+  <si>
+    <t>39.738775, 66.969501</t>
+  </si>
+  <si>
+    <t>Yangiyo'l sh., Bahor MFY, Shodiyona ko'chasi, 68 a uy: г. Янгиюль, Бахор МФИ, улица Шодийона, дом 68 а</t>
+  </si>
+  <si>
+    <t>FrЯНГ-15</t>
+  </si>
+  <si>
+    <t>998 93 313 47 01</t>
+  </si>
+  <si>
+    <t>@FRYAN_15</t>
+  </si>
+  <si>
+    <t>41.148576, 69.089501</t>
+  </si>
+  <si>
+    <t>Gullanbog' sh., Xiva tumani, Qishloq Ravnaqi ko'chasi, 287 uy: г. Гулланбаг, Хивинский район, улица Кишлок Равнаки, дом 287</t>
+  </si>
+  <si>
+    <t>FrГЛЛ-1</t>
+  </si>
+  <si>
+    <t>998 50 907 67 37</t>
+  </si>
+  <si>
+    <t>@FrGLL1</t>
+  </si>
+  <si>
+    <t>41.403832, 60.472987</t>
+  </si>
+  <si>
+    <t>Xiva sh., Xorazmiy ko'chasi, 50/3 uy: г. Хива, улица Хоразмий, дом 50/3</t>
+  </si>
+  <si>
+    <t>FrХИВ-11</t>
+  </si>
+  <si>
+    <t>@FrXIV11</t>
+  </si>
+  <si>
+    <t>41.412419, 60.338409</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -20217,63 +20372,75 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -20580,7 +20747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1666"/>
+  <dimension ref="A1:E1676"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.33203125" style="1" customWidth="1"/>
@@ -48895,20 +49062,190 @@
       </c>
     </row>
     <row r="1666" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A1666" s="5" t="s">
+      <c r="A1666" s="10" t="s">
         <v>6684</v>
       </c>
-      <c r="B1666" s="6" t="s">
+      <c r="B1666" s="20" t="s">
         <v>6685</v>
       </c>
-      <c r="C1666" s="19" t="s">
+      <c r="C1666" s="21" t="s">
         <v>6686</v>
       </c>
-      <c r="D1666" s="8" t="s">
+      <c r="D1666" s="11" t="s">
         <v>6687</v>
       </c>
-      <c r="E1666" s="8" t="s">
+      <c r="E1666" s="11" t="s">
         <v>6688</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1667" s="5" t="s">
+        <v>6689</v>
+      </c>
+      <c r="B1667" s="13" t="s">
+        <v>6690</v>
+      </c>
+      <c r="C1667" s="22" t="s">
+        <v>6691</v>
+      </c>
+      <c r="D1667" s="8" t="s">
+        <v>6692</v>
+      </c>
+      <c r="E1667" s="8" t="s">
+        <v>6693</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1668" s="15" t="s">
+        <v>6694</v>
+      </c>
+      <c r="B1668" s="13" t="s">
+        <v>6695</v>
+      </c>
+      <c r="C1668" s="23" t="s">
+        <v>6696</v>
+      </c>
+      <c r="D1668" s="13" t="s">
+        <v>6697</v>
+      </c>
+      <c r="E1668" s="13" t="s">
+        <v>6698</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1669" s="5" t="s">
+        <v>6699</v>
+      </c>
+      <c r="B1669" s="13" t="s">
+        <v>6700</v>
+      </c>
+      <c r="C1669" s="22" t="s">
+        <v>6701</v>
+      </c>
+      <c r="D1669" s="8" t="s">
+        <v>6702</v>
+      </c>
+      <c r="E1669" s="8" t="s">
+        <v>6703</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1670" s="15" t="s">
+        <v>6704</v>
+      </c>
+      <c r="B1670" s="13" t="s">
+        <v>6705</v>
+      </c>
+      <c r="C1670" s="23" t="s">
+        <v>6706</v>
+      </c>
+      <c r="D1670" s="13" t="s">
+        <v>6707</v>
+      </c>
+      <c r="E1670" s="13" t="s">
+        <v>6708</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1671" s="5" t="s">
+        <v>6709</v>
+      </c>
+      <c r="B1671" s="13" t="s">
+        <v>6710</v>
+      </c>
+      <c r="C1671" s="22" t="s">
+        <v>6711</v>
+      </c>
+      <c r="D1671" s="8" t="s">
+        <v>6712</v>
+      </c>
+      <c r="E1671" s="8" t="s">
+        <v>6713</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1672" s="5" t="s">
+        <v>6714</v>
+      </c>
+      <c r="B1672" s="13" t="s">
+        <v>6715</v>
+      </c>
+      <c r="C1672" s="22" t="s">
+        <v>6716</v>
+      </c>
+      <c r="D1672" s="8" t="s">
+        <v>6717</v>
+      </c>
+      <c r="E1672" s="8" t="s">
+        <v>6718</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1673" s="5" t="s">
+        <v>6719</v>
+      </c>
+      <c r="B1673" s="13" t="s">
+        <v>6720</v>
+      </c>
+      <c r="C1673" s="22" t="s">
+        <v>6721</v>
+      </c>
+      <c r="D1673" s="8" t="s">
+        <v>6722</v>
+      </c>
+      <c r="E1673" s="8" t="s">
+        <v>6723</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1674" s="5" t="s">
+        <v>6724</v>
+      </c>
+      <c r="B1674" s="13" t="s">
+        <v>6725</v>
+      </c>
+      <c r="C1674" s="22" t="s">
+        <v>6726</v>
+      </c>
+      <c r="D1674" s="8" t="s">
+        <v>6727</v>
+      </c>
+      <c r="E1674" s="8" t="s">
+        <v>6728</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1675" s="5" t="s">
+        <v>6729</v>
+      </c>
+      <c r="B1675" s="13" t="s">
+        <v>6730</v>
+      </c>
+      <c r="C1675" s="22" t="s">
+        <v>6731</v>
+      </c>
+      <c r="D1675" s="8" t="s">
+        <v>6732</v>
+      </c>
+      <c r="E1675" s="8" t="s">
+        <v>6733</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1676" s="5" t="s">
+        <v>6734</v>
+      </c>
+      <c r="B1676" s="13" t="s">
+        <v>6735</v>
+      </c>
+      <c r="C1676" s="22" t="s">
+        <v>6731</v>
+      </c>
+      <c r="D1676" s="8" t="s">
+        <v>6736</v>
+      </c>
+      <c r="E1676" s="8" t="s">
+        <v>6737</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E760BC-E0DE-4EC7-BE2B-89173D0677FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96ABFE03-51DE-490D-AA5F-95FB0C2E2AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6743" uniqueCount="6738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6778" uniqueCount="6773">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -20250,18 +20250,131 @@
   </si>
   <si>
     <t>41.412419, 60.338409</t>
+  </si>
+  <si>
+    <t>Fayziobod sh., Uychi tumani, Xayrullayev ko'chasi, 38 uy: г. Файзиабад, Уйчинский район, улица Хайруллаева, дом 38</t>
+  </si>
+  <si>
+    <t>FrФЗБ-2</t>
+  </si>
+  <si>
+    <t>998 33 303 25 55</t>
+  </si>
+  <si>
+    <t>@UzumFrFZB2</t>
+  </si>
+  <si>
+    <t>41.003799, 71.808663</t>
+  </si>
+  <si>
+    <t>Chandavul sh., Kosonsoy tumani, Go‘zalkent ko‘chasi, 131 uy: г. Чандавуль, Касансайский район, улица Гузалкент, дом 131</t>
+  </si>
+  <si>
+    <t>FrЧАН-1</t>
+  </si>
+  <si>
+    <t>998 90 069 21 26</t>
+  </si>
+  <si>
+    <t>@UzumFrCHAN1</t>
+  </si>
+  <si>
+    <t>41.187581, 71.515779</t>
+  </si>
+  <si>
+    <t>Oltinko'l sh., Oltinko‘l tumani, Boʻston MFY, Yaxshilik ko'chasi, 39 uy: г. Алтынкуль, Алтынкульский район, Бустон МФИ, улица Яхшилик, дом 39</t>
+  </si>
+  <si>
+    <t>FrАЛУ-2</t>
+  </si>
+  <si>
+    <t>998 92 150 81 98</t>
+  </si>
+  <si>
+    <t>@FrALU_2</t>
+  </si>
+  <si>
+    <t>40.802484, 72.108651</t>
+  </si>
+  <si>
+    <t>Marg‘uzar sh., Pop tumani, Amir Temur ko'chasi, 16 uy: г. Маргузар, Папский район, улица Амира Темура, дом 16</t>
+  </si>
+  <si>
+    <t>FrМГР-1</t>
+  </si>
+  <si>
+    <t>998 95 591 04 04</t>
+  </si>
+  <si>
+    <t>@UzumFrMGR1</t>
+  </si>
+  <si>
+    <t>40.841817, 71.029901</t>
+  </si>
+  <si>
+    <t>Yarkatoy sh., Uychi tumani, Amir Temur ko'chasi, 99 uy: г. Яркатай, Уйчинский район, улица Амира Темура, дом 99</t>
+  </si>
+  <si>
+    <t>FrЯРТ-1</t>
+  </si>
+  <si>
+    <t>998 90 705 03 15</t>
+  </si>
+  <si>
+    <t>@UzumFrYART1</t>
+  </si>
+  <si>
+    <t>41.023845, 71.807683</t>
+  </si>
+  <si>
+    <t>Jaloyir sh., Qumqo‘rg‘on tumani, Afrosiyob ko'chasi, 72 а uy: г. Джалаир, Кумкурганский район, улица Афросиёб, дом 72а</t>
+  </si>
+  <si>
+    <t>FrДЖЛ-1</t>
+  </si>
+  <si>
+    <t>998 77 832 21 20</t>
+  </si>
+  <si>
+    <t>@FrDJL1</t>
+  </si>
+  <si>
+    <t>37.755865, 67.543348</t>
+  </si>
+  <si>
+    <t>Chinoz sh., Madaniyat MFY, Rovot ko‘chasi, 7 uy: г. Чиназ, Маданият МФИ, улица Ровот, дом 7</t>
+  </si>
+  <si>
+    <t>FrЧИН-9</t>
+  </si>
+  <si>
+    <t>998 88 093 44 83</t>
+  </si>
+  <si>
+    <t>@uzunfrchin_9</t>
+  </si>
+  <si>
+    <t>41.037315, 68.860009</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -20372,57 +20485,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -20431,16 +20553,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -20747,7 +20866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1676"/>
+  <dimension ref="A1:E1683"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="58.33203125" style="1" customWidth="1"/>
@@ -49232,20 +49351,139 @@
       </c>
     </row>
     <row r="1676" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A1676" s="5" t="s">
+      <c r="A1676" s="10" t="s">
         <v>6734</v>
       </c>
-      <c r="B1676" s="13" t="s">
+      <c r="B1676" s="17" t="s">
         <v>6735</v>
       </c>
-      <c r="C1676" s="22" t="s">
+      <c r="C1676" s="24" t="s">
         <v>6731</v>
       </c>
-      <c r="D1676" s="8" t="s">
+      <c r="D1676" s="11" t="s">
         <v>6736</v>
       </c>
-      <c r="E1676" s="8" t="s">
+      <c r="E1676" s="11" t="s">
         <v>6737</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1677" s="5" t="s">
+        <v>6738</v>
+      </c>
+      <c r="B1677" s="13" t="s">
+        <v>6739</v>
+      </c>
+      <c r="C1677" s="25" t="s">
+        <v>6740</v>
+      </c>
+      <c r="D1677" s="8" t="s">
+        <v>6741</v>
+      </c>
+      <c r="E1677" s="8" t="s">
+        <v>6742</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1678" s="5" t="s">
+        <v>6743</v>
+      </c>
+      <c r="B1678" s="13" t="s">
+        <v>6744</v>
+      </c>
+      <c r="C1678" s="25" t="s">
+        <v>6745</v>
+      </c>
+      <c r="D1678" s="8" t="s">
+        <v>6746</v>
+      </c>
+      <c r="E1678" s="8" t="s">
+        <v>6747</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A1679" s="5" t="s">
+        <v>6748</v>
+      </c>
+      <c r="B1679" s="13" t="s">
+        <v>6749</v>
+      </c>
+      <c r="C1679" s="25" t="s">
+        <v>6750</v>
+      </c>
+      <c r="D1679" s="8" t="s">
+        <v>6751</v>
+      </c>
+      <c r="E1679" s="8" t="s">
+        <v>6752</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1680" s="5" t="s">
+        <v>6753</v>
+      </c>
+      <c r="B1680" s="13" t="s">
+        <v>6754</v>
+      </c>
+      <c r="C1680" s="25" t="s">
+        <v>6755</v>
+      </c>
+      <c r="D1680" s="8" t="s">
+        <v>6756</v>
+      </c>
+      <c r="E1680" s="8" t="s">
+        <v>6757</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1681" s="5" t="s">
+        <v>6758</v>
+      </c>
+      <c r="B1681" s="13" t="s">
+        <v>6759</v>
+      </c>
+      <c r="C1681" s="25" t="s">
+        <v>6760</v>
+      </c>
+      <c r="D1681" s="8" t="s">
+        <v>6761</v>
+      </c>
+      <c r="E1681" s="8" t="s">
+        <v>6762</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1682" s="5" t="s">
+        <v>6763</v>
+      </c>
+      <c r="B1682" s="13" t="s">
+        <v>6764</v>
+      </c>
+      <c r="C1682" s="25" t="s">
+        <v>6765</v>
+      </c>
+      <c r="D1682" s="8" t="s">
+        <v>6766</v>
+      </c>
+      <c r="E1682" s="8" t="s">
+        <v>6767</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:5" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1683" s="5" t="s">
+        <v>6768</v>
+      </c>
+      <c r="B1683" s="13" t="s">
+        <v>6769</v>
+      </c>
+      <c r="C1683" s="25" t="s">
+        <v>6770</v>
+      </c>
+      <c r="D1683" s="8" t="s">
+        <v>6771</v>
+      </c>
+      <c r="E1683" s="8" t="s">
+        <v>6772</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC4AF2C-BF14-46D8-8780-2AFA2CD563A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D13FBBC-55DF-4252-A3CC-46F461DCF89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="2535" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6923" uniqueCount="6916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7038" uniqueCount="7030">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -20784,18 +20784,368 @@
   </si>
   <si>
     <t>39.947479, 65.933013</t>
+  </si>
+  <si>
+    <t>Zangiota sh., Madaniyat MFI, Amir Temur ko‘chasi, 74 uy: г. Зангиота, Маданият МФИ, улица Эмира Тимура, дом 74</t>
+  </si>
+  <si>
+    <t>FrЗГН-3</t>
+  </si>
+  <si>
+    <t>998 50 111 39 18</t>
+  </si>
+  <si>
+    <t>@FrZGN3</t>
+  </si>
+  <si>
+    <t>41.210804, 69.170781</t>
+  </si>
+  <si>
+    <t>Shofirkon sh., Alisher Navoiy MFY, Ko‘hna Qumbosti ko'chasi, 99 uy: г. Шафиркан, Алишер Навои МФИ, улица Кухна Кумбости, дом 99</t>
+  </si>
+  <si>
+    <t>FrШРН-5</t>
+  </si>
+  <si>
+    <t>998 99 983 71 03</t>
+  </si>
+  <si>
+    <t>@frshrn_5</t>
+  </si>
+  <si>
+    <t>40.110271, 64.454134</t>
+  </si>
+  <si>
+    <t>Navbahor sh., Namangan tumai, Gulbahor kochasi 61A uy: г. Навбахор, Наманганский район, улица Гулбахор, 61A</t>
+  </si>
+  <si>
+    <t>FrНВХ-1</t>
+  </si>
+  <si>
+    <t>998 77 687 30 06</t>
+  </si>
+  <si>
+    <t>@UzumFrNVX1</t>
+  </si>
+  <si>
+    <t>40.965618, 71.666409</t>
+  </si>
+  <si>
+    <t>Vobkent sh., Kumushkent ko'chasi, 436 uy: г. Вабкент, улица Кумушкент, дом 436</t>
+  </si>
+  <si>
+    <t>FrВБК-3</t>
+  </si>
+  <si>
+    <t>998 50 785 59 82</t>
+  </si>
+  <si>
+    <t>@FRVBK_3</t>
+  </si>
+  <si>
+    <t>40.015329, 64.628401</t>
+  </si>
+  <si>
+    <t>Asaka sh., Karvonsaroy ko'chasi, 112 uy: г. Асака, улица Карвонсарой, дом 112</t>
+  </si>
+  <si>
+    <t>FrАСК-7</t>
+  </si>
+  <si>
+    <t>998 94 182 97 02</t>
+  </si>
+  <si>
+    <t>@frask_7</t>
+  </si>
+  <si>
+    <t>40.642417, 72.262545</t>
+  </si>
+  <si>
+    <t>G‘ijduvon sh., Zarafshon MFI, Janubiy Yangirabot ko‘chasi, 19 uy: г. Гиждуван, Зарафшон МФИ, улица Жанубий Янгиработ, дом 19</t>
+  </si>
+  <si>
+    <t>FrГЖД-7</t>
+  </si>
+  <si>
+    <t>998 95 781 95 45</t>
+  </si>
+  <si>
+    <t>@FrGJD7</t>
+  </si>
+  <si>
+    <t>40.057546, 64.636756</t>
+  </si>
+  <si>
+    <t>Shahidmazar sh., Uychi tumani, Churtuki ko'chasi, 13 uy: г. Шахидмазар, Уйчинский район, улица Чуртукй, дом 13</t>
+  </si>
+  <si>
+    <t>FrШАХ-1</t>
+  </si>
+  <si>
+    <t>998 94 518 70 20</t>
+  </si>
+  <si>
+    <t>@UzumFrSHAX1</t>
+  </si>
+  <si>
+    <t>41.007569, 71.789513</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yunusobod tumani, Shahriston ko'chasi, 1-1А uy: г. Ташкент, Юнусабадский район, улица Шахристанская, дом 1-1А</t>
+  </si>
+  <si>
+    <t>FrТАШ-448</t>
+  </si>
+  <si>
+    <t>998 50 302 69 84</t>
+  </si>
+  <si>
+    <t>@frtash_448</t>
+  </si>
+  <si>
+    <t>41.351586, 69.285142</t>
+  </si>
+  <si>
+    <t>Bo'ka sh., Yorkin ko'chasi, 333 uy: г. Бука, улица Ёркин, дом 333</t>
+  </si>
+  <si>
+    <t>FrБУК-6</t>
+  </si>
+  <si>
+    <t>998 93 386 66 11</t>
+  </si>
+  <si>
+    <t>@uzumfrbuk_6</t>
+  </si>
+  <si>
+    <t>40.813523, 69.186517</t>
+  </si>
+  <si>
+    <t>Qoraqum sh., Muborak tumani, Qoraqum ko'chasi, 39 uy: г. Каракум, Мубарекский район, улица Каракум, дом 39</t>
+  </si>
+  <si>
+    <t>FrККМ-1</t>
+  </si>
+  <si>
+    <t>998 93 627 16 36</t>
+  </si>
+  <si>
+    <t>@KKM1UZUM</t>
+  </si>
+  <si>
+    <t>39.114792, 65.428964</t>
+  </si>
+  <si>
+    <t>Dashtabad sh., Zaamin tumani, Mustaqillik ko'chasi, 27c uy: г. Даштабад, Зааминский район, улица Мустакиллик, дом 27c</t>
+  </si>
+  <si>
+    <t>FrДШТ-2</t>
+  </si>
+  <si>
+    <t>998 99 947 04 27</t>
+  </si>
+  <si>
+    <t>@FrDSHT2</t>
+  </si>
+  <si>
+    <t>40.113299, 68.489096</t>
+  </si>
+  <si>
+    <t>Aimcha Kakir sh., O‘zbekiston tumani, Aimcha Kakir ko'chasi, 28 а uy: г. Аимча Какыр, Узбекистанский район, улица Аимча Какыр, дом 28 а</t>
+  </si>
+  <si>
+    <t>FrАМЧ-1</t>
+  </si>
+  <si>
+    <t>998 70 329 20 27</t>
+  </si>
+  <si>
+    <t>@uzum_yaypan</t>
+  </si>
+  <si>
+    <t>40.335238, 70.786770</t>
+  </si>
+  <si>
+    <t>Ziyodin sh., Amir Temur ko'chasi, 15 uy: г. Зиадин, улица Амира Темура, дом 15</t>
+  </si>
+  <si>
+    <t>FrЗИН-4</t>
+  </si>
+  <si>
+    <t>998 99 653 60 30</t>
+  </si>
+  <si>
+    <t>@uzumzin4</t>
+  </si>
+  <si>
+    <t>40.037900, 65.652000</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Usta Umarqul Jo‘raqulova ko'chasi, 7 uy: г. Самарканд, улица Уста Умаркула Журакулова, дом 7</t>
+  </si>
+  <si>
+    <t>FrСМК-82</t>
+  </si>
+  <si>
+    <t>998 77 500 02 33</t>
+  </si>
+  <si>
+    <t>@fr_smk_82</t>
+  </si>
+  <si>
+    <t>39.661406, 66.984978</t>
+  </si>
+  <si>
+    <t>Kakirchek sh., Baliqchi tumani, Dilkushod ko'chasi, 66 uy: г. Какирчек, Балыкчинский район, Улица Дилкушод, дом 66</t>
+  </si>
+  <si>
+    <t>FrКИК-1</t>
+  </si>
+  <si>
+    <t>998 94 433 35 36</t>
+  </si>
+  <si>
+    <t>@frKIK_1</t>
+  </si>
+  <si>
+    <t>40.789800, 71.880800</t>
+  </si>
+  <si>
+    <t>Yangiqurilish sh., Oltinsoy tumani, Yangiqurilish ko'chasi, 70 a uy: г. Янгикурилиш, Алтынсайский район, улица Янгикурилиш, дом 70 а</t>
+  </si>
+  <si>
+    <t>FrЯКШ-1</t>
+  </si>
+  <si>
+    <t>998 99 832 75 55</t>
+  </si>
+  <si>
+    <t>@Btp_1604</t>
+  </si>
+  <si>
+    <t>38.156692, 67.760303</t>
+  </si>
+  <si>
+    <t>Qo'ng'irot sh., O'rnak guzari ko'chasi, 13 b uy: г. Кунград, улица Орнек Гузари, дом 13 б</t>
+  </si>
+  <si>
+    <t>FrКУН-4</t>
+  </si>
+  <si>
+    <t>998 99 372 84 53</t>
+  </si>
+  <si>
+    <t>@uzumkungrad_4</t>
+  </si>
+  <si>
+    <t>43.055897, 58.797312</t>
+  </si>
+  <si>
+    <t>Muratali sh., Fidoilar ko'chasi, 1 а uy: г. Муратали, улица Фидойлар, дом 1 а</t>
+  </si>
+  <si>
+    <t>FrМРТ-1</t>
+  </si>
+  <si>
+    <t>998 88 758 19 85</t>
+  </si>
+  <si>
+    <t>@uzumfrmrt_1</t>
+  </si>
+  <si>
+    <t>40.820353, 69.338187</t>
+  </si>
+  <si>
+    <t>Pop sh., Paxtakor ko'chasi, 163 uy: г. Пап, улица Пахтакор, дом 163</t>
+  </si>
+  <si>
+    <t>FrПАП-7</t>
+  </si>
+  <si>
+    <t>@UzumFrPAP7</t>
+  </si>
+  <si>
+    <t>40.879881, 71.105841</t>
+  </si>
+  <si>
+    <t>Bo'ston sh., Alisher Navoiy ko'chasi, 272 uy: г. Бустан, улица Алишера Навои, дом 272</t>
+  </si>
+  <si>
+    <t>FrБТН-4</t>
+  </si>
+  <si>
+    <t>998 87 864 96 00</t>
+  </si>
+  <si>
+    <t>@FrBTH_4</t>
+  </si>
+  <si>
+    <t>41.835125, 60.917744</t>
+  </si>
+  <si>
+    <t>Karnab sh., Paxtachi tumani, Kaxramon ko'chasi, 41 uy: г. Карнаб, Пахтачийский район, улица Кахрамон, дом 41</t>
+  </si>
+  <si>
+    <t>FrКНБ-1</t>
+  </si>
+  <si>
+    <t>998 97 393 73 37</t>
+  </si>
+  <si>
+    <t>@Uzum_qarnab</t>
+  </si>
+  <si>
+    <t>39.837894, 65.500748</t>
+  </si>
+  <si>
+    <t>Sherobod sh., Doʻstlik MFY, Mustaqillik ko'chasi, 31 g uy: г. Шерабад, Дустлик МФИ, улица Мустакиллик, дом 31 г</t>
+  </si>
+  <si>
+    <t>FrШЕР-6</t>
+  </si>
+  <si>
+    <t>998 77 407 02 21</t>
+  </si>
+  <si>
+    <t>@FrSHER6</t>
+  </si>
+  <si>
+    <t>37.666813, 67.027089</t>
+  </si>
+  <si>
+    <t>Ziyodin sh., Istiqlol ko'chasi, 39 uy: г. Зиадин, улица Истиклол, дом 39</t>
+  </si>
+  <si>
+    <t>FrЗИН-5</t>
+  </si>
+  <si>
+    <t>998 99 195 00 78</t>
+  </si>
+  <si>
+    <t>@uzumzin5</t>
+  </si>
+  <si>
+    <t>40.024588, 65.664144</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -20922,57 +21272,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -20981,7 +21340,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -20990,16 +21349,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21312,7 +21674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1712"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -50409,20 +50771,411 @@
       </c>
     </row>
     <row r="1712" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1712" s="15" t="s">
+      <c r="A1712" s="29" t="s">
         <v>6911</v>
       </c>
-      <c r="B1712" s="13" t="s">
+      <c r="B1712" s="17" t="s">
         <v>6912</v>
       </c>
-      <c r="C1712" s="28" t="s">
+      <c r="C1712" s="30" t="s">
         <v>6913</v>
       </c>
-      <c r="D1712" s="13" t="s">
+      <c r="D1712" s="17" t="s">
         <v>6914</v>
       </c>
-      <c r="E1712" s="13" t="s">
+      <c r="E1712" s="17" t="s">
         <v>6915</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1713" s="5" t="s">
+        <v>6916</v>
+      </c>
+      <c r="B1713" s="13" t="s">
+        <v>6917</v>
+      </c>
+      <c r="C1713" s="31" t="s">
+        <v>6918</v>
+      </c>
+      <c r="D1713" s="8" t="s">
+        <v>6919</v>
+      </c>
+      <c r="E1713" s="8" t="s">
+        <v>6920</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1714" s="5" t="s">
+        <v>6921</v>
+      </c>
+      <c r="B1714" s="13" t="s">
+        <v>6922</v>
+      </c>
+      <c r="C1714" s="31" t="s">
+        <v>6923</v>
+      </c>
+      <c r="D1714" s="8" t="s">
+        <v>6924</v>
+      </c>
+      <c r="E1714" s="8" t="s">
+        <v>6925</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1715" s="5" t="s">
+        <v>6926</v>
+      </c>
+      <c r="B1715" s="13" t="s">
+        <v>6927</v>
+      </c>
+      <c r="C1715" s="31" t="s">
+        <v>6928</v>
+      </c>
+      <c r="D1715" s="8" t="s">
+        <v>6929</v>
+      </c>
+      <c r="E1715" s="8" t="s">
+        <v>6930</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1716" s="5" t="s">
+        <v>6931</v>
+      </c>
+      <c r="B1716" s="13" t="s">
+        <v>6932</v>
+      </c>
+      <c r="C1716" s="31" t="s">
+        <v>6933</v>
+      </c>
+      <c r="D1716" s="8" t="s">
+        <v>6934</v>
+      </c>
+      <c r="E1716" s="8" t="s">
+        <v>6935</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1717" s="5" t="s">
+        <v>6936</v>
+      </c>
+      <c r="B1717" s="13" t="s">
+        <v>6937</v>
+      </c>
+      <c r="C1717" s="31" t="s">
+        <v>6938</v>
+      </c>
+      <c r="D1717" s="8" t="s">
+        <v>6939</v>
+      </c>
+      <c r="E1717" s="8" t="s">
+        <v>6940</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1718" s="5" t="s">
+        <v>6941</v>
+      </c>
+      <c r="B1718" s="13" t="s">
+        <v>6942</v>
+      </c>
+      <c r="C1718" s="31" t="s">
+        <v>6943</v>
+      </c>
+      <c r="D1718" s="8" t="s">
+        <v>6944</v>
+      </c>
+      <c r="E1718" s="8" t="s">
+        <v>6945</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1719" s="5" t="s">
+        <v>6946</v>
+      </c>
+      <c r="B1719" s="13" t="s">
+        <v>6947</v>
+      </c>
+      <c r="C1719" s="31" t="s">
+        <v>6948</v>
+      </c>
+      <c r="D1719" s="8" t="s">
+        <v>6949</v>
+      </c>
+      <c r="E1719" s="8" t="s">
+        <v>6950</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1720" s="15" t="s">
+        <v>6951</v>
+      </c>
+      <c r="B1720" s="13" t="s">
+        <v>6952</v>
+      </c>
+      <c r="C1720" s="32" t="s">
+        <v>6953</v>
+      </c>
+      <c r="D1720" s="13" t="s">
+        <v>6954</v>
+      </c>
+      <c r="E1720" s="13" t="s">
+        <v>6955</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1721" s="5" t="s">
+        <v>6956</v>
+      </c>
+      <c r="B1721" s="13" t="s">
+        <v>6957</v>
+      </c>
+      <c r="C1721" s="31" t="s">
+        <v>6958</v>
+      </c>
+      <c r="D1721" s="8" t="s">
+        <v>6959</v>
+      </c>
+      <c r="E1721" s="8" t="s">
+        <v>6960</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1722" s="5" t="s">
+        <v>6961</v>
+      </c>
+      <c r="B1722" s="13" t="s">
+        <v>6962</v>
+      </c>
+      <c r="C1722" s="31" t="s">
+        <v>6963</v>
+      </c>
+      <c r="D1722" s="8" t="s">
+        <v>6964</v>
+      </c>
+      <c r="E1722" s="8" t="s">
+        <v>6965</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1723" s="5" t="s">
+        <v>6966</v>
+      </c>
+      <c r="B1723" s="13" t="s">
+        <v>6967</v>
+      </c>
+      <c r="C1723" s="31" t="s">
+        <v>6968</v>
+      </c>
+      <c r="D1723" s="8" t="s">
+        <v>6969</v>
+      </c>
+      <c r="E1723" s="8" t="s">
+        <v>6970</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1724" s="5" t="s">
+        <v>6971</v>
+      </c>
+      <c r="B1724" s="13" t="s">
+        <v>6972</v>
+      </c>
+      <c r="C1724" s="31" t="s">
+        <v>6973</v>
+      </c>
+      <c r="D1724" s="8" t="s">
+        <v>6974</v>
+      </c>
+      <c r="E1724" s="8" t="s">
+        <v>6975</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1725" s="15" t="s">
+        <v>6976</v>
+      </c>
+      <c r="B1725" s="13" t="s">
+        <v>6977</v>
+      </c>
+      <c r="C1725" s="32" t="s">
+        <v>6978</v>
+      </c>
+      <c r="D1725" s="13" t="s">
+        <v>6979</v>
+      </c>
+      <c r="E1725" s="13" t="s">
+        <v>6980</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1726" s="15" t="s">
+        <v>6981</v>
+      </c>
+      <c r="B1726" s="13" t="s">
+        <v>6982</v>
+      </c>
+      <c r="C1726" s="32" t="s">
+        <v>6983</v>
+      </c>
+      <c r="D1726" s="13" t="s">
+        <v>6984</v>
+      </c>
+      <c r="E1726" s="13" t="s">
+        <v>6985</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1727" s="15" t="s">
+        <v>6986</v>
+      </c>
+      <c r="B1727" s="13" t="s">
+        <v>6987</v>
+      </c>
+      <c r="C1727" s="32" t="s">
+        <v>6988</v>
+      </c>
+      <c r="D1727" s="13" t="s">
+        <v>6989</v>
+      </c>
+      <c r="E1727" s="13" t="s">
+        <v>6990</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1728" s="15" t="s">
+        <v>6991</v>
+      </c>
+      <c r="B1728" s="13" t="s">
+        <v>6992</v>
+      </c>
+      <c r="C1728" s="32" t="s">
+        <v>6993</v>
+      </c>
+      <c r="D1728" s="13" t="s">
+        <v>6994</v>
+      </c>
+      <c r="E1728" s="13" t="s">
+        <v>6995</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1729" s="15" t="s">
+        <v>6996</v>
+      </c>
+      <c r="B1729" s="13" t="s">
+        <v>6997</v>
+      </c>
+      <c r="C1729" s="32" t="s">
+        <v>6998</v>
+      </c>
+      <c r="D1729" s="13" t="s">
+        <v>6999</v>
+      </c>
+      <c r="E1729" s="13" t="s">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1730" s="15" t="s">
+        <v>7001</v>
+      </c>
+      <c r="B1730" s="13" t="s">
+        <v>7002</v>
+      </c>
+      <c r="C1730" s="31" t="s">
+        <v>7003</v>
+      </c>
+      <c r="D1730" s="8" t="s">
+        <v>7004</v>
+      </c>
+      <c r="E1730" s="8" t="s">
+        <v>7005</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1731" s="5" t="s">
+        <v>7006</v>
+      </c>
+      <c r="B1731" s="13" t="s">
+        <v>7007</v>
+      </c>
+      <c r="C1731" s="31" t="s">
+        <v>6948</v>
+      </c>
+      <c r="D1731" s="8" t="s">
+        <v>7008</v>
+      </c>
+      <c r="E1731" s="8" t="s">
+        <v>7009</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1732" s="5" t="s">
+        <v>7010</v>
+      </c>
+      <c r="B1732" s="13" t="s">
+        <v>7011</v>
+      </c>
+      <c r="C1732" s="31" t="s">
+        <v>7012</v>
+      </c>
+      <c r="D1732" s="8" t="s">
+        <v>7013</v>
+      </c>
+      <c r="E1732" s="8" t="s">
+        <v>7014</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1733" s="5" t="s">
+        <v>7015</v>
+      </c>
+      <c r="B1733" s="13" t="s">
+        <v>7016</v>
+      </c>
+      <c r="C1733" s="31" t="s">
+        <v>7017</v>
+      </c>
+      <c r="D1733" s="8" t="s">
+        <v>7018</v>
+      </c>
+      <c r="E1733" s="8" t="s">
+        <v>7019</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1734" s="15" t="s">
+        <v>7020</v>
+      </c>
+      <c r="B1734" s="13" t="s">
+        <v>7021</v>
+      </c>
+      <c r="C1734" s="32" t="s">
+        <v>7022</v>
+      </c>
+      <c r="D1734" s="13" t="s">
+        <v>7023</v>
+      </c>
+      <c r="E1734" s="13" t="s">
+        <v>7024</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1735" s="5" t="s">
+        <v>7025</v>
+      </c>
+      <c r="B1735" s="8" t="s">
+        <v>7026</v>
+      </c>
+      <c r="C1735" s="31" t="s">
+        <v>7027</v>
+      </c>
+      <c r="D1735" s="8" t="s">
+        <v>7028</v>
+      </c>
+      <c r="E1735" s="8" t="s">
+        <v>7029</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D13FBBC-55DF-4252-A3CC-46F461DCF89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F41D5C-560D-4EC5-97B5-0F870D21D123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="2535" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7038" uniqueCount="7030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7108" uniqueCount="7100">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -21126,18 +21126,236 @@
   </si>
   <si>
     <t>40.024588, 65.664144</t>
+  </si>
+  <si>
+    <t>Kulla sh., Ittifoq ko'chasi, 10 uy: г. Кулла, улица Иттифок, дом 10</t>
+  </si>
+  <si>
+    <t>FrКУЛ-1</t>
+  </si>
+  <si>
+    <t>998 33 498 50 50</t>
+  </si>
+  <si>
+    <t>@FrKUL_1</t>
+  </si>
+  <si>
+    <t>40.630306, 72.375788</t>
+  </si>
+  <si>
+    <t>Yangi Turmush sh., Angor tumani, Markaz ko'chasi, 3 v uy: г Янги Турмуш, Ангорский район, улица Марказ, дом 3в</t>
+  </si>
+  <si>
+    <t>FrЯТМ-1</t>
+  </si>
+  <si>
+    <t>998 87 935 68 68</t>
+  </si>
+  <si>
+    <t>@Tohir6868</t>
+  </si>
+  <si>
+    <t>37.444148, 67.156752</t>
+  </si>
+  <si>
+    <t>Nurobod sh., Qilichli MFY, Qilichli 4 ko'chasi, 20 uy: г. Нурабад, Клычли МФИ, улица Клычли 4, дом 20</t>
+  </si>
+  <si>
+    <t>FrНРД-3</t>
+  </si>
+  <si>
+    <t>998 33 703 22 77</t>
+  </si>
+  <si>
+    <t>@theeksb</t>
+  </si>
+  <si>
+    <t>39.615634, 66.262011</t>
+  </si>
+  <si>
+    <t>Nukus sh., Islom Karimov shoh ko'chasi, 179 B uy: г. Нукус, проспект Ислама Каримова, 179 Б</t>
+  </si>
+  <si>
+    <t>FrНУК-25</t>
+  </si>
+  <si>
+    <t>998 95 730 62 40</t>
+  </si>
+  <si>
+    <t>@uzumnuk25</t>
+  </si>
+  <si>
+    <t>42.480024, 59.611149</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Olimlar ko'chasi, 1 а uy: г. Карши, улица Олимлар , дом 1 а</t>
+  </si>
+  <si>
+    <t>FrКРШ-33</t>
+  </si>
+  <si>
+    <t>998 93 177 14 39</t>
+  </si>
+  <si>
+    <t>@Qarshi1439</t>
+  </si>
+  <si>
+    <t>38.854660, 65.813965</t>
+  </si>
+  <si>
+    <t>Uchqo‘rg‘on sh., Yoshlik MFY, Andijon ko'chasi, 1 a uy: г. Учкурган, Ёшлик МФИ, улица Андижан, дом 1 а</t>
+  </si>
+  <si>
+    <t>FrУЧН-6</t>
+  </si>
+  <si>
+    <t>99850 040 02 08</t>
+  </si>
+  <si>
+    <t>@UzumFrUCHN6</t>
+  </si>
+  <si>
+    <t>41.097015, 72.078079</t>
+  </si>
+  <si>
+    <t>Guliston sh., Guliston shoh ko'chasi, 68 uy: г. Гулистан, проспект Гулистон, дом 68</t>
+  </si>
+  <si>
+    <t>FrГУЛ-11</t>
+  </si>
+  <si>
+    <t>998 77 317 94 86</t>
+  </si>
+  <si>
+    <t>@Uzum_mikrarayon4</t>
+  </si>
+  <si>
+    <t>40.513889, 68.783287</t>
+  </si>
+  <si>
+    <t>Nurabod sh., Jirmizobod ko'chasi, 156 uy: г. Нурабад, улица Жирмизобод, дом 156</t>
+  </si>
+  <si>
+    <t>FrНБД-1</t>
+  </si>
+  <si>
+    <t>998 77 305 34 99</t>
+  </si>
+  <si>
+    <t>@frnbd1</t>
+  </si>
+  <si>
+    <t>41.439216, 60.652834</t>
+  </si>
+  <si>
+    <t>Angren sh, Korabog‘ ko'chasi, 220 uy: г. Ангрен, улица Корабог, дом 220</t>
+  </si>
+  <si>
+    <t>FrАНГ-14</t>
+  </si>
+  <si>
+    <t>998 70 312 25 94</t>
+  </si>
+  <si>
+    <t>@FrANG14uzum</t>
+  </si>
+  <si>
+    <t>41.022303, 70.057120</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Asrlar Sadosi ko‘chasi, 1A : г. Ташкент, Чиланзарский район, улица Асрлар Cадоси, 1A</t>
+  </si>
+  <si>
+    <t>FrТАШ-449</t>
+  </si>
+  <si>
+    <t>998 50 302 69 26</t>
+  </si>
+  <si>
+    <t>@frtash_449</t>
+  </si>
+  <si>
+    <t>41.299619, 69.194477</t>
+  </si>
+  <si>
+    <t>Badal sh, Samarqand tumani, Shuhrat ko'chasi, 13 uy: г. Бадаль, Самаркандский район, улица Шухрат, дом 13</t>
+  </si>
+  <si>
+    <t>FrБДЛ-1</t>
+  </si>
+  <si>
+    <t>998 20 028 06 73</t>
+  </si>
+  <si>
+    <t>@BadalBTB</t>
+  </si>
+  <si>
+    <t>39.615618, 67.034467</t>
+  </si>
+  <si>
+    <t>Kichik Toshloq sh, Uychi tumani, Orom ko'chasi, 66 uy: г. Кичик Ташлак, Уйчинский район, улица Ором, дом 66</t>
+  </si>
+  <si>
+    <t>FrКТШ-1</t>
+  </si>
+  <si>
+    <t>998 50 791 59 93</t>
+  </si>
+  <si>
+    <t>@UzumFrKSHT1</t>
+  </si>
+  <si>
+    <t>40.944742, 71.795371</t>
+  </si>
+  <si>
+    <t>Alokhatin sh, Urgut tumani, Algar ko'chasi, 11 uy: г. Алохатын, Ургутский район, улица Алгар, дом 11</t>
+  </si>
+  <si>
+    <t>FrАЛХ-1</t>
+  </si>
+  <si>
+    <t>998 90 899 00 49</t>
+  </si>
+  <si>
+    <t>@uzumalgar</t>
+  </si>
+  <si>
+    <t>39.460593, 67.210786</t>
+  </si>
+  <si>
+    <t>Sherobod sh., Doʻstlik MFY, Mustaqillik ko'chasi, 125 uy: г. Шерабад, Дустлик МФИ, улица Мустакиллик, дом 125</t>
+  </si>
+  <si>
+    <t>FrШЕР-5</t>
+  </si>
+  <si>
+    <t>998 77 402 02 21</t>
+  </si>
+  <si>
+    <t>@FrSher5</t>
+  </si>
+  <si>
+    <t>37.649398, 67.035024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -21272,57 +21490,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21331,7 +21558,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21340,16 +21567,19 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21358,16 +21588,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21674,7 +21898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1735"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -51162,20 +51386,258 @@
       </c>
     </row>
     <row r="1735" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1735" s="5" t="s">
+      <c r="A1735" s="10" t="s">
         <v>7025</v>
       </c>
-      <c r="B1735" s="8" t="s">
+      <c r="B1735" s="11" t="s">
         <v>7026</v>
       </c>
-      <c r="C1735" s="31" t="s">
+      <c r="C1735" s="33" t="s">
         <v>7027</v>
       </c>
-      <c r="D1735" s="8" t="s">
+      <c r="D1735" s="11" t="s">
         <v>7028</v>
       </c>
-      <c r="E1735" s="8" t="s">
+      <c r="E1735" s="11" t="s">
         <v>7029</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1736" s="5" t="s">
+        <v>7030</v>
+      </c>
+      <c r="B1736" s="13" t="s">
+        <v>7031</v>
+      </c>
+      <c r="C1736" s="34" t="s">
+        <v>7032</v>
+      </c>
+      <c r="D1736" s="8" t="s">
+        <v>7033</v>
+      </c>
+      <c r="E1736" s="8" t="s">
+        <v>7034</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1737" s="5" t="s">
+        <v>7035</v>
+      </c>
+      <c r="B1737" s="13" t="s">
+        <v>7036</v>
+      </c>
+      <c r="C1737" s="34" t="s">
+        <v>7037</v>
+      </c>
+      <c r="D1737" s="8" t="s">
+        <v>7038</v>
+      </c>
+      <c r="E1737" s="8" t="s">
+        <v>7039</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1738" s="5" t="s">
+        <v>7040</v>
+      </c>
+      <c r="B1738" s="13" t="s">
+        <v>7041</v>
+      </c>
+      <c r="C1738" s="34" t="s">
+        <v>7042</v>
+      </c>
+      <c r="D1738" s="8" t="s">
+        <v>7043</v>
+      </c>
+      <c r="E1738" s="8" t="s">
+        <v>7044</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1739" s="5" t="s">
+        <v>7045</v>
+      </c>
+      <c r="B1739" s="13" t="s">
+        <v>7046</v>
+      </c>
+      <c r="C1739" s="34" t="s">
+        <v>7047</v>
+      </c>
+      <c r="D1739" s="8" t="s">
+        <v>7048</v>
+      </c>
+      <c r="E1739" s="8" t="s">
+        <v>7049</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1740" s="5" t="s">
+        <v>7050</v>
+      </c>
+      <c r="B1740" s="13" t="s">
+        <v>7051</v>
+      </c>
+      <c r="C1740" s="34" t="s">
+        <v>7052</v>
+      </c>
+      <c r="D1740" s="8" t="s">
+        <v>7053</v>
+      </c>
+      <c r="E1740" s="8" t="s">
+        <v>7054</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1741" s="5" t="s">
+        <v>7055</v>
+      </c>
+      <c r="B1741" s="13" t="s">
+        <v>7056</v>
+      </c>
+      <c r="C1741" s="34" t="s">
+        <v>7057</v>
+      </c>
+      <c r="D1741" s="8" t="s">
+        <v>7058</v>
+      </c>
+      <c r="E1741" s="8" t="s">
+        <v>7059</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1742" s="5" t="s">
+        <v>7060</v>
+      </c>
+      <c r="B1742" s="13" t="s">
+        <v>7061</v>
+      </c>
+      <c r="C1742" s="34" t="s">
+        <v>7062</v>
+      </c>
+      <c r="D1742" s="8" t="s">
+        <v>7063</v>
+      </c>
+      <c r="E1742" s="8" t="s">
+        <v>7064</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1743" s="5" t="s">
+        <v>7065</v>
+      </c>
+      <c r="B1743" s="13" t="s">
+        <v>7066</v>
+      </c>
+      <c r="C1743" s="34" t="s">
+        <v>7067</v>
+      </c>
+      <c r="D1743" s="8" t="s">
+        <v>7068</v>
+      </c>
+      <c r="E1743" s="8" t="s">
+        <v>7069</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1744" s="5" t="s">
+        <v>7070</v>
+      </c>
+      <c r="B1744" s="13" t="s">
+        <v>7071</v>
+      </c>
+      <c r="C1744" s="34" t="s">
+        <v>7072</v>
+      </c>
+      <c r="D1744" s="8" t="s">
+        <v>7073</v>
+      </c>
+      <c r="E1744" s="8" t="s">
+        <v>7074</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1745" s="5" t="s">
+        <v>7075</v>
+      </c>
+      <c r="B1745" s="13" t="s">
+        <v>7076</v>
+      </c>
+      <c r="C1745" s="34" t="s">
+        <v>7077</v>
+      </c>
+      <c r="D1745" s="8" t="s">
+        <v>7078</v>
+      </c>
+      <c r="E1745" s="8" t="s">
+        <v>7079</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1746" s="5" t="s">
+        <v>7080</v>
+      </c>
+      <c r="B1746" s="13" t="s">
+        <v>7081</v>
+      </c>
+      <c r="C1746" s="34" t="s">
+        <v>7082</v>
+      </c>
+      <c r="D1746" s="8" t="s">
+        <v>7083</v>
+      </c>
+      <c r="E1746" s="8" t="s">
+        <v>7084</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1747" s="5" t="s">
+        <v>7085</v>
+      </c>
+      <c r="B1747" s="13" t="s">
+        <v>7086</v>
+      </c>
+      <c r="C1747" s="34" t="s">
+        <v>7087</v>
+      </c>
+      <c r="D1747" s="8" t="s">
+        <v>7088</v>
+      </c>
+      <c r="E1747" s="8" t="s">
+        <v>7089</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1748" s="5" t="s">
+        <v>7090</v>
+      </c>
+      <c r="B1748" s="13" t="s">
+        <v>7091</v>
+      </c>
+      <c r="C1748" s="34" t="s">
+        <v>7092</v>
+      </c>
+      <c r="D1748" s="8" t="s">
+        <v>7093</v>
+      </c>
+      <c r="E1748" s="8" t="s">
+        <v>7094</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1749" s="5" t="s">
+        <v>7095</v>
+      </c>
+      <c r="B1749" s="8" t="s">
+        <v>7096</v>
+      </c>
+      <c r="C1749" s="34" t="s">
+        <v>7097</v>
+      </c>
+      <c r="D1749" s="8" t="s">
+        <v>7098</v>
+      </c>
+      <c r="E1749" s="8" t="s">
+        <v>7099</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F41D5C-560D-4EC5-97B5-0F870D21D123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21311680-BE93-471D-86CC-BD740C382CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="135" yWindow="2535" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7108" uniqueCount="7100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7143" uniqueCount="7134">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -21336,18 +21336,128 @@
   </si>
   <si>
     <t>37.649398, 67.035024</t>
+  </si>
+  <si>
+    <t>Turk sh., Quva tumani, Qaqir ko'chasi, 6/1/1 uy: г. Турк, Кувинский район, улица Какир, дом 6/1/1</t>
+  </si>
+  <si>
+    <t>FrТУК-1</t>
+  </si>
+  <si>
+    <t>998 99 130 98 18</t>
+  </si>
+  <si>
+    <t>@frTUK_1</t>
+  </si>
+  <si>
+    <t>40.493497, 72.031691</t>
+  </si>
+  <si>
+    <t>Farg‘ona sh., Oqoltin tumani, Mustaqillik ko'chasi, 30 uy : г. Фергана, Акалтынский район, улица Мустакиллик, дом 30</t>
+  </si>
+  <si>
+    <t>FrФРГ-1</t>
+  </si>
+  <si>
+    <t>998 93 816 00 05</t>
+  </si>
+  <si>
+    <t>@UzumFrFRG1</t>
+  </si>
+  <si>
+    <t>40.580600, 68.327351</t>
+  </si>
+  <si>
+    <t>Bekobod sh., Paxtakor MFY, Gafur G'ulom ko'chasi, 401 uy: г. Бекабад, Пахтакор МФИ, улица Гафур Гулом, дом 401</t>
+  </si>
+  <si>
+    <t>FrБЕК-10</t>
+  </si>
+  <si>
+    <t>998 95 002 52 74</t>
+  </si>
+  <si>
+    <t>@UzumfrBEK_10</t>
+  </si>
+  <si>
+    <t>40.239456, 69.268275</t>
+  </si>
+  <si>
+    <t>Yangijoy sh., Oʻrtashiq MFY, Registon ko‘chasi, 358 uy: г. Янгижой, Урташик МФИ, улица Регистон, дом 358</t>
+  </si>
+  <si>
+    <t>FrЯГЖ-2</t>
+  </si>
+  <si>
+    <t>998 94 223 15 99</t>
+  </si>
+  <si>
+    <t>@fr_ygj_2</t>
+  </si>
+  <si>
+    <t>39.601800, 66.936800</t>
+  </si>
+  <si>
+    <t>Qamashi sh., Farovon ko'chasi, 60 uy: г. Камаши, улица Фаровон, дом 60</t>
+  </si>
+  <si>
+    <t>FrКМШ-6</t>
+  </si>
+  <si>
+    <t>998 77 048 12 62</t>
+  </si>
+  <si>
+    <t>@FrKMSH_6</t>
+  </si>
+  <si>
+    <t>38.813718, 66.467633</t>
+  </si>
+  <si>
+    <t>Quvasoy sh., Azizov ko'chasi, 190: г. Кувасай, улица Азизова, дом 190</t>
+  </si>
+  <si>
+    <t>FrКУВ-3</t>
+  </si>
+  <si>
+    <t>998 77 026 39 28</t>
+  </si>
+  <si>
+    <t>@FRQUV_3</t>
+  </si>
+  <si>
+    <t>40.293618, 71.987727</t>
+  </si>
+  <si>
+    <t>Oqoltin sh., Mirzaobod tumani, Chorvador ko‘chasi, 42 uy : г. Акалтын, Мирзаабадский район, улица Чорвадор, дом 42</t>
+  </si>
+  <si>
+    <t>FrАТН-1</t>
+  </si>
+  <si>
+    <t>@fratn_1</t>
+  </si>
+  <si>
+    <t>40.603231, 68.730944</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -21490,57 +21600,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21549,7 +21668,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21558,16 +21677,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21576,22 +21698,19 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21898,7 +22017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -51624,20 +51743,139 @@
       </c>
     </row>
     <row r="1749" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1749" s="5" t="s">
+      <c r="A1749" s="10" t="s">
         <v>7095</v>
       </c>
-      <c r="B1749" s="8" t="s">
+      <c r="B1749" s="11" t="s">
         <v>7096</v>
       </c>
-      <c r="C1749" s="34" t="s">
+      <c r="C1749" s="35" t="s">
         <v>7097</v>
       </c>
-      <c r="D1749" s="8" t="s">
+      <c r="D1749" s="11" t="s">
         <v>7098</v>
       </c>
-      <c r="E1749" s="8" t="s">
+      <c r="E1749" s="11" t="s">
         <v>7099</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1750" s="5" t="s">
+        <v>7100</v>
+      </c>
+      <c r="B1750" s="13" t="s">
+        <v>7101</v>
+      </c>
+      <c r="C1750" s="36" t="s">
+        <v>7102</v>
+      </c>
+      <c r="D1750" s="8" t="s">
+        <v>7103</v>
+      </c>
+      <c r="E1750" s="8" t="s">
+        <v>7104</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1751" s="5" t="s">
+        <v>7105</v>
+      </c>
+      <c r="B1751" s="13" t="s">
+        <v>7106</v>
+      </c>
+      <c r="C1751" s="36" t="s">
+        <v>7107</v>
+      </c>
+      <c r="D1751" s="8" t="s">
+        <v>7108</v>
+      </c>
+      <c r="E1751" s="8" t="s">
+        <v>7109</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1752" s="5" t="s">
+        <v>7110</v>
+      </c>
+      <c r="B1752" s="13" t="s">
+        <v>7111</v>
+      </c>
+      <c r="C1752" s="36" t="s">
+        <v>7112</v>
+      </c>
+      <c r="D1752" s="8" t="s">
+        <v>7113</v>
+      </c>
+      <c r="E1752" s="8" t="s">
+        <v>7114</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1753" s="5" t="s">
+        <v>7115</v>
+      </c>
+      <c r="B1753" s="13" t="s">
+        <v>7116</v>
+      </c>
+      <c r="C1753" s="36" t="s">
+        <v>7117</v>
+      </c>
+      <c r="D1753" s="8" t="s">
+        <v>7118</v>
+      </c>
+      <c r="E1753" s="8" t="s">
+        <v>7119</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1754" s="5" t="s">
+        <v>7120</v>
+      </c>
+      <c r="B1754" s="13" t="s">
+        <v>7121</v>
+      </c>
+      <c r="C1754" s="36" t="s">
+        <v>7122</v>
+      </c>
+      <c r="D1754" s="8" t="s">
+        <v>7123</v>
+      </c>
+      <c r="E1754" s="8" t="s">
+        <v>7124</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1755" s="5" t="s">
+        <v>7125</v>
+      </c>
+      <c r="B1755" s="13" t="s">
+        <v>7126</v>
+      </c>
+      <c r="C1755" s="36" t="s">
+        <v>7127</v>
+      </c>
+      <c r="D1755" s="8" t="s">
+        <v>7128</v>
+      </c>
+      <c r="E1755" s="8" t="s">
+        <v>7129</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1756" s="15" t="s">
+        <v>7130</v>
+      </c>
+      <c r="B1756" s="13" t="s">
+        <v>7131</v>
+      </c>
+      <c r="C1756" s="37" t="s">
+        <v>7117</v>
+      </c>
+      <c r="D1756" s="13" t="s">
+        <v>7132</v>
+      </c>
+      <c r="E1756" s="13" t="s">
+        <v>7133</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21311680-BE93-471D-86CC-BD740C382CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B07F64F-C057-4783-9A22-4C8770911AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="2535" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7143" uniqueCount="7134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7223" uniqueCount="7213">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -21438,18 +21438,263 @@
   </si>
   <si>
     <t>40.603231, 68.730944</t>
+  </si>
+  <si>
+    <t>Bo'ston sh., Oltinsoy tumani, Sarbon ko'chasi, 25 uy: г. Бустон, Алтынсайский район, улица Сарбон, дом 25</t>
+  </si>
+  <si>
+    <t>FrБУС-3</t>
+  </si>
+  <si>
+    <t>998 99 021 04 24</t>
+  </si>
+  <si>
+    <t>@FrBUS_3</t>
+  </si>
+  <si>
+    <t>38.174741, 67.735161</t>
+  </si>
+  <si>
+    <t>Shahrisabz sh., Namaton ko‘chasi, 97uy: г. Шахрисабз, улица Наматон, дом 97</t>
+  </si>
+  <si>
+    <t>FrШРЗ-13</t>
+  </si>
+  <si>
+    <t>99887 798 01 90</t>
+  </si>
+  <si>
+    <t>@FrSHRZ13</t>
+  </si>
+  <si>
+    <t>39.077017, 66.856933</t>
+  </si>
+  <si>
+    <t>Pamuk sh., Mirishkor tumani, Ma'daniyat ko'chasi, 123 uy: г. Памук, Миришкорский район, улица Маъданият, дом 123</t>
+  </si>
+  <si>
+    <t>FrПАМ-1</t>
+  </si>
+  <si>
+    <t>998 50 879 78 59</t>
+  </si>
+  <si>
+    <t>@frpam_1</t>
+  </si>
+  <si>
+    <t>39.028039, 65.086437</t>
+  </si>
+  <si>
+    <t>Oltinko'l sh., Oltinko'l tumani, Nurli Hayot ko'chasi, 87 uy: г. Алтынкуль, Алтынкульский район, улица Нурли Хаёт, дом 87</t>
+  </si>
+  <si>
+    <t>FrАЛУ-3</t>
+  </si>
+  <si>
+    <t>998 93 419 03 06</t>
+  </si>
+  <si>
+    <t>@frALU3</t>
+  </si>
+  <si>
+    <t>40.796292, 72.184750</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Sirg'ali tumani, Xonobod 3 o‘tish yo‘li, 2 uy: г. Ташкент, Сергелийский район, 3-й проезд Ханабад, дом 2</t>
+  </si>
+  <si>
+    <t>FrТАШ-408</t>
+  </si>
+  <si>
+    <t>998 77 012 63 02</t>
+  </si>
+  <si>
+    <t>@FrTash408</t>
+  </si>
+  <si>
+    <t>41.224604, 69.289250</t>
+  </si>
+  <si>
+    <t>Qizilko‘prik sh., Izboskan tumani, Madaniyat yo‘li ko‘chasi, 70 uy :г. Кызылкуприк, Избасканский район, улица Маданият Йули, дом 70</t>
+  </si>
+  <si>
+    <t>FrКПР-1</t>
+  </si>
+  <si>
+    <t>998 95 161 29 03</t>
+  </si>
+  <si>
+    <t>@frkpr_1</t>
+  </si>
+  <si>
+    <t>40.895710, 72.316791</t>
+  </si>
+  <si>
+    <t>Xumar sh., Paxtachi tumani, Xumo ko‘chasi, 77 uy: г. Хумар, Пахтачийский район, улица Хумо, дом 77</t>
+  </si>
+  <si>
+    <t>FrХУМ-1</t>
+  </si>
+  <si>
+    <t>998 94 713 99 88</t>
+  </si>
+  <si>
+    <t>@FrXum1</t>
+  </si>
+  <si>
+    <t>39.993092, 65.744696</t>
+  </si>
+  <si>
+    <t>Qoratepa sh., Paxtachi tumani, Hunarmand Shox ko‘chasi, 134 uy: г. Каратепа, Пахтачийский район, улица Хунарманд Шох, дом 134</t>
+  </si>
+  <si>
+    <t>FrКРТ-1</t>
+  </si>
+  <si>
+    <t>@FrKPT1</t>
+  </si>
+  <si>
+    <t>39.986134, 65.697772</t>
+  </si>
+  <si>
+    <t>Kogon sh., Amir Temur ko'chasi, 20 uy: г. Каган, улица Амира Тимура, дом 20</t>
+  </si>
+  <si>
+    <t>FrКАГ-7</t>
+  </si>
+  <si>
+    <t>998 77 032 31 19</t>
+  </si>
+  <si>
+    <t>@frkag_7</t>
+  </si>
+  <si>
+    <t>39.730609, 64.568759</t>
+  </si>
+  <si>
+    <t>Yangiyer sh., Fazilat MFY, Samarqand ko'chasi, 20 uy: г. Янгиер, Фазилат МСГ, улица Самарканд, дом 20</t>
+  </si>
+  <si>
+    <t>FrЯНР-6</t>
+  </si>
+  <si>
+    <t>998 50 735 30 96</t>
+  </si>
+  <si>
+    <t>@FrYANR6</t>
+  </si>
+  <si>
+    <t>40.269232, 68.813605</t>
+  </si>
+  <si>
+    <t>Chirchiq sh., Tiklanish ko'chasi, 24 b uy: г. Чирчик, улица Тикланиш, дом 24 б</t>
+  </si>
+  <si>
+    <t>FrЧИР-22</t>
+  </si>
+  <si>
+    <t>998 90 859 95 56</t>
+  </si>
+  <si>
+    <t>@FRCHIR_22</t>
+  </si>
+  <si>
+    <t>41.501481, 69.617785</t>
+  </si>
+  <si>
+    <t>Qiziltepa sh., Qiziltepa tumani, Tavois qishlog'i ko'chasi, 351 uy: г. Кызылтепа, Кызылтепинский район, улица кишлак Тавоис, дом 351</t>
+  </si>
+  <si>
+    <t>FrКЗТ-5</t>
+  </si>
+  <si>
+    <t>998 95 366 87 57</t>
+  </si>
+  <si>
+    <t>@uzumqiziltepa</t>
+  </si>
+  <si>
+    <t>40.059910, 64.827577</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yuqorichirchiq tumani, Istiqlol MFY, Zukkolo ko‘chasi, 7 uy : г. Ташкент, Юкоричирчикский район, МФИ Истикбол, улица Зукколар, дом 7</t>
+  </si>
+  <si>
+    <t>FrТАШ-423</t>
+  </si>
+  <si>
+    <t>998 95 636 58 39</t>
+  </si>
+  <si>
+    <t>@FrTash423</t>
+  </si>
+  <si>
+    <t>41.306530, 69.467878</t>
+  </si>
+  <si>
+    <t>Bogot sh., Oʻzbekiston MFY, 1-chi Mexmondust o‘tish yo‘li, 341 uy: г. Багат, Узбекистон МФИ, 1-й проезд Мехмондуст, дом 341</t>
+  </si>
+  <si>
+    <t>FrБГТ-5</t>
+  </si>
+  <si>
+    <t>998 20 004 01 09</t>
+  </si>
+  <si>
+    <t>@FrBGT_5</t>
+  </si>
+  <si>
+    <t>41.312506, 60.927689</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, 16 kvartal, 14A uy: г. Ташкент, Чиланзарский район, 16 квартал, дом 14А</t>
+  </si>
+  <si>
+    <t>FrТАШ-444</t>
+  </si>
+  <si>
+    <t>998 70 171 03 43</t>
+  </si>
+  <si>
+    <t>@frtash_444</t>
+  </si>
+  <si>
+    <t>41.275168, 69.201930</t>
+  </si>
+  <si>
+    <t>Yangiyo'l sh., Yangibogʻ MFY, Beruniy ko'chasi, 11 uy: г. Янгиюль, Янгибог МФИ, Беруни улица, дом 11</t>
+  </si>
+  <si>
+    <t>FrЯНГ-16</t>
+  </si>
+  <si>
+    <t>998 93 518 49 66</t>
+  </si>
+  <si>
+    <t>@FrYang16</t>
+  </si>
+  <si>
+    <t>41.135476, 69.060753</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -21600,57 +21845,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21659,7 +21913,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21668,16 +21922,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21686,16 +21943,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21704,7 +21955,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22017,7 +22268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1772"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -51862,20 +52113,292 @@
       </c>
     </row>
     <row r="1756" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1756" s="15" t="s">
+      <c r="A1756" s="29" t="s">
         <v>7130</v>
       </c>
-      <c r="B1756" s="13" t="s">
+      <c r="B1756" s="17" t="s">
         <v>7131</v>
       </c>
       <c r="C1756" s="37" t="s">
         <v>7117</v>
       </c>
-      <c r="D1756" s="13" t="s">
+      <c r="D1756" s="17" t="s">
         <v>7132</v>
       </c>
-      <c r="E1756" s="13" t="s">
+      <c r="E1756" s="17" t="s">
         <v>7133</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1757" s="5" t="s">
+        <v>7134</v>
+      </c>
+      <c r="B1757" s="13" t="s">
+        <v>7135</v>
+      </c>
+      <c r="C1757" s="38" t="s">
+        <v>7136</v>
+      </c>
+      <c r="D1757" s="8" t="s">
+        <v>7137</v>
+      </c>
+      <c r="E1757" s="8" t="s">
+        <v>7138</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1758" s="5" t="s">
+        <v>7139</v>
+      </c>
+      <c r="B1758" s="13" t="s">
+        <v>7140</v>
+      </c>
+      <c r="C1758" s="38" t="s">
+        <v>7141</v>
+      </c>
+      <c r="D1758" s="8" t="s">
+        <v>7142</v>
+      </c>
+      <c r="E1758" s="8" t="s">
+        <v>7143</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1759" s="15" t="s">
+        <v>7144</v>
+      </c>
+      <c r="B1759" s="13" t="s">
+        <v>7145</v>
+      </c>
+      <c r="C1759" s="39" t="s">
+        <v>7146</v>
+      </c>
+      <c r="D1759" s="13" t="s">
+        <v>7147</v>
+      </c>
+      <c r="E1759" s="13" t="s">
+        <v>7148</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1760" s="5" t="s">
+        <v>7149</v>
+      </c>
+      <c r="B1760" s="13" t="s">
+        <v>7150</v>
+      </c>
+      <c r="C1760" s="38" t="s">
+        <v>7151</v>
+      </c>
+      <c r="D1760" s="8" t="s">
+        <v>7152</v>
+      </c>
+      <c r="E1760" s="8" t="s">
+        <v>7153</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1761" s="15" t="s">
+        <v>7154</v>
+      </c>
+      <c r="B1761" s="13" t="s">
+        <v>7155</v>
+      </c>
+      <c r="C1761" s="39" t="s">
+        <v>7156</v>
+      </c>
+      <c r="D1761" s="13" t="s">
+        <v>7157</v>
+      </c>
+      <c r="E1761" s="13" t="s">
+        <v>7158</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1762" s="5" t="s">
+        <v>7159</v>
+      </c>
+      <c r="B1762" s="13" t="s">
+        <v>7160</v>
+      </c>
+      <c r="C1762" s="38" t="s">
+        <v>7161</v>
+      </c>
+      <c r="D1762" s="8" t="s">
+        <v>7162</v>
+      </c>
+      <c r="E1762" s="8" t="s">
+        <v>7163</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1763" s="15" t="s">
+        <v>7164</v>
+      </c>
+      <c r="B1763" s="13" t="s">
+        <v>7165</v>
+      </c>
+      <c r="C1763" s="39" t="s">
+        <v>7166</v>
+      </c>
+      <c r="D1763" s="13" t="s">
+        <v>7167</v>
+      </c>
+      <c r="E1763" s="13" t="s">
+        <v>7168</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1764" s="15" t="s">
+        <v>7169</v>
+      </c>
+      <c r="B1764" s="13" t="s">
+        <v>7170</v>
+      </c>
+      <c r="C1764" s="39" t="s">
+        <v>7166</v>
+      </c>
+      <c r="D1764" s="13" t="s">
+        <v>7171</v>
+      </c>
+      <c r="E1764" s="13" t="s">
+        <v>7172</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1765" s="5" t="s">
+        <v>7173</v>
+      </c>
+      <c r="B1765" s="13" t="s">
+        <v>7174</v>
+      </c>
+      <c r="C1765" s="38" t="s">
+        <v>7175</v>
+      </c>
+      <c r="D1765" s="8" t="s">
+        <v>7176</v>
+      </c>
+      <c r="E1765" s="8" t="s">
+        <v>7177</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1766" s="5" t="s">
+        <v>7178</v>
+      </c>
+      <c r="B1766" s="13" t="s">
+        <v>7179</v>
+      </c>
+      <c r="C1766" s="38" t="s">
+        <v>7180</v>
+      </c>
+      <c r="D1766" s="8" t="s">
+        <v>7181</v>
+      </c>
+      <c r="E1766" s="8" t="s">
+        <v>7182</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1767" s="5" t="s">
+        <v>7183</v>
+      </c>
+      <c r="B1767" s="13" t="s">
+        <v>7184</v>
+      </c>
+      <c r="C1767" s="38" t="s">
+        <v>7185</v>
+      </c>
+      <c r="D1767" s="8" t="s">
+        <v>7186</v>
+      </c>
+      <c r="E1767" s="8" t="s">
+        <v>7187</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1768" s="5" t="s">
+        <v>7188</v>
+      </c>
+      <c r="B1768" s="13" t="s">
+        <v>7189</v>
+      </c>
+      <c r="C1768" s="38" t="s">
+        <v>7190</v>
+      </c>
+      <c r="D1768" s="8" t="s">
+        <v>7191</v>
+      </c>
+      <c r="E1768" s="8" t="s">
+        <v>7192</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1769" s="5" t="s">
+        <v>7193</v>
+      </c>
+      <c r="B1769" s="13" t="s">
+        <v>7194</v>
+      </c>
+      <c r="C1769" s="38" t="s">
+        <v>7195</v>
+      </c>
+      <c r="D1769" s="8" t="s">
+        <v>7196</v>
+      </c>
+      <c r="E1769" s="8" t="s">
+        <v>7197</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1770" s="5" t="s">
+        <v>7198</v>
+      </c>
+      <c r="B1770" s="13" t="s">
+        <v>7199</v>
+      </c>
+      <c r="C1770" s="38" t="s">
+        <v>7200</v>
+      </c>
+      <c r="D1770" s="8" t="s">
+        <v>7201</v>
+      </c>
+      <c r="E1770" s="8" t="s">
+        <v>7202</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1771" s="5" t="s">
+        <v>7203</v>
+      </c>
+      <c r="B1771" s="13" t="s">
+        <v>7204</v>
+      </c>
+      <c r="C1771" s="38" t="s">
+        <v>7205</v>
+      </c>
+      <c r="D1771" s="8" t="s">
+        <v>7206</v>
+      </c>
+      <c r="E1771" s="8" t="s">
+        <v>7207</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1772" s="5" t="s">
+        <v>7208</v>
+      </c>
+      <c r="B1772" s="13" t="s">
+        <v>7209</v>
+      </c>
+      <c r="C1772" s="38" t="s">
+        <v>7210</v>
+      </c>
+      <c r="D1772" s="8" t="s">
+        <v>7211</v>
+      </c>
+      <c r="E1772" s="8" t="s">
+        <v>7212</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B07F64F-C057-4783-9A22-4C8770911AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BCDCE-EA2F-4EFF-A00F-9534DAD4F3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7223" uniqueCount="7213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7453" uniqueCount="7441">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -21675,18 +21675,710 @@
   </si>
   <si>
     <t>41.135476, 69.060753</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Sirg'ali tumani, kKatta halqa yo‘li, 29A : г. Ташкент, Сергелийский район, Большая кольцевая дорога, 29А</t>
+  </si>
+  <si>
+    <t>FrТАШ-436</t>
+  </si>
+  <si>
+    <t>998 50 201 17 46</t>
+  </si>
+  <si>
+    <t>@uzumfrtash_436</t>
+  </si>
+  <si>
+    <t>41.244776, 69.274935</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Feruza ko'chasi, 8-uy : г. Ташкент, Мирзо Улугбекский район, улица Феруза, дом 8</t>
+  </si>
+  <si>
+    <t>FrТАШ-433</t>
+  </si>
+  <si>
+    <t>998 70 188 87 29</t>
+  </si>
+  <si>
+    <t>@FrTash433</t>
+  </si>
+  <si>
+    <t>41.355068, 69.364099</t>
+  </si>
+  <si>
+    <t>Nuriston sh., O'zbekiston ko'chasi, 207 uy : г. Нуристан,улица Узбекистон, дом 207</t>
+  </si>
+  <si>
+    <t>FrНРС-2</t>
+  </si>
+  <si>
+    <t>998 77 339 29 39</t>
+  </si>
+  <si>
+    <t>@FrNRS_2</t>
+  </si>
+  <si>
+    <t>38.492408, 65.655380</t>
+  </si>
+  <si>
+    <t>Karapchi sh., Boyovut tumani, Guliston dahasi, Samarqand ko‘chasi, 28 uy : г. Карапчи, Баяутский район, массив Гулистан, улица Самарканд, дом 28</t>
+  </si>
+  <si>
+    <t>FrКРЧ-1</t>
+  </si>
+  <si>
+    <t>@fr_krch_1</t>
+  </si>
+  <si>
+    <t>40.476789, 68.787977</t>
+  </si>
+  <si>
+    <t>Nukus sh., 22 mitti tuman dahasi, 22/10-uy: г. Нукус, 22 й микрорайон, дом 22/10</t>
+  </si>
+  <si>
+    <t>FrНУК-26</t>
+  </si>
+  <si>
+    <t>998 97 720 48 58</t>
+  </si>
+  <si>
+    <t>@uzumnuk26</t>
+  </si>
+  <si>
+    <t>42.437029, 59.631414</t>
+  </si>
+  <si>
+    <t>Namangan sh., Kukumboy ko'chasi, 1 Minora yo‘lagi, 56 uy : г. Наманган, улица Кукумбой, 1 й проезд Минора, дом 56</t>
+  </si>
+  <si>
+    <t>FrНАМ-35</t>
+  </si>
+  <si>
+    <t>998 94 187 52 42</t>
+  </si>
+  <si>
+    <t>@UzumFrNAM35</t>
+  </si>
+  <si>
+    <t>41.031905, 71.588530</t>
+  </si>
+  <si>
+    <t>Urgutsh sh., Amir Temur ko'chasi, 286 uy: г. Ургут, улица Амира Темура, дом 286</t>
+  </si>
+  <si>
+    <t>FrУГТ-5</t>
+  </si>
+  <si>
+    <t>998 94 003 34 45</t>
+  </si>
+  <si>
+    <t>@FR_UGT_5</t>
+  </si>
+  <si>
+    <t>39.424034, 67.192316</t>
+  </si>
+  <si>
+    <t>Narpay sh., Karmana tumani, Alpomish ko‘chasi, 79 uy: г. Нарпай, Карманинский район, улица Алпомиш, дом 79</t>
+  </si>
+  <si>
+    <t>FrНРП-1</t>
+  </si>
+  <si>
+    <t>998 99 187 05 87</t>
+  </si>
+  <si>
+    <t>@FrNRP1</t>
+  </si>
+  <si>
+    <t>40.091828, 65.438576</t>
+  </si>
+  <si>
+    <t>Baxmal sh., Baxmal qishlog'i ko'chasi, 88 uy: г. Бахмал, улица кишлака Бахмал, дом 88</t>
+  </si>
+  <si>
+    <t>FrБХЛ-1</t>
+  </si>
+  <si>
+    <t>998 70 527 98 98</t>
+  </si>
+  <si>
+    <t>@frbxl_1</t>
+  </si>
+  <si>
+    <t>39.738577, 67.976682</t>
+  </si>
+  <si>
+    <t>Oqtosh sh., Toshkent tumani, Archa ko'chasi, 84 uy: г. Октош, Ташкентский район, улица Арча, дом 84</t>
+  </si>
+  <si>
+    <t>FrОКТ-1</t>
+  </si>
+  <si>
+    <t>998 88 920 04 09</t>
+  </si>
+  <si>
+    <t>@FrOKT_1</t>
+  </si>
+  <si>
+    <t>41.349797, 69.082978</t>
+  </si>
+  <si>
+    <t>Qushkanot sh., Shahrisabz tumani, Dotkush ko‘chasi, 531 uy: г. Кушканот, Шахрисабзский район, улица Доткуш, дом 531</t>
+  </si>
+  <si>
+    <t>FrКАТ-1</t>
+  </si>
+  <si>
+    <t>998 95 081 70 99</t>
+  </si>
+  <si>
+    <t>@FrKAT_1</t>
+  </si>
+  <si>
+    <t>38.997918, 66.966468</t>
+  </si>
+  <si>
+    <t>G‘ijduvon sh., Sardor MFY, Sharq ko'chasi, 184 uy : г. Гиждуван, Сардор МФИ, улица Шарк, дом 184</t>
+  </si>
+  <si>
+    <t>FrГЖД-9</t>
+  </si>
+  <si>
+    <t>998 97 288 09 90</t>
+  </si>
+  <si>
+    <t>@FrGJD_9</t>
+  </si>
+  <si>
+    <t>40.103278, 64.695407</t>
+  </si>
+  <si>
+    <t>Oqqoʻrgʻon sh., Tortuvli MFY, Zafar koʻchasi, 13 uy : г. Аккурган, МФИ Тортувли, улица Зафар, дом 13</t>
+  </si>
+  <si>
+    <t>FrАКК-3</t>
+  </si>
+  <si>
+    <t>998 94 989 22 07</t>
+  </si>
+  <si>
+    <t>@UzumFrAKK3</t>
+  </si>
+  <si>
+    <t>40.816080, 69.014016</t>
+  </si>
+  <si>
+    <t>Sariasiya sh., Sariosiyo tumani, Mahrshavqat MFY, Birdamlik ko'chasi, 8 uy : г. Сариасия, Сариасийский район, МФИ Мехр-шавкат, улица Бирдамлик, дом 8</t>
+  </si>
+  <si>
+    <t>FrСРС-7</t>
+  </si>
+  <si>
+    <t>998 33 120 77 11</t>
+  </si>
+  <si>
+    <t>@FrCPC_7</t>
+  </si>
+  <si>
+    <t>38.422452, 67.966212</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Sirg'ali tumani, Alisher Navoiy dahasi, 307/35 uy: г. Ташкент, Сергелийский район, массив Алишера Навои, дом 307/35</t>
+  </si>
+  <si>
+    <t>FrТАШ-427</t>
+  </si>
+  <si>
+    <t>998 92 182 06 48</t>
+  </si>
+  <si>
+    <t>@UzumSergeli</t>
+  </si>
+  <si>
+    <t>41.232850, 69.217707</t>
+  </si>
+  <si>
+    <t>Kattatupi sh., Uchqo'rg'on tumani, Urikzor 1 ko'chasi, 26 uy: г. Каттатупи, Учкурганский район, улица Урикзор 1, дом 26</t>
+  </si>
+  <si>
+    <t>FrКТТ-1</t>
+  </si>
+  <si>
+    <t>998 70 526 32 26</t>
+  </si>
+  <si>
+    <t>@UzumFrKTT1</t>
+  </si>
+  <si>
+    <t>40.965623, 71.945529</t>
+  </si>
+  <si>
+    <t>Kusharti sh., Qiziltepa tumani, Balandg'ardiyon qishlog kochasi, 15 uy: г. Кушарти, Кызылтепинский район, улица кишлак Баландгардиён, дом 15</t>
+  </si>
+  <si>
+    <t>FrКШТ-1</t>
+  </si>
+  <si>
+    <t>998 99 249 39 59</t>
+  </si>
+  <si>
+    <t>@FrKSHT1</t>
+  </si>
+  <si>
+    <t>40.106543, 64.822095</t>
+  </si>
+  <si>
+    <t>Chirchiq sh., Privokzalnaya ko'chasi, 2 uy, : г. Чирчик, Привокзальная улица, дом 2</t>
+  </si>
+  <si>
+    <t>FrЧИР-25</t>
+  </si>
+  <si>
+    <t>998 50 796 69 40</t>
+  </si>
+  <si>
+    <t>@Frchir25</t>
+  </si>
+  <si>
+    <t>41.479387, 69.595435</t>
+  </si>
+  <si>
+    <t>Yangiyo'l sh., Samarqand ko'chasi, 191 uy: г. Янгиюль, Самаркандская улица, дом 191</t>
+  </si>
+  <si>
+    <t>FrЯНГ-17</t>
+  </si>
+  <si>
+    <t>998 93 314 47 01</t>
+  </si>
+  <si>
+    <t>@FRYAN0017</t>
+  </si>
+  <si>
+    <t>41.103051, 69.043807</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Nasaf ko'chasi, 4/250 uy: г. Карши, улица Насаф, дом 4/250</t>
+  </si>
+  <si>
+    <t>FrКРШ-32</t>
+  </si>
+  <si>
+    <t>998 77 689 89 79</t>
+  </si>
+  <si>
+    <t>@FrKRSH32</t>
+  </si>
+  <si>
+    <t>38.821301, 65.789629</t>
+  </si>
+  <si>
+    <t>Yangiyer sh., Abdurahmon Jomiy MFY, Amir Temur ko'chasi, 51 A uy: г. Янгиер, Абдурахмон Жомий МФИ, улица Амира Темура, дом 51 A</t>
+  </si>
+  <si>
+    <t>FrЯНР-8</t>
+  </si>
+  <si>
+    <t>998 33 958 75 08</t>
+  </si>
+  <si>
+    <t>@frynr_8</t>
+  </si>
+  <si>
+    <t>40.292452, 68.822711</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yakkasaroy tumani, , Bahodir ko'chasi, 2/1-uy г. Ташкент, Яккасарайский район, улица Баходыра, дом 2/1</t>
+  </si>
+  <si>
+    <t>FrТАШ-421</t>
+  </si>
+  <si>
+    <t>998 70 188 87 36</t>
+  </si>
+  <si>
+    <t>@Fr_TASH421</t>
+  </si>
+  <si>
+    <t>41.298368, 69.246409</t>
+  </si>
+  <si>
+    <t>Angor sh., At Termiziy ko'chasi, 18 g uy: г. Ангор, улица Ат Термизи. дом 18 ж</t>
+  </si>
+  <si>
+    <t>FrНГР-4</t>
+  </si>
+  <si>
+    <t>998 77 410 77 26</t>
+  </si>
+  <si>
+    <t>@Uzum_angor</t>
+  </si>
+  <si>
+    <t>37.467849, 67.145431</t>
+  </si>
+  <si>
+    <t>Manguobod sh., Beshariq tumani, Yakkatut MFY, Navro‘z ko'chasi, 105 А uy: г. Мангуобод, Бешарыкский район, Яккатут МФИ, улица Навруз, дом 105 А</t>
+  </si>
+  <si>
+    <t>FrМГБ-1</t>
+  </si>
+  <si>
+    <t>998 95 111 92 98</t>
+  </si>
+  <si>
+    <t>@UzumFrMGB1</t>
+  </si>
+  <si>
+    <t>40.407802, 70.520175</t>
+  </si>
+  <si>
+    <t>Bog‘ishamol sh., Karmana tumani, Bog'ishamol kochasi 722 uy: г. Богишамол, Карманинский район, улица Богишамол, дом 722</t>
+  </si>
+  <si>
+    <t>FrБШЛ-2</t>
+  </si>
+  <si>
+    <t>@FrBShL2</t>
+  </si>
+  <si>
+    <t>40.071963, 65.437760</t>
+  </si>
+  <si>
+    <t>Buxoro sh., Gazli shossesi ko'chasi , 18 uy : г. Бухара, улица Газлийское шоссе, дом 18</t>
+  </si>
+  <si>
+    <t>FrБХР-40</t>
+  </si>
+  <si>
+    <t>998 50 302 82 53</t>
+  </si>
+  <si>
+    <t>@FrBXR_40</t>
+  </si>
+  <si>
+    <t>39.786389, 64.449280</t>
+  </si>
+  <si>
+    <t>G‘azalkent sh., O‘zgaris ko'chasi, 215 uy: г. Газалкент, улица Узгариш, дом 215</t>
+  </si>
+  <si>
+    <t>FrГАЗ-6</t>
+  </si>
+  <si>
+    <t>998 70 188 87 39</t>
+  </si>
+  <si>
+    <t>@FrGAZ_6</t>
+  </si>
+  <si>
+    <t>41.572336, 69.791283</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Bogʻobod MFY, Feron qishlog'i, 25 uy : г. Карши, Богобод МФИ, село Ферон, дом 25</t>
+  </si>
+  <si>
+    <t>FrКРШ-37</t>
+  </si>
+  <si>
+    <t>998 90 879 46 46</t>
+  </si>
+  <si>
+    <t>@FrKRSH_37</t>
+  </si>
+  <si>
+    <t>38.901369, 65.816068</t>
+  </si>
+  <si>
+    <t>Xaqqulobod sh., Norin tumani, Kuyultepa ko'chasi, 71 uy: г. Хаккулабад, Норинский район, улица Куюлтепа, дом 71</t>
+  </si>
+  <si>
+    <t>FrХАК-3</t>
+  </si>
+  <si>
+    <t>998 77 335 56 46</t>
+  </si>
+  <si>
+    <t>@UzumFrXAK3</t>
+  </si>
+  <si>
+    <t>40.924695, 72.129867</t>
+  </si>
+  <si>
+    <t>Sariasiya sh., Sariosiyo tumani, Erman ko'chasi, 3 uy : г. Сариасия, Сариасийский район, улица Эрман, дом 3</t>
+  </si>
+  <si>
+    <t>FrСРС-8</t>
+  </si>
+  <si>
+    <t>998 77 832 27 01</t>
+  </si>
+  <si>
+    <t>@FrSRS_8</t>
+  </si>
+  <si>
+    <t>38.433863, 67.937427</t>
+  </si>
+  <si>
+    <t>Gishtman sh., Qo‘shtepa tumani, Qiyqi MFY, Soxibkor ko'chasi, 33a uy : г. Гиштман, Куштепинский район, МФИ Кийки, улица Сохибкор, дом 33а</t>
+  </si>
+  <si>
+    <t>FrГТН-1</t>
+  </si>
+  <si>
+    <t>998 77 839 00 11</t>
+  </si>
+  <si>
+    <t>@FrGTN_1</t>
+  </si>
+  <si>
+    <t>40.470563, 71.647952</t>
+  </si>
+  <si>
+    <t>Nurafshon sh., Kogon tumani, Abad Chukurkul ko‘chasi, 398 uy : г. Нурафшон, Каганский район, улица Абад Чукуркуль, дом 398</t>
+  </si>
+  <si>
+    <t>FrНФН-1</t>
+  </si>
+  <si>
+    <t>998 70 518 14 25</t>
+  </si>
+  <si>
+    <t>@Frnfn_1</t>
+  </si>
+  <si>
+    <t>39.665228, 64.465270</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Hamid Olimjon maydoni, 13B uy : г. Ташкент, Мирзо Улугбекский район, площадь Хамида Алимджана, дом 13Б</t>
+  </si>
+  <si>
+    <t>FrТАШ-430</t>
+  </si>
+  <si>
+    <t>998 50 796 30 96</t>
+  </si>
+  <si>
+    <t>@FrTASH_430</t>
+  </si>
+  <si>
+    <t>41.318629, 69.295303</t>
+  </si>
+  <si>
+    <t>Jushota sh., Qo‘shrabot tumani, Joʻsh-ota MFY, Buloqboshi qishlogʻ, 157 uy : г. Джушота, Кошрабадский район, МФИ Джуш-ота, кишлак Булокбаши, дом 157</t>
+  </si>
+  <si>
+    <t>FrЖУШ-1</t>
+  </si>
+  <si>
+    <t>998 95 073 77 89</t>
+  </si>
+  <si>
+    <t>@fr_jush_1</t>
+  </si>
+  <si>
+    <t>40.408285, 66.345696</t>
+  </si>
+  <si>
+    <t>Buloqboshi sh., Chilonzor ko'chasi, 35 uy: г. Булакбаши, улица Чилонзор, дом 35</t>
+  </si>
+  <si>
+    <t>FrБКБ-3</t>
+  </si>
+  <si>
+    <t>998 94 704 42 06</t>
+  </si>
+  <si>
+    <t>@frBKB3</t>
+  </si>
+  <si>
+    <t>40.627834, 72.515036</t>
+  </si>
+  <si>
+    <t>Soyliq sh., Bo'stonliq tumani, Mirzo Ulugʻbek ko'chasi, 172 uy : г. Сайлык, Бостанлыкский район, улица Мирзо Улугбека, дом 172</t>
+  </si>
+  <si>
+    <t>FrСЛК-1</t>
+  </si>
+  <si>
+    <t>998 70 188 87 69</t>
+  </si>
+  <si>
+    <t>@FrSLK_1</t>
+  </si>
+  <si>
+    <t>41.607006, 69.766446</t>
+  </si>
+  <si>
+    <t>Nukus sh., Pirjan Seytov ko‘chasi, 37 uy: г. Нукус, улица Пиржана Сейтова, 37 дом</t>
+  </si>
+  <si>
+    <t>FrНУК-27</t>
+  </si>
+  <si>
+    <t>998 97 220 04 99</t>
+  </si>
+  <si>
+    <t>@uzumnuk27</t>
+  </si>
+  <si>
+    <t>42.471112, 59.585878</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Uchtepa tumani, Uchtepa ko‘chasi, 90 uy: г. Ташкент, Учтепинский район, улица Учтепа, дом 90</t>
+  </si>
+  <si>
+    <t>FrТАШ-458</t>
+  </si>
+  <si>
+    <t>998 50 302 84 43</t>
+  </si>
+  <si>
+    <t>@FrTash458</t>
+  </si>
+  <si>
+    <t>41.295600, 69.159900</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Shifokorlar ko'chasi, 6 b uy: г. Ташкент, Алмазарский район, улица Шифокорлар, дом 6Б</t>
+  </si>
+  <si>
+    <t>FrТАШ-424</t>
+  </si>
+  <si>
+    <t>998 50 302 71 33</t>
+  </si>
+  <si>
+    <t>@FRTASH424</t>
+  </si>
+  <si>
+    <t>41.351310, 69.178781</t>
+  </si>
+  <si>
+    <t>Andijon sh., Al-Farg‘oniy ko‘chasi, 18 uy: г. Андижан, улица Аль Фаргоний, 18 дом</t>
+  </si>
+  <si>
+    <t>FrАНД-35</t>
+  </si>
+  <si>
+    <t>998 99 717 66 00</t>
+  </si>
+  <si>
+    <t>@FrAND_35_Mirgiyoz</t>
+  </si>
+  <si>
+    <t>40.811156, 72.314803</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, 1 kvartal, Arnasoy ko‘chasi, 35 uy: г. Ташкент, Чиланзарский район, 1 квартал, улица Арнасой, 35 дом</t>
+  </si>
+  <si>
+    <t>FrТАШ-450</t>
+  </si>
+  <si>
+    <t>998 90 932 59 81</t>
+  </si>
+  <si>
+    <t>@frTASH_450</t>
+  </si>
+  <si>
+    <t>41.282455, 69.229551</t>
+  </si>
+  <si>
+    <t>Namangan sh., Soli Adasheva ko'chasi, 147 uy: г. Наманган, улица Соли Адашева, 147 дом</t>
+  </si>
+  <si>
+    <t>FrНАМ-33</t>
+  </si>
+  <si>
+    <t>998 77 211 06 12</t>
+  </si>
+  <si>
+    <t>@UzumFrNAM33</t>
+  </si>
+  <si>
+    <t>41.012726, 71.687956</t>
+  </si>
+  <si>
+    <t>Quvasoy sh., Kichik bog‘ ko‘chasi, 102 uy : г. Кувасай, улица Кичик бог, дом 102</t>
+  </si>
+  <si>
+    <t>FrКУВ-4</t>
+  </si>
+  <si>
+    <t>998 94 396 24 03</t>
+  </si>
+  <si>
+    <t>@Frnay_1</t>
+  </si>
+  <si>
+    <t>40.273432, 72.020124</t>
+  </si>
+  <si>
+    <t>Chambil sh., Denov tumani, Chambil ko‘chasi, 34 uy : г. Чамбиль, Денауский район, улица Чамбиль, дом 34</t>
+  </si>
+  <si>
+    <t>FrЧАМ-1</t>
+  </si>
+  <si>
+    <t>998 70 021 85 76</t>
+  </si>
+  <si>
+    <t>@FrCham_1</t>
+  </si>
+  <si>
+    <t>38.382054, 67.911833</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Qizil masjid ko'chasi, 22 uy: г. Карши, улица Кизил Масжид, дом 22</t>
+  </si>
+  <si>
+    <t>FrКРШ-30</t>
+  </si>
+  <si>
+    <t>998 70 131 14 92</t>
+  </si>
+  <si>
+    <t>@FrKSHR30</t>
+  </si>
+  <si>
+    <t>38.874638, 65.792351</t>
+  </si>
+  <si>
+    <t>Beshariq sh., Yangihayot MFY, Beshariq ko‘chasi, 185 а uy: г. Бешарык, Янгихаёт МФИ, улица Бешарык, дом 185 а</t>
+  </si>
+  <si>
+    <t>FrБШК-4</t>
+  </si>
+  <si>
+    <t>998 95 657 21 75</t>
+  </si>
+  <si>
+    <t>@UzumFrBSHK4</t>
+  </si>
+  <si>
+    <t>40.437012, 70.630706</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -21845,57 +22537,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21904,7 +22605,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21913,16 +22614,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21931,16 +22635,10 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -21949,13 +22647,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22268,7 +22969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1772"/>
+  <dimension ref="A1:E1818"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -52385,20 +53086,802 @@
       </c>
     </row>
     <row r="1772" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1772" s="5" t="s">
+      <c r="A1772" s="10" t="s">
         <v>7208</v>
       </c>
-      <c r="B1772" s="13" t="s">
+      <c r="B1772" s="17" t="s">
         <v>7209</v>
       </c>
-      <c r="C1772" s="38" t="s">
+      <c r="C1772" s="40" t="s">
         <v>7210</v>
       </c>
-      <c r="D1772" s="8" t="s">
+      <c r="D1772" s="11" t="s">
         <v>7211</v>
       </c>
-      <c r="E1772" s="8" t="s">
+      <c r="E1772" s="11" t="s">
         <v>7212</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1773" s="5" t="s">
+        <v>7213</v>
+      </c>
+      <c r="B1773" s="13" t="s">
+        <v>7214</v>
+      </c>
+      <c r="C1773" s="41" t="s">
+        <v>7215</v>
+      </c>
+      <c r="D1773" s="8" t="s">
+        <v>7216</v>
+      </c>
+      <c r="E1773" s="8" t="s">
+        <v>7217</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1774" s="5" t="s">
+        <v>7218</v>
+      </c>
+      <c r="B1774" s="13" t="s">
+        <v>7219</v>
+      </c>
+      <c r="C1774" s="41" t="s">
+        <v>7220</v>
+      </c>
+      <c r="D1774" s="8" t="s">
+        <v>7221</v>
+      </c>
+      <c r="E1774" s="8" t="s">
+        <v>7222</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1775" s="5" t="s">
+        <v>7223</v>
+      </c>
+      <c r="B1775" s="13" t="s">
+        <v>7224</v>
+      </c>
+      <c r="C1775" s="41" t="s">
+        <v>7225</v>
+      </c>
+      <c r="D1775" s="8" t="s">
+        <v>7226</v>
+      </c>
+      <c r="E1775" s="8" t="s">
+        <v>7227</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1776" s="5" t="s">
+        <v>7228</v>
+      </c>
+      <c r="B1776" s="13" t="s">
+        <v>7229</v>
+      </c>
+      <c r="C1776" s="41" t="s">
+        <v>7210</v>
+      </c>
+      <c r="D1776" s="8" t="s">
+        <v>7230</v>
+      </c>
+      <c r="E1776" s="8" t="s">
+        <v>7231</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1777" s="5" t="s">
+        <v>7232</v>
+      </c>
+      <c r="B1777" s="13" t="s">
+        <v>7233</v>
+      </c>
+      <c r="C1777" s="41" t="s">
+        <v>7234</v>
+      </c>
+      <c r="D1777" s="8" t="s">
+        <v>7235</v>
+      </c>
+      <c r="E1777" s="8" t="s">
+        <v>7236</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1778" s="5" t="s">
+        <v>7237</v>
+      </c>
+      <c r="B1778" s="13" t="s">
+        <v>7238</v>
+      </c>
+      <c r="C1778" s="41" t="s">
+        <v>7239</v>
+      </c>
+      <c r="D1778" s="8" t="s">
+        <v>7240</v>
+      </c>
+      <c r="E1778" s="8" t="s">
+        <v>7241</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1779" s="5" t="s">
+        <v>7242</v>
+      </c>
+      <c r="B1779" s="13" t="s">
+        <v>7243</v>
+      </c>
+      <c r="C1779" s="41" t="s">
+        <v>7244</v>
+      </c>
+      <c r="D1779" s="8" t="s">
+        <v>7245</v>
+      </c>
+      <c r="E1779" s="8" t="s">
+        <v>7246</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1780" s="15" t="s">
+        <v>7247</v>
+      </c>
+      <c r="B1780" s="13" t="s">
+        <v>7248</v>
+      </c>
+      <c r="C1780" s="42" t="s">
+        <v>7249</v>
+      </c>
+      <c r="D1780" s="13" t="s">
+        <v>7250</v>
+      </c>
+      <c r="E1780" s="13" t="s">
+        <v>7251</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1781" s="5" t="s">
+        <v>7252</v>
+      </c>
+      <c r="B1781" s="13" t="s">
+        <v>7253</v>
+      </c>
+      <c r="C1781" s="41" t="s">
+        <v>7254</v>
+      </c>
+      <c r="D1781" s="8" t="s">
+        <v>7255</v>
+      </c>
+      <c r="E1781" s="8" t="s">
+        <v>7256</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1782" s="5" t="s">
+        <v>7257</v>
+      </c>
+      <c r="B1782" s="13" t="s">
+        <v>7258</v>
+      </c>
+      <c r="C1782" s="41" t="s">
+        <v>7259</v>
+      </c>
+      <c r="D1782" s="8" t="s">
+        <v>7260</v>
+      </c>
+      <c r="E1782" s="8" t="s">
+        <v>7261</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1783" s="5" t="s">
+        <v>7262</v>
+      </c>
+      <c r="B1783" s="13" t="s">
+        <v>7263</v>
+      </c>
+      <c r="C1783" s="41" t="s">
+        <v>7264</v>
+      </c>
+      <c r="D1783" s="8" t="s">
+        <v>7265</v>
+      </c>
+      <c r="E1783" s="8" t="s">
+        <v>7266</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1784" s="5" t="s">
+        <v>7267</v>
+      </c>
+      <c r="B1784" s="13" t="s">
+        <v>7268</v>
+      </c>
+      <c r="C1784" s="41" t="s">
+        <v>7269</v>
+      </c>
+      <c r="D1784" s="8" t="s">
+        <v>7270</v>
+      </c>
+      <c r="E1784" s="8" t="s">
+        <v>7271</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1785" s="5" t="s">
+        <v>7272</v>
+      </c>
+      <c r="B1785" s="13" t="s">
+        <v>7273</v>
+      </c>
+      <c r="C1785" s="41" t="s">
+        <v>7274</v>
+      </c>
+      <c r="D1785" s="8" t="s">
+        <v>7275</v>
+      </c>
+      <c r="E1785" s="8" t="s">
+        <v>7276</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1786" s="5" t="s">
+        <v>7277</v>
+      </c>
+      <c r="B1786" s="13" t="s">
+        <v>7278</v>
+      </c>
+      <c r="C1786" s="41" t="s">
+        <v>7279</v>
+      </c>
+      <c r="D1786" s="8" t="s">
+        <v>7280</v>
+      </c>
+      <c r="E1786" s="8" t="s">
+        <v>7281</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1787" s="5" t="s">
+        <v>7282</v>
+      </c>
+      <c r="B1787" s="13" t="s">
+        <v>7283</v>
+      </c>
+      <c r="C1787" s="41" t="s">
+        <v>7284</v>
+      </c>
+      <c r="D1787" s="8" t="s">
+        <v>7285</v>
+      </c>
+      <c r="E1787" s="8" t="s">
+        <v>7286</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1788" s="5" t="s">
+        <v>7287</v>
+      </c>
+      <c r="B1788" s="13" t="s">
+        <v>7288</v>
+      </c>
+      <c r="C1788" s="41" t="s">
+        <v>7289</v>
+      </c>
+      <c r="D1788" s="8" t="s">
+        <v>7290</v>
+      </c>
+      <c r="E1788" s="8" t="s">
+        <v>7291</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1789" s="5" t="s">
+        <v>7292</v>
+      </c>
+      <c r="B1789" s="13" t="s">
+        <v>7293</v>
+      </c>
+      <c r="C1789" s="41" t="s">
+        <v>7294</v>
+      </c>
+      <c r="D1789" s="8" t="s">
+        <v>7295</v>
+      </c>
+      <c r="E1789" s="8" t="s">
+        <v>7296</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1790" s="5" t="s">
+        <v>7297</v>
+      </c>
+      <c r="B1790" s="13" t="s">
+        <v>7298</v>
+      </c>
+      <c r="C1790" s="41" t="s">
+        <v>7299</v>
+      </c>
+      <c r="D1790" s="8" t="s">
+        <v>7300</v>
+      </c>
+      <c r="E1790" s="8" t="s">
+        <v>7301</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1791" s="15" t="s">
+        <v>7302</v>
+      </c>
+      <c r="B1791" s="13" t="s">
+        <v>7303</v>
+      </c>
+      <c r="C1791" s="42" t="s">
+        <v>7304</v>
+      </c>
+      <c r="D1791" s="13" t="s">
+        <v>7305</v>
+      </c>
+      <c r="E1791" s="13" t="s">
+        <v>7306</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1792" s="5" t="s">
+        <v>7307</v>
+      </c>
+      <c r="B1792" s="13" t="s">
+        <v>7308</v>
+      </c>
+      <c r="C1792" s="41" t="s">
+        <v>7309</v>
+      </c>
+      <c r="D1792" s="8" t="s">
+        <v>7310</v>
+      </c>
+      <c r="E1792" s="8" t="s">
+        <v>7311</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1793" s="15" t="s">
+        <v>7312</v>
+      </c>
+      <c r="B1793" s="13" t="s">
+        <v>7313</v>
+      </c>
+      <c r="C1793" s="42" t="s">
+        <v>7314</v>
+      </c>
+      <c r="D1793" s="13" t="s">
+        <v>7315</v>
+      </c>
+      <c r="E1793" s="13" t="s">
+        <v>7316</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1794" s="5" t="s">
+        <v>7317</v>
+      </c>
+      <c r="B1794" s="13" t="s">
+        <v>7318</v>
+      </c>
+      <c r="C1794" s="41" t="s">
+        <v>7319</v>
+      </c>
+      <c r="D1794" s="8" t="s">
+        <v>7320</v>
+      </c>
+      <c r="E1794" s="8" t="s">
+        <v>7321</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1795" s="15" t="s">
+        <v>7322</v>
+      </c>
+      <c r="B1795" s="13" t="s">
+        <v>7323</v>
+      </c>
+      <c r="C1795" s="42" t="s">
+        <v>7324</v>
+      </c>
+      <c r="D1795" s="13" t="s">
+        <v>7325</v>
+      </c>
+      <c r="E1795" s="13" t="s">
+        <v>7326</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1796" s="15" t="s">
+        <v>7327</v>
+      </c>
+      <c r="B1796" s="13" t="s">
+        <v>7328</v>
+      </c>
+      <c r="C1796" s="41" t="s">
+        <v>7329</v>
+      </c>
+      <c r="D1796" s="8" t="s">
+        <v>7330</v>
+      </c>
+      <c r="E1796" s="8" t="s">
+        <v>7331</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1797" s="5" t="s">
+        <v>7332</v>
+      </c>
+      <c r="B1797" s="13" t="s">
+        <v>7333</v>
+      </c>
+      <c r="C1797" s="42" t="s">
+        <v>7294</v>
+      </c>
+      <c r="D1797" s="8" t="s">
+        <v>7334</v>
+      </c>
+      <c r="E1797" s="8" t="s">
+        <v>7335</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1798" s="5" t="s">
+        <v>7336</v>
+      </c>
+      <c r="B1798" s="13" t="s">
+        <v>7337</v>
+      </c>
+      <c r="C1798" s="41" t="s">
+        <v>7338</v>
+      </c>
+      <c r="D1798" s="8" t="s">
+        <v>7339</v>
+      </c>
+      <c r="E1798" s="8" t="s">
+        <v>7340</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1799" s="5" t="s">
+        <v>7341</v>
+      </c>
+      <c r="B1799" s="13" t="s">
+        <v>7342</v>
+      </c>
+      <c r="C1799" s="41" t="s">
+        <v>7343</v>
+      </c>
+      <c r="D1799" s="8" t="s">
+        <v>7344</v>
+      </c>
+      <c r="E1799" s="8" t="s">
+        <v>7345</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1800" s="5" t="s">
+        <v>7346</v>
+      </c>
+      <c r="B1800" s="13" t="s">
+        <v>7347</v>
+      </c>
+      <c r="C1800" s="41" t="s">
+        <v>7348</v>
+      </c>
+      <c r="D1800" s="8" t="s">
+        <v>7349</v>
+      </c>
+      <c r="E1800" s="8" t="s">
+        <v>7350</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1801" s="5" t="s">
+        <v>7351</v>
+      </c>
+      <c r="B1801" s="13" t="s">
+        <v>7352</v>
+      </c>
+      <c r="C1801" s="41" t="s">
+        <v>7353</v>
+      </c>
+      <c r="D1801" s="8" t="s">
+        <v>7354</v>
+      </c>
+      <c r="E1801" s="8" t="s">
+        <v>7355</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1802" s="15" t="s">
+        <v>7356</v>
+      </c>
+      <c r="B1802" s="13" t="s">
+        <v>7357</v>
+      </c>
+      <c r="C1802" s="42" t="s">
+        <v>7358</v>
+      </c>
+      <c r="D1802" s="13" t="s">
+        <v>7359</v>
+      </c>
+      <c r="E1802" s="13" t="s">
+        <v>7360</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1803" s="15" t="s">
+        <v>7361</v>
+      </c>
+      <c r="B1803" s="13" t="s">
+        <v>7362</v>
+      </c>
+      <c r="C1803" s="42" t="s">
+        <v>7363</v>
+      </c>
+      <c r="D1803" s="13" t="s">
+        <v>7364</v>
+      </c>
+      <c r="E1803" s="13" t="s">
+        <v>7365</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1804" s="15" t="s">
+        <v>7366</v>
+      </c>
+      <c r="B1804" s="13" t="s">
+        <v>7367</v>
+      </c>
+      <c r="C1804" s="42" t="s">
+        <v>7368</v>
+      </c>
+      <c r="D1804" s="13" t="s">
+        <v>7369</v>
+      </c>
+      <c r="E1804" s="13" t="s">
+        <v>7370</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1805" s="5" t="s">
+        <v>7371</v>
+      </c>
+      <c r="B1805" s="13" t="s">
+        <v>7372</v>
+      </c>
+      <c r="C1805" s="41" t="s">
+        <v>7373</v>
+      </c>
+      <c r="D1805" s="8" t="s">
+        <v>7374</v>
+      </c>
+      <c r="E1805" s="8" t="s">
+        <v>7375</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1806" s="5" t="s">
+        <v>7376</v>
+      </c>
+      <c r="B1806" s="13" t="s">
+        <v>7377</v>
+      </c>
+      <c r="C1806" s="41" t="s">
+        <v>7378</v>
+      </c>
+      <c r="D1806" s="8" t="s">
+        <v>7379</v>
+      </c>
+      <c r="E1806" s="8" t="s">
+        <v>7380</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1807" s="5" t="s">
+        <v>7381</v>
+      </c>
+      <c r="B1807" s="13" t="s">
+        <v>7382</v>
+      </c>
+      <c r="C1807" s="41" t="s">
+        <v>7383</v>
+      </c>
+      <c r="D1807" s="8" t="s">
+        <v>7384</v>
+      </c>
+      <c r="E1807" s="8" t="s">
+        <v>7385</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1808" s="5" t="s">
+        <v>7386</v>
+      </c>
+      <c r="B1808" s="13" t="s">
+        <v>7387</v>
+      </c>
+      <c r="C1808" s="41" t="s">
+        <v>7388</v>
+      </c>
+      <c r="D1808" s="8" t="s">
+        <v>7389</v>
+      </c>
+      <c r="E1808" s="8" t="s">
+        <v>7390</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1809" s="5" t="s">
+        <v>7391</v>
+      </c>
+      <c r="B1809" s="13" t="s">
+        <v>7392</v>
+      </c>
+      <c r="C1809" s="41" t="s">
+        <v>7393</v>
+      </c>
+      <c r="D1809" s="8" t="s">
+        <v>7394</v>
+      </c>
+      <c r="E1809" s="8" t="s">
+        <v>7395</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1810" s="5" t="s">
+        <v>7396</v>
+      </c>
+      <c r="B1810" s="13" t="s">
+        <v>7397</v>
+      </c>
+      <c r="C1810" s="41" t="s">
+        <v>7398</v>
+      </c>
+      <c r="D1810" s="8" t="s">
+        <v>7399</v>
+      </c>
+      <c r="E1810" s="8" t="s">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1811" s="5" t="s">
+        <v>7401</v>
+      </c>
+      <c r="B1811" s="13" t="s">
+        <v>7402</v>
+      </c>
+      <c r="C1811" s="41" t="s">
+        <v>7403</v>
+      </c>
+      <c r="D1811" s="8" t="s">
+        <v>7404</v>
+      </c>
+      <c r="E1811" s="8" t="s">
+        <v>7405</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1812" s="15" t="s">
+        <v>7406</v>
+      </c>
+      <c r="B1812" s="13" t="s">
+        <v>7407</v>
+      </c>
+      <c r="C1812" s="42" t="s">
+        <v>7408</v>
+      </c>
+      <c r="D1812" s="13" t="s">
+        <v>7409</v>
+      </c>
+      <c r="E1812" s="13" t="s">
+        <v>7410</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1813" s="15" t="s">
+        <v>7411</v>
+      </c>
+      <c r="B1813" s="13" t="s">
+        <v>7412</v>
+      </c>
+      <c r="C1813" s="42" t="s">
+        <v>7413</v>
+      </c>
+      <c r="D1813" s="13" t="s">
+        <v>7414</v>
+      </c>
+      <c r="E1813" s="13" t="s">
+        <v>7415</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1814" s="15" t="s">
+        <v>7416</v>
+      </c>
+      <c r="B1814" s="13" t="s">
+        <v>7417</v>
+      </c>
+      <c r="C1814" s="42" t="s">
+        <v>7418</v>
+      </c>
+      <c r="D1814" s="13" t="s">
+        <v>7419</v>
+      </c>
+      <c r="E1814" s="13" t="s">
+        <v>7420</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1815" s="15" t="s">
+        <v>7421</v>
+      </c>
+      <c r="B1815" s="13" t="s">
+        <v>7422</v>
+      </c>
+      <c r="C1815" s="42" t="s">
+        <v>7423</v>
+      </c>
+      <c r="D1815" s="13" t="s">
+        <v>7424</v>
+      </c>
+      <c r="E1815" s="13" t="s">
+        <v>7425</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1816" s="15" t="s">
+        <v>7426</v>
+      </c>
+      <c r="B1816" s="13" t="s">
+        <v>7427</v>
+      </c>
+      <c r="C1816" s="42" t="s">
+        <v>7428</v>
+      </c>
+      <c r="D1816" s="13" t="s">
+        <v>7429</v>
+      </c>
+      <c r="E1816" s="13" t="s">
+        <v>7430</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1817" s="15" t="s">
+        <v>7431</v>
+      </c>
+      <c r="B1817" s="13" t="s">
+        <v>7432</v>
+      </c>
+      <c r="C1817" s="42" t="s">
+        <v>7433</v>
+      </c>
+      <c r="D1817" s="13" t="s">
+        <v>7434</v>
+      </c>
+      <c r="E1817" s="13" t="s">
+        <v>7435</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1818" s="15" t="s">
+        <v>7436</v>
+      </c>
+      <c r="B1818" s="13" t="s">
+        <v>7437</v>
+      </c>
+      <c r="C1818" s="42" t="s">
+        <v>7438</v>
+      </c>
+      <c r="D1818" s="13" t="s">
+        <v>7439</v>
+      </c>
+      <c r="E1818" s="13" t="s">
+        <v>7440</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4BCDCE-EA2F-4EFF-A00F-9534DAD4F3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091E824C-06B3-481F-B2DE-43E873124D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1740" yWindow="975" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7453" uniqueCount="7441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7473" uniqueCount="7461">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -22359,18 +22359,86 @@
   </si>
   <si>
     <t>40.437012, 70.630706</t>
+  </si>
+  <si>
+    <t>Yandama sh., To‘raqo‘rg‘on tumani, Navbahor ko'chasi, 212 uy : г. Яндама, Туракурганский район, улица Навбахор, дом 212</t>
+  </si>
+  <si>
+    <t>FrЯДМ-1</t>
+  </si>
+  <si>
+    <t>99890 694 16 96</t>
+  </si>
+  <si>
+    <t>@UzumFrYADM1</t>
+  </si>
+  <si>
+    <t>40.955885, 71.439711</t>
+  </si>
+  <si>
+    <t>Chorvoqguzar sh., Navbahor tumani, Yangiqo'rg'on ko'chasi, 38 uy : г. Чарвокгузар, Навбахорский район, улица Янгикурган, дом 38</t>
+  </si>
+  <si>
+    <t>FrЧАР-1</t>
+  </si>
+  <si>
+    <t>998 99 044 12 05</t>
+  </si>
+  <si>
+    <t>@Uzum_BTP</t>
+  </si>
+  <si>
+    <t>40.189962, 65.246247</t>
+  </si>
+  <si>
+    <t>Aqshaqul sh., Ellikkala tumani, Umar Hayyom koʻchasi, 269 uy : г. Акшакуль, Элликкалинский район, улица Омара Хайяма, дом 269</t>
+  </si>
+  <si>
+    <t>FrАКШ-1</t>
+  </si>
+  <si>
+    <t>998 99 806 80 21</t>
+  </si>
+  <si>
+    <t>@FrAKSH1</t>
+  </si>
+  <si>
+    <t>41.873368, 60.881607</t>
+  </si>
+  <si>
+    <t>Chust sh., Chustiy koʻchasi, 208 uy : г. Чуст, улица Чустий, дом 208</t>
+  </si>
+  <si>
+    <t>FrЧСТ-9</t>
+  </si>
+  <si>
+    <t>998 50 991 14 56</t>
+  </si>
+  <si>
+    <t>@frchst9</t>
+  </si>
+  <si>
+    <t>41.015301, 71.222488</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -22537,57 +22605,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22596,7 +22673,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22605,16 +22682,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22623,16 +22703,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22641,13 +22715,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22656,13 +22733,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -22969,7 +23046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1818"/>
+  <dimension ref="A1:E1822"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -53868,20 +53945,88 @@
       </c>
     </row>
     <row r="1818" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1818" s="15" t="s">
+      <c r="A1818" s="29" t="s">
         <v>7436</v>
       </c>
-      <c r="B1818" s="13" t="s">
+      <c r="B1818" s="17" t="s">
         <v>7437</v>
       </c>
-      <c r="C1818" s="42" t="s">
+      <c r="C1818" s="43" t="s">
         <v>7438</v>
       </c>
-      <c r="D1818" s="13" t="s">
+      <c r="D1818" s="17" t="s">
         <v>7439</v>
       </c>
-      <c r="E1818" s="13" t="s">
+      <c r="E1818" s="17" t="s">
         <v>7440</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1819" s="44" t="s">
+        <v>7441</v>
+      </c>
+      <c r="B1819" s="6" t="s">
+        <v>7442</v>
+      </c>
+      <c r="C1819" s="45" t="s">
+        <v>7443</v>
+      </c>
+      <c r="D1819" s="6" t="s">
+        <v>7444</v>
+      </c>
+      <c r="E1819" s="6" t="s">
+        <v>7445</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1820" s="44" t="s">
+        <v>7446</v>
+      </c>
+      <c r="B1820" s="6" t="s">
+        <v>7447</v>
+      </c>
+      <c r="C1820" s="45" t="s">
+        <v>7448</v>
+      </c>
+      <c r="D1820" s="6" t="s">
+        <v>7449</v>
+      </c>
+      <c r="E1820" s="6" t="s">
+        <v>7450</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1821" s="44" t="s">
+        <v>7451</v>
+      </c>
+      <c r="B1821" s="6" t="s">
+        <v>7452</v>
+      </c>
+      <c r="C1821" s="45" t="s">
+        <v>7453</v>
+      </c>
+      <c r="D1821" s="6" t="s">
+        <v>7454</v>
+      </c>
+      <c r="E1821" s="6" t="s">
+        <v>7455</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1822" s="44" t="s">
+        <v>7456</v>
+      </c>
+      <c r="B1822" s="6" t="s">
+        <v>7457</v>
+      </c>
+      <c r="C1822" s="45" t="s">
+        <v>7458</v>
+      </c>
+      <c r="D1822" s="6" t="s">
+        <v>7459</v>
+      </c>
+      <c r="E1822" s="6" t="s">
+        <v>7460</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091E824C-06B3-481F-B2DE-43E873124D2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DAF1B9-AE24-42FF-ACA4-58BA8FBD63DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="975" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1800" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7473" uniqueCount="7461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7523" uniqueCount="7511">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -22419,18 +22419,176 @@
   </si>
   <si>
     <t>41.015301, 71.222488</t>
+  </si>
+  <si>
+    <t>Xishrov sh., Samarqand tumani, Isfahon koʻchasi, 24 uy : г. Хишров, Самаркандский район, улица Исфахон, дом 24</t>
+  </si>
+  <si>
+    <t>FrХАШ-1</t>
+  </si>
+  <si>
+    <t>998 70 313 56 59</t>
+  </si>
+  <si>
+    <t>@fr_XASH_1</t>
+  </si>
+  <si>
+    <t>39.646152, 66.893631</t>
+  </si>
+  <si>
+    <t>Vodil sh., Oralik ko‘chasi, 6A uy: г. Вуадиль, улица Оралик, дом 6А</t>
+  </si>
+  <si>
+    <t>FrВАД-2</t>
+  </si>
+  <si>
+    <t>998 91 060 15 75</t>
+  </si>
+  <si>
+    <t>@FrVad2</t>
+  </si>
+  <si>
+    <t>40.169491, 71.729522</t>
+  </si>
+  <si>
+    <t>Qoʻshariq sh., Andijon tumani, Matbuotchi koʻchasi, 223 uy : г. Кошарык, Андижанский район, улица Матбуотчи, дом 223</t>
+  </si>
+  <si>
+    <t>FrКОШ-2</t>
+  </si>
+  <si>
+    <t>998 50 794 30 23</t>
+  </si>
+  <si>
+    <t>@FrKosh2</t>
+  </si>
+  <si>
+    <t>40.833377, 72.324589</t>
+  </si>
+  <si>
+    <t>Zarafshon sh., 2 mavzesi, 3A uy: г. Зарафшан, 2 й микрорайон, дом 3A</t>
+  </si>
+  <si>
+    <t>FrЗАР-8</t>
+  </si>
+  <si>
+    <t>998 70 165 79 75</t>
+  </si>
+  <si>
+    <t>@ZarafshonUzum</t>
+  </si>
+  <si>
+    <t>41.566894, 64.207490</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Takzar 2 proyezd, 3 uy: г. Ташкент, Чиланзарский район, 2 й проезд Такзар, дом 3</t>
+  </si>
+  <si>
+    <t>FrТАШ-452</t>
+  </si>
+  <si>
+    <t>998 50 302 86 63</t>
+  </si>
+  <si>
+    <t>@FRTASH_452</t>
+  </si>
+  <si>
+    <t>41.264521, 69.197846</t>
+  </si>
+  <si>
+    <t>Guliston sh., Soyibobod MFY, Sinchalak ko'chasi, 2 uy: г. Гулистан, Сойбобод МФИ, улица Синчалак, дом 2</t>
+  </si>
+  <si>
+    <t>FrГУЛ-10</t>
+  </si>
+  <si>
+    <t>998 90 020 23 26</t>
+  </si>
+  <si>
+    <t>@frgul_10</t>
+  </si>
+  <si>
+    <t>40.488341, 68.874178</t>
+  </si>
+  <si>
+    <t>Boboxoji sh., Peshku tumani, Shovare ko'chasi, 21 uy : г. Бобохожи, Пешкунский район, улица Шоваре, дом 21</t>
+  </si>
+  <si>
+    <t>FrБОБ-1</t>
+  </si>
+  <si>
+    <t>998 87 787 24 99</t>
+  </si>
+  <si>
+    <t>@FrBOB_1</t>
+  </si>
+  <si>
+    <t>40.108431, 64.279381</t>
+  </si>
+  <si>
+    <t>Shirin sh., 4-blok, Yurtsevar ko'chasi, 1 uy : г. Ширин, 4-й блок, улица Юртсевар, дом 1</t>
+  </si>
+  <si>
+    <t>FrШИР-2</t>
+  </si>
+  <si>
+    <t>998 20 006 26 67</t>
+  </si>
+  <si>
+    <t>@Uzum_marketshirin</t>
+  </si>
+  <si>
+    <t>40.229333, 69.123176</t>
+  </si>
+  <si>
+    <t>Turkibolo sh., Payariq tumani, Istiqlol ko‘chasi, 9 uy : г. Туркиболо, Пайарыкский район, улица Истиклол, дом 9</t>
+  </si>
+  <si>
+    <t>FrТБЛ-1</t>
+  </si>
+  <si>
+    <t>998 90 514 36 26</t>
+  </si>
+  <si>
+    <t>@fr_tbl_1</t>
+  </si>
+  <si>
+    <t>39.927359, 66.899398</t>
+  </si>
+  <si>
+    <t>Koʻkmuyin sh., Oʻrtachirchiq tumani, Temirchi ko‘chasi, 90A uy : г. Кукмуйин, Уртачирчикский район, улица Темирчи, дом 90А</t>
+  </si>
+  <si>
+    <t>FrКМН-1</t>
+  </si>
+  <si>
+    <t>998 33 185 20 75</t>
+  </si>
+  <si>
+    <t>@FR_KMN_1</t>
+  </si>
+  <si>
+    <t>41.138806, 69.394391</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -22605,57 +22763,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22664,7 +22831,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22673,16 +22840,19 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22691,16 +22861,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22709,13 +22873,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22724,23 +22891,26 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23046,7 +23216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1822"/>
+  <dimension ref="A1:E1833"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -54013,21 +54183,194 @@
       </c>
     </row>
     <row r="1822" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1822" s="44" t="s">
+      <c r="A1822" s="46" t="s">
         <v>7456</v>
       </c>
-      <c r="B1822" s="6" t="s">
+      <c r="B1822" s="20" t="s">
         <v>7457</v>
       </c>
-      <c r="C1822" s="45" t="s">
+      <c r="C1822" s="47" t="s">
         <v>7458</v>
       </c>
-      <c r="D1822" s="6" t="s">
+      <c r="D1822" s="20" t="s">
         <v>7459</v>
       </c>
-      <c r="E1822" s="6" t="s">
+      <c r="E1822" s="20" t="s">
         <v>7460</v>
       </c>
+    </row>
+    <row r="1823" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1823" s="5" t="s">
+        <v>7461</v>
+      </c>
+      <c r="B1823" s="6" t="s">
+        <v>7462</v>
+      </c>
+      <c r="C1823" s="48" t="s">
+        <v>7463</v>
+      </c>
+      <c r="D1823" s="8" t="s">
+        <v>7464</v>
+      </c>
+      <c r="E1823" s="8" t="s">
+        <v>7465</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1824" s="5" t="s">
+        <v>7466</v>
+      </c>
+      <c r="B1824" s="6" t="s">
+        <v>7467</v>
+      </c>
+      <c r="C1824" s="48" t="s">
+        <v>7468</v>
+      </c>
+      <c r="D1824" s="8" t="s">
+        <v>7469</v>
+      </c>
+      <c r="E1824" s="8" t="s">
+        <v>7470</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1825" s="5" t="s">
+        <v>7471</v>
+      </c>
+      <c r="B1825" s="6" t="s">
+        <v>7472</v>
+      </c>
+      <c r="C1825" s="48" t="s">
+        <v>7473</v>
+      </c>
+      <c r="D1825" s="8" t="s">
+        <v>7474</v>
+      </c>
+      <c r="E1825" s="8" t="s">
+        <v>7475</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1826" s="5" t="s">
+        <v>7476</v>
+      </c>
+      <c r="B1826" s="6" t="s">
+        <v>7477</v>
+      </c>
+      <c r="C1826" s="48" t="s">
+        <v>7478</v>
+      </c>
+      <c r="D1826" s="8" t="s">
+        <v>7479</v>
+      </c>
+      <c r="E1826" s="8" t="s">
+        <v>7480</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1827" s="5" t="s">
+        <v>7481</v>
+      </c>
+      <c r="B1827" s="6" t="s">
+        <v>7482</v>
+      </c>
+      <c r="C1827" s="48" t="s">
+        <v>7483</v>
+      </c>
+      <c r="D1827" s="8" t="s">
+        <v>7484</v>
+      </c>
+      <c r="E1827" s="8" t="s">
+        <v>7485</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1828" s="5" t="s">
+        <v>7486</v>
+      </c>
+      <c r="B1828" s="6" t="s">
+        <v>7487</v>
+      </c>
+      <c r="C1828" s="48" t="s">
+        <v>7488</v>
+      </c>
+      <c r="D1828" s="8" t="s">
+        <v>7489</v>
+      </c>
+      <c r="E1828" s="8" t="s">
+        <v>7490</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1829" s="5" t="s">
+        <v>7491</v>
+      </c>
+      <c r="B1829" s="6" t="s">
+        <v>7492</v>
+      </c>
+      <c r="C1829" s="48" t="s">
+        <v>7493</v>
+      </c>
+      <c r="D1829" s="8" t="s">
+        <v>7494</v>
+      </c>
+      <c r="E1829" s="8" t="s">
+        <v>7495</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1830" s="5" t="s">
+        <v>7496</v>
+      </c>
+      <c r="B1830" s="6" t="s">
+        <v>7497</v>
+      </c>
+      <c r="C1830" s="48" t="s">
+        <v>7498</v>
+      </c>
+      <c r="D1830" s="8" t="s">
+        <v>7499</v>
+      </c>
+      <c r="E1830" s="8" t="s">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1831" s="5" t="s">
+        <v>7501</v>
+      </c>
+      <c r="B1831" s="6" t="s">
+        <v>7502</v>
+      </c>
+      <c r="C1831" s="48" t="s">
+        <v>7503</v>
+      </c>
+      <c r="D1831" s="8" t="s">
+        <v>7504</v>
+      </c>
+      <c r="E1831" s="8" t="s">
+        <v>7505</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1832" s="5" t="s">
+        <v>7506</v>
+      </c>
+      <c r="B1832" s="6" t="s">
+        <v>7507</v>
+      </c>
+      <c r="C1832" s="48" t="s">
+        <v>7508</v>
+      </c>
+      <c r="D1832" s="8" t="s">
+        <v>7509</v>
+      </c>
+      <c r="E1832" s="8" t="s">
+        <v>7510</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1833" s="49"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75DAF1B9-AE24-42FF-ACA4-58BA8FBD63DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100CCAF3-5978-4553-826C-81539A0E2525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1800" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7523" uniqueCount="7511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7533" uniqueCount="7516">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -22569,18 +22569,41 @@
   </si>
   <si>
     <t>41.138806, 69.394391</t>
+  </si>
+  <si>
+    <t>Cho'rindi sh., Bag‘dod tumani, Quvasoy ko‘chasi, 152 uy : г. Чуринди, Багдадский район, улица Кувасой дом 152</t>
+  </si>
+  <si>
+    <t>FrЧРН-1</t>
+  </si>
+  <si>
+    <t>998 90 364 15 02</t>
+  </si>
+  <si>
+    <t>@UzumFrCHRN1</t>
+  </si>
+  <si>
+    <t>40.451168, 71.177726</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -22763,57 +22786,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22822,7 +22854,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22831,16 +22863,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22849,16 +22884,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22867,13 +22896,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22882,35 +22914,32 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23216,7 +23245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1833"/>
+  <dimension ref="A1:E1834"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -54353,24 +54382,55 @@
       </c>
     </row>
     <row r="1832" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1832" s="5" t="s">
+      <c r="A1832" s="10" t="s">
         <v>7506</v>
       </c>
-      <c r="B1832" s="6" t="s">
+      <c r="B1832" s="20" t="s">
         <v>7507</v>
       </c>
-      <c r="C1832" s="48" t="s">
+      <c r="C1832" s="49" t="s">
         <v>7508</v>
       </c>
-      <c r="D1832" s="8" t="s">
+      <c r="D1832" s="11" t="s">
         <v>7509</v>
       </c>
-      <c r="E1832" s="8" t="s">
+      <c r="E1832" s="11" t="s">
         <v>7510</v>
       </c>
     </row>
-    <row r="1833" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B1833" s="49"/>
+    <row r="1833" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1833" s="15" t="s">
+        <v>7506</v>
+      </c>
+      <c r="B1833" s="13" t="s">
+        <v>7507</v>
+      </c>
+      <c r="C1833" s="50" t="s">
+        <v>7508</v>
+      </c>
+      <c r="D1833" s="13" t="s">
+        <v>7509</v>
+      </c>
+      <c r="E1833" s="13" t="s">
+        <v>7510</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1834" s="5" t="s">
+        <v>7511</v>
+      </c>
+      <c r="B1834" s="8" t="s">
+        <v>7512</v>
+      </c>
+      <c r="C1834" s="51" t="s">
+        <v>7513</v>
+      </c>
+      <c r="D1834" s="8" t="s">
+        <v>7514</v>
+      </c>
+      <c r="E1834" s="8" t="s">
+        <v>7515</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100CCAF3-5978-4553-826C-81539A0E2525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C8DA3D-74A1-472C-92D8-06BD70A4F416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15600" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="2145" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21317,9 +21317,6 @@
     <t>998 90 899 00 49</t>
   </si>
   <si>
-    <t>@uzumalgar</t>
-  </si>
-  <si>
     <t>39.460593, 67.210786</t>
   </si>
   <si>
@@ -22584,6 +22581,9 @@
   </si>
   <si>
     <t>40.451168, 71.177726</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @frALX_1</t>
   </si>
 </sst>
 </file>
@@ -52964,1472 +52964,1472 @@
         <v>7092</v>
       </c>
       <c r="D1748" s="8" t="s">
+        <v>7515</v>
+      </c>
+      <c r="E1748" s="8" t="s">
         <v>7093</v>
-      </c>
-      <c r="E1748" s="8" t="s">
-        <v>7094</v>
       </c>
     </row>
     <row r="1749" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1749" s="10" t="s">
+        <v>7094</v>
+      </c>
+      <c r="B1749" s="11" t="s">
         <v>7095</v>
       </c>
-      <c r="B1749" s="11" t="s">
+      <c r="C1749" s="35" t="s">
         <v>7096</v>
       </c>
-      <c r="C1749" s="35" t="s">
+      <c r="D1749" s="11" t="s">
         <v>7097</v>
       </c>
-      <c r="D1749" s="11" t="s">
+      <c r="E1749" s="11" t="s">
         <v>7098</v>
-      </c>
-      <c r="E1749" s="11" t="s">
-        <v>7099</v>
       </c>
     </row>
     <row r="1750" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1750" s="5" t="s">
+        <v>7099</v>
+      </c>
+      <c r="B1750" s="13" t="s">
         <v>7100</v>
       </c>
-      <c r="B1750" s="13" t="s">
+      <c r="C1750" s="36" t="s">
         <v>7101</v>
       </c>
-      <c r="C1750" s="36" t="s">
+      <c r="D1750" s="8" t="s">
         <v>7102</v>
       </c>
-      <c r="D1750" s="8" t="s">
+      <c r="E1750" s="8" t="s">
         <v>7103</v>
-      </c>
-      <c r="E1750" s="8" t="s">
-        <v>7104</v>
       </c>
     </row>
     <row r="1751" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1751" s="5" t="s">
+        <v>7104</v>
+      </c>
+      <c r="B1751" s="13" t="s">
         <v>7105</v>
       </c>
-      <c r="B1751" s="13" t="s">
+      <c r="C1751" s="36" t="s">
         <v>7106</v>
       </c>
-      <c r="C1751" s="36" t="s">
+      <c r="D1751" s="8" t="s">
         <v>7107</v>
       </c>
-      <c r="D1751" s="8" t="s">
+      <c r="E1751" s="8" t="s">
         <v>7108</v>
-      </c>
-      <c r="E1751" s="8" t="s">
-        <v>7109</v>
       </c>
     </row>
     <row r="1752" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1752" s="5" t="s">
+        <v>7109</v>
+      </c>
+      <c r="B1752" s="13" t="s">
         <v>7110</v>
       </c>
-      <c r="B1752" s="13" t="s">
+      <c r="C1752" s="36" t="s">
         <v>7111</v>
       </c>
-      <c r="C1752" s="36" t="s">
+      <c r="D1752" s="8" t="s">
         <v>7112</v>
       </c>
-      <c r="D1752" s="8" t="s">
+      <c r="E1752" s="8" t="s">
         <v>7113</v>
-      </c>
-      <c r="E1752" s="8" t="s">
-        <v>7114</v>
       </c>
     </row>
     <row r="1753" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1753" s="5" t="s">
+        <v>7114</v>
+      </c>
+      <c r="B1753" s="13" t="s">
         <v>7115</v>
       </c>
-      <c r="B1753" s="13" t="s">
+      <c r="C1753" s="36" t="s">
         <v>7116</v>
       </c>
-      <c r="C1753" s="36" t="s">
+      <c r="D1753" s="8" t="s">
         <v>7117</v>
       </c>
-      <c r="D1753" s="8" t="s">
+      <c r="E1753" s="8" t="s">
         <v>7118</v>
-      </c>
-      <c r="E1753" s="8" t="s">
-        <v>7119</v>
       </c>
     </row>
     <row r="1754" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1754" s="5" t="s">
+        <v>7119</v>
+      </c>
+      <c r="B1754" s="13" t="s">
         <v>7120</v>
       </c>
-      <c r="B1754" s="13" t="s">
+      <c r="C1754" s="36" t="s">
         <v>7121</v>
       </c>
-      <c r="C1754" s="36" t="s">
+      <c r="D1754" s="8" t="s">
         <v>7122</v>
       </c>
-      <c r="D1754" s="8" t="s">
+      <c r="E1754" s="8" t="s">
         <v>7123</v>
-      </c>
-      <c r="E1754" s="8" t="s">
-        <v>7124</v>
       </c>
     </row>
     <row r="1755" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1755" s="5" t="s">
+        <v>7124</v>
+      </c>
+      <c r="B1755" s="13" t="s">
         <v>7125</v>
       </c>
-      <c r="B1755" s="13" t="s">
+      <c r="C1755" s="36" t="s">
         <v>7126</v>
       </c>
-      <c r="C1755" s="36" t="s">
+      <c r="D1755" s="8" t="s">
         <v>7127</v>
       </c>
-      <c r="D1755" s="8" t="s">
+      <c r="E1755" s="8" t="s">
         <v>7128</v>
-      </c>
-      <c r="E1755" s="8" t="s">
-        <v>7129</v>
       </c>
     </row>
     <row r="1756" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1756" s="29" t="s">
+        <v>7129</v>
+      </c>
+      <c r="B1756" s="17" t="s">
         <v>7130</v>
       </c>
-      <c r="B1756" s="17" t="s">
+      <c r="C1756" s="37" t="s">
+        <v>7116</v>
+      </c>
+      <c r="D1756" s="17" t="s">
         <v>7131</v>
       </c>
-      <c r="C1756" s="37" t="s">
-        <v>7117</v>
-      </c>
-      <c r="D1756" s="17" t="s">
+      <c r="E1756" s="17" t="s">
         <v>7132</v>
-      </c>
-      <c r="E1756" s="17" t="s">
-        <v>7133</v>
       </c>
     </row>
     <row r="1757" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1757" s="5" t="s">
+        <v>7133</v>
+      </c>
+      <c r="B1757" s="13" t="s">
         <v>7134</v>
       </c>
-      <c r="B1757" s="13" t="s">
+      <c r="C1757" s="38" t="s">
         <v>7135</v>
       </c>
-      <c r="C1757" s="38" t="s">
+      <c r="D1757" s="8" t="s">
         <v>7136</v>
       </c>
-      <c r="D1757" s="8" t="s">
+      <c r="E1757" s="8" t="s">
         <v>7137</v>
-      </c>
-      <c r="E1757" s="8" t="s">
-        <v>7138</v>
       </c>
     </row>
     <row r="1758" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1758" s="5" t="s">
+        <v>7138</v>
+      </c>
+      <c r="B1758" s="13" t="s">
         <v>7139</v>
       </c>
-      <c r="B1758" s="13" t="s">
+      <c r="C1758" s="38" t="s">
         <v>7140</v>
       </c>
-      <c r="C1758" s="38" t="s">
+      <c r="D1758" s="8" t="s">
         <v>7141</v>
       </c>
-      <c r="D1758" s="8" t="s">
+      <c r="E1758" s="8" t="s">
         <v>7142</v>
-      </c>
-      <c r="E1758" s="8" t="s">
-        <v>7143</v>
       </c>
     </row>
     <row r="1759" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1759" s="15" t="s">
+        <v>7143</v>
+      </c>
+      <c r="B1759" s="13" t="s">
         <v>7144</v>
       </c>
-      <c r="B1759" s="13" t="s">
+      <c r="C1759" s="39" t="s">
         <v>7145</v>
       </c>
-      <c r="C1759" s="39" t="s">
+      <c r="D1759" s="13" t="s">
         <v>7146</v>
       </c>
-      <c r="D1759" s="13" t="s">
+      <c r="E1759" s="13" t="s">
         <v>7147</v>
-      </c>
-      <c r="E1759" s="13" t="s">
-        <v>7148</v>
       </c>
     </row>
     <row r="1760" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1760" s="5" t="s">
+        <v>7148</v>
+      </c>
+      <c r="B1760" s="13" t="s">
         <v>7149</v>
       </c>
-      <c r="B1760" s="13" t="s">
+      <c r="C1760" s="38" t="s">
         <v>7150</v>
       </c>
-      <c r="C1760" s="38" t="s">
+      <c r="D1760" s="8" t="s">
         <v>7151</v>
       </c>
-      <c r="D1760" s="8" t="s">
+      <c r="E1760" s="8" t="s">
         <v>7152</v>
-      </c>
-      <c r="E1760" s="8" t="s">
-        <v>7153</v>
       </c>
     </row>
     <row r="1761" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1761" s="15" t="s">
+        <v>7153</v>
+      </c>
+      <c r="B1761" s="13" t="s">
         <v>7154</v>
       </c>
-      <c r="B1761" s="13" t="s">
+      <c r="C1761" s="39" t="s">
         <v>7155</v>
       </c>
-      <c r="C1761" s="39" t="s">
+      <c r="D1761" s="13" t="s">
         <v>7156</v>
       </c>
-      <c r="D1761" s="13" t="s">
+      <c r="E1761" s="13" t="s">
         <v>7157</v>
-      </c>
-      <c r="E1761" s="13" t="s">
-        <v>7158</v>
       </c>
     </row>
     <row r="1762" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1762" s="5" t="s">
+        <v>7158</v>
+      </c>
+      <c r="B1762" s="13" t="s">
         <v>7159</v>
       </c>
-      <c r="B1762" s="13" t="s">
+      <c r="C1762" s="38" t="s">
         <v>7160</v>
       </c>
-      <c r="C1762" s="38" t="s">
+      <c r="D1762" s="8" t="s">
         <v>7161</v>
       </c>
-      <c r="D1762" s="8" t="s">
+      <c r="E1762" s="8" t="s">
         <v>7162</v>
-      </c>
-      <c r="E1762" s="8" t="s">
-        <v>7163</v>
       </c>
     </row>
     <row r="1763" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1763" s="15" t="s">
+        <v>7163</v>
+      </c>
+      <c r="B1763" s="13" t="s">
         <v>7164</v>
       </c>
-      <c r="B1763" s="13" t="s">
+      <c r="C1763" s="39" t="s">
         <v>7165</v>
       </c>
-      <c r="C1763" s="39" t="s">
+      <c r="D1763" s="13" t="s">
         <v>7166</v>
       </c>
-      <c r="D1763" s="13" t="s">
+      <c r="E1763" s="13" t="s">
         <v>7167</v>
-      </c>
-      <c r="E1763" s="13" t="s">
-        <v>7168</v>
       </c>
     </row>
     <row r="1764" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1764" s="15" t="s">
+        <v>7168</v>
+      </c>
+      <c r="B1764" s="13" t="s">
         <v>7169</v>
       </c>
-      <c r="B1764" s="13" t="s">
+      <c r="C1764" s="39" t="s">
+        <v>7165</v>
+      </c>
+      <c r="D1764" s="13" t="s">
         <v>7170</v>
       </c>
-      <c r="C1764" s="39" t="s">
-        <v>7166</v>
-      </c>
-      <c r="D1764" s="13" t="s">
+      <c r="E1764" s="13" t="s">
         <v>7171</v>
-      </c>
-      <c r="E1764" s="13" t="s">
-        <v>7172</v>
       </c>
     </row>
     <row r="1765" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1765" s="5" t="s">
+        <v>7172</v>
+      </c>
+      <c r="B1765" s="13" t="s">
         <v>7173</v>
       </c>
-      <c r="B1765" s="13" t="s">
+      <c r="C1765" s="38" t="s">
         <v>7174</v>
       </c>
-      <c r="C1765" s="38" t="s">
+      <c r="D1765" s="8" t="s">
         <v>7175</v>
       </c>
-      <c r="D1765" s="8" t="s">
+      <c r="E1765" s="8" t="s">
         <v>7176</v>
-      </c>
-      <c r="E1765" s="8" t="s">
-        <v>7177</v>
       </c>
     </row>
     <row r="1766" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1766" s="5" t="s">
+        <v>7177</v>
+      </c>
+      <c r="B1766" s="13" t="s">
         <v>7178</v>
       </c>
-      <c r="B1766" s="13" t="s">
+      <c r="C1766" s="38" t="s">
         <v>7179</v>
       </c>
-      <c r="C1766" s="38" t="s">
+      <c r="D1766" s="8" t="s">
         <v>7180</v>
       </c>
-      <c r="D1766" s="8" t="s">
+      <c r="E1766" s="8" t="s">
         <v>7181</v>
-      </c>
-      <c r="E1766" s="8" t="s">
-        <v>7182</v>
       </c>
     </row>
     <row r="1767" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1767" s="5" t="s">
+        <v>7182</v>
+      </c>
+      <c r="B1767" s="13" t="s">
         <v>7183</v>
       </c>
-      <c r="B1767" s="13" t="s">
+      <c r="C1767" s="38" t="s">
         <v>7184</v>
       </c>
-      <c r="C1767" s="38" t="s">
+      <c r="D1767" s="8" t="s">
         <v>7185</v>
       </c>
-      <c r="D1767" s="8" t="s">
+      <c r="E1767" s="8" t="s">
         <v>7186</v>
-      </c>
-      <c r="E1767" s="8" t="s">
-        <v>7187</v>
       </c>
     </row>
     <row r="1768" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1768" s="5" t="s">
+        <v>7187</v>
+      </c>
+      <c r="B1768" s="13" t="s">
         <v>7188</v>
       </c>
-      <c r="B1768" s="13" t="s">
+      <c r="C1768" s="38" t="s">
         <v>7189</v>
       </c>
-      <c r="C1768" s="38" t="s">
+      <c r="D1768" s="8" t="s">
         <v>7190</v>
       </c>
-      <c r="D1768" s="8" t="s">
+      <c r="E1768" s="8" t="s">
         <v>7191</v>
-      </c>
-      <c r="E1768" s="8" t="s">
-        <v>7192</v>
       </c>
     </row>
     <row r="1769" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1769" s="5" t="s">
+        <v>7192</v>
+      </c>
+      <c r="B1769" s="13" t="s">
         <v>7193</v>
       </c>
-      <c r="B1769" s="13" t="s">
+      <c r="C1769" s="38" t="s">
         <v>7194</v>
       </c>
-      <c r="C1769" s="38" t="s">
+      <c r="D1769" s="8" t="s">
         <v>7195</v>
       </c>
-      <c r="D1769" s="8" t="s">
+      <c r="E1769" s="8" t="s">
         <v>7196</v>
-      </c>
-      <c r="E1769" s="8" t="s">
-        <v>7197</v>
       </c>
     </row>
     <row r="1770" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1770" s="5" t="s">
+        <v>7197</v>
+      </c>
+      <c r="B1770" s="13" t="s">
         <v>7198</v>
       </c>
-      <c r="B1770" s="13" t="s">
+      <c r="C1770" s="38" t="s">
         <v>7199</v>
       </c>
-      <c r="C1770" s="38" t="s">
+      <c r="D1770" s="8" t="s">
         <v>7200</v>
       </c>
-      <c r="D1770" s="8" t="s">
+      <c r="E1770" s="8" t="s">
         <v>7201</v>
-      </c>
-      <c r="E1770" s="8" t="s">
-        <v>7202</v>
       </c>
     </row>
     <row r="1771" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1771" s="5" t="s">
+        <v>7202</v>
+      </c>
+      <c r="B1771" s="13" t="s">
         <v>7203</v>
       </c>
-      <c r="B1771" s="13" t="s">
+      <c r="C1771" s="38" t="s">
         <v>7204</v>
       </c>
-      <c r="C1771" s="38" t="s">
+      <c r="D1771" s="8" t="s">
         <v>7205</v>
       </c>
-      <c r="D1771" s="8" t="s">
+      <c r="E1771" s="8" t="s">
         <v>7206</v>
-      </c>
-      <c r="E1771" s="8" t="s">
-        <v>7207</v>
       </c>
     </row>
     <row r="1772" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1772" s="10" t="s">
+        <v>7207</v>
+      </c>
+      <c r="B1772" s="17" t="s">
         <v>7208</v>
       </c>
-      <c r="B1772" s="17" t="s">
+      <c r="C1772" s="40" t="s">
         <v>7209</v>
       </c>
-      <c r="C1772" s="40" t="s">
+      <c r="D1772" s="11" t="s">
         <v>7210</v>
       </c>
-      <c r="D1772" s="11" t="s">
+      <c r="E1772" s="11" t="s">
         <v>7211</v>
-      </c>
-      <c r="E1772" s="11" t="s">
-        <v>7212</v>
       </c>
     </row>
     <row r="1773" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1773" s="5" t="s">
+        <v>7212</v>
+      </c>
+      <c r="B1773" s="13" t="s">
         <v>7213</v>
       </c>
-      <c r="B1773" s="13" t="s">
+      <c r="C1773" s="41" t="s">
         <v>7214</v>
       </c>
-      <c r="C1773" s="41" t="s">
+      <c r="D1773" s="8" t="s">
         <v>7215</v>
       </c>
-      <c r="D1773" s="8" t="s">
+      <c r="E1773" s="8" t="s">
         <v>7216</v>
-      </c>
-      <c r="E1773" s="8" t="s">
-        <v>7217</v>
       </c>
     </row>
     <row r="1774" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1774" s="5" t="s">
+        <v>7217</v>
+      </c>
+      <c r="B1774" s="13" t="s">
         <v>7218</v>
       </c>
-      <c r="B1774" s="13" t="s">
+      <c r="C1774" s="41" t="s">
         <v>7219</v>
       </c>
-      <c r="C1774" s="41" t="s">
+      <c r="D1774" s="8" t="s">
         <v>7220</v>
       </c>
-      <c r="D1774" s="8" t="s">
+      <c r="E1774" s="8" t="s">
         <v>7221</v>
-      </c>
-      <c r="E1774" s="8" t="s">
-        <v>7222</v>
       </c>
     </row>
     <row r="1775" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1775" s="5" t="s">
+        <v>7222</v>
+      </c>
+      <c r="B1775" s="13" t="s">
         <v>7223</v>
       </c>
-      <c r="B1775" s="13" t="s">
+      <c r="C1775" s="41" t="s">
         <v>7224</v>
       </c>
-      <c r="C1775" s="41" t="s">
+      <c r="D1775" s="8" t="s">
         <v>7225</v>
       </c>
-      <c r="D1775" s="8" t="s">
+      <c r="E1775" s="8" t="s">
         <v>7226</v>
-      </c>
-      <c r="E1775" s="8" t="s">
-        <v>7227</v>
       </c>
     </row>
     <row r="1776" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1776" s="5" t="s">
+        <v>7227</v>
+      </c>
+      <c r="B1776" s="13" t="s">
         <v>7228</v>
       </c>
-      <c r="B1776" s="13" t="s">
+      <c r="C1776" s="41" t="s">
+        <v>7209</v>
+      </c>
+      <c r="D1776" s="8" t="s">
         <v>7229</v>
       </c>
-      <c r="C1776" s="41" t="s">
-        <v>7210</v>
-      </c>
-      <c r="D1776" s="8" t="s">
+      <c r="E1776" s="8" t="s">
         <v>7230</v>
-      </c>
-      <c r="E1776" s="8" t="s">
-        <v>7231</v>
       </c>
     </row>
     <row r="1777" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1777" s="5" t="s">
+        <v>7231</v>
+      </c>
+      <c r="B1777" s="13" t="s">
         <v>7232</v>
       </c>
-      <c r="B1777" s="13" t="s">
+      <c r="C1777" s="41" t="s">
         <v>7233</v>
       </c>
-      <c r="C1777" s="41" t="s">
+      <c r="D1777" s="8" t="s">
         <v>7234</v>
       </c>
-      <c r="D1777" s="8" t="s">
+      <c r="E1777" s="8" t="s">
         <v>7235</v>
-      </c>
-      <c r="E1777" s="8" t="s">
-        <v>7236</v>
       </c>
     </row>
     <row r="1778" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1778" s="5" t="s">
+        <v>7236</v>
+      </c>
+      <c r="B1778" s="13" t="s">
         <v>7237</v>
       </c>
-      <c r="B1778" s="13" t="s">
+      <c r="C1778" s="41" t="s">
         <v>7238</v>
       </c>
-      <c r="C1778" s="41" t="s">
+      <c r="D1778" s="8" t="s">
         <v>7239</v>
       </c>
-      <c r="D1778" s="8" t="s">
+      <c r="E1778" s="8" t="s">
         <v>7240</v>
-      </c>
-      <c r="E1778" s="8" t="s">
-        <v>7241</v>
       </c>
     </row>
     <row r="1779" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1779" s="5" t="s">
+        <v>7241</v>
+      </c>
+      <c r="B1779" s="13" t="s">
         <v>7242</v>
       </c>
-      <c r="B1779" s="13" t="s">
+      <c r="C1779" s="41" t="s">
         <v>7243</v>
       </c>
-      <c r="C1779" s="41" t="s">
+      <c r="D1779" s="8" t="s">
         <v>7244</v>
       </c>
-      <c r="D1779" s="8" t="s">
+      <c r="E1779" s="8" t="s">
         <v>7245</v>
-      </c>
-      <c r="E1779" s="8" t="s">
-        <v>7246</v>
       </c>
     </row>
     <row r="1780" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1780" s="15" t="s">
+        <v>7246</v>
+      </c>
+      <c r="B1780" s="13" t="s">
         <v>7247</v>
       </c>
-      <c r="B1780" s="13" t="s">
+      <c r="C1780" s="42" t="s">
         <v>7248</v>
       </c>
-      <c r="C1780" s="42" t="s">
+      <c r="D1780" s="13" t="s">
         <v>7249</v>
       </c>
-      <c r="D1780" s="13" t="s">
+      <c r="E1780" s="13" t="s">
         <v>7250</v>
-      </c>
-      <c r="E1780" s="13" t="s">
-        <v>7251</v>
       </c>
     </row>
     <row r="1781" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1781" s="5" t="s">
+        <v>7251</v>
+      </c>
+      <c r="B1781" s="13" t="s">
         <v>7252</v>
       </c>
-      <c r="B1781" s="13" t="s">
+      <c r="C1781" s="41" t="s">
         <v>7253</v>
       </c>
-      <c r="C1781" s="41" t="s">
+      <c r="D1781" s="8" t="s">
         <v>7254</v>
       </c>
-      <c r="D1781" s="8" t="s">
+      <c r="E1781" s="8" t="s">
         <v>7255</v>
-      </c>
-      <c r="E1781" s="8" t="s">
-        <v>7256</v>
       </c>
     </row>
     <row r="1782" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1782" s="5" t="s">
+        <v>7256</v>
+      </c>
+      <c r="B1782" s="13" t="s">
         <v>7257</v>
       </c>
-      <c r="B1782" s="13" t="s">
+      <c r="C1782" s="41" t="s">
         <v>7258</v>
       </c>
-      <c r="C1782" s="41" t="s">
+      <c r="D1782" s="8" t="s">
         <v>7259</v>
       </c>
-      <c r="D1782" s="8" t="s">
+      <c r="E1782" s="8" t="s">
         <v>7260</v>
-      </c>
-      <c r="E1782" s="8" t="s">
-        <v>7261</v>
       </c>
     </row>
     <row r="1783" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1783" s="5" t="s">
+        <v>7261</v>
+      </c>
+      <c r="B1783" s="13" t="s">
         <v>7262</v>
       </c>
-      <c r="B1783" s="13" t="s">
+      <c r="C1783" s="41" t="s">
         <v>7263</v>
       </c>
-      <c r="C1783" s="41" t="s">
+      <c r="D1783" s="8" t="s">
         <v>7264</v>
       </c>
-      <c r="D1783" s="8" t="s">
+      <c r="E1783" s="8" t="s">
         <v>7265</v>
-      </c>
-      <c r="E1783" s="8" t="s">
-        <v>7266</v>
       </c>
     </row>
     <row r="1784" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1784" s="5" t="s">
+        <v>7266</v>
+      </c>
+      <c r="B1784" s="13" t="s">
         <v>7267</v>
       </c>
-      <c r="B1784" s="13" t="s">
+      <c r="C1784" s="41" t="s">
         <v>7268</v>
       </c>
-      <c r="C1784" s="41" t="s">
+      <c r="D1784" s="8" t="s">
         <v>7269</v>
       </c>
-      <c r="D1784" s="8" t="s">
+      <c r="E1784" s="8" t="s">
         <v>7270</v>
-      </c>
-      <c r="E1784" s="8" t="s">
-        <v>7271</v>
       </c>
     </row>
     <row r="1785" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1785" s="5" t="s">
+        <v>7271</v>
+      </c>
+      <c r="B1785" s="13" t="s">
         <v>7272</v>
       </c>
-      <c r="B1785" s="13" t="s">
+      <c r="C1785" s="41" t="s">
         <v>7273</v>
       </c>
-      <c r="C1785" s="41" t="s">
+      <c r="D1785" s="8" t="s">
         <v>7274</v>
       </c>
-      <c r="D1785" s="8" t="s">
+      <c r="E1785" s="8" t="s">
         <v>7275</v>
-      </c>
-      <c r="E1785" s="8" t="s">
-        <v>7276</v>
       </c>
     </row>
     <row r="1786" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1786" s="5" t="s">
+        <v>7276</v>
+      </c>
+      <c r="B1786" s="13" t="s">
         <v>7277</v>
       </c>
-      <c r="B1786" s="13" t="s">
+      <c r="C1786" s="41" t="s">
         <v>7278</v>
       </c>
-      <c r="C1786" s="41" t="s">
+      <c r="D1786" s="8" t="s">
         <v>7279</v>
       </c>
-      <c r="D1786" s="8" t="s">
+      <c r="E1786" s="8" t="s">
         <v>7280</v>
-      </c>
-      <c r="E1786" s="8" t="s">
-        <v>7281</v>
       </c>
     </row>
     <row r="1787" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1787" s="5" t="s">
+        <v>7281</v>
+      </c>
+      <c r="B1787" s="13" t="s">
         <v>7282</v>
       </c>
-      <c r="B1787" s="13" t="s">
+      <c r="C1787" s="41" t="s">
         <v>7283</v>
       </c>
-      <c r="C1787" s="41" t="s">
+      <c r="D1787" s="8" t="s">
         <v>7284</v>
       </c>
-      <c r="D1787" s="8" t="s">
+      <c r="E1787" s="8" t="s">
         <v>7285</v>
-      </c>
-      <c r="E1787" s="8" t="s">
-        <v>7286</v>
       </c>
     </row>
     <row r="1788" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1788" s="5" t="s">
+        <v>7286</v>
+      </c>
+      <c r="B1788" s="13" t="s">
         <v>7287</v>
       </c>
-      <c r="B1788" s="13" t="s">
+      <c r="C1788" s="41" t="s">
         <v>7288</v>
       </c>
-      <c r="C1788" s="41" t="s">
+      <c r="D1788" s="8" t="s">
         <v>7289</v>
       </c>
-      <c r="D1788" s="8" t="s">
+      <c r="E1788" s="8" t="s">
         <v>7290</v>
-      </c>
-      <c r="E1788" s="8" t="s">
-        <v>7291</v>
       </c>
     </row>
     <row r="1789" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1789" s="5" t="s">
+        <v>7291</v>
+      </c>
+      <c r="B1789" s="13" t="s">
         <v>7292</v>
       </c>
-      <c r="B1789" s="13" t="s">
+      <c r="C1789" s="41" t="s">
         <v>7293</v>
       </c>
-      <c r="C1789" s="41" t="s">
+      <c r="D1789" s="8" t="s">
         <v>7294</v>
       </c>
-      <c r="D1789" s="8" t="s">
+      <c r="E1789" s="8" t="s">
         <v>7295</v>
-      </c>
-      <c r="E1789" s="8" t="s">
-        <v>7296</v>
       </c>
     </row>
     <row r="1790" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1790" s="5" t="s">
+        <v>7296</v>
+      </c>
+      <c r="B1790" s="13" t="s">
         <v>7297</v>
       </c>
-      <c r="B1790" s="13" t="s">
+      <c r="C1790" s="41" t="s">
         <v>7298</v>
       </c>
-      <c r="C1790" s="41" t="s">
+      <c r="D1790" s="8" t="s">
         <v>7299</v>
       </c>
-      <c r="D1790" s="8" t="s">
+      <c r="E1790" s="8" t="s">
         <v>7300</v>
-      </c>
-      <c r="E1790" s="8" t="s">
-        <v>7301</v>
       </c>
     </row>
     <row r="1791" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1791" s="15" t="s">
+        <v>7301</v>
+      </c>
+      <c r="B1791" s="13" t="s">
         <v>7302</v>
       </c>
-      <c r="B1791" s="13" t="s">
+      <c r="C1791" s="42" t="s">
         <v>7303</v>
       </c>
-      <c r="C1791" s="42" t="s">
+      <c r="D1791" s="13" t="s">
         <v>7304</v>
       </c>
-      <c r="D1791" s="13" t="s">
+      <c r="E1791" s="13" t="s">
         <v>7305</v>
-      </c>
-      <c r="E1791" s="13" t="s">
-        <v>7306</v>
       </c>
     </row>
     <row r="1792" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1792" s="5" t="s">
+        <v>7306</v>
+      </c>
+      <c r="B1792" s="13" t="s">
         <v>7307</v>
       </c>
-      <c r="B1792" s="13" t="s">
+      <c r="C1792" s="41" t="s">
         <v>7308</v>
       </c>
-      <c r="C1792" s="41" t="s">
+      <c r="D1792" s="8" t="s">
         <v>7309</v>
       </c>
-      <c r="D1792" s="8" t="s">
+      <c r="E1792" s="8" t="s">
         <v>7310</v>
-      </c>
-      <c r="E1792" s="8" t="s">
-        <v>7311</v>
       </c>
     </row>
     <row r="1793" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1793" s="15" t="s">
+        <v>7311</v>
+      </c>
+      <c r="B1793" s="13" t="s">
         <v>7312</v>
       </c>
-      <c r="B1793" s="13" t="s">
+      <c r="C1793" s="42" t="s">
         <v>7313</v>
       </c>
-      <c r="C1793" s="42" t="s">
+      <c r="D1793" s="13" t="s">
         <v>7314</v>
       </c>
-      <c r="D1793" s="13" t="s">
+      <c r="E1793" s="13" t="s">
         <v>7315</v>
-      </c>
-      <c r="E1793" s="13" t="s">
-        <v>7316</v>
       </c>
     </row>
     <row r="1794" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1794" s="5" t="s">
+        <v>7316</v>
+      </c>
+      <c r="B1794" s="13" t="s">
         <v>7317</v>
       </c>
-      <c r="B1794" s="13" t="s">
+      <c r="C1794" s="41" t="s">
         <v>7318</v>
       </c>
-      <c r="C1794" s="41" t="s">
+      <c r="D1794" s="8" t="s">
         <v>7319</v>
       </c>
-      <c r="D1794" s="8" t="s">
+      <c r="E1794" s="8" t="s">
         <v>7320</v>
-      </c>
-      <c r="E1794" s="8" t="s">
-        <v>7321</v>
       </c>
     </row>
     <row r="1795" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1795" s="15" t="s">
+        <v>7321</v>
+      </c>
+      <c r="B1795" s="13" t="s">
         <v>7322</v>
       </c>
-      <c r="B1795" s="13" t="s">
+      <c r="C1795" s="42" t="s">
         <v>7323</v>
       </c>
-      <c r="C1795" s="42" t="s">
+      <c r="D1795" s="13" t="s">
         <v>7324</v>
       </c>
-      <c r="D1795" s="13" t="s">
+      <c r="E1795" s="13" t="s">
         <v>7325</v>
-      </c>
-      <c r="E1795" s="13" t="s">
-        <v>7326</v>
       </c>
     </row>
     <row r="1796" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1796" s="15" t="s">
+        <v>7326</v>
+      </c>
+      <c r="B1796" s="13" t="s">
         <v>7327</v>
       </c>
-      <c r="B1796" s="13" t="s">
+      <c r="C1796" s="41" t="s">
         <v>7328</v>
       </c>
-      <c r="C1796" s="41" t="s">
+      <c r="D1796" s="8" t="s">
         <v>7329</v>
       </c>
-      <c r="D1796" s="8" t="s">
+      <c r="E1796" s="8" t="s">
         <v>7330</v>
-      </c>
-      <c r="E1796" s="8" t="s">
-        <v>7331</v>
       </c>
     </row>
     <row r="1797" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1797" s="5" t="s">
+        <v>7331</v>
+      </c>
+      <c r="B1797" s="13" t="s">
         <v>7332</v>
       </c>
-      <c r="B1797" s="13" t="s">
+      <c r="C1797" s="42" t="s">
+        <v>7293</v>
+      </c>
+      <c r="D1797" s="8" t="s">
         <v>7333</v>
       </c>
-      <c r="C1797" s="42" t="s">
-        <v>7294</v>
-      </c>
-      <c r="D1797" s="8" t="s">
+      <c r="E1797" s="8" t="s">
         <v>7334</v>
-      </c>
-      <c r="E1797" s="8" t="s">
-        <v>7335</v>
       </c>
     </row>
     <row r="1798" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1798" s="5" t="s">
+        <v>7335</v>
+      </c>
+      <c r="B1798" s="13" t="s">
         <v>7336</v>
       </c>
-      <c r="B1798" s="13" t="s">
+      <c r="C1798" s="41" t="s">
         <v>7337</v>
       </c>
-      <c r="C1798" s="41" t="s">
+      <c r="D1798" s="8" t="s">
         <v>7338</v>
       </c>
-      <c r="D1798" s="8" t="s">
+      <c r="E1798" s="8" t="s">
         <v>7339</v>
-      </c>
-      <c r="E1798" s="8" t="s">
-        <v>7340</v>
       </c>
     </row>
     <row r="1799" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1799" s="5" t="s">
+        <v>7340</v>
+      </c>
+      <c r="B1799" s="13" t="s">
         <v>7341</v>
       </c>
-      <c r="B1799" s="13" t="s">
+      <c r="C1799" s="41" t="s">
         <v>7342</v>
       </c>
-      <c r="C1799" s="41" t="s">
+      <c r="D1799" s="8" t="s">
         <v>7343</v>
       </c>
-      <c r="D1799" s="8" t="s">
+      <c r="E1799" s="8" t="s">
         <v>7344</v>
-      </c>
-      <c r="E1799" s="8" t="s">
-        <v>7345</v>
       </c>
     </row>
     <row r="1800" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1800" s="5" t="s">
+        <v>7345</v>
+      </c>
+      <c r="B1800" s="13" t="s">
         <v>7346</v>
       </c>
-      <c r="B1800" s="13" t="s">
+      <c r="C1800" s="41" t="s">
         <v>7347</v>
       </c>
-      <c r="C1800" s="41" t="s">
+      <c r="D1800" s="8" t="s">
         <v>7348</v>
       </c>
-      <c r="D1800" s="8" t="s">
+      <c r="E1800" s="8" t="s">
         <v>7349</v>
-      </c>
-      <c r="E1800" s="8" t="s">
-        <v>7350</v>
       </c>
     </row>
     <row r="1801" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1801" s="5" t="s">
+        <v>7350</v>
+      </c>
+      <c r="B1801" s="13" t="s">
         <v>7351</v>
       </c>
-      <c r="B1801" s="13" t="s">
+      <c r="C1801" s="41" t="s">
         <v>7352</v>
       </c>
-      <c r="C1801" s="41" t="s">
+      <c r="D1801" s="8" t="s">
         <v>7353</v>
       </c>
-      <c r="D1801" s="8" t="s">
+      <c r="E1801" s="8" t="s">
         <v>7354</v>
-      </c>
-      <c r="E1801" s="8" t="s">
-        <v>7355</v>
       </c>
     </row>
     <row r="1802" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1802" s="15" t="s">
+        <v>7355</v>
+      </c>
+      <c r="B1802" s="13" t="s">
         <v>7356</v>
       </c>
-      <c r="B1802" s="13" t="s">
+      <c r="C1802" s="42" t="s">
         <v>7357</v>
       </c>
-      <c r="C1802" s="42" t="s">
+      <c r="D1802" s="13" t="s">
         <v>7358</v>
       </c>
-      <c r="D1802" s="13" t="s">
+      <c r="E1802" s="13" t="s">
         <v>7359</v>
-      </c>
-      <c r="E1802" s="13" t="s">
-        <v>7360</v>
       </c>
     </row>
     <row r="1803" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1803" s="15" t="s">
+        <v>7360</v>
+      </c>
+      <c r="B1803" s="13" t="s">
         <v>7361</v>
       </c>
-      <c r="B1803" s="13" t="s">
+      <c r="C1803" s="42" t="s">
         <v>7362</v>
       </c>
-      <c r="C1803" s="42" t="s">
+      <c r="D1803" s="13" t="s">
         <v>7363</v>
       </c>
-      <c r="D1803" s="13" t="s">
+      <c r="E1803" s="13" t="s">
         <v>7364</v>
-      </c>
-      <c r="E1803" s="13" t="s">
-        <v>7365</v>
       </c>
     </row>
     <row r="1804" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1804" s="15" t="s">
+        <v>7365</v>
+      </c>
+      <c r="B1804" s="13" t="s">
         <v>7366</v>
       </c>
-      <c r="B1804" s="13" t="s">
+      <c r="C1804" s="42" t="s">
         <v>7367</v>
       </c>
-      <c r="C1804" s="42" t="s">
+      <c r="D1804" s="13" t="s">
         <v>7368</v>
       </c>
-      <c r="D1804" s="13" t="s">
+      <c r="E1804" s="13" t="s">
         <v>7369</v>
-      </c>
-      <c r="E1804" s="13" t="s">
-        <v>7370</v>
       </c>
     </row>
     <row r="1805" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1805" s="5" t="s">
+        <v>7370</v>
+      </c>
+      <c r="B1805" s="13" t="s">
         <v>7371</v>
       </c>
-      <c r="B1805" s="13" t="s">
+      <c r="C1805" s="41" t="s">
         <v>7372</v>
       </c>
-      <c r="C1805" s="41" t="s">
+      <c r="D1805" s="8" t="s">
         <v>7373</v>
       </c>
-      <c r="D1805" s="8" t="s">
+      <c r="E1805" s="8" t="s">
         <v>7374</v>
-      </c>
-      <c r="E1805" s="8" t="s">
-        <v>7375</v>
       </c>
     </row>
     <row r="1806" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1806" s="5" t="s">
+        <v>7375</v>
+      </c>
+      <c r="B1806" s="13" t="s">
         <v>7376</v>
       </c>
-      <c r="B1806" s="13" t="s">
+      <c r="C1806" s="41" t="s">
         <v>7377</v>
       </c>
-      <c r="C1806" s="41" t="s">
+      <c r="D1806" s="8" t="s">
         <v>7378</v>
       </c>
-      <c r="D1806" s="8" t="s">
+      <c r="E1806" s="8" t="s">
         <v>7379</v>
-      </c>
-      <c r="E1806" s="8" t="s">
-        <v>7380</v>
       </c>
     </row>
     <row r="1807" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1807" s="5" t="s">
+        <v>7380</v>
+      </c>
+      <c r="B1807" s="13" t="s">
         <v>7381</v>
       </c>
-      <c r="B1807" s="13" t="s">
+      <c r="C1807" s="41" t="s">
         <v>7382</v>
       </c>
-      <c r="C1807" s="41" t="s">
+      <c r="D1807" s="8" t="s">
         <v>7383</v>
       </c>
-      <c r="D1807" s="8" t="s">
+      <c r="E1807" s="8" t="s">
         <v>7384</v>
-      </c>
-      <c r="E1807" s="8" t="s">
-        <v>7385</v>
       </c>
     </row>
     <row r="1808" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1808" s="5" t="s">
+        <v>7385</v>
+      </c>
+      <c r="B1808" s="13" t="s">
         <v>7386</v>
       </c>
-      <c r="B1808" s="13" t="s">
+      <c r="C1808" s="41" t="s">
         <v>7387</v>
       </c>
-      <c r="C1808" s="41" t="s">
+      <c r="D1808" s="8" t="s">
         <v>7388</v>
       </c>
-      <c r="D1808" s="8" t="s">
+      <c r="E1808" s="8" t="s">
         <v>7389</v>
-      </c>
-      <c r="E1808" s="8" t="s">
-        <v>7390</v>
       </c>
     </row>
     <row r="1809" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1809" s="5" t="s">
+        <v>7390</v>
+      </c>
+      <c r="B1809" s="13" t="s">
         <v>7391</v>
       </c>
-      <c r="B1809" s="13" t="s">
+      <c r="C1809" s="41" t="s">
         <v>7392</v>
       </c>
-      <c r="C1809" s="41" t="s">
+      <c r="D1809" s="8" t="s">
         <v>7393</v>
       </c>
-      <c r="D1809" s="8" t="s">
+      <c r="E1809" s="8" t="s">
         <v>7394</v>
-      </c>
-      <c r="E1809" s="8" t="s">
-        <v>7395</v>
       </c>
     </row>
     <row r="1810" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1810" s="5" t="s">
+        <v>7395</v>
+      </c>
+      <c r="B1810" s="13" t="s">
         <v>7396</v>
       </c>
-      <c r="B1810" s="13" t="s">
+      <c r="C1810" s="41" t="s">
         <v>7397</v>
       </c>
-      <c r="C1810" s="41" t="s">
+      <c r="D1810" s="8" t="s">
         <v>7398</v>
       </c>
-      <c r="D1810" s="8" t="s">
+      <c r="E1810" s="8" t="s">
         <v>7399</v>
-      </c>
-      <c r="E1810" s="8" t="s">
-        <v>7400</v>
       </c>
     </row>
     <row r="1811" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1811" s="5" t="s">
+        <v>7400</v>
+      </c>
+      <c r="B1811" s="13" t="s">
         <v>7401</v>
       </c>
-      <c r="B1811" s="13" t="s">
+      <c r="C1811" s="41" t="s">
         <v>7402</v>
       </c>
-      <c r="C1811" s="41" t="s">
+      <c r="D1811" s="8" t="s">
         <v>7403</v>
       </c>
-      <c r="D1811" s="8" t="s">
+      <c r="E1811" s="8" t="s">
         <v>7404</v>
-      </c>
-      <c r="E1811" s="8" t="s">
-        <v>7405</v>
       </c>
     </row>
     <row r="1812" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1812" s="15" t="s">
+        <v>7405</v>
+      </c>
+      <c r="B1812" s="13" t="s">
         <v>7406</v>
       </c>
-      <c r="B1812" s="13" t="s">
+      <c r="C1812" s="42" t="s">
         <v>7407</v>
       </c>
-      <c r="C1812" s="42" t="s">
+      <c r="D1812" s="13" t="s">
         <v>7408</v>
       </c>
-      <c r="D1812" s="13" t="s">
+      <c r="E1812" s="13" t="s">
         <v>7409</v>
-      </c>
-      <c r="E1812" s="13" t="s">
-        <v>7410</v>
       </c>
     </row>
     <row r="1813" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1813" s="15" t="s">
+        <v>7410</v>
+      </c>
+      <c r="B1813" s="13" t="s">
         <v>7411</v>
       </c>
-      <c r="B1813" s="13" t="s">
+      <c r="C1813" s="42" t="s">
         <v>7412</v>
       </c>
-      <c r="C1813" s="42" t="s">
+      <c r="D1813" s="13" t="s">
         <v>7413</v>
       </c>
-      <c r="D1813" s="13" t="s">
+      <c r="E1813" s="13" t="s">
         <v>7414</v>
-      </c>
-      <c r="E1813" s="13" t="s">
-        <v>7415</v>
       </c>
     </row>
     <row r="1814" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1814" s="15" t="s">
+        <v>7415</v>
+      </c>
+      <c r="B1814" s="13" t="s">
         <v>7416</v>
       </c>
-      <c r="B1814" s="13" t="s">
+      <c r="C1814" s="42" t="s">
         <v>7417</v>
       </c>
-      <c r="C1814" s="42" t="s">
+      <c r="D1814" s="13" t="s">
         <v>7418</v>
       </c>
-      <c r="D1814" s="13" t="s">
+      <c r="E1814" s="13" t="s">
         <v>7419</v>
-      </c>
-      <c r="E1814" s="13" t="s">
-        <v>7420</v>
       </c>
     </row>
     <row r="1815" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1815" s="15" t="s">
+        <v>7420</v>
+      </c>
+      <c r="B1815" s="13" t="s">
         <v>7421</v>
       </c>
-      <c r="B1815" s="13" t="s">
+      <c r="C1815" s="42" t="s">
         <v>7422</v>
       </c>
-      <c r="C1815" s="42" t="s">
+      <c r="D1815" s="13" t="s">
         <v>7423</v>
       </c>
-      <c r="D1815" s="13" t="s">
+      <c r="E1815" s="13" t="s">
         <v>7424</v>
-      </c>
-      <c r="E1815" s="13" t="s">
-        <v>7425</v>
       </c>
     </row>
     <row r="1816" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1816" s="15" t="s">
+        <v>7425</v>
+      </c>
+      <c r="B1816" s="13" t="s">
         <v>7426</v>
       </c>
-      <c r="B1816" s="13" t="s">
+      <c r="C1816" s="42" t="s">
         <v>7427</v>
       </c>
-      <c r="C1816" s="42" t="s">
+      <c r="D1816" s="13" t="s">
         <v>7428</v>
       </c>
-      <c r="D1816" s="13" t="s">
+      <c r="E1816" s="13" t="s">
         <v>7429</v>
-      </c>
-      <c r="E1816" s="13" t="s">
-        <v>7430</v>
       </c>
     </row>
     <row r="1817" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1817" s="15" t="s">
+        <v>7430</v>
+      </c>
+      <c r="B1817" s="13" t="s">
         <v>7431</v>
       </c>
-      <c r="B1817" s="13" t="s">
+      <c r="C1817" s="42" t="s">
         <v>7432</v>
       </c>
-      <c r="C1817" s="42" t="s">
+      <c r="D1817" s="13" t="s">
         <v>7433</v>
       </c>
-      <c r="D1817" s="13" t="s">
+      <c r="E1817" s="13" t="s">
         <v>7434</v>
-      </c>
-      <c r="E1817" s="13" t="s">
-        <v>7435</v>
       </c>
     </row>
     <row r="1818" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1818" s="29" t="s">
+        <v>7435</v>
+      </c>
+      <c r="B1818" s="17" t="s">
         <v>7436</v>
       </c>
-      <c r="B1818" s="17" t="s">
+      <c r="C1818" s="43" t="s">
         <v>7437</v>
       </c>
-      <c r="C1818" s="43" t="s">
+      <c r="D1818" s="17" t="s">
         <v>7438</v>
       </c>
-      <c r="D1818" s="17" t="s">
+      <c r="E1818" s="17" t="s">
         <v>7439</v>
-      </c>
-      <c r="E1818" s="17" t="s">
-        <v>7440</v>
       </c>
     </row>
     <row r="1819" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1819" s="44" t="s">
+        <v>7440</v>
+      </c>
+      <c r="B1819" s="6" t="s">
         <v>7441</v>
       </c>
-      <c r="B1819" s="6" t="s">
+      <c r="C1819" s="45" t="s">
         <v>7442</v>
       </c>
-      <c r="C1819" s="45" t="s">
+      <c r="D1819" s="6" t="s">
         <v>7443</v>
       </c>
-      <c r="D1819" s="6" t="s">
+      <c r="E1819" s="6" t="s">
         <v>7444</v>
-      </c>
-      <c r="E1819" s="6" t="s">
-        <v>7445</v>
       </c>
     </row>
     <row r="1820" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1820" s="44" t="s">
+        <v>7445</v>
+      </c>
+      <c r="B1820" s="6" t="s">
         <v>7446</v>
       </c>
-      <c r="B1820" s="6" t="s">
+      <c r="C1820" s="45" t="s">
         <v>7447</v>
       </c>
-      <c r="C1820" s="45" t="s">
+      <c r="D1820" s="6" t="s">
         <v>7448</v>
       </c>
-      <c r="D1820" s="6" t="s">
+      <c r="E1820" s="6" t="s">
         <v>7449</v>
-      </c>
-      <c r="E1820" s="6" t="s">
-        <v>7450</v>
       </c>
     </row>
     <row r="1821" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1821" s="44" t="s">
+        <v>7450</v>
+      </c>
+      <c r="B1821" s="6" t="s">
         <v>7451</v>
       </c>
-      <c r="B1821" s="6" t="s">
+      <c r="C1821" s="45" t="s">
         <v>7452</v>
       </c>
-      <c r="C1821" s="45" t="s">
+      <c r="D1821" s="6" t="s">
         <v>7453</v>
       </c>
-      <c r="D1821" s="6" t="s">
+      <c r="E1821" s="6" t="s">
         <v>7454</v>
-      </c>
-      <c r="E1821" s="6" t="s">
-        <v>7455</v>
       </c>
     </row>
     <row r="1822" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1822" s="46" t="s">
+        <v>7455</v>
+      </c>
+      <c r="B1822" s="20" t="s">
         <v>7456</v>
       </c>
-      <c r="B1822" s="20" t="s">
+      <c r="C1822" s="47" t="s">
         <v>7457</v>
       </c>
-      <c r="C1822" s="47" t="s">
+      <c r="D1822" s="20" t="s">
         <v>7458</v>
       </c>
-      <c r="D1822" s="20" t="s">
+      <c r="E1822" s="20" t="s">
         <v>7459</v>
-      </c>
-      <c r="E1822" s="20" t="s">
-        <v>7460</v>
       </c>
     </row>
     <row r="1823" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1823" s="5" t="s">
+        <v>7460</v>
+      </c>
+      <c r="B1823" s="6" t="s">
         <v>7461</v>
       </c>
-      <c r="B1823" s="6" t="s">
+      <c r="C1823" s="48" t="s">
         <v>7462</v>
       </c>
-      <c r="C1823" s="48" t="s">
+      <c r="D1823" s="8" t="s">
         <v>7463</v>
       </c>
-      <c r="D1823" s="8" t="s">
+      <c r="E1823" s="8" t="s">
         <v>7464</v>
-      </c>
-      <c r="E1823" s="8" t="s">
-        <v>7465</v>
       </c>
     </row>
     <row r="1824" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1824" s="5" t="s">
+        <v>7465</v>
+      </c>
+      <c r="B1824" s="6" t="s">
         <v>7466</v>
       </c>
-      <c r="B1824" s="6" t="s">
+      <c r="C1824" s="48" t="s">
         <v>7467</v>
       </c>
-      <c r="C1824" s="48" t="s">
+      <c r="D1824" s="8" t="s">
         <v>7468</v>
       </c>
-      <c r="D1824" s="8" t="s">
+      <c r="E1824" s="8" t="s">
         <v>7469</v>
-      </c>
-      <c r="E1824" s="8" t="s">
-        <v>7470</v>
       </c>
     </row>
     <row r="1825" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1825" s="5" t="s">
+        <v>7470</v>
+      </c>
+      <c r="B1825" s="6" t="s">
         <v>7471</v>
       </c>
-      <c r="B1825" s="6" t="s">
+      <c r="C1825" s="48" t="s">
         <v>7472</v>
       </c>
-      <c r="C1825" s="48" t="s">
+      <c r="D1825" s="8" t="s">
         <v>7473</v>
       </c>
-      <c r="D1825" s="8" t="s">
+      <c r="E1825" s="8" t="s">
         <v>7474</v>
-      </c>
-      <c r="E1825" s="8" t="s">
-        <v>7475</v>
       </c>
     </row>
     <row r="1826" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1826" s="5" t="s">
+        <v>7475</v>
+      </c>
+      <c r="B1826" s="6" t="s">
         <v>7476</v>
       </c>
-      <c r="B1826" s="6" t="s">
+      <c r="C1826" s="48" t="s">
         <v>7477</v>
       </c>
-      <c r="C1826" s="48" t="s">
+      <c r="D1826" s="8" t="s">
         <v>7478</v>
       </c>
-      <c r="D1826" s="8" t="s">
+      <c r="E1826" s="8" t="s">
         <v>7479</v>
-      </c>
-      <c r="E1826" s="8" t="s">
-        <v>7480</v>
       </c>
     </row>
     <row r="1827" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1827" s="5" t="s">
+        <v>7480</v>
+      </c>
+      <c r="B1827" s="6" t="s">
         <v>7481</v>
       </c>
-      <c r="B1827" s="6" t="s">
+      <c r="C1827" s="48" t="s">
         <v>7482</v>
       </c>
-      <c r="C1827" s="48" t="s">
+      <c r="D1827" s="8" t="s">
         <v>7483</v>
       </c>
-      <c r="D1827" s="8" t="s">
+      <c r="E1827" s="8" t="s">
         <v>7484</v>
-      </c>
-      <c r="E1827" s="8" t="s">
-        <v>7485</v>
       </c>
     </row>
     <row r="1828" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1828" s="5" t="s">
+        <v>7485</v>
+      </c>
+      <c r="B1828" s="6" t="s">
         <v>7486</v>
       </c>
-      <c r="B1828" s="6" t="s">
+      <c r="C1828" s="48" t="s">
         <v>7487</v>
       </c>
-      <c r="C1828" s="48" t="s">
+      <c r="D1828" s="8" t="s">
         <v>7488</v>
       </c>
-      <c r="D1828" s="8" t="s">
+      <c r="E1828" s="8" t="s">
         <v>7489</v>
-      </c>
-      <c r="E1828" s="8" t="s">
-        <v>7490</v>
       </c>
     </row>
     <row r="1829" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1829" s="5" t="s">
+        <v>7490</v>
+      </c>
+      <c r="B1829" s="6" t="s">
         <v>7491</v>
       </c>
-      <c r="B1829" s="6" t="s">
+      <c r="C1829" s="48" t="s">
         <v>7492</v>
       </c>
-      <c r="C1829" s="48" t="s">
+      <c r="D1829" s="8" t="s">
         <v>7493</v>
       </c>
-      <c r="D1829" s="8" t="s">
+      <c r="E1829" s="8" t="s">
         <v>7494</v>
-      </c>
-      <c r="E1829" s="8" t="s">
-        <v>7495</v>
       </c>
     </row>
     <row r="1830" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1830" s="5" t="s">
+        <v>7495</v>
+      </c>
+      <c r="B1830" s="6" t="s">
         <v>7496</v>
       </c>
-      <c r="B1830" s="6" t="s">
+      <c r="C1830" s="48" t="s">
         <v>7497</v>
       </c>
-      <c r="C1830" s="48" t="s">
+      <c r="D1830" s="8" t="s">
         <v>7498</v>
       </c>
-      <c r="D1830" s="8" t="s">
+      <c r="E1830" s="8" t="s">
         <v>7499</v>
-      </c>
-      <c r="E1830" s="8" t="s">
-        <v>7500</v>
       </c>
     </row>
     <row r="1831" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1831" s="5" t="s">
+        <v>7500</v>
+      </c>
+      <c r="B1831" s="6" t="s">
         <v>7501</v>
       </c>
-      <c r="B1831" s="6" t="s">
+      <c r="C1831" s="48" t="s">
         <v>7502</v>
       </c>
-      <c r="C1831" s="48" t="s">
+      <c r="D1831" s="8" t="s">
         <v>7503</v>
       </c>
-      <c r="D1831" s="8" t="s">
+      <c r="E1831" s="8" t="s">
         <v>7504</v>
-      </c>
-      <c r="E1831" s="8" t="s">
-        <v>7505</v>
       </c>
     </row>
     <row r="1832" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1832" s="10" t="s">
+        <v>7505</v>
+      </c>
+      <c r="B1832" s="20" t="s">
         <v>7506</v>
       </c>
-      <c r="B1832" s="20" t="s">
+      <c r="C1832" s="49" t="s">
         <v>7507</v>
       </c>
-      <c r="C1832" s="49" t="s">
+      <c r="D1832" s="11" t="s">
         <v>7508</v>
       </c>
-      <c r="D1832" s="11" t="s">
+      <c r="E1832" s="11" t="s">
         <v>7509</v>
-      </c>
-      <c r="E1832" s="11" t="s">
-        <v>7510</v>
       </c>
     </row>
     <row r="1833" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1833" s="15" t="s">
+        <v>7505</v>
+      </c>
+      <c r="B1833" s="13" t="s">
         <v>7506</v>
       </c>
-      <c r="B1833" s="13" t="s">
+      <c r="C1833" s="50" t="s">
         <v>7507</v>
       </c>
-      <c r="C1833" s="50" t="s">
+      <c r="D1833" s="13" t="s">
         <v>7508</v>
       </c>
-      <c r="D1833" s="13" t="s">
+      <c r="E1833" s="13" t="s">
         <v>7509</v>
-      </c>
-      <c r="E1833" s="13" t="s">
-        <v>7510</v>
       </c>
     </row>
     <row r="1834" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1834" s="5" t="s">
+        <v>7510</v>
+      </c>
+      <c r="B1834" s="8" t="s">
         <v>7511</v>
       </c>
-      <c r="B1834" s="8" t="s">
+      <c r="C1834" s="51" t="s">
         <v>7512</v>
       </c>
-      <c r="C1834" s="51" t="s">
+      <c r="D1834" s="8" t="s">
         <v>7513</v>
       </c>
-      <c r="D1834" s="8" t="s">
+      <c r="E1834" s="8" t="s">
         <v>7514</v>
-      </c>
-      <c r="E1834" s="8" t="s">
-        <v>7515</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C8DA3D-74A1-472C-92D8-06BD70A4F416}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA47872A-8366-46D9-B8F4-06ABD88DFC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1770" yWindow="2145" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7533" uniqueCount="7516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7558" uniqueCount="7546">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -22584,6 +22584,96 @@
   </si>
   <si>
     <t xml:space="preserve"> @frALX_1</t>
+  </si>
+  <si>
+    <t>O‘ramas sh., Urgut tumani, Ogahiy ko‘chasi, 1 uy: г. Урамас, Ургутский район, улица Огахи, дом 1</t>
+  </si>
+  <si>
+    <t>FrУРА-1</t>
+  </si>
+  <si>
+    <t>998 77 321 90 80</t>
+  </si>
+  <si>
+    <t>@FrURA1</t>
+  </si>
+  <si>
+    <t>39.480759, 67.251862</t>
+  </si>
+  <si>
+    <t>Mulloyon sh., Romitan tumani, Mulloyon koʻchasi, 02 uy : г. Муллоён, Ромитанский район, улица Муллоён, дом 02</t>
+  </si>
+  <si>
+    <t>FrМЛН-1</t>
+  </si>
+  <si>
+    <t>998 33 262 77 70</t>
+  </si>
+  <si>
+    <t>@FRMLN_1</t>
+  </si>
+  <si>
+    <t>39.918361, 64.247253</t>
+  </si>
+  <si>
+    <t>Alaja sh., Xonqa tumani, Istiqlol ko'chasi, 6/2 uy : г. Аладжа, Ханкинский район, улица Истиклол, дом 6/2</t>
+  </si>
+  <si>
+    <t>FrАЛД-1</t>
+  </si>
+  <si>
+    <t>998 33 655 25 25</t>
+  </si>
+  <si>
+    <t>@FrALD1</t>
+  </si>
+  <si>
+    <t>41.408550, 60.815668</t>
+  </si>
+  <si>
+    <t>Zarafshon sh., Shark massiv, 6A uy: г. Зарафшан, массив Шарк, дом 6A</t>
+  </si>
+  <si>
+    <t>FrЗАР-9</t>
+  </si>
+  <si>
+    <t>998 50 077 50 72</t>
+  </si>
+  <si>
+    <t>@FrZAR9</t>
+  </si>
+  <si>
+    <t>41.594877, 64.227674</t>
+  </si>
+  <si>
+    <t>Nursux sh., O‘zbekiston tumani, Obod dasht ko'chasi, 21 uy : г. Нурсух, Узбекистанский район, Улица Обод Дашт, дом 21</t>
+  </si>
+  <si>
+    <t>FrНРХ-1</t>
+  </si>
+  <si>
+    <t>998 50 505 99 47</t>
+  </si>
+  <si>
+    <t>@UzumFrNRX1</t>
+  </si>
+  <si>
+    <t>40.366185, 70.750679</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yunusobod tumani, Husniobod MFY, 2 mavzesi, 14b uy : г. Ташкент, Юнусабадский район, МФИ Хусниабад, 2-й квартал, дом 14б</t>
+  </si>
+  <si>
+    <t>FrТАШ-431</t>
+  </si>
+  <si>
+    <t>998 99 787 00 26</t>
+  </si>
+  <si>
+    <t>@FrTash431</t>
+  </si>
+  <si>
+    <t>41.359809, 69.286405</t>
   </si>
 </sst>
 </file>
@@ -22935,10 +23025,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -23245,7 +23335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1834"/>
+  <dimension ref="A1:E1839"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -54399,37 +54489,122 @@
       </c>
     </row>
     <row r="1833" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1833" s="15" t="s">
-        <v>7505</v>
+      <c r="A1833" s="5" t="s">
+        <v>7510</v>
       </c>
       <c r="B1833" s="13" t="s">
-        <v>7506</v>
+        <v>7511</v>
       </c>
       <c r="C1833" s="50" t="s">
-        <v>7507</v>
-      </c>
-      <c r="D1833" s="13" t="s">
-        <v>7508</v>
-      </c>
-      <c r="E1833" s="13" t="s">
-        <v>7509</v>
+        <v>7512</v>
+      </c>
+      <c r="D1833" s="8" t="s">
+        <v>7513</v>
+      </c>
+      <c r="E1833" s="8" t="s">
+        <v>7514</v>
       </c>
     </row>
     <row r="1834" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1834" s="5" t="s">
-        <v>7510</v>
-      </c>
-      <c r="B1834" s="8" t="s">
-        <v>7511</v>
-      </c>
-      <c r="C1834" s="51" t="s">
-        <v>7512</v>
+        <v>7516</v>
+      </c>
+      <c r="B1834" s="13" t="s">
+        <v>7517</v>
+      </c>
+      <c r="C1834" s="50" t="s">
+        <v>7518</v>
       </c>
       <c r="D1834" s="8" t="s">
-        <v>7513</v>
+        <v>7519</v>
       </c>
       <c r="E1834" s="8" t="s">
-        <v>7514</v>
+        <v>7520</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1835" s="15" t="s">
+        <v>7521</v>
+      </c>
+      <c r="B1835" s="13" t="s">
+        <v>7522</v>
+      </c>
+      <c r="C1835" s="51" t="s">
+        <v>7523</v>
+      </c>
+      <c r="D1835" s="13" t="s">
+        <v>7524</v>
+      </c>
+      <c r="E1835" s="13" t="s">
+        <v>7525</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1836" s="5" t="s">
+        <v>7526</v>
+      </c>
+      <c r="B1836" s="13" t="s">
+        <v>7527</v>
+      </c>
+      <c r="C1836" s="50" t="s">
+        <v>7528</v>
+      </c>
+      <c r="D1836" s="8" t="s">
+        <v>7529</v>
+      </c>
+      <c r="E1836" s="8" t="s">
+        <v>7530</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1837" s="5" t="s">
+        <v>7531</v>
+      </c>
+      <c r="B1837" s="13" t="s">
+        <v>7532</v>
+      </c>
+      <c r="C1837" s="50" t="s">
+        <v>7533</v>
+      </c>
+      <c r="D1837" s="8" t="s">
+        <v>7534</v>
+      </c>
+      <c r="E1837" s="8" t="s">
+        <v>7535</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1838" s="5" t="s">
+        <v>7536</v>
+      </c>
+      <c r="B1838" s="13" t="s">
+        <v>7537</v>
+      </c>
+      <c r="C1838" s="50" t="s">
+        <v>7538</v>
+      </c>
+      <c r="D1838" s="8" t="s">
+        <v>7539</v>
+      </c>
+      <c r="E1838" s="8" t="s">
+        <v>7540</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1839" s="5" t="s">
+        <v>7541</v>
+      </c>
+      <c r="B1839" s="13" t="s">
+        <v>7542</v>
+      </c>
+      <c r="C1839" s="50" t="s">
+        <v>7543</v>
+      </c>
+      <c r="D1839" s="8" t="s">
+        <v>7544</v>
+      </c>
+      <c r="E1839" s="8" t="s">
+        <v>7545</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA47872A-8366-46D9-B8F4-06ABD88DFC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F594B6AA-768C-46A0-A9FF-67B085AA3C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="2145" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7558" uniqueCount="7546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7628" uniqueCount="7616">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -22674,18 +22674,236 @@
   </si>
   <si>
     <t>41.359809, 69.286405</t>
+  </si>
+  <si>
+    <t>Jizzax sh., O‘zbekiston ko'chasi, 71uy: г. Джизак, улица Узбекистон, дом 71</t>
+  </si>
+  <si>
+    <t>FrДЗК-19</t>
+  </si>
+  <si>
+    <t>998 50 105 41 93</t>
+  </si>
+  <si>
+    <t>@FRDZK_19</t>
+  </si>
+  <si>
+    <t>40.149502, 67.846632</t>
+  </si>
+  <si>
+    <t>Chelak sh., Farxod ko'chasi, 35 uy: г. Челек, улица Фарход, дом 35</t>
+  </si>
+  <si>
+    <t>FrЧЕЛ-4</t>
+  </si>
+  <si>
+    <t>998 33 100 36 26</t>
+  </si>
+  <si>
+    <t>@frchel_4</t>
+  </si>
+  <si>
+    <t>39.924980, 66.867944</t>
+  </si>
+  <si>
+    <t>Yangi Nishon sh., Bobur koʻchasi, 1 uy : г. Янги Нишан, улица Бобур, дом 1</t>
+  </si>
+  <si>
+    <t>FrЯНШ-4</t>
+  </si>
+  <si>
+    <t>998 77 139 29 39</t>
+  </si>
+  <si>
+    <t>@FrYANSH_4</t>
+  </si>
+  <si>
+    <t>38.561956, 65.550057</t>
+  </si>
+  <si>
+    <t>Taxtako'pir sh., Berdaq ko'chasi, 4 uy: г. Тахтакупир, улица Бердак, дом 4</t>
+  </si>
+  <si>
+    <t>FrТХТ-1</t>
+  </si>
+  <si>
+    <t>998 87 157 16 25</t>
+  </si>
+  <si>
+    <t>@UzumTaxta</t>
+  </si>
+  <si>
+    <t>43.019812, 60.287799</t>
+  </si>
+  <si>
+    <t>Malikrabot sh., Buyuk Ipak Yoʻli MFY, Doʻstlik koʻchasi, 12 uy : г. Маликработ, МФИ Буюк Ипак Йули, улица Дустлик, дом 12</t>
+  </si>
+  <si>
+    <t>FrМКР-2</t>
+  </si>
+  <si>
+    <t>998 70 115 94 48</t>
+  </si>
+  <si>
+    <t>@FrMKR_2</t>
+  </si>
+  <si>
+    <t>40.129997, 65.185648</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Sirg'ali tumani, Uzumzor ko‘chasi, 3a uy : г. Ташкент, Сергелийский район, улица Узумзар, дом 3а</t>
+  </si>
+  <si>
+    <t>FrТАШ-443</t>
+  </si>
+  <si>
+    <t>998 88 448 74 94</t>
+  </si>
+  <si>
+    <t>@frtash_443</t>
+  </si>
+  <si>
+    <t>41.243194, 69.223982</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Voha Gavhari TJM, Chovkay dahasi, 368/15 uy : г. Карши, ЖК Воха Гавхари, массив Човкай, дом 368/15</t>
+  </si>
+  <si>
+    <t>FrКРШ-36</t>
+  </si>
+  <si>
+    <t>998 33 514 40 03</t>
+  </si>
+  <si>
+    <t>@frkrsh_36</t>
+  </si>
+  <si>
+    <t>38.862065, 65.864894</t>
+  </si>
+  <si>
+    <t>Farg‘ona sh., Sanoat ko'chasi, 70/1 uy : г. Фергана, улица Саноат, дом 70/1</t>
+  </si>
+  <si>
+    <t>FrФЕР-45</t>
+  </si>
+  <si>
+    <t>998 50 203 86 37</t>
+  </si>
+  <si>
+    <t>@FrFER_45</t>
+  </si>
+  <si>
+    <t>40.397015, 71.786748</t>
+  </si>
+  <si>
+    <t>Qo'ng'irot sh., Toʻlegen Aybergenov koʻchasi, 37 uy : г. Кунград, улица Тулеген Айбергенов, дом 37</t>
+  </si>
+  <si>
+    <t>FrКУН-5</t>
+  </si>
+  <si>
+    <t>998 90 183 78 87</t>
+  </si>
+  <si>
+    <t>@frkun_5</t>
+  </si>
+  <si>
+    <t>43.048792, 58.836105</t>
+  </si>
+  <si>
+    <t>Guliston sh., Yukori Chirchiq tumani, Kuzmunchok ko'chasi 62 uy: г. Гулистан, Юкори Чирчикский район, улица Кузмунчок, дом 62</t>
+  </si>
+  <si>
+    <t>FrГСТ-1</t>
+  </si>
+  <si>
+    <t>998 87 399 06 18</t>
+  </si>
+  <si>
+    <t>@FrGST1</t>
+  </si>
+  <si>
+    <t>41.250085, 69.483691</t>
+  </si>
+  <si>
+    <t>Qoraqaltoq sh., Qo‘shtepa tumani, Shoftolibog' ko'chasi, 66A uy : г. Каракальтак, Куштепинский район, улица Шофтолибог, дом 66А</t>
+  </si>
+  <si>
+    <t>FrККТ-1</t>
+  </si>
+  <si>
+    <t>998 77 293 44 00</t>
+  </si>
+  <si>
+    <t>@frKKT1</t>
+  </si>
+  <si>
+    <t>40.527856, 71.638641</t>
+  </si>
+  <si>
+    <t>G‘ijduvon sh., Shimoliy Shurobod ko‘chasi, 102 uy: г. Гиждуван, улица Шимолий Шуробод, дом 102</t>
+  </si>
+  <si>
+    <t>FrГЖД-8</t>
+  </si>
+  <si>
+    <t>998 50 701 47 35</t>
+  </si>
+  <si>
+    <t>@frAND32</t>
+  </si>
+  <si>
+    <t>40.089657, 64.768066</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Buyuk Ipak Yo'li ko'chasi, 123 uy: г. Ташкент, Мирзо Улугбекский район, улица Буюк Ипак Йули, дом 123</t>
+  </si>
+  <si>
+    <t>FrТАШ-437</t>
+  </si>
+  <si>
+    <t>998 99 853 81 15</t>
+  </si>
+  <si>
+    <t>@FrTash437</t>
+  </si>
+  <si>
+    <t>41.327764, 69.336688</t>
+  </si>
+  <si>
+    <t>Qo'qon sh., Alisher Navoiy koʻchasi, 117A uy : г. Коканд, улица Алишера Навоий, дом 117А</t>
+  </si>
+  <si>
+    <t>FrККД-20</t>
+  </si>
+  <si>
+    <t>998 92 026 71 84</t>
+  </si>
+  <si>
+    <t>@UzumFrKKD20</t>
+  </si>
+  <si>
+    <t>40.537070, 70.963127</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -22876,57 +23094,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22935,7 +23162,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22944,16 +23171,19 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22962,16 +23192,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22980,13 +23204,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -22995,40 +23222,37 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -23335,7 +23559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1839"/>
+  <dimension ref="A1:E1853"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -54591,20 +54815,258 @@
       </c>
     </row>
     <row r="1839" spans="1:5" ht="39" x14ac:dyDescent="0.25">
-      <c r="A1839" s="5" t="s">
+      <c r="A1839" s="10" t="s">
         <v>7541</v>
       </c>
-      <c r="B1839" s="13" t="s">
+      <c r="B1839" s="17" t="s">
         <v>7542</v>
       </c>
-      <c r="C1839" s="50" t="s">
+      <c r="C1839" s="52" t="s">
         <v>7543</v>
       </c>
-      <c r="D1839" s="8" t="s">
+      <c r="D1839" s="11" t="s">
         <v>7544</v>
       </c>
-      <c r="E1839" s="8" t="s">
+      <c r="E1839" s="11" t="s">
         <v>7545</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1840" s="5" t="s">
+        <v>7546</v>
+      </c>
+      <c r="B1840" s="13" t="s">
+        <v>7547</v>
+      </c>
+      <c r="C1840" s="53" t="s">
+        <v>7548</v>
+      </c>
+      <c r="D1840" s="8" t="s">
+        <v>7549</v>
+      </c>
+      <c r="E1840" s="8" t="s">
+        <v>7550</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1841" s="5" t="s">
+        <v>7551</v>
+      </c>
+      <c r="B1841" s="13" t="s">
+        <v>7552</v>
+      </c>
+      <c r="C1841" s="53" t="s">
+        <v>7553</v>
+      </c>
+      <c r="D1841" s="8" t="s">
+        <v>7554</v>
+      </c>
+      <c r="E1841" s="8" t="s">
+        <v>7555</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1842" s="5" t="s">
+        <v>7556</v>
+      </c>
+      <c r="B1842" s="13" t="s">
+        <v>7557</v>
+      </c>
+      <c r="C1842" s="53" t="s">
+        <v>7558</v>
+      </c>
+      <c r="D1842" s="8" t="s">
+        <v>7559</v>
+      </c>
+      <c r="E1842" s="8" t="s">
+        <v>7560</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1843" s="5" t="s">
+        <v>7561</v>
+      </c>
+      <c r="B1843" s="13" t="s">
+        <v>7562</v>
+      </c>
+      <c r="C1843" s="53" t="s">
+        <v>7563</v>
+      </c>
+      <c r="D1843" s="8" t="s">
+        <v>7564</v>
+      </c>
+      <c r="E1843" s="8" t="s">
+        <v>7565</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1844" s="5" t="s">
+        <v>7566</v>
+      </c>
+      <c r="B1844" s="13" t="s">
+        <v>7567</v>
+      </c>
+      <c r="C1844" s="53" t="s">
+        <v>7568</v>
+      </c>
+      <c r="D1844" s="8" t="s">
+        <v>7569</v>
+      </c>
+      <c r="E1844" s="8" t="s">
+        <v>7570</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1845" s="5" t="s">
+        <v>7571</v>
+      </c>
+      <c r="B1845" s="13" t="s">
+        <v>7572</v>
+      </c>
+      <c r="C1845" s="53" t="s">
+        <v>7573</v>
+      </c>
+      <c r="D1845" s="8" t="s">
+        <v>7574</v>
+      </c>
+      <c r="E1845" s="8" t="s">
+        <v>7575</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1846" s="5" t="s">
+        <v>7576</v>
+      </c>
+      <c r="B1846" s="13" t="s">
+        <v>7577</v>
+      </c>
+      <c r="C1846" s="53" t="s">
+        <v>7578</v>
+      </c>
+      <c r="D1846" s="8" t="s">
+        <v>7579</v>
+      </c>
+      <c r="E1846" s="8" t="s">
+        <v>7580</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1847" s="5" t="s">
+        <v>7581</v>
+      </c>
+      <c r="B1847" s="13" t="s">
+        <v>7582</v>
+      </c>
+      <c r="C1847" s="53" t="s">
+        <v>7583</v>
+      </c>
+      <c r="D1847" s="8" t="s">
+        <v>7584</v>
+      </c>
+      <c r="E1847" s="8" t="s">
+        <v>7585</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1848" s="5" t="s">
+        <v>7586</v>
+      </c>
+      <c r="B1848" s="13" t="s">
+        <v>7587</v>
+      </c>
+      <c r="C1848" s="53" t="s">
+        <v>7588</v>
+      </c>
+      <c r="D1848" s="8" t="s">
+        <v>7589</v>
+      </c>
+      <c r="E1848" s="8" t="s">
+        <v>7590</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1849" s="5" t="s">
+        <v>7591</v>
+      </c>
+      <c r="B1849" s="13" t="s">
+        <v>7592</v>
+      </c>
+      <c r="C1849" s="53" t="s">
+        <v>7593</v>
+      </c>
+      <c r="D1849" s="8" t="s">
+        <v>7594</v>
+      </c>
+      <c r="E1849" s="8" t="s">
+        <v>7595</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1850" s="5" t="s">
+        <v>7596</v>
+      </c>
+      <c r="B1850" s="13" t="s">
+        <v>7597</v>
+      </c>
+      <c r="C1850" s="53" t="s">
+        <v>7598</v>
+      </c>
+      <c r="D1850" s="8" t="s">
+        <v>7599</v>
+      </c>
+      <c r="E1850" s="8" t="s">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1851" s="5" t="s">
+        <v>7601</v>
+      </c>
+      <c r="B1851" s="13" t="s">
+        <v>7602</v>
+      </c>
+      <c r="C1851" s="53" t="s">
+        <v>7603</v>
+      </c>
+      <c r="D1851" s="8" t="s">
+        <v>7604</v>
+      </c>
+      <c r="E1851" s="8" t="s">
+        <v>7605</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1852" s="5" t="s">
+        <v>7606</v>
+      </c>
+      <c r="B1852" s="13" t="s">
+        <v>7607</v>
+      </c>
+      <c r="C1852" s="53" t="s">
+        <v>7608</v>
+      </c>
+      <c r="D1852" s="8" t="s">
+        <v>7609</v>
+      </c>
+      <c r="E1852" s="8" t="s">
+        <v>7610</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1853" s="5" t="s">
+        <v>7611</v>
+      </c>
+      <c r="B1853" s="13" t="s">
+        <v>7612</v>
+      </c>
+      <c r="C1853" s="53" t="s">
+        <v>7613</v>
+      </c>
+      <c r="D1853" s="8" t="s">
+        <v>7614</v>
+      </c>
+      <c r="E1853" s="8" t="s">
+        <v>7615</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F594B6AA-768C-46A0-A9FF-67B085AA3C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F62156-3502-4E9D-9914-207E0EB74F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7628" uniqueCount="7616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7697" uniqueCount="7685">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -22884,18 +22884,233 @@
   </si>
   <si>
     <t>40.537070, 70.963127</t>
+  </si>
+  <si>
+    <t>Uchtepa sh., Buloqboshi tumani, Mehnatobod ko'chasi, 92 uy: г. Учтепа, Булакбашинский район, улица Мехнатобод, дом 92</t>
+  </si>
+  <si>
+    <t>FrУЧТ-1</t>
+  </si>
+  <si>
+    <t>998 90 018 04 03</t>
+  </si>
+  <si>
+    <t>@FrUCHT1uzum</t>
+  </si>
+  <si>
+    <t>40.612827, 72.456805</t>
+  </si>
+  <si>
+    <t>Shahrisabz sh., Chilonzor ko‘chasi, 77 uy: г. Шахрисабз, улица Чиланзар, дом 77</t>
+  </si>
+  <si>
+    <t>FrШРЗ-11</t>
+  </si>
+  <si>
+    <t>998 70 324 91 92</t>
+  </si>
+  <si>
+    <t>@FrSHRZ_11</t>
+  </si>
+  <si>
+    <t>39.049743, 66.820658</t>
+  </si>
+  <si>
+    <t>Urganch sh., Al-Beruniy ko'chasi, 5 tor ko'chasi, 1/1-uy: г. Ургенч, 5 й проезд, улица Ал-Беруний, дом 1/1</t>
+  </si>
+  <si>
+    <t>FrУРГ-30</t>
+  </si>
+  <si>
+    <t>998 70 475 25 01</t>
+  </si>
+  <si>
+    <t>@FrURG30</t>
+  </si>
+  <si>
+    <t>41.551920, 60.660718</t>
+  </si>
+  <si>
+    <t>Bahouddin Naqshband sh., Kogon tumani, Sheyxon ko‘chasi, 263 uy : г. Бахоуддин Накшбанд, Каганский район, улица Шейхон, дом 263</t>
+  </si>
+  <si>
+    <t>FrБДН-1</t>
+  </si>
+  <si>
+    <t>998 97 237 26 03</t>
+  </si>
+  <si>
+    <t>@FrBDN_1</t>
+  </si>
+  <si>
+    <t>39.798987, 64.540873</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Bektemir tumani, Qo'yliqota ko'chasi, 25 uy : г. Ташкент, Бектемирский район, улица Куйликота, дом 25</t>
+  </si>
+  <si>
+    <t>FrТАШ-460</t>
+  </si>
+  <si>
+    <t>998 99 099 89 46</t>
+  </si>
+  <si>
+    <t>@FrTash460</t>
+  </si>
+  <si>
+    <t>41.239843, 69.326741</t>
+  </si>
+  <si>
+    <t>Tuda sh., Pop tumani, Tudasoy ko'chasi, 1 uy: г. Туда, Папский район, улица Тудасой, дом 1</t>
+  </si>
+  <si>
+    <t>FrТДА-1</t>
+  </si>
+  <si>
+    <t>998 94 441 44 97</t>
+  </si>
+  <si>
+    <t>@UzumFrTDA1</t>
+  </si>
+  <si>
+    <t>40.867328, 71.222181</t>
+  </si>
+  <si>
+    <t>G'oybu sh., Xiva yo‘li ko‘chasi, 3 uy : г. Гайбу, улица Хива Йули, дом 3</t>
+  </si>
+  <si>
+    <t>FrГАБ-2</t>
+  </si>
+  <si>
+    <t>998 93 859 72 52</t>
+  </si>
+  <si>
+    <t>@Frgab_2</t>
+  </si>
+  <si>
+    <t>41.531690, 60.592093</t>
+  </si>
+  <si>
+    <t>Buramatut sh., To‘raqo‘rg‘on tumani, Mustaqillik ko‘chasi, 53 uy : г. Бураматут, Туракурганский район, улица Мустакиллик, дом 53</t>
+  </si>
+  <si>
+    <t>FrБРТ-1</t>
+  </si>
+  <si>
+    <t>99894 263 48 98</t>
+  </si>
+  <si>
+    <t>@UzumFrBRT1</t>
+  </si>
+  <si>
+    <t>40.921000, 71.437388</t>
+  </si>
+  <si>
+    <t>Andijon sh., Soy ko‘chasi, 23 uy : г. Андижан, Улица Сой, дом 23</t>
+  </si>
+  <si>
+    <t>FrАНД-36</t>
+  </si>
+  <si>
+    <t>998 94 711 00 27</t>
+  </si>
+  <si>
+    <t>@soy_uzum_market</t>
+  </si>
+  <si>
+    <t>40.799367, 72.352978</t>
+  </si>
+  <si>
+    <t>Yangiyo'l sh., Baxt koʻchasi, 69 uy : г. Янгиюль, улица Бахт, дом 69</t>
+  </si>
+  <si>
+    <t>FrЯНГ-18</t>
+  </si>
+  <si>
+    <t>998 95 359 87 80</t>
+  </si>
+  <si>
+    <t>@FrYANG18</t>
+  </si>
+  <si>
+    <t>41.097366, 69.089466</t>
+  </si>
+  <si>
+    <t>Salpi sh., Xo‘jaobod tumani, Shifokorlar ko'chasi, 13 uy : г. Сальпи, Ходжаабадский район, улица Шифокорлар, дом 13</t>
+  </si>
+  <si>
+    <t>FrСЛП-1</t>
+  </si>
+  <si>
+    <t>998 70 027 14 13</t>
+  </si>
+  <si>
+    <t>@FR_SLP1</t>
+  </si>
+  <si>
+    <t>40.628715, 72.594648</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Jayxun ko'chasi, 6/8A uy: г. Карши, улица Жайхун, дом 6/8A</t>
+  </si>
+  <si>
+    <t>FrКРШ-29</t>
+  </si>
+  <si>
+    <t>998 70 123 14 93</t>
+  </si>
+  <si>
+    <t>@FrKRSH29</t>
+  </si>
+  <si>
+    <t>38.873953, 65.815204</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Mirzo Gʻolib koʻchasi, 7b uy, 310 uy : г. Ташкент, Алмазарский район, ул. Мирзо Голиб, дом 7б</t>
+  </si>
+  <si>
+    <t>FrТАШ-440</t>
+  </si>
+  <si>
+    <t>@frtash_440</t>
+  </si>
+  <si>
+    <t>41.353020, 69.198441</t>
+  </si>
+  <si>
+    <t>Qo'shtamg'ali sh., Samarqand tumani, Obodyurt ko‘chasi, 8 uy: г. Куштамгали, Самаркандский район, улица Ободюрт, дом 8</t>
+  </si>
+  <si>
+    <t>FrКМГ-1</t>
+  </si>
+  <si>
+    <t>998 99 462 37 13</t>
+  </si>
+  <si>
+    <t>@frkmg_1</t>
+  </si>
+  <si>
+    <t>39.657302, 67.039308</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23094,57 +23309,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23153,7 +23377,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23162,16 +23386,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23180,16 +23407,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23198,13 +23419,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23213,40 +23437,37 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23559,7 +23780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1853"/>
+  <dimension ref="A1:E1867"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -55053,20 +55274,256 @@
       </c>
     </row>
     <row r="1853" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1853" s="5" t="s">
+      <c r="A1853" s="10" t="s">
         <v>7611</v>
       </c>
-      <c r="B1853" s="13" t="s">
+      <c r="B1853" s="17" t="s">
         <v>7612</v>
       </c>
-      <c r="C1853" s="53" t="s">
+      <c r="C1853" s="54" t="s">
         <v>7613</v>
       </c>
-      <c r="D1853" s="8" t="s">
+      <c r="D1853" s="11" t="s">
         <v>7614</v>
       </c>
-      <c r="E1853" s="8" t="s">
+      <c r="E1853" s="11" t="s">
         <v>7615</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1854" s="5" t="s">
+        <v>7616</v>
+      </c>
+      <c r="B1854" s="6" t="s">
+        <v>7617</v>
+      </c>
+      <c r="C1854" s="55" t="s">
+        <v>7618</v>
+      </c>
+      <c r="D1854" s="8" t="s">
+        <v>7619</v>
+      </c>
+      <c r="E1854" s="8" t="s">
+        <v>7620</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1855" s="5" t="s">
+        <v>7621</v>
+      </c>
+      <c r="B1855" s="6" t="s">
+        <v>7622</v>
+      </c>
+      <c r="C1855" s="55" t="s">
+        <v>7623</v>
+      </c>
+      <c r="D1855" s="8" t="s">
+        <v>7624</v>
+      </c>
+      <c r="E1855" s="8" t="s">
+        <v>7625</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1856" s="5" t="s">
+        <v>7626</v>
+      </c>
+      <c r="B1856" s="6" t="s">
+        <v>7627</v>
+      </c>
+      <c r="C1856" s="55" t="s">
+        <v>7628</v>
+      </c>
+      <c r="D1856" s="8" t="s">
+        <v>7629</v>
+      </c>
+      <c r="E1856" s="8" t="s">
+        <v>7630</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1857" s="5" t="s">
+        <v>7631</v>
+      </c>
+      <c r="B1857" s="6" t="s">
+        <v>7632</v>
+      </c>
+      <c r="C1857" s="55" t="s">
+        <v>7633</v>
+      </c>
+      <c r="D1857" s="8" t="s">
+        <v>7634</v>
+      </c>
+      <c r="E1857" s="8" t="s">
+        <v>7635</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1858" s="5" t="s">
+        <v>7636</v>
+      </c>
+      <c r="B1858" s="6" t="s">
+        <v>7637</v>
+      </c>
+      <c r="C1858" s="55" t="s">
+        <v>7638</v>
+      </c>
+      <c r="D1858" s="8" t="s">
+        <v>7639</v>
+      </c>
+      <c r="E1858" s="8" t="s">
+        <v>7640</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1859" s="5" t="s">
+        <v>7641</v>
+      </c>
+      <c r="B1859" s="6" t="s">
+        <v>7642</v>
+      </c>
+      <c r="C1859" s="55" t="s">
+        <v>7643</v>
+      </c>
+      <c r="D1859" s="8" t="s">
+        <v>7644</v>
+      </c>
+      <c r="E1859" s="8" t="s">
+        <v>7645</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1860" s="5" t="s">
+        <v>7646</v>
+      </c>
+      <c r="B1860" s="6" t="s">
+        <v>7647</v>
+      </c>
+      <c r="C1860" s="55" t="s">
+        <v>7648</v>
+      </c>
+      <c r="D1860" s="8" t="s">
+        <v>7649</v>
+      </c>
+      <c r="E1860" s="8" t="s">
+        <v>7650</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1861" s="5" t="s">
+        <v>7651</v>
+      </c>
+      <c r="B1861" s="6" t="s">
+        <v>7652</v>
+      </c>
+      <c r="C1861" s="55" t="s">
+        <v>7653</v>
+      </c>
+      <c r="D1861" s="8" t="s">
+        <v>7654</v>
+      </c>
+      <c r="E1861" s="8" t="s">
+        <v>7655</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1862" s="5" t="s">
+        <v>7656</v>
+      </c>
+      <c r="B1862" s="6" t="s">
+        <v>7657</v>
+      </c>
+      <c r="C1862" s="55" t="s">
+        <v>7658</v>
+      </c>
+      <c r="D1862" s="8" t="s">
+        <v>7659</v>
+      </c>
+      <c r="E1862" s="8" t="s">
+        <v>7660</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1863" s="5" t="s">
+        <v>7661</v>
+      </c>
+      <c r="B1863" s="6" t="s">
+        <v>7662</v>
+      </c>
+      <c r="C1863" s="55" t="s">
+        <v>7663</v>
+      </c>
+      <c r="D1863" s="8" t="s">
+        <v>7664</v>
+      </c>
+      <c r="E1863" s="8" t="s">
+        <v>7665</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1864" s="5" t="s">
+        <v>7666</v>
+      </c>
+      <c r="B1864" s="8" t="s">
+        <v>7667</v>
+      </c>
+      <c r="C1864" s="55" t="s">
+        <v>7668</v>
+      </c>
+      <c r="D1864" s="8" t="s">
+        <v>7669</v>
+      </c>
+      <c r="E1864" s="8" t="s">
+        <v>7670</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1865" s="5" t="s">
+        <v>7671</v>
+      </c>
+      <c r="B1865" s="8" t="s">
+        <v>7672</v>
+      </c>
+      <c r="C1865" s="55" t="s">
+        <v>7673</v>
+      </c>
+      <c r="D1865" s="8" t="s">
+        <v>7674</v>
+      </c>
+      <c r="E1865" s="8" t="s">
+        <v>7675</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1866" s="5" t="s">
+        <v>7676</v>
+      </c>
+      <c r="B1866" s="8" t="s">
+        <v>7677</v>
+      </c>
+      <c r="C1866" s="5"/>
+      <c r="D1866" s="8" t="s">
+        <v>7678</v>
+      </c>
+      <c r="E1866" s="8" t="s">
+        <v>7679</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1867" s="5" t="s">
+        <v>7680</v>
+      </c>
+      <c r="B1867" s="8" t="s">
+        <v>7681</v>
+      </c>
+      <c r="C1867" s="55" t="s">
+        <v>7682</v>
+      </c>
+      <c r="D1867" s="8" t="s">
+        <v>7683</v>
+      </c>
+      <c r="E1867" s="8" t="s">
+        <v>7684</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F62156-3502-4E9D-9914-207E0EB74F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B79487A-E1B2-4E38-AD00-835298ECA3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7697" uniqueCount="7685">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7707" uniqueCount="7695">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -23091,18 +23091,56 @@
   </si>
   <si>
     <t>39.657302, 67.039308</t>
+  </si>
+  <si>
+    <t>Yakkabog' sh., Yakkabog' tumani, Xujailg‘or ko'chasi, 18 uy : г. Яккабаг, Яккабагский район, улица Ходжаилгор, дом 18</t>
+  </si>
+  <si>
+    <t>FrЯКК-9</t>
+  </si>
+  <si>
+    <t>998 95 783 00 97</t>
+  </si>
+  <si>
+    <t>@FrYKK_9</t>
+  </si>
+  <si>
+    <t>38.984709, 66.691274</t>
+  </si>
+  <si>
+    <t>Shavat sh., Az-Zamaxshariy ko'chasi, 33 uy.: г. Шават, улица Аз Замахшарий, дом 33</t>
+  </si>
+  <si>
+    <t>FrШВТ-4</t>
+  </si>
+  <si>
+    <t>998 90 100 66 97</t>
+  </si>
+  <si>
+    <t>@FrSHVT4</t>
+  </si>
+  <si>
+    <t>41.660749, 60.283981</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23309,57 +23347,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23368,7 +23415,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23377,16 +23424,19 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23395,16 +23445,10 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23413,13 +23457,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23428,40 +23475,37 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23780,7 +23824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1867"/>
+  <dimension ref="A1:E1869"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -55510,20 +55554,54 @@
       </c>
     </row>
     <row r="1867" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1867" s="5" t="s">
+      <c r="A1867" s="10" t="s">
         <v>7680</v>
       </c>
-      <c r="B1867" s="8" t="s">
+      <c r="B1867" s="11" t="s">
         <v>7681</v>
       </c>
-      <c r="C1867" s="55" t="s">
+      <c r="C1867" s="56" t="s">
         <v>7682</v>
       </c>
-      <c r="D1867" s="8" t="s">
+      <c r="D1867" s="11" t="s">
         <v>7683</v>
       </c>
-      <c r="E1867" s="8" t="s">
+      <c r="E1867" s="11" t="s">
         <v>7684</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1868" s="5" t="s">
+        <v>7685</v>
+      </c>
+      <c r="B1868" s="13" t="s">
+        <v>7686</v>
+      </c>
+      <c r="C1868" s="57" t="s">
+        <v>7687</v>
+      </c>
+      <c r="D1868" s="8" t="s">
+        <v>7688</v>
+      </c>
+      <c r="E1868" s="8" t="s">
+        <v>7689</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1869" s="5" t="s">
+        <v>7690</v>
+      </c>
+      <c r="B1869" s="13" t="s">
+        <v>7691</v>
+      </c>
+      <c r="C1869" s="57" t="s">
+        <v>7692</v>
+      </c>
+      <c r="D1869" s="8" t="s">
+        <v>7693</v>
+      </c>
+      <c r="E1869" s="8" t="s">
+        <v>7694</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B79487A-E1B2-4E38-AD00-835298ECA3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77224CD-45B7-43DB-808D-754FDB665BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7707" uniqueCount="7695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7727" uniqueCount="7715">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -23121,18 +23121,86 @@
   </si>
   <si>
     <t>41.660749, 60.283981</t>
+  </si>
+  <si>
+    <t>Fayziobod sh., Oltiariq tumani, Mustaqillik ko'chasi, 123 uy: г. Файзиабад, Алтыарыкский район, улица Мустакиллик, дом 123</t>
+  </si>
+  <si>
+    <t>FrФАЙ-1</t>
+  </si>
+  <si>
+    <t>998 70 512 70 76</t>
+  </si>
+  <si>
+    <t>@FrFay_1</t>
+  </si>
+  <si>
+    <t>40.412151, 71.602397</t>
+  </si>
+  <si>
+    <t>Qoraqo'yli sh., Qorako'l tumani, Regha Haidar ko‘chasi, 52 s uy : г. Каракуль, Каракульский район ,улица Реги Хайдар, дом 52 с</t>
+  </si>
+  <si>
+    <t>FrКРК-6</t>
+  </si>
+  <si>
+    <t>998 50 887 31 20</t>
+  </si>
+  <si>
+    <t>@Frkrk_6</t>
+  </si>
+  <si>
+    <t>39.544887, 63.834596</t>
+  </si>
+  <si>
+    <t>Bekobod sh., Muqimiy koʻchasi, 312 uy : г. Бекабад, улица Мукими, дом 312</t>
+  </si>
+  <si>
+    <t>FrБЕК-12</t>
+  </si>
+  <si>
+    <t>998 91 013 89 94</t>
+  </si>
+  <si>
+    <t>@uzumfrbek_12</t>
+  </si>
+  <si>
+    <t>40.221761, 69.275536</t>
+  </si>
+  <si>
+    <t>Farg'ona sh., Mustaqillik ko'chasi, 292/1 uy : г. Фергана, улица Мустакиллик, дом 292/1</t>
+  </si>
+  <si>
+    <t>FrФЕР-46</t>
+  </si>
+  <si>
+    <t>998 92 059 91 63</t>
+  </si>
+  <si>
+    <t>@FrFER_46</t>
+  </si>
+  <si>
+    <t>40.362837, 71.771752</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23347,57 +23415,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23406,7 +23483,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23415,16 +23492,19 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23433,16 +23513,10 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23451,13 +23525,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23466,40 +23543,37 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23824,7 +23898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1869"/>
+  <dimension ref="A1:E1873"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -55588,20 +55662,88 @@
       </c>
     </row>
     <row r="1869" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1869" s="5" t="s">
+      <c r="A1869" s="10" t="s">
         <v>7690</v>
       </c>
-      <c r="B1869" s="13" t="s">
+      <c r="B1869" s="17" t="s">
         <v>7691</v>
       </c>
-      <c r="C1869" s="57" t="s">
+      <c r="C1869" s="58" t="s">
         <v>7692</v>
       </c>
-      <c r="D1869" s="8" t="s">
+      <c r="D1869" s="11" t="s">
         <v>7693</v>
       </c>
-      <c r="E1869" s="8" t="s">
+      <c r="E1869" s="11" t="s">
         <v>7694</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1870" s="5" t="s">
+        <v>7695</v>
+      </c>
+      <c r="B1870" s="13" t="s">
+        <v>7696</v>
+      </c>
+      <c r="C1870" s="59" t="s">
+        <v>7697</v>
+      </c>
+      <c r="D1870" s="8" t="s">
+        <v>7698</v>
+      </c>
+      <c r="E1870" s="8" t="s">
+        <v>7699</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1871" s="5" t="s">
+        <v>7700</v>
+      </c>
+      <c r="B1871" s="13" t="s">
+        <v>7701</v>
+      </c>
+      <c r="C1871" s="59" t="s">
+        <v>7702</v>
+      </c>
+      <c r="D1871" s="8" t="s">
+        <v>7703</v>
+      </c>
+      <c r="E1871" s="8" t="s">
+        <v>7704</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1872" s="5" t="s">
+        <v>7705</v>
+      </c>
+      <c r="B1872" s="13" t="s">
+        <v>7706</v>
+      </c>
+      <c r="C1872" s="59" t="s">
+        <v>7707</v>
+      </c>
+      <c r="D1872" s="8" t="s">
+        <v>7708</v>
+      </c>
+      <c r="E1872" s="8" t="s">
+        <v>7709</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1873" s="5" t="s">
+        <v>7710</v>
+      </c>
+      <c r="B1873" s="13" t="s">
+        <v>7711</v>
+      </c>
+      <c r="C1873" s="59" t="s">
+        <v>7712</v>
+      </c>
+      <c r="D1873" s="8" t="s">
+        <v>7713</v>
+      </c>
+      <c r="E1873" s="8" t="s">
+        <v>7714</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77224CD-45B7-43DB-808D-754FDB665BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE73652-F5D5-4BDC-9CC3-82797E067CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7727" uniqueCount="7715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7882" uniqueCount="7870">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -23181,18 +23181,491 @@
   </si>
   <si>
     <t>40.362837, 71.771752</t>
+  </si>
+  <si>
+    <t>Chinoz sh., Yoʻltushgan koʻchasi, 51 uy : г. Чиназ, ул. Йултушган, дом 51</t>
+  </si>
+  <si>
+    <t>FrЧИН-10</t>
+  </si>
+  <si>
+    <t>998 88 213 52 62</t>
+  </si>
+  <si>
+    <t>@FrCHIN_10</t>
+  </si>
+  <si>
+    <t>40.944288, 68.791147</t>
+  </si>
+  <si>
+    <t>Botir sh., Zangiota tumani, Kamoliddin Behzod ko‘chasi, 2 uy: г. Батыр, Зангиатинский район, улица Камолиддин Бехзод, дом 2</t>
+  </si>
+  <si>
+    <t>FrБАТ-1</t>
+  </si>
+  <si>
+    <t>998 50 053 25 64</t>
+  </si>
+  <si>
+    <t>@FrBAT1</t>
+  </si>
+  <si>
+    <t>41.222971, 69.070332</t>
+  </si>
+  <si>
+    <t>Yangiyer sh., Paxtakor koʻchasi, 27 uy : г. Янгиер, улица Пахтакор, дом 27</t>
+  </si>
+  <si>
+    <t>FrЯНР-7</t>
+  </si>
+  <si>
+    <t>998 91 017 77 20</t>
+  </si>
+  <si>
+    <t>@FrYANR7</t>
+  </si>
+  <si>
+    <t>40.273979, 68.815218</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Yoshlik MFY, Riga koʻchasi, 15 uy : г. Самарканд, МФИ Ёшлик, улица Рига, дом 15</t>
+  </si>
+  <si>
+    <t>FrСМК-84</t>
+  </si>
+  <si>
+    <t>998 70 481 56 59</t>
+  </si>
+  <si>
+    <t>@frSMK84</t>
+  </si>
+  <si>
+    <t>39.639726, 66.889271</t>
+  </si>
+  <si>
+    <t>G‘ijduvon sh., Namatgaron ko'chasi, 206 uy: г. Гиждуван, улица Наматгарон, дом 206</t>
+  </si>
+  <si>
+    <t>FrГЖД-11</t>
+  </si>
+  <si>
+    <t>998 50 072 73 04</t>
+  </si>
+  <si>
+    <t>@FrGJD_11</t>
+  </si>
+  <si>
+    <t>40.096893, 64.729605</t>
+  </si>
+  <si>
+    <t>Shayxlar sh., Ishtixon tumani, Sheyxlar qishlog'i ko'chasi, 92 uy: г. Шейхлар, Иштыханский район, улица кишлака Шейхлар, дом 92</t>
+  </si>
+  <si>
+    <t>FrШЕХ-1</t>
+  </si>
+  <si>
+    <t>998 50 112 71 76</t>
+  </si>
+  <si>
+    <t>@fr_shex_1</t>
+  </si>
+  <si>
+    <t>39.903663, 66.551786</t>
+  </si>
+  <si>
+    <t>Buloqboshi sh., Ohangaron koʻchasi, 11 uy : г. Булакбаши, улица Охангарон, дом 11</t>
+  </si>
+  <si>
+    <t>FrБКБ-5</t>
+  </si>
+  <si>
+    <t>998 93 791 98 30</t>
+  </si>
+  <si>
+    <t>@frbkb_5</t>
+  </si>
+  <si>
+    <t>40.656165, 72.406132</t>
+  </si>
+  <si>
+    <t>Oʻqchi Dasht sh., O‘zbekiston tumani, Soy boʼyi ko‘chasi, 973 uy: г. Укчи Дашт, Узбекистанский район, улица Сой Буйи, дом 973</t>
+  </si>
+  <si>
+    <t>FrУКД-1</t>
+  </si>
+  <si>
+    <t>998 77 078 99 55</t>
+  </si>
+  <si>
+    <t>@UzumFrUKD1</t>
+  </si>
+  <si>
+    <t>40.341316, 70.995864</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Shayxontohur tumani, Qoratosh ko‘chasi, 4 uy : г. Ташкент, Шайхантахурский район, улица Караташ, дом 4</t>
+  </si>
+  <si>
+    <t>FrТАШ-467</t>
+  </si>
+  <si>
+    <t>998 77 014 46 87</t>
+  </si>
+  <si>
+    <t>@FrTASH_467</t>
+  </si>
+  <si>
+    <t>41.318187, 69.230936</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Oltin Boshoq ko‘chasi, 100 uy : г. Карши, улица Олтин Бошок, дом 100</t>
+  </si>
+  <si>
+    <t>FrКРШ-40</t>
+  </si>
+  <si>
+    <t>998 95 721 52 25</t>
+  </si>
+  <si>
+    <t>@FrKRSH_40</t>
+  </si>
+  <si>
+    <t>38.924223, 65.751818</t>
+  </si>
+  <si>
+    <t>Angren sh, 4 mavzesi, 14 uy: г. Ангрен, 4-й квартал, дом 14</t>
+  </si>
+  <si>
+    <t>FrАНГ-13</t>
+  </si>
+  <si>
+    <t>998 95 670 43 45</t>
+  </si>
+  <si>
+    <t>@FrANG_13</t>
+  </si>
+  <si>
+    <t>41.003516, 70.079797</t>
+  </si>
+  <si>
+    <t>Toyloq sh., Ukrach MFY, Davlatobod ko‘chasi, 23 uy: г. Тайлак, Украч МФИ, улица Давлатобад, дом 23</t>
+  </si>
+  <si>
+    <t>FrТАЙ-4</t>
+  </si>
+  <si>
+    <t>998 91 522 72 80</t>
+  </si>
+  <si>
+    <t>@FrTAY4</t>
+  </si>
+  <si>
+    <t>39.578903, 67.048663</t>
+  </si>
+  <si>
+    <t>Katta Nayman sh., Pastdarg‘om tumani, Yangiyo‘l ko‘chasi, 10 uy : г. Катта Найман, Пастдаргомский район, улица Кишлак Янгийул, дом 10</t>
+  </si>
+  <si>
+    <t>FrНАЙ-1</t>
+  </si>
+  <si>
+    <t>998 70 229 41 23</t>
+  </si>
+  <si>
+    <t>@uzum_nay1</t>
+  </si>
+  <si>
+    <t>39.684217, 66.665828</t>
+  </si>
+  <si>
+    <t>Mugʻlon sh., Xalkaiuli ko'chasi, 28 uy: г. Муглан, улица Халкайули, дом 28</t>
+  </si>
+  <si>
+    <t>FrМНГ-2</t>
+  </si>
+  <si>
+    <t>998 88 428 19 19</t>
+  </si>
+  <si>
+    <t>@FrMNG_2</t>
+  </si>
+  <si>
+    <t>38.924319, 65.426018</t>
+  </si>
+  <si>
+    <t>Yakhtanlik sh., Sharof Rashidov tumani, Tukchara ko‘chasi, 106 uy : г. Яхтанлик, Шараф Рашидовский район, улица Тукчара, дом 106</t>
+  </si>
+  <si>
+    <t>FrЯТН-1</t>
+  </si>
+  <si>
+    <t>998 50 525 26 32</t>
+  </si>
+  <si>
+    <t>@FrYatn_1</t>
+  </si>
+  <si>
+    <t>40.167891, 67.802758</t>
+  </si>
+  <si>
+    <t>Karateri sh., Norin tumani, Temur Malik ko‘chasi, 18 uy : г. Каратери, Нарынский район, улица Темур Малик, дом 18</t>
+  </si>
+  <si>
+    <t>FrКТР-1</t>
+  </si>
+  <si>
+    <t>998 87 963 69 63</t>
+  </si>
+  <si>
+    <t>@UzumFRKTR1</t>
+  </si>
+  <si>
+    <t>40.915319, 71.931206</t>
+  </si>
+  <si>
+    <t>Sho'rchi sh., Аmir Temur ko'chasi, 66 d uy : г. Шурчи, улица Амира Темура, дом 66 д</t>
+  </si>
+  <si>
+    <t>FrШУР-5</t>
+  </si>
+  <si>
+    <t>998 90 522 55 88</t>
+  </si>
+  <si>
+    <t>@FrSHUR5</t>
+  </si>
+  <si>
+    <t>38.013366, 67.798861</t>
+  </si>
+  <si>
+    <t>Namangan sh., Ulug‘bek ko'chasi, 3 в uy: г. Наманган, улица Улугбек, дом 3 б</t>
+  </si>
+  <si>
+    <t>FrНАМ-39</t>
+  </si>
+  <si>
+    <t>998 90 740 28 98</t>
+  </si>
+  <si>
+    <t>@UzumFrNAM39</t>
+  </si>
+  <si>
+    <t>40.979195, 71.621606</t>
+  </si>
+  <si>
+    <t>Uchqo‘rg‘on sh., Akmal Ikromov koʻchasi, 1 uy : г. Учкурган, улица Акмал Икромов, дом 1</t>
+  </si>
+  <si>
+    <t>FrУЧН-7</t>
+  </si>
+  <si>
+    <t>998 99 217 40 77</t>
+  </si>
+  <si>
+    <t>@UzumFrUCHN7</t>
+  </si>
+  <si>
+    <t>41.119805, 72.091846</t>
+  </si>
+  <si>
+    <t>Gulbog sh., Mingbuloq tumani, Birlashgan ko'chasi, 27/2 uy: г. Гульбаг, Мингбулакский район, улица Бирлашган, дом 27/2</t>
+  </si>
+  <si>
+    <t>FrГУБ-1</t>
+  </si>
+  <si>
+    <t>998 93 158 77 21</t>
+  </si>
+  <si>
+    <t>@UzumFrGUB1</t>
+  </si>
+  <si>
+    <t>40.817486, 71.171709</t>
+  </si>
+  <si>
+    <t>Konigil sh., Samarqand Darvozasi ko'chasi, 146 uy.: г. Конигиль, улица Самарканд Дарвозаси, дом 146</t>
+  </si>
+  <si>
+    <t>FrКОН-2</t>
+  </si>
+  <si>
+    <t>998 99 159 68 46</t>
+  </si>
+  <si>
+    <t>@FrKON2</t>
+  </si>
+  <si>
+    <t>39.666660, 67.041986</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Olmazor tumani, Chig'atoy Darboza MFY, Nurafshon ko'chasi, 7A uy : г. Ташкент, Алмазарский район, Чигатай Дарбоза МФИ, улица Нурафшон, дом 7А</t>
+  </si>
+  <si>
+    <t>FrТАШ-432</t>
+  </si>
+  <si>
+    <t>998 99 470 55 11</t>
+  </si>
+  <si>
+    <t>@UzumFrTash432</t>
+  </si>
+  <si>
+    <t>41.337805, 69.223035</t>
+  </si>
+  <si>
+    <t>Vobkent sh., Kulolchi koʻchasi, 43 uy : г. Вабкент, улица Кулолчи, дом 43</t>
+  </si>
+  <si>
+    <t>FrВБК-4</t>
+  </si>
+  <si>
+    <t>998 50 077 47 24</t>
+  </si>
+  <si>
+    <t>@frVbk_4</t>
+  </si>
+  <si>
+    <t>40.030472, 64.523310</t>
+  </si>
+  <si>
+    <t>Yuqori Qaynama sh., Shahrisabz ko'chasi, 77 uy : г. Юкори Кайнама, улица Шахрисабз, дом 77</t>
+  </si>
+  <si>
+    <t>FrЮКМ-1</t>
+  </si>
+  <si>
+    <t>998 70 525 72 04</t>
+  </si>
+  <si>
+    <t>@fr_yukm_1</t>
+  </si>
+  <si>
+    <t>39.693856, 66.873266</t>
+  </si>
+  <si>
+    <t>Namangan sh., Mustaqillik 10 yilligi koʻchasi, 24 uy : г. Наманган, улица Мустакиллик 10 йиллиги, дом 24</t>
+  </si>
+  <si>
+    <t>FrНАМ-43</t>
+  </si>
+  <si>
+    <t>998 94 109 39 93</t>
+  </si>
+  <si>
+    <t>@UzumFrNAM43</t>
+  </si>
+  <si>
+    <t>41.065930, 71.628558</t>
+  </si>
+  <si>
+    <t>Bekobod sh., Sayxun MFY, Yorqin ko'chasi, 235-uy : г. Бекабад, МФИ Сайхун, улица Ёркин, дом 235</t>
+  </si>
+  <si>
+    <t>FrБЕК-11</t>
+  </si>
+  <si>
+    <t>998 93 222 88 56</t>
+  </si>
+  <si>
+    <t>@frbek_11</t>
+  </si>
+  <si>
+    <t>40.208246, 69.281558</t>
+  </si>
+  <si>
+    <t>Quduqli sh., Jomboy tumani, Katagon ko'chasi, 23 uy: г. Кудукли, Джамбайский район, улица Катагон, дом 23</t>
+  </si>
+  <si>
+    <t>FrКУД-1</t>
+  </si>
+  <si>
+    <t>998 93 313 83 20</t>
+  </si>
+  <si>
+    <t>@FrKUD_1</t>
+  </si>
+  <si>
+    <t>39.682942, 67.197911</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Mirzo Ulug'bek tumani, Xislat koʻchasi, 62 uy : г. Ташкент, Мирзо Улугбекский район, улица Хислат, дом 62</t>
+  </si>
+  <si>
+    <t>FrТАШ-451</t>
+  </si>
+  <si>
+    <t>998 70 533 03 45</t>
+  </si>
+  <si>
+    <t>@FrTASH451uzum</t>
+  </si>
+  <si>
+    <t>41.337369, 69.390923</t>
+  </si>
+  <si>
+    <t>Buyrachi sh., Shovot tumani, G'ayrat ko'chasi ,19 uy : г. Буйрачи, Шаватский район, улица Гайрат, дом 19</t>
+  </si>
+  <si>
+    <t>FrБУЙ-1</t>
+  </si>
+  <si>
+    <t>998 50 007 98 69</t>
+  </si>
+  <si>
+    <t>@frbuy_1</t>
+  </si>
+  <si>
+    <t>41.654273, 60.406494</t>
+  </si>
+  <si>
+    <t>Marg'ilon sh., Mustaqillik ko'chasi, 476 uy : г. Маргилан, улица Мустакиллик, дом 476</t>
+  </si>
+  <si>
+    <t>FrМРГ-10</t>
+  </si>
+  <si>
+    <t>998 50 300 60 66</t>
+  </si>
+  <si>
+    <t>@frmrg_10</t>
+  </si>
+  <si>
+    <t>40.463761, 71.720630</t>
+  </si>
+  <si>
+    <t>Polati sh., Koson tumani, Polati ko'chasi, 24 uy: г. Пулаты, Касанский район, улица Пулаты, дом 24</t>
+  </si>
+  <si>
+    <t>FrПЛТ-1</t>
+  </si>
+  <si>
+    <t>998 95 895 24 35</t>
+  </si>
+  <si>
+    <t>@FrPlt_01</t>
+  </si>
+  <si>
+    <t>39.047582, 65.721723</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23415,57 +23888,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23474,7 +23956,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23483,16 +23965,19 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23501,16 +23986,10 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23519,13 +23998,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23534,40 +24016,37 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23898,7 +24377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1873"/>
+  <dimension ref="A1:E1904"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -55730,20 +56209,547 @@
       </c>
     </row>
     <row r="1873" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1873" s="5" t="s">
+      <c r="A1873" s="10" t="s">
         <v>7710</v>
       </c>
-      <c r="B1873" s="13" t="s">
+      <c r="B1873" s="17" t="s">
         <v>7711</v>
       </c>
-      <c r="C1873" s="59" t="s">
+      <c r="C1873" s="60" t="s">
         <v>7712</v>
       </c>
-      <c r="D1873" s="8" t="s">
+      <c r="D1873" s="11" t="s">
         <v>7713</v>
       </c>
-      <c r="E1873" s="8" t="s">
+      <c r="E1873" s="11" t="s">
         <v>7714</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1874" s="5" t="s">
+        <v>7715</v>
+      </c>
+      <c r="B1874" s="13" t="s">
+        <v>7716</v>
+      </c>
+      <c r="C1874" s="61" t="s">
+        <v>7717</v>
+      </c>
+      <c r="D1874" s="8" t="s">
+        <v>7718</v>
+      </c>
+      <c r="E1874" s="8" t="s">
+        <v>7719</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1875" s="5" t="s">
+        <v>7720</v>
+      </c>
+      <c r="B1875" s="13" t="s">
+        <v>7721</v>
+      </c>
+      <c r="C1875" s="61" t="s">
+        <v>7722</v>
+      </c>
+      <c r="D1875" s="8" t="s">
+        <v>7723</v>
+      </c>
+      <c r="E1875" s="8" t="s">
+        <v>7724</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1876" s="5" t="s">
+        <v>7725</v>
+      </c>
+      <c r="B1876" s="13" t="s">
+        <v>7726</v>
+      </c>
+      <c r="C1876" s="61" t="s">
+        <v>7727</v>
+      </c>
+      <c r="D1876" s="8" t="s">
+        <v>7728</v>
+      </c>
+      <c r="E1876" s="8" t="s">
+        <v>7729</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1877" s="5" t="s">
+        <v>7730</v>
+      </c>
+      <c r="B1877" s="13" t="s">
+        <v>7731</v>
+      </c>
+      <c r="C1877" s="61" t="s">
+        <v>7732</v>
+      </c>
+      <c r="D1877" s="8" t="s">
+        <v>7733</v>
+      </c>
+      <c r="E1877" s="8" t="s">
+        <v>7734</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1878" s="5" t="s">
+        <v>7735</v>
+      </c>
+      <c r="B1878" s="13" t="s">
+        <v>7736</v>
+      </c>
+      <c r="C1878" s="61" t="s">
+        <v>7737</v>
+      </c>
+      <c r="D1878" s="8" t="s">
+        <v>7738</v>
+      </c>
+      <c r="E1878" s="8" t="s">
+        <v>7739</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1879" s="5" t="s">
+        <v>7740</v>
+      </c>
+      <c r="B1879" s="13" t="s">
+        <v>7741</v>
+      </c>
+      <c r="C1879" s="61" t="s">
+        <v>7742</v>
+      </c>
+      <c r="D1879" s="8" t="s">
+        <v>7743</v>
+      </c>
+      <c r="E1879" s="8" t="s">
+        <v>7744</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1880" s="5" t="s">
+        <v>7745</v>
+      </c>
+      <c r="B1880" s="13" t="s">
+        <v>7746</v>
+      </c>
+      <c r="C1880" s="61" t="s">
+        <v>7747</v>
+      </c>
+      <c r="D1880" s="8" t="s">
+        <v>7748</v>
+      </c>
+      <c r="E1880" s="8" t="s">
+        <v>7749</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1881" s="5" t="s">
+        <v>7750</v>
+      </c>
+      <c r="B1881" s="13" t="s">
+        <v>7751</v>
+      </c>
+      <c r="C1881" s="61" t="s">
+        <v>7752</v>
+      </c>
+      <c r="D1881" s="8" t="s">
+        <v>7753</v>
+      </c>
+      <c r="E1881" s="8" t="s">
+        <v>7754</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1882" s="5" t="s">
+        <v>7755</v>
+      </c>
+      <c r="B1882" s="13" t="s">
+        <v>7756</v>
+      </c>
+      <c r="C1882" s="61" t="s">
+        <v>7757</v>
+      </c>
+      <c r="D1882" s="8" t="s">
+        <v>7758</v>
+      </c>
+      <c r="E1882" s="8" t="s">
+        <v>7759</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1883" s="5" t="s">
+        <v>7760</v>
+      </c>
+      <c r="B1883" s="13" t="s">
+        <v>7761</v>
+      </c>
+      <c r="C1883" s="61" t="s">
+        <v>7762</v>
+      </c>
+      <c r="D1883" s="8" t="s">
+        <v>7763</v>
+      </c>
+      <c r="E1883" s="8" t="s">
+        <v>7764</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1884" s="5" t="s">
+        <v>7765</v>
+      </c>
+      <c r="B1884" s="13" t="s">
+        <v>7766</v>
+      </c>
+      <c r="C1884" s="61" t="s">
+        <v>7767</v>
+      </c>
+      <c r="D1884" s="8" t="s">
+        <v>7768</v>
+      </c>
+      <c r="E1884" s="8" t="s">
+        <v>7769</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1885" s="5" t="s">
+        <v>7770</v>
+      </c>
+      <c r="B1885" s="13" t="s">
+        <v>7771</v>
+      </c>
+      <c r="C1885" s="61" t="s">
+        <v>7772</v>
+      </c>
+      <c r="D1885" s="8" t="s">
+        <v>7773</v>
+      </c>
+      <c r="E1885" s="8" t="s">
+        <v>7774</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1886" s="5" t="s">
+        <v>7775</v>
+      </c>
+      <c r="B1886" s="13" t="s">
+        <v>7776</v>
+      </c>
+      <c r="C1886" s="61" t="s">
+        <v>7777</v>
+      </c>
+      <c r="D1886" s="8" t="s">
+        <v>7778</v>
+      </c>
+      <c r="E1886" s="8" t="s">
+        <v>7779</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1887" s="5" t="s">
+        <v>7780</v>
+      </c>
+      <c r="B1887" s="13" t="s">
+        <v>7781</v>
+      </c>
+      <c r="C1887" s="61" t="s">
+        <v>7782</v>
+      </c>
+      <c r="D1887" s="8" t="s">
+        <v>7783</v>
+      </c>
+      <c r="E1887" s="8" t="s">
+        <v>7784</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1888" s="5" t="s">
+        <v>7785</v>
+      </c>
+      <c r="B1888" s="13" t="s">
+        <v>7786</v>
+      </c>
+      <c r="C1888" s="61" t="s">
+        <v>7787</v>
+      </c>
+      <c r="D1888" s="8" t="s">
+        <v>7788</v>
+      </c>
+      <c r="E1888" s="8" t="s">
+        <v>7789</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1889" s="5" t="s">
+        <v>7790</v>
+      </c>
+      <c r="B1889" s="13" t="s">
+        <v>7791</v>
+      </c>
+      <c r="C1889" s="61" t="s">
+        <v>7792</v>
+      </c>
+      <c r="D1889" s="8" t="s">
+        <v>7793</v>
+      </c>
+      <c r="E1889" s="8" t="s">
+        <v>7794</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1890" s="5" t="s">
+        <v>7795</v>
+      </c>
+      <c r="B1890" s="13" t="s">
+        <v>7796</v>
+      </c>
+      <c r="C1890" s="61" t="s">
+        <v>7797</v>
+      </c>
+      <c r="D1890" s="8" t="s">
+        <v>7798</v>
+      </c>
+      <c r="E1890" s="8" t="s">
+        <v>7799</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1891" s="5" t="s">
+        <v>7800</v>
+      </c>
+      <c r="B1891" s="13" t="s">
+        <v>7801</v>
+      </c>
+      <c r="C1891" s="61" t="s">
+        <v>7802</v>
+      </c>
+      <c r="D1891" s="8" t="s">
+        <v>7803</v>
+      </c>
+      <c r="E1891" s="8" t="s">
+        <v>7804</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1892" s="5" t="s">
+        <v>7805</v>
+      </c>
+      <c r="B1892" s="13" t="s">
+        <v>7806</v>
+      </c>
+      <c r="C1892" s="61" t="s">
+        <v>7807</v>
+      </c>
+      <c r="D1892" s="8" t="s">
+        <v>7808</v>
+      </c>
+      <c r="E1892" s="8" t="s">
+        <v>7809</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1893" s="5" t="s">
+        <v>7810</v>
+      </c>
+      <c r="B1893" s="13" t="s">
+        <v>7811</v>
+      </c>
+      <c r="C1893" s="61" t="s">
+        <v>7812</v>
+      </c>
+      <c r="D1893" s="8" t="s">
+        <v>7813</v>
+      </c>
+      <c r="E1893" s="8" t="s">
+        <v>7814</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1894" s="5" t="s">
+        <v>7815</v>
+      </c>
+      <c r="B1894" s="13" t="s">
+        <v>7816</v>
+      </c>
+      <c r="C1894" s="61" t="s">
+        <v>7817</v>
+      </c>
+      <c r="D1894" s="8" t="s">
+        <v>7818</v>
+      </c>
+      <c r="E1894" s="8" t="s">
+        <v>7819</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1895" s="5" t="s">
+        <v>7820</v>
+      </c>
+      <c r="B1895" s="13" t="s">
+        <v>7821</v>
+      </c>
+      <c r="C1895" s="61" t="s">
+        <v>7822</v>
+      </c>
+      <c r="D1895" s="8" t="s">
+        <v>7823</v>
+      </c>
+      <c r="E1895" s="8" t="s">
+        <v>7824</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1896" s="5" t="s">
+        <v>7825</v>
+      </c>
+      <c r="B1896" s="13" t="s">
+        <v>7826</v>
+      </c>
+      <c r="C1896" s="61" t="s">
+        <v>7827</v>
+      </c>
+      <c r="D1896" s="8" t="s">
+        <v>7828</v>
+      </c>
+      <c r="E1896" s="8" t="s">
+        <v>7829</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1897" s="5" t="s">
+        <v>7830</v>
+      </c>
+      <c r="B1897" s="13" t="s">
+        <v>7831</v>
+      </c>
+      <c r="C1897" s="61" t="s">
+        <v>7832</v>
+      </c>
+      <c r="D1897" s="8" t="s">
+        <v>7833</v>
+      </c>
+      <c r="E1897" s="8" t="s">
+        <v>7834</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1898" s="5" t="s">
+        <v>7835</v>
+      </c>
+      <c r="B1898" s="13" t="s">
+        <v>7836</v>
+      </c>
+      <c r="C1898" s="61" t="s">
+        <v>7837</v>
+      </c>
+      <c r="D1898" s="8" t="s">
+        <v>7838</v>
+      </c>
+      <c r="E1898" s="8" t="s">
+        <v>7839</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1899" s="5" t="s">
+        <v>7840</v>
+      </c>
+      <c r="B1899" s="13" t="s">
+        <v>7841</v>
+      </c>
+      <c r="C1899" s="61" t="s">
+        <v>7842</v>
+      </c>
+      <c r="D1899" s="8" t="s">
+        <v>7843</v>
+      </c>
+      <c r="E1899" s="8" t="s">
+        <v>7844</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1900" s="5" t="s">
+        <v>7845</v>
+      </c>
+      <c r="B1900" s="13" t="s">
+        <v>7846</v>
+      </c>
+      <c r="C1900" s="61" t="s">
+        <v>7847</v>
+      </c>
+      <c r="D1900" s="8" t="s">
+        <v>7848</v>
+      </c>
+      <c r="E1900" s="8" t="s">
+        <v>7849</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1901" s="5" t="s">
+        <v>7850</v>
+      </c>
+      <c r="B1901" s="13" t="s">
+        <v>7851</v>
+      </c>
+      <c r="C1901" s="61" t="s">
+        <v>7852</v>
+      </c>
+      <c r="D1901" s="8" t="s">
+        <v>7853</v>
+      </c>
+      <c r="E1901" s="8" t="s">
+        <v>7854</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1902" s="5" t="s">
+        <v>7855</v>
+      </c>
+      <c r="B1902" s="13" t="s">
+        <v>7856</v>
+      </c>
+      <c r="C1902" s="61" t="s">
+        <v>7857</v>
+      </c>
+      <c r="D1902" s="8" t="s">
+        <v>7858</v>
+      </c>
+      <c r="E1902" s="8" t="s">
+        <v>7859</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1903" s="5" t="s">
+        <v>7860</v>
+      </c>
+      <c r="B1903" s="13" t="s">
+        <v>7861</v>
+      </c>
+      <c r="C1903" s="61" t="s">
+        <v>7862</v>
+      </c>
+      <c r="D1903" s="8" t="s">
+        <v>7863</v>
+      </c>
+      <c r="E1903" s="8" t="s">
+        <v>7864</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1904" s="5" t="s">
+        <v>7865</v>
+      </c>
+      <c r="B1904" s="13" t="s">
+        <v>7866</v>
+      </c>
+      <c r="C1904" s="61" t="s">
+        <v>7867</v>
+      </c>
+      <c r="D1904" s="8" t="s">
+        <v>7868</v>
+      </c>
+      <c r="E1904" s="8" t="s">
+        <v>7869</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE73652-F5D5-4BDC-9CC3-82797E067CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719067C9-6B15-4CC9-BA63-FADACF89DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2565" yWindow="2415" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7882" uniqueCount="7870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7947" uniqueCount="7933">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -23646,18 +23646,215 @@
   </si>
   <si>
     <t>39.047582, 65.721723</t>
+  </si>
+  <si>
+    <t>Xiva sh., Madamin Matkarimov ko'chasi, 42-uy : г. Хива, улица Мадамина Маткаримова, дом 42</t>
+  </si>
+  <si>
+    <t>FrХИВ-12</t>
+  </si>
+  <si>
+    <t>998 99 578 62 26</t>
+  </si>
+  <si>
+    <t>@Frxiv12</t>
+  </si>
+  <si>
+    <t>41.407914, 60.336212</t>
+  </si>
+  <si>
+    <t>Andijon sh., Jalabek kuchasi, 72 uy: г. Андижан, улица Жалабек, дом 72</t>
+  </si>
+  <si>
+    <t>FrАНД-32</t>
+  </si>
+  <si>
+    <t>40.760006, 72.322475</t>
+  </si>
+  <si>
+    <t>Uchtepa sh., Otchopar ko'chasi, 33 uy: г. Учтепа, улица Отчопар, дом 33</t>
+  </si>
+  <si>
+    <t>FrУЧП-3</t>
+  </si>
+  <si>
+    <t>998 50 504 66 86</t>
+  </si>
+  <si>
+    <t>@Otchoparfruchp3</t>
+  </si>
+  <si>
+    <t>40.192048, 67.883821</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Ahmadi Jom ko'chasi, 3 а uy: г. Самарканд, улица Ахмади Жом, дом 3 а</t>
+  </si>
+  <si>
+    <t>FrСМК-81</t>
+  </si>
+  <si>
+    <t>998 95 129 27 06</t>
+  </si>
+  <si>
+    <t>@fr_smk_81</t>
+  </si>
+  <si>
+    <t>39.680122, 66.982704</t>
+  </si>
+  <si>
+    <t>Paxtakurash sh., Denov tumani, Katta Karvon Yo‘li ko‘chasi 6-berk ko‘chasi, 39 uy : г. Пахтакураш, Денауский район, 6-й тупик улицы Катта Карвон Йули, дом 39</t>
+  </si>
+  <si>
+    <t>FrПТШ-1</t>
+  </si>
+  <si>
+    <t>998 95 668 98 85</t>
+  </si>
+  <si>
+    <t>@FrPTSH_1</t>
+  </si>
+  <si>
+    <t>38.157955, 67.898901</t>
+  </si>
+  <si>
+    <t>Dashtabad sh., Zaamin tumani, Latofat koʻchasi, 10a uy : г. Даштабад, Зааминский район, улица Латофат, дом 10а</t>
+  </si>
+  <si>
+    <t>FrДШТ-3</t>
+  </si>
+  <si>
+    <t>998 99 477 99 38</t>
+  </si>
+  <si>
+    <t>@frdsht_3</t>
+  </si>
+  <si>
+    <t>40.129369, 68.498148</t>
+  </si>
+  <si>
+    <t>Ko‘kcha sh., Xatirchin tumani, Yangi ko‘chasi, 223 uy: г. Кукча, Хатирчинский район, улица Янги, дом 223</t>
+  </si>
+  <si>
+    <t>FrККЧ-1</t>
+  </si>
+  <si>
+    <t>998 99 750 50 08</t>
+  </si>
+  <si>
+    <t>@FrKK1x</t>
+  </si>
+  <si>
+    <t>40.065712, 65.933660</t>
+  </si>
+  <si>
+    <t>Karaskan sh., Chortoq tumani, Uychi ko'chasi, 13 uy : г. Караскан, Чартакский район, улица Уйчи, дом 13</t>
+  </si>
+  <si>
+    <t>FrКОР-2</t>
+  </si>
+  <si>
+    <t>998 95 793 22 00</t>
+  </si>
+  <si>
+    <t>@UzumFrKOR2</t>
+  </si>
+  <si>
+    <t>41.056012, 71.832039</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Yashnobod tumani, Aviasozlar ko'chasi 5 tor ko'chasi, 55 uy: г. Ташкент, Яшнабадский район, улица Авиасозлар 5 й проезд, дом 55</t>
+  </si>
+  <si>
+    <t>FrТАШ-459</t>
+  </si>
+  <si>
+    <t>998 87 146 04 96</t>
+  </si>
+  <si>
+    <t>@FRTASH459</t>
+  </si>
+  <si>
+    <t>41.293890, 69.346488</t>
+  </si>
+  <si>
+    <t>Iftixor sh., Muzrabot tumani, Porloq yo‘l ko‘chasi, 51 uy : г. Ифтихор, Музрабадский район, улица Порлок йул, 51 дом</t>
+  </si>
+  <si>
+    <t>FrИФР-1</t>
+  </si>
+  <si>
+    <t>998 33 029 84 84</t>
+  </si>
+  <si>
+    <t>@FrIFR_1</t>
+  </si>
+  <si>
+    <t>37.446045, 66.814330</t>
+  </si>
+  <si>
+    <t>Xiva sh., Elobod koʻchasi, 57B uy : г. Хива, улица Элобод, дом 57Б</t>
+  </si>
+  <si>
+    <t>FrХИВ-13</t>
+  </si>
+  <si>
+    <t>998 94 510 63 93</t>
+  </si>
+  <si>
+    <t>@FrXIV13</t>
+  </si>
+  <si>
+    <t>41.393033, 60.374700</t>
+  </si>
+  <si>
+    <t>Yangi Chinoz sh., Chinoz tumani, Yoshlik ko‘chasi, 90 uy : г. Янги Чиназ, Чиназский район, улица Ёшлик, дом 90</t>
+  </si>
+  <si>
+    <t>FrЯЧН-2</t>
+  </si>
+  <si>
+    <t>998 88 883 09 40</t>
+  </si>
+  <si>
+    <t>@FrYACHN_2</t>
+  </si>
+  <si>
+    <t>40.913879, 68.704201</t>
+  </si>
+  <si>
+    <t>Qo'rg'oncha sh., Alisher Navoiy ko'chasi, 462 uy : г. Курганча, улица Алишера Навоий, дом 462</t>
+  </si>
+  <si>
+    <t>FrКРГ-1</t>
+  </si>
+  <si>
+    <t>998 50 108 84 00</t>
+  </si>
+  <si>
+    <t>@FrKRG_1</t>
+  </si>
+  <si>
+    <t>40.909610, 68.792872</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -23888,57 +24085,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23947,7 +24153,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23956,16 +24162,19 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23974,16 +24183,10 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -23992,13 +24195,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24007,40 +24213,37 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24377,7 +24580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1904"/>
+  <dimension ref="A1:E1917"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -56736,20 +56939,241 @@
       </c>
     </row>
     <row r="1904" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1904" s="5" t="s">
+      <c r="A1904" s="10" t="s">
         <v>7865</v>
       </c>
-      <c r="B1904" s="13" t="s">
+      <c r="B1904" s="17" t="s">
         <v>7866</v>
       </c>
-      <c r="C1904" s="61" t="s">
+      <c r="C1904" s="62" t="s">
         <v>7867</v>
       </c>
-      <c r="D1904" s="8" t="s">
+      <c r="D1904" s="11" t="s">
         <v>7868</v>
       </c>
-      <c r="E1904" s="8" t="s">
+      <c r="E1904" s="11" t="s">
         <v>7869</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1905" s="5" t="s">
+        <v>7870</v>
+      </c>
+      <c r="B1905" s="13" t="s">
+        <v>7871</v>
+      </c>
+      <c r="C1905" s="63" t="s">
+        <v>7872</v>
+      </c>
+      <c r="D1905" s="8" t="s">
+        <v>7873</v>
+      </c>
+      <c r="E1905" s="8" t="s">
+        <v>7874</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1906" s="5" t="s">
+        <v>7875</v>
+      </c>
+      <c r="B1906" s="13" t="s">
+        <v>7876</v>
+      </c>
+      <c r="C1906" s="63" t="s">
+        <v>7603</v>
+      </c>
+      <c r="D1906" s="8" t="s">
+        <v>7604</v>
+      </c>
+      <c r="E1906" s="8" t="s">
+        <v>7877</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1907" s="5" t="s">
+        <v>7878</v>
+      </c>
+      <c r="B1907" s="13" t="s">
+        <v>7879</v>
+      </c>
+      <c r="C1907" s="63" t="s">
+        <v>7880</v>
+      </c>
+      <c r="D1907" s="8" t="s">
+        <v>7881</v>
+      </c>
+      <c r="E1907" s="8" t="s">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1908" s="5" t="s">
+        <v>7883</v>
+      </c>
+      <c r="B1908" s="13" t="s">
+        <v>7884</v>
+      </c>
+      <c r="C1908" s="63" t="s">
+        <v>7885</v>
+      </c>
+      <c r="D1908" s="8" t="s">
+        <v>7886</v>
+      </c>
+      <c r="E1908" s="8" t="s">
+        <v>7887</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1909" s="5" t="s">
+        <v>7888</v>
+      </c>
+      <c r="B1909" s="13" t="s">
+        <v>7889</v>
+      </c>
+      <c r="C1909" s="63" t="s">
+        <v>7890</v>
+      </c>
+      <c r="D1909" s="8" t="s">
+        <v>7891</v>
+      </c>
+      <c r="E1909" s="8" t="s">
+        <v>7892</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1910" s="5" t="s">
+        <v>7893</v>
+      </c>
+      <c r="B1910" s="13" t="s">
+        <v>7894</v>
+      </c>
+      <c r="C1910" s="63" t="s">
+        <v>7895</v>
+      </c>
+      <c r="D1910" s="8" t="s">
+        <v>7896</v>
+      </c>
+      <c r="E1910" s="8" t="s">
+        <v>7897</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1911" s="5" t="s">
+        <v>7898</v>
+      </c>
+      <c r="B1911" s="13" t="s">
+        <v>7899</v>
+      </c>
+      <c r="C1911" s="63" t="s">
+        <v>7900</v>
+      </c>
+      <c r="D1911" s="8" t="s">
+        <v>7901</v>
+      </c>
+      <c r="E1911" s="8" t="s">
+        <v>7902</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1912" s="5" t="s">
+        <v>7903</v>
+      </c>
+      <c r="B1912" s="13" t="s">
+        <v>7904</v>
+      </c>
+      <c r="C1912" s="63" t="s">
+        <v>7905</v>
+      </c>
+      <c r="D1912" s="8" t="s">
+        <v>7906</v>
+      </c>
+      <c r="E1912" s="8" t="s">
+        <v>7907</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1913" s="5" t="s">
+        <v>7908</v>
+      </c>
+      <c r="B1913" s="13" t="s">
+        <v>7909</v>
+      </c>
+      <c r="C1913" s="63" t="s">
+        <v>7910</v>
+      </c>
+      <c r="D1913" s="8" t="s">
+        <v>7911</v>
+      </c>
+      <c r="E1913" s="8" t="s">
+        <v>7912</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1914" s="5" t="s">
+        <v>7913</v>
+      </c>
+      <c r="B1914" s="13" t="s">
+        <v>7914</v>
+      </c>
+      <c r="C1914" s="63" t="s">
+        <v>7915</v>
+      </c>
+      <c r="D1914" s="8" t="s">
+        <v>7916</v>
+      </c>
+      <c r="E1914" s="8" t="s">
+        <v>7917</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1915" s="5" t="s">
+        <v>7918</v>
+      </c>
+      <c r="B1915" s="13" t="s">
+        <v>7919</v>
+      </c>
+      <c r="C1915" s="63" t="s">
+        <v>7920</v>
+      </c>
+      <c r="D1915" s="8" t="s">
+        <v>7921</v>
+      </c>
+      <c r="E1915" s="8" t="s">
+        <v>7922</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1916" s="5" t="s">
+        <v>7923</v>
+      </c>
+      <c r="B1916" s="13" t="s">
+        <v>7924</v>
+      </c>
+      <c r="C1916" s="63" t="s">
+        <v>7925</v>
+      </c>
+      <c r="D1916" s="8" t="s">
+        <v>7926</v>
+      </c>
+      <c r="E1916" s="8" t="s">
+        <v>7927</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1917" s="5" t="s">
+        <v>7928</v>
+      </c>
+      <c r="B1917" s="13" t="s">
+        <v>7929</v>
+      </c>
+      <c r="C1917" s="63" t="s">
+        <v>7930</v>
+      </c>
+      <c r="D1917" s="8" t="s">
+        <v>7931</v>
+      </c>
+      <c r="E1917" s="8" t="s">
+        <v>7932</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719067C9-6B15-4CC9-BA63-FADACF89DD75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D250A5E-305A-4684-9CC0-AF302BA1FB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2565" yWindow="2415" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7947" uniqueCount="7933">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8097" uniqueCount="8083">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -23835,18 +23835,476 @@
   </si>
   <si>
     <t>40.909610, 68.792872</t>
+  </si>
+  <si>
+    <t>Qahramon sh., Termiz tumani, Qaxramon MFY, Amir Temur ko'chasi, 68b uy : г. Кахрамон, Термезский район, МФИ Кахрамон, улица Амира Темура, дом 68б</t>
+  </si>
+  <si>
+    <t>FrКАХ-1</t>
+  </si>
+  <si>
+    <t>998 99 060 29 30</t>
+  </si>
+  <si>
+    <t>@frkax_1</t>
+  </si>
+  <si>
+    <t>37.257411, 67.257778</t>
+  </si>
+  <si>
+    <t>Nush sh., Jomboy tumani, Qishloq Nush ko‘chasi, 174 uy : г. Нуш, Джамбайский район, улица Кишлак Нуш, 174 дом</t>
+  </si>
+  <si>
+    <t>FrНУШ-1</t>
+  </si>
+  <si>
+    <t>998 99 639 77 97</t>
+  </si>
+  <si>
+    <t>@FrNush_1</t>
+  </si>
+  <si>
+    <t>39.805977, 67.002654</t>
+  </si>
+  <si>
+    <t>Chambil sh., Norin tumani, Otbozor ko‘chasi, 54 uy: г. Чамбил, Нарынский район, улица Отбозор, дом 54</t>
+  </si>
+  <si>
+    <t>FrЧМБ-1</t>
+  </si>
+  <si>
+    <t>998 77 833 38 25</t>
+  </si>
+  <si>
+    <t>@UzumFrCHMB1</t>
+  </si>
+  <si>
+    <t>40.936701, 71.985055</t>
+  </si>
+  <si>
+    <t>Xiva sh., Parchanxos MFY, Mustaqillik ko'chasi, 118 uy : г. Хива, МФИ Парчанхос, улица Мустакиллик, дом 118</t>
+  </si>
+  <si>
+    <t>FrХИВ-14</t>
+  </si>
+  <si>
+    <t>998 95 656 69 69</t>
+  </si>
+  <si>
+    <t>@FrXIV14</t>
+  </si>
+  <si>
+    <t>41.429576, 60.435079</t>
+  </si>
+  <si>
+    <t>Damariq sh., Quva tumani, Damarik ko‘chasi, 71 uy: г. Дамарык, Кувинский район, улица Дамарык, дом 71</t>
+  </si>
+  <si>
+    <t>FrДМР-1</t>
+  </si>
+  <si>
+    <t>998 91 172 38 38</t>
+  </si>
+  <si>
+    <t>@frDMR1</t>
+  </si>
+  <si>
+    <t>40.513958, 71.925989</t>
+  </si>
+  <si>
+    <t>Shaxrixon sh., Qumtepa MFY, Qumtepa koʻchasi, r/s uy : г. Шахрихан, МФИ Кумтепа, ул. Кумтепа, дом р/с</t>
+  </si>
+  <si>
+    <t>FrШХР-6</t>
+  </si>
+  <si>
+    <t>998 93 759 37 30</t>
+  </si>
+  <si>
+    <t>@Frshxr_6</t>
+  </si>
+  <si>
+    <t>40.678223, 72.067752</t>
+  </si>
+  <si>
+    <t>Qarshi sh., Jayxun ko'chasi, 7/75 uy: г. Карши, улица Жайхун, дом 7/75</t>
+  </si>
+  <si>
+    <t>FrКРШ-31</t>
+  </si>
+  <si>
+    <t>998 70 218 12 39</t>
+  </si>
+  <si>
+    <t>@FrKRSH31</t>
+  </si>
+  <si>
+    <t>38.815346, 65.813848</t>
+  </si>
+  <si>
+    <t>Sazagan sh., Saroy 4 ko‘chasi, 53 uy : г. Сазаган, 4-я улица Сарой, дом 53</t>
+  </si>
+  <si>
+    <t>FrСАЗ-1</t>
+  </si>
+  <si>
+    <t>998 50 307 64 15</t>
+  </si>
+  <si>
+    <t>@frsaz_1</t>
+  </si>
+  <si>
+    <t>39.537555, 66.750986</t>
+  </si>
+  <si>
+    <t>Madjar sh., Paxtachi tumani, Oqoltin ko‘chasi, 147 uy : г. Маджар, Пахтачийский район, улица Околтин, 147 дом</t>
+  </si>
+  <si>
+    <t>FrМЖР-1</t>
+  </si>
+  <si>
+    <t>998 94 479 04 45</t>
+  </si>
+  <si>
+    <t>@FrMJR1uzum</t>
+  </si>
+  <si>
+    <t>40.091802, 65.576892</t>
+  </si>
+  <si>
+    <t>Chust sh., Ipak yoʻli koʻchasi, 9 uy : г. Чуст, улица Ипак Юли, дом 9</t>
+  </si>
+  <si>
+    <t>FrЧСТ-8</t>
+  </si>
+  <si>
+    <t>998 50 801 22 35</t>
+  </si>
+  <si>
+    <t>@frchst_8</t>
+  </si>
+  <si>
+    <t>40.993806, 71.231188</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Shayxontohur tumani, Qoratosh koʻchasi, 2A uy : г. Ташкент, Шайхантахурский район, улица Караташ, 2А</t>
+  </si>
+  <si>
+    <t>FrТАШ-438</t>
+  </si>
+  <si>
+    <t>998 97 623 72 52</t>
+  </si>
+  <si>
+    <t>@frtash_438</t>
+  </si>
+  <si>
+    <t>41.313213, 69.236625</t>
+  </si>
+  <si>
+    <t>Zarkent sh., Qo'shrabot tumani, Solpi qishlog'i ko'chasi, 246 uy: г. Заркент, Кошрабадский район, улица кишлака Солпи, дом 246</t>
+  </si>
+  <si>
+    <t>FrЗРТ-2</t>
+  </si>
+  <si>
+    <t>998 99 667 27 20</t>
+  </si>
+  <si>
+    <t>@uzum34</t>
+  </si>
+  <si>
+    <t>40.305800, 66.735500</t>
+  </si>
+  <si>
+    <t>Zarbdor sh., Qiziriq tumani, Tadbirkorlar ko‘chasi, 119 uy : г. Зарбдор, Кизирикский район, улица Тадбиркорлар, дом 119</t>
+  </si>
+  <si>
+    <t>FrЗДР-1</t>
+  </si>
+  <si>
+    <t>998 77 116 02 21</t>
+  </si>
+  <si>
+    <t>@FrZDR1</t>
+  </si>
+  <si>
+    <t>37.709608, 67.259575</t>
+  </si>
+  <si>
+    <t>Bo'ston sh., Ellikqali tumani, Kirikkizobod MFY, Alimov ko'chasi, 317 uy: г. Бустан, Элликкалинский район, Кириккизобод ССГ, улица Алимова, дом 317</t>
+  </si>
+  <si>
+    <t>FrБТН-2</t>
+  </si>
+  <si>
+    <t>998 77 317 92 22</t>
+  </si>
+  <si>
+    <t>@FrBTN2</t>
+  </si>
+  <si>
+    <t>41.809080, 61.064713</t>
+  </si>
+  <si>
+    <t>Talisafed sh., Talisafed ko'chasi, 611 uy : г. Талисафед, улица Талисафед, дом 611</t>
+  </si>
+  <si>
+    <t>FrТЛС-1</t>
+  </si>
+  <si>
+    <t>998 94 222 84 41</t>
+  </si>
+  <si>
+    <t>@FrTLS1</t>
+  </si>
+  <si>
+    <t>40.121179, 64.417767</t>
+  </si>
+  <si>
+    <t>Mang'it sh., Qipchoq shohkoʻchasi, 11 uy : г. Мангит, проспект Кипчок, дом 11</t>
+  </si>
+  <si>
+    <t>FrМНТ-5</t>
+  </si>
+  <si>
+    <t>998 99 462 79 27</t>
+  </si>
+  <si>
+    <t>@FrMHT5</t>
+  </si>
+  <si>
+    <t>42.122292, 60.060792</t>
+  </si>
+  <si>
+    <t>Oqtepa sh., Toshkent tumani, Buzsuv buyi ko‘chasi, 25 uy : г. Актепа, Ташкентский район, улица Бузсув буйи, дом 25</t>
+  </si>
+  <si>
+    <t>FrАТП-1</t>
+  </si>
+  <si>
+    <t>998 99 382 30 03</t>
+  </si>
+  <si>
+    <t>@FrATP_1</t>
+  </si>
+  <si>
+    <t>41.366180, 69.330230</t>
+  </si>
+  <si>
+    <t>To'rtko'l sh., Turtko'l tumani, Vatanparvar ko'chasi, 120/16 uy: г. Турткуль, Турткульский район, улица Ватанпарвар, дом 120/16</t>
+  </si>
+  <si>
+    <t>FrТРТ-8</t>
+  </si>
+  <si>
+    <t>998 93 634 08 30</t>
+  </si>
+  <si>
+    <t>@FrTRT_8</t>
+  </si>
+  <si>
+    <t>41.555068, 61.010856</t>
+  </si>
+  <si>
+    <t>Saidota sh., Yangiyo‘l tumani, Qorasuv ko‘chasi, 41 uy : г. Саидота, Янгиюльский район, улица Корасув, дом 41</t>
+  </si>
+  <si>
+    <t>FrСАИ-1</t>
+  </si>
+  <si>
+    <t>998 94 951 17 72</t>
+  </si>
+  <si>
+    <t>@FR_SAI_1</t>
+  </si>
+  <si>
+    <t>41.142488, 69.139628</t>
+  </si>
+  <si>
+    <t>G‘oliblar sh., Porloq ko‘chasi, 83 uy: г. Голиблар, улица Порлок, дом 83</t>
+  </si>
+  <si>
+    <t>FrГБР-2</t>
+  </si>
+  <si>
+    <t>998 87 355 96 49</t>
+  </si>
+  <si>
+    <t>@frgbr_2</t>
+  </si>
+  <si>
+    <t>40.494837, 67.876828</t>
+  </si>
+  <si>
+    <t>Farg‘ona sh., Universitet koʻchasi, 66 uy : г. Фергана, улица Университет, дом 66</t>
+  </si>
+  <si>
+    <t>FrФЕР-47</t>
+  </si>
+  <si>
+    <t>998 90 134 46 48</t>
+  </si>
+  <si>
+    <t>@frFER47</t>
+  </si>
+  <si>
+    <t>40.391628, 71.780035</t>
+  </si>
+  <si>
+    <t>Baxt sh., Sirdaryo tumani, Turkiston koʻchasi, 37 uy : г. Бахт, Сырдарьинский район, улица Туркистан, дом 37</t>
+  </si>
+  <si>
+    <t>FrБХТ-2</t>
+  </si>
+  <si>
+    <t>998 50 071 79 19</t>
+  </si>
+  <si>
+    <t>@frbxt_2</t>
+  </si>
+  <si>
+    <t>40.730755, 68.688134</t>
+  </si>
+  <si>
+    <t>Nanay sh., Yangiqo‘rg‘on tumani, Navoiy ko‘chasi, 116 uy: г. Нанай, Янгикурганский район, улица Навоий, дом 116</t>
+  </si>
+  <si>
+    <t>FrНАН-1</t>
+  </si>
+  <si>
+    <t>998 94 053 52 79</t>
+  </si>
+  <si>
+    <t>@UzumFrNAN1</t>
+  </si>
+  <si>
+    <t>41.514588, 71.704035</t>
+  </si>
+  <si>
+    <t>Povulgon sh., Sayohat ko‘chasi, 99 uy : г. Повулган, улица Саёхат, дом 99</t>
+  </si>
+  <si>
+    <t>FrПВГ-1</t>
+  </si>
+  <si>
+    <t>998 90 534 11 17</t>
+  </si>
+  <si>
+    <t>@frpvg_1</t>
+  </si>
+  <si>
+    <t>40.379217, 71.527101</t>
+  </si>
+  <si>
+    <t>Ayrilish sh., Andijon tumani, Xovuz Bo‘yi ko‘chasi, 829 uy : г. Айрилиш, Андижанский район, улица Ховуз Буйи, дом 829</t>
+  </si>
+  <si>
+    <t>FrАЙШ-1</t>
+  </si>
+  <si>
+    <t>998 99 393 66 00</t>
+  </si>
+  <si>
+    <t>@FrAYSH_1_MirgiyozSaidov</t>
+  </si>
+  <si>
+    <t>40.811836, 72.367212</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, Bunyodkor ko'chasi, 1 uy : г. Ташкент, Чиланзарский район, ул. Бунёдкор, дом 1</t>
+  </si>
+  <si>
+    <t>FrТАШ-447</t>
+  </si>
+  <si>
+    <t>998 95 319 51 56</t>
+  </si>
+  <si>
+    <t>@FrTash447</t>
+  </si>
+  <si>
+    <t>41.294300, 69.224832</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Shayxontohur tumani, Tinchlik ko'chasi, 8 uy: г. Ташкент, Шайхантахурский район, улица Тинчлик, дом 8</t>
+  </si>
+  <si>
+    <t>FrТАШ-442</t>
+  </si>
+  <si>
+    <t>998 77 844 38 00</t>
+  </si>
+  <si>
+    <t>@frtash_442</t>
+  </si>
+  <si>
+    <t>41.336650, 69.209990</t>
+  </si>
+  <si>
+    <t>Karluk sh., Muborak tumani, Mehridil ko‘chasi, 33 uy : г. Карлук, Мубарекский район, улица Мехридил, дом 33</t>
+  </si>
+  <si>
+    <t>FrКРЛ-1</t>
+  </si>
+  <si>
+    <t>998 95 445 34 14</t>
+  </si>
+  <si>
+    <t>@frkrl_1</t>
+  </si>
+  <si>
+    <t>39.101702, 65.334704</t>
+  </si>
+  <si>
+    <t>Beruniy sh., Qiyichirchiq tumani, Sharof Rashidov koʻchasi, 38 uy : г. Беруни, Куйичирчикский район, улица Шарофа Рашидова, дом 38</t>
+  </si>
+  <si>
+    <t>FrБНИ-1</t>
+  </si>
+  <si>
+    <t>998 97 184 47 01</t>
+  </si>
+  <si>
+    <t>@Beruniy0001</t>
+  </si>
+  <si>
+    <t>41.004296, 69.149059</t>
+  </si>
+  <si>
+    <t>Mindon sh., Farg‘ona viloyati, Farog‘at ko'chasi 94 a uy : г. Миндан, Ферганский район, улица Фарогат, дом 94 а</t>
+  </si>
+  <si>
+    <t>FrМНД-1</t>
+  </si>
+  <si>
+    <t>998 33 333 21 20</t>
+  </si>
+  <si>
+    <t>@frmnd_1</t>
+  </si>
+  <si>
+    <t>40.228385, 71.556132</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -24045,7 +24503,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -24081,61 +24539,85 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24144,7 +24626,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24153,16 +24635,19 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24171,16 +24656,10 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24189,13 +24668,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24204,40 +24686,37 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24273,7 +24752,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -24580,7 +25065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1917"/>
+  <dimension ref="A1:E1947"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -57160,20 +57645,530 @@
       </c>
     </row>
     <row r="1917" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1917" s="5" t="s">
+      <c r="A1917" s="10" t="s">
         <v>7928</v>
       </c>
-      <c r="B1917" s="13" t="s">
+      <c r="B1917" s="17" t="s">
         <v>7929</v>
       </c>
-      <c r="C1917" s="63" t="s">
+      <c r="C1917" s="64" t="s">
         <v>7930</v>
       </c>
-      <c r="D1917" s="8" t="s">
+      <c r="D1917" s="11" t="s">
         <v>7931</v>
       </c>
-      <c r="E1917" s="8" t="s">
+      <c r="E1917" s="11" t="s">
         <v>7932</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1918" s="65" t="s">
+        <v>7933</v>
+      </c>
+      <c r="B1918" s="66" t="s">
+        <v>7934</v>
+      </c>
+      <c r="C1918" s="67" t="s">
+        <v>7935</v>
+      </c>
+      <c r="D1918" s="66" t="s">
+        <v>7936</v>
+      </c>
+      <c r="E1918" s="66" t="s">
+        <v>7937</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1919" s="65" t="s">
+        <v>7938</v>
+      </c>
+      <c r="B1919" s="66" t="s">
+        <v>7939</v>
+      </c>
+      <c r="C1919" s="67" t="s">
+        <v>7940</v>
+      </c>
+      <c r="D1919" s="66" t="s">
+        <v>7941</v>
+      </c>
+      <c r="E1919" s="66" t="s">
+        <v>7942</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1920" s="65" t="s">
+        <v>7943</v>
+      </c>
+      <c r="B1920" s="66" t="s">
+        <v>7944</v>
+      </c>
+      <c r="C1920" s="67" t="s">
+        <v>7945</v>
+      </c>
+      <c r="D1920" s="66" t="s">
+        <v>7946</v>
+      </c>
+      <c r="E1920" s="66" t="s">
+        <v>7947</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1921" s="65" t="s">
+        <v>7948</v>
+      </c>
+      <c r="B1921" s="66" t="s">
+        <v>7949</v>
+      </c>
+      <c r="C1921" s="67" t="s">
+        <v>7950</v>
+      </c>
+      <c r="D1921" s="66" t="s">
+        <v>7951</v>
+      </c>
+      <c r="E1921" s="66" t="s">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1922" s="65" t="s">
+        <v>7953</v>
+      </c>
+      <c r="B1922" s="66" t="s">
+        <v>7954</v>
+      </c>
+      <c r="C1922" s="67" t="s">
+        <v>7955</v>
+      </c>
+      <c r="D1922" s="66" t="s">
+        <v>7956</v>
+      </c>
+      <c r="E1922" s="66" t="s">
+        <v>7957</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1923" s="65" t="s">
+        <v>7958</v>
+      </c>
+      <c r="B1923" s="66" t="s">
+        <v>7959</v>
+      </c>
+      <c r="C1923" s="67" t="s">
+        <v>7960</v>
+      </c>
+      <c r="D1923" s="66" t="s">
+        <v>7961</v>
+      </c>
+      <c r="E1923" s="66" t="s">
+        <v>7962</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1924" s="65" t="s">
+        <v>7963</v>
+      </c>
+      <c r="B1924" s="66" t="s">
+        <v>7964</v>
+      </c>
+      <c r="C1924" s="67" t="s">
+        <v>7965</v>
+      </c>
+      <c r="D1924" s="66" t="s">
+        <v>7966</v>
+      </c>
+      <c r="E1924" s="66" t="s">
+        <v>7967</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1925" s="65" t="s">
+        <v>7968</v>
+      </c>
+      <c r="B1925" s="66" t="s">
+        <v>7969</v>
+      </c>
+      <c r="C1925" s="67" t="s">
+        <v>7970</v>
+      </c>
+      <c r="D1925" s="66" t="s">
+        <v>7971</v>
+      </c>
+      <c r="E1925" s="66" t="s">
+        <v>7972</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1926" s="65" t="s">
+        <v>7973</v>
+      </c>
+      <c r="B1926" s="66" t="s">
+        <v>7974</v>
+      </c>
+      <c r="C1926" s="67" t="s">
+        <v>7975</v>
+      </c>
+      <c r="D1926" s="66" t="s">
+        <v>7976</v>
+      </c>
+      <c r="E1926" s="66" t="s">
+        <v>7977</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1927" s="65" t="s">
+        <v>7978</v>
+      </c>
+      <c r="B1927" s="66" t="s">
+        <v>7979</v>
+      </c>
+      <c r="C1927" s="67" t="s">
+        <v>7980</v>
+      </c>
+      <c r="D1927" s="66" t="s">
+        <v>7981</v>
+      </c>
+      <c r="E1927" s="66" t="s">
+        <v>7982</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1928" s="65" t="s">
+        <v>7983</v>
+      </c>
+      <c r="B1928" s="66" t="s">
+        <v>7984</v>
+      </c>
+      <c r="C1928" s="67" t="s">
+        <v>7985</v>
+      </c>
+      <c r="D1928" s="66" t="s">
+        <v>7986</v>
+      </c>
+      <c r="E1928" s="66" t="s">
+        <v>7987</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1929" s="65" t="s">
+        <v>7988</v>
+      </c>
+      <c r="B1929" s="66" t="s">
+        <v>7989</v>
+      </c>
+      <c r="C1929" s="67" t="s">
+        <v>7990</v>
+      </c>
+      <c r="D1929" s="66" t="s">
+        <v>7991</v>
+      </c>
+      <c r="E1929" s="66" t="s">
+        <v>7992</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1930" s="65" t="s">
+        <v>7993</v>
+      </c>
+      <c r="B1930" s="66" t="s">
+        <v>7994</v>
+      </c>
+      <c r="C1930" s="67" t="s">
+        <v>7995</v>
+      </c>
+      <c r="D1930" s="66" t="s">
+        <v>7996</v>
+      </c>
+      <c r="E1930" s="66" t="s">
+        <v>7997</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1931" s="65" t="s">
+        <v>7998</v>
+      </c>
+      <c r="B1931" s="66" t="s">
+        <v>7999</v>
+      </c>
+      <c r="C1931" s="67" t="s">
+        <v>8000</v>
+      </c>
+      <c r="D1931" s="66" t="s">
+        <v>8001</v>
+      </c>
+      <c r="E1931" s="66" t="s">
+        <v>8002</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1932" s="65" t="s">
+        <v>8003</v>
+      </c>
+      <c r="B1932" s="66" t="s">
+        <v>8004</v>
+      </c>
+      <c r="C1932" s="67" t="s">
+        <v>8005</v>
+      </c>
+      <c r="D1932" s="66" t="s">
+        <v>8006</v>
+      </c>
+      <c r="E1932" s="66" t="s">
+        <v>8007</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1933" s="65" t="s">
+        <v>8008</v>
+      </c>
+      <c r="B1933" s="66" t="s">
+        <v>8009</v>
+      </c>
+      <c r="C1933" s="67" t="s">
+        <v>8010</v>
+      </c>
+      <c r="D1933" s="66" t="s">
+        <v>8011</v>
+      </c>
+      <c r="E1933" s="66" t="s">
+        <v>8012</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1934" s="65" t="s">
+        <v>8013</v>
+      </c>
+      <c r="B1934" s="66" t="s">
+        <v>8014</v>
+      </c>
+      <c r="C1934" s="67" t="s">
+        <v>8015</v>
+      </c>
+      <c r="D1934" s="66" t="s">
+        <v>8016</v>
+      </c>
+      <c r="E1934" s="66" t="s">
+        <v>8017</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1935" s="65" t="s">
+        <v>8018</v>
+      </c>
+      <c r="B1935" s="66" t="s">
+        <v>8019</v>
+      </c>
+      <c r="C1935" s="67" t="s">
+        <v>8020</v>
+      </c>
+      <c r="D1935" s="66" t="s">
+        <v>8021</v>
+      </c>
+      <c r="E1935" s="66" t="s">
+        <v>8022</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1936" s="65" t="s">
+        <v>8023</v>
+      </c>
+      <c r="B1936" s="66" t="s">
+        <v>8024</v>
+      </c>
+      <c r="C1936" s="67" t="s">
+        <v>8025</v>
+      </c>
+      <c r="D1936" s="66" t="s">
+        <v>8026</v>
+      </c>
+      <c r="E1936" s="66" t="s">
+        <v>8027</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1937" s="65" t="s">
+        <v>8028</v>
+      </c>
+      <c r="B1937" s="66" t="s">
+        <v>8029</v>
+      </c>
+      <c r="C1937" s="67" t="s">
+        <v>8030</v>
+      </c>
+      <c r="D1937" s="66" t="s">
+        <v>8031</v>
+      </c>
+      <c r="E1937" s="66" t="s">
+        <v>8032</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1938" s="65" t="s">
+        <v>8033</v>
+      </c>
+      <c r="B1938" s="66" t="s">
+        <v>8034</v>
+      </c>
+      <c r="C1938" s="67" t="s">
+        <v>8035</v>
+      </c>
+      <c r="D1938" s="66" t="s">
+        <v>8036</v>
+      </c>
+      <c r="E1938" s="66" t="s">
+        <v>8037</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1939" s="65" t="s">
+        <v>8038</v>
+      </c>
+      <c r="B1939" s="66" t="s">
+        <v>8039</v>
+      </c>
+      <c r="C1939" s="67" t="s">
+        <v>8040</v>
+      </c>
+      <c r="D1939" s="66" t="s">
+        <v>8041</v>
+      </c>
+      <c r="E1939" s="66" t="s">
+        <v>8042</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1940" s="65" t="s">
+        <v>8043</v>
+      </c>
+      <c r="B1940" s="66" t="s">
+        <v>8044</v>
+      </c>
+      <c r="C1940" s="67" t="s">
+        <v>8045</v>
+      </c>
+      <c r="D1940" s="66" t="s">
+        <v>8046</v>
+      </c>
+      <c r="E1940" s="66" t="s">
+        <v>8047</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1941" s="65" t="s">
+        <v>8048</v>
+      </c>
+      <c r="B1941" s="66" t="s">
+        <v>8049</v>
+      </c>
+      <c r="C1941" s="67" t="s">
+        <v>8050</v>
+      </c>
+      <c r="D1941" s="66" t="s">
+        <v>8051</v>
+      </c>
+      <c r="E1941" s="66" t="s">
+        <v>8052</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1942" s="65" t="s">
+        <v>8053</v>
+      </c>
+      <c r="B1942" s="66" t="s">
+        <v>8054</v>
+      </c>
+      <c r="C1942" s="67" t="s">
+        <v>8055</v>
+      </c>
+      <c r="D1942" s="66" t="s">
+        <v>8056</v>
+      </c>
+      <c r="E1942" s="66" t="s">
+        <v>8057</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1943" s="65" t="s">
+        <v>8058</v>
+      </c>
+      <c r="B1943" s="66" t="s">
+        <v>8059</v>
+      </c>
+      <c r="C1943" s="67" t="s">
+        <v>8060</v>
+      </c>
+      <c r="D1943" s="66" t="s">
+        <v>8061</v>
+      </c>
+      <c r="E1943" s="66" t="s">
+        <v>8062</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1944" s="65" t="s">
+        <v>8063</v>
+      </c>
+      <c r="B1944" s="66" t="s">
+        <v>8064</v>
+      </c>
+      <c r="C1944" s="67" t="s">
+        <v>8065</v>
+      </c>
+      <c r="D1944" s="66" t="s">
+        <v>8066</v>
+      </c>
+      <c r="E1944" s="66" t="s">
+        <v>8067</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1945" s="65" t="s">
+        <v>8068</v>
+      </c>
+      <c r="B1945" s="66" t="s">
+        <v>8069</v>
+      </c>
+      <c r="C1945" s="67" t="s">
+        <v>8070</v>
+      </c>
+      <c r="D1945" s="66" t="s">
+        <v>8071</v>
+      </c>
+      <c r="E1945" s="66" t="s">
+        <v>8072</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1946" s="65" t="s">
+        <v>8073</v>
+      </c>
+      <c r="B1946" s="66" t="s">
+        <v>8074</v>
+      </c>
+      <c r="C1946" s="67" t="s">
+        <v>8075</v>
+      </c>
+      <c r="D1946" s="66" t="s">
+        <v>8076</v>
+      </c>
+      <c r="E1946" s="66" t="s">
+        <v>8077</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1947" s="65" t="s">
+        <v>8078</v>
+      </c>
+      <c r="B1947" s="66" t="s">
+        <v>8079</v>
+      </c>
+      <c r="C1947" s="67" t="s">
+        <v>8080</v>
+      </c>
+      <c r="D1947" s="66" t="s">
+        <v>8081</v>
+      </c>
+      <c r="E1947" s="66" t="s">
+        <v>8082</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D250A5E-305A-4684-9CC0-AF302BA1FB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824AF896-D89A-47F3-B1CE-5836BEB59E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2565" yWindow="2415" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8097" uniqueCount="8083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8112" uniqueCount="8098">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -24285,18 +24285,71 @@
   </si>
   <si>
     <t>40.228385, 71.556132</t>
+  </si>
+  <si>
+    <t>Ahmad Yassaviy sh., Zangiota tumani, Buston ko'chasi, 74 uy: г. Ахмад Яссавий, Зангиатинский район, улица Бустон, дом 74</t>
+  </si>
+  <si>
+    <t>FrАСВ-1</t>
+  </si>
+  <si>
+    <t>998 50 112 31 41</t>
+  </si>
+  <si>
+    <t>@FrASV1</t>
+  </si>
+  <si>
+    <t>41.331014, 69.144016</t>
+  </si>
+  <si>
+    <t>Karkidan sh., Chust tumani, Do‘stlik ko‘chasi, 347 uy : г. Каркидан, Чустский район, улица Дустлик, дом 347</t>
+  </si>
+  <si>
+    <t>FrКАД-1</t>
+  </si>
+  <si>
+    <t>998 50 125 55 67</t>
+  </si>
+  <si>
+    <t>@UzumFrKAD1</t>
+  </si>
+  <si>
+    <t>41.073218, 71.203845</t>
+  </si>
+  <si>
+    <t>Baxt sh., Uchqo‘rg‘on tumani, Mustaqillik ko‘chasi, 14 uy : г. Бахт, Учкурганский район, улица Мустакиллик, дом 14</t>
+  </si>
+  <si>
+    <t>FrБТХ-1</t>
+  </si>
+  <si>
+    <t>998 33 594 78 18</t>
+  </si>
+  <si>
+    <t>@FrBTX1</t>
+  </si>
+  <si>
+    <t>40.997284, 71.966361</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -24503,7 +24556,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -24554,61 +24607,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24617,7 +24692,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24626,16 +24701,19 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24644,16 +24722,10 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24662,13 +24734,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24677,40 +24752,37 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24746,19 +24818,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -25065,7 +25146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1947"/>
+  <dimension ref="A1:E1950"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -58155,20 +58236,71 @@
       </c>
     </row>
     <row r="1947" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1947" s="65" t="s">
+      <c r="A1947" s="68" t="s">
         <v>8078</v>
       </c>
-      <c r="B1947" s="66" t="s">
+      <c r="B1947" s="69" t="s">
         <v>8079</v>
       </c>
-      <c r="C1947" s="67" t="s">
+      <c r="C1947" s="70" t="s">
         <v>8080</v>
       </c>
-      <c r="D1947" s="66" t="s">
+      <c r="D1947" s="69" t="s">
         <v>8081</v>
       </c>
-      <c r="E1947" s="66" t="s">
+      <c r="E1947" s="69" t="s">
         <v>8082</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1948" s="15" t="s">
+        <v>8083</v>
+      </c>
+      <c r="B1948" s="13" t="s">
+        <v>8084</v>
+      </c>
+      <c r="C1948" s="71" t="s">
+        <v>8085</v>
+      </c>
+      <c r="D1948" s="13" t="s">
+        <v>8086</v>
+      </c>
+      <c r="E1948" s="13" t="s">
+        <v>8087</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1949" s="15" t="s">
+        <v>8088</v>
+      </c>
+      <c r="B1949" s="13" t="s">
+        <v>8089</v>
+      </c>
+      <c r="C1949" s="71" t="s">
+        <v>8090</v>
+      </c>
+      <c r="D1949" s="13" t="s">
+        <v>8091</v>
+      </c>
+      <c r="E1949" s="13" t="s">
+        <v>8092</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1950" s="5" t="s">
+        <v>8093</v>
+      </c>
+      <c r="B1950" s="8" t="s">
+        <v>8094</v>
+      </c>
+      <c r="C1950" s="72" t="s">
+        <v>8095</v>
+      </c>
+      <c r="D1950" s="8" t="s">
+        <v>8096</v>
+      </c>
+      <c r="E1950" s="8" t="s">
+        <v>8097</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{824AF896-D89A-47F3-B1CE-5836BEB59E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9E02E2-BB79-46DC-9914-0BFA0BBC6635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2565" yWindow="2415" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8112" uniqueCount="8098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8232" uniqueCount="8218">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -24330,18 +24330,386 @@
   </si>
   <si>
     <t>40.997284, 71.966361</t>
+  </si>
+  <si>
+    <t>Piskent, Amir Temur ko'chasi, 203 uy : г. Пскент, улица Эмира Тимура, 203 дом</t>
+  </si>
+  <si>
+    <t>FrПСК-6</t>
+  </si>
+  <si>
+    <t>998 94 865 75 50</t>
+  </si>
+  <si>
+    <t>@FrPSK6</t>
+  </si>
+  <si>
+    <t>40.909584, 69.358828</t>
+  </si>
+  <si>
+    <t>Yangibozor sh., Yuqorichirchiq tumani, Shodon koʻchasi, 30 uy : г. Янгибазар, Юкори Чирчикский район, улица Шодон, дом 30</t>
+  </si>
+  <si>
+    <t>FrЯНБ-3</t>
+  </si>
+  <si>
+    <t>998 70 188 87 63</t>
+  </si>
+  <si>
+    <t>@FrYNB_3</t>
+  </si>
+  <si>
+    <t>41.318180, 69.520140</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Shayxontohur tumani, Labzak koʻchasi, 119 uy : г. Ташкент, Шайхантахурский район, улица Лабзак, дом 119</t>
+  </si>
+  <si>
+    <t>FrТАШ-435</t>
+  </si>
+  <si>
+    <t>998 90 038 57 51</t>
+  </si>
+  <si>
+    <t>@FrTash435</t>
+  </si>
+  <si>
+    <t>41.336887, 69.266286</t>
+  </si>
+  <si>
+    <t>Paxtaobod sh., Sardoba tumani, Fazilobod koʻchasi, 47 uy : г. Пахтаабад, Сардабинский район, улица Фазилобод, дом 47</t>
+  </si>
+  <si>
+    <t>FrПАХ-2</t>
+  </si>
+  <si>
+    <t>998 77 707 03 88</t>
+  </si>
+  <si>
+    <t>@UzumFrPAX1</t>
+  </si>
+  <si>
+    <t>40.341229, 68.182255</t>
+  </si>
+  <si>
+    <t>Akkum sh., Gurlan tumani, Mustaqillik ko'chasi, 202 uy: г. Аккум, Гурленский район, улица Мустакиллик, дом 202</t>
+  </si>
+  <si>
+    <t>FrАКУ-1</t>
+  </si>
+  <si>
+    <t>998 93 073 61 93</t>
+  </si>
+  <si>
+    <t>@FrAKU_1</t>
+  </si>
+  <si>
+    <t>41.936795, 60.382615</t>
+  </si>
+  <si>
+    <t>Muborak sh., 4 a mitti tuman dahasi, 57 uy: г. Мубарек, микрорайон 4 а, дом 57</t>
+  </si>
+  <si>
+    <t>FrМУБ-5</t>
+  </si>
+  <si>
+    <t>998 77 064 70 84</t>
+  </si>
+  <si>
+    <t>@FrMUB5</t>
+  </si>
+  <si>
+    <t>39.264267, 65.156624</t>
+  </si>
+  <si>
+    <t>To'rarik sh., Torariq qishlog'i, 15 uy : г. Торарик, село Торарик, дом 15</t>
+  </si>
+  <si>
+    <t>FrТОР-1</t>
+  </si>
+  <si>
+    <t>998 93 238 65 01</t>
+  </si>
+  <si>
+    <t>@FrTOR_1</t>
+  </si>
+  <si>
+    <t>39.692808, 66.723948</t>
+  </si>
+  <si>
+    <t>Samarqand sh., Ato Safoev ko'chasi, 1 uy : г. Самарканд, улица Ато Сафоева, дом 1</t>
+  </si>
+  <si>
+    <t>FrСМК-85</t>
+  </si>
+  <si>
+    <t>998 50 118 90 34</t>
+  </si>
+  <si>
+    <t>@FrSMK_85</t>
+  </si>
+  <si>
+    <t>39.634916, 66.971840</t>
+  </si>
+  <si>
+    <t>Urgutsh sh.,Yukori Tegana ko'chasi, 241B uy: г. Ургут, улица Юкори Тегана, дом 241B</t>
+  </si>
+  <si>
+    <t>FrУГТ-4</t>
+  </si>
+  <si>
+    <t>998 88 199 55 06</t>
+  </si>
+  <si>
+    <t>@Frugt4</t>
+  </si>
+  <si>
+    <t>39.463404, 67.238767</t>
+  </si>
+  <si>
+    <t>Bogdan sh., Forish tumani, Bog'iboston ko'chasi, 21 uy : г. Багдан, Фаришский район, улица Богибустон, дом 21</t>
+  </si>
+  <si>
+    <t>FrБГД-2</t>
+  </si>
+  <si>
+    <t>998 20 028 06 80</t>
+  </si>
+  <si>
+    <t>@FrBGD_2</t>
+  </si>
+  <si>
+    <t>40.420728, 67.174773</t>
+  </si>
+  <si>
+    <t>Xitoytepa sh., Yugorichirchiq tumani, Chashma ko‘chasi, 19 uy : г. Китайтепа, Юкарычирчикский район, улица Чашма, дом 19</t>
+  </si>
+  <si>
+    <t>FrКТП-1</t>
+  </si>
+  <si>
+    <t>998 70 188 87 30</t>
+  </si>
+  <si>
+    <t>@FrKTP1</t>
+  </si>
+  <si>
+    <t>41.321265, 69.475927</t>
+  </si>
+  <si>
+    <t>Andijon sh., Behbudiy koʻchasi, 251 uy : г. Андижан, улица Бехбудий, дом 251</t>
+  </si>
+  <si>
+    <t>FrАНД-39</t>
+  </si>
+  <si>
+    <t>998 91 600 05 20</t>
+  </si>
+  <si>
+    <t>@frand_39</t>
+  </si>
+  <si>
+    <t>40.729731, 72.331849</t>
+  </si>
+  <si>
+    <t>Oltiariq sh., Oltiariq tumani, Do‘stlik ko'chasi, 90 uy: г. Алтиарик, Олтиарикский район, улица Дустлик, дом 90</t>
+  </si>
+  <si>
+    <t>FrАЛК-5</t>
+  </si>
+  <si>
+    <t>998 50 477 45 63</t>
+  </si>
+  <si>
+    <t>@Fr_Alk5</t>
+  </si>
+  <si>
+    <t>40.374068, 71.501182</t>
+  </si>
+  <si>
+    <t>To‘qimachilik sh., Zangiota tumani, I. Shomuratov ko‘chasi, 74 uy : г. Тукимачи, Зангиатинский район, улица И. Шомуратова, дом 74</t>
+  </si>
+  <si>
+    <t>FrТМЧ-1</t>
+  </si>
+  <si>
+    <t>998 93 359 12 90</t>
+  </si>
+  <si>
+    <t>@FrTmch1</t>
+  </si>
+  <si>
+    <t>41.278784, 69.066482</t>
+  </si>
+  <si>
+    <t>Quva sh., Istiqlol ko'chasi, 32 uy : г. Кува, улица Истиклол, дом 32</t>
+  </si>
+  <si>
+    <t>FrКВА-6</t>
+  </si>
+  <si>
+    <t>998 77 079 11 01</t>
+  </si>
+  <si>
+    <t>@FrKVA_6</t>
+  </si>
+  <si>
+    <t>40.561173, 72.075538</t>
+  </si>
+  <si>
+    <t>Shahrisabz sh., Charog'on ko'chasi, 61 uy : г. Шахрисабз, улица Чарогон, дом 61</t>
+  </si>
+  <si>
+    <t>FrШРЗ-12</t>
+  </si>
+  <si>
+    <t>998 77 788 05 07</t>
+  </si>
+  <si>
+    <t>@Fr_SHRZ_12</t>
+  </si>
+  <si>
+    <t>39.039896, 66.854433</t>
+  </si>
+  <si>
+    <t>Ittifoq sh., Toshkent viloyati, Yangiyo'l tumani, Iftixor ko'chasi, 69a uy : г. Иттифок, Ташкентская область, Янгиюльский район, улица Ифтихор, дом 69а</t>
+  </si>
+  <si>
+    <t>FrИТФ-1</t>
+  </si>
+  <si>
+    <t>998 94 595 38 10</t>
+  </si>
+  <si>
+    <t>@Fritf_1</t>
+  </si>
+  <si>
+    <t>41.107614, 68.924235</t>
+  </si>
+  <si>
+    <t>Telov sh., Ma'rifat ko'chasi, 79 uy : г. Телов, улица Маърифат, дом 79</t>
+  </si>
+  <si>
+    <t>FrТЛВ-1</t>
+  </si>
+  <si>
+    <t>998 20 005 11 19</t>
+  </si>
+  <si>
+    <t>@FrTLV1</t>
+  </si>
+  <si>
+    <t>40.880509, 69.811633</t>
+  </si>
+  <si>
+    <t>G‘azalkent sh., Konchilar koʻchasi, 2 uy : г. Газалкент, улица Кончилар, дом 2</t>
+  </si>
+  <si>
+    <t>FrГАЗ-7</t>
+  </si>
+  <si>
+    <t>998 50 987 08 27</t>
+  </si>
+  <si>
+    <t>@FrGaz_7</t>
+  </si>
+  <si>
+    <t>41.553191, 69.762363</t>
+  </si>
+  <si>
+    <t>Toshloq sh., Qiyichirchiq tumani, Gulbaxor ko'chasi, 9a uy : г. Ташлак Куйичирчикский район, улица Гульбахор, 9а дом</t>
+  </si>
+  <si>
+    <t>FrТШЛ-1</t>
+  </si>
+  <si>
+    <t>998 20 021 80 25</t>
+  </si>
+  <si>
+    <t>@UzumFrTSHL_11</t>
+  </si>
+  <si>
+    <t>41.129665, 69.196630</t>
+  </si>
+  <si>
+    <t>Karmana sh., Argun MFY, Alisher Navoiy ko'chasi, 65 uy : г. Кармана, МФИ Аргун, улица Алишера Навои, дом 65</t>
+  </si>
+  <si>
+    <t>FrКРМ-9</t>
+  </si>
+  <si>
+    <t>998 99 718 20 26</t>
+  </si>
+  <si>
+    <t>@Frkpm9</t>
+  </si>
+  <si>
+    <t>40.127600, 65.352000</t>
+  </si>
+  <si>
+    <t>Gulobod sh., Yuqorichirchiq tumani, Parvoz koʻchasi, 10 uy : г. Гулобод, Юкарычирчикский район, улица Парваз, дом 10</t>
+  </si>
+  <si>
+    <t>FrГЛБ-1</t>
+  </si>
+  <si>
+    <t>998 90 823 73 44</t>
+  </si>
+  <si>
+    <t>@frGLB_1</t>
+  </si>
+  <si>
+    <t>41.323537, 69.491878</t>
+  </si>
+  <si>
+    <t>Bogot sh., Yosh o'smir MFY, Iftixor ko'chasi, 74A uy : г. Багат, МФИ Ёш Усмир, улица Ифтихор, дом 74А</t>
+  </si>
+  <si>
+    <t>FrБГТ-7</t>
+  </si>
+  <si>
+    <t>998 77 734 35 84</t>
+  </si>
+  <si>
+    <t>@FrBGT_7</t>
+  </si>
+  <si>
+    <t>41.366129, 60.917189</t>
+  </si>
+  <si>
+    <t>Xovos sh., Xovos tumani, Tumaqshina koʻchasi, 1 uy : г. Хаваст, Хавастский район, улица Тумакшина, дом 1</t>
+  </si>
+  <si>
+    <t>FrХАВ-6</t>
+  </si>
+  <si>
+    <t>998 50 119 04 14</t>
+  </si>
+  <si>
+    <t>@FrXAB_6</t>
+  </si>
+  <si>
+    <t>40.234233, 68.840763</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -24624,57 +24992,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24683,7 +25060,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24692,16 +25069,19 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24710,16 +25090,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24728,13 +25102,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24743,40 +25120,37 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24812,31 +25186,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25146,7 +25517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1950"/>
+  <dimension ref="A1:E1974"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -58287,20 +58658,428 @@
       </c>
     </row>
     <row r="1950" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1950" s="5" t="s">
+      <c r="A1950" s="10" t="s">
         <v>8093</v>
       </c>
-      <c r="B1950" s="8" t="s">
+      <c r="B1950" s="11" t="s">
         <v>8094</v>
       </c>
       <c r="C1950" s="72" t="s">
         <v>8095</v>
       </c>
-      <c r="D1950" s="8" t="s">
+      <c r="D1950" s="11" t="s">
         <v>8096</v>
       </c>
-      <c r="E1950" s="8" t="s">
+      <c r="E1950" s="11" t="s">
         <v>8097</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1951" s="5" t="s">
+        <v>8098</v>
+      </c>
+      <c r="B1951" s="13" t="s">
+        <v>8099</v>
+      </c>
+      <c r="C1951" s="73" t="s">
+        <v>8100</v>
+      </c>
+      <c r="D1951" s="8" t="s">
+        <v>8101</v>
+      </c>
+      <c r="E1951" s="8" t="s">
+        <v>8102</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1952" s="5" t="s">
+        <v>8103</v>
+      </c>
+      <c r="B1952" s="13" t="s">
+        <v>8104</v>
+      </c>
+      <c r="C1952" s="73" t="s">
+        <v>8105</v>
+      </c>
+      <c r="D1952" s="8" t="s">
+        <v>8106</v>
+      </c>
+      <c r="E1952" s="8" t="s">
+        <v>8107</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1953" s="5" t="s">
+        <v>8108</v>
+      </c>
+      <c r="B1953" s="13" t="s">
+        <v>8109</v>
+      </c>
+      <c r="C1953" s="73" t="s">
+        <v>8110</v>
+      </c>
+      <c r="D1953" s="8" t="s">
+        <v>8111</v>
+      </c>
+      <c r="E1953" s="8" t="s">
+        <v>8112</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1954" s="5" t="s">
+        <v>8113</v>
+      </c>
+      <c r="B1954" s="13" t="s">
+        <v>8114</v>
+      </c>
+      <c r="C1954" s="73" t="s">
+        <v>8115</v>
+      </c>
+      <c r="D1954" s="8" t="s">
+        <v>8116</v>
+      </c>
+      <c r="E1954" s="8" t="s">
+        <v>8117</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1955" s="5" t="s">
+        <v>8118</v>
+      </c>
+      <c r="B1955" s="13" t="s">
+        <v>8119</v>
+      </c>
+      <c r="C1955" s="73" t="s">
+        <v>8120</v>
+      </c>
+      <c r="D1955" s="8" t="s">
+        <v>8121</v>
+      </c>
+      <c r="E1955" s="8" t="s">
+        <v>8122</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1956" s="5" t="s">
+        <v>8123</v>
+      </c>
+      <c r="B1956" s="13" t="s">
+        <v>8124</v>
+      </c>
+      <c r="C1956" s="73" t="s">
+        <v>8125</v>
+      </c>
+      <c r="D1956" s="8" t="s">
+        <v>8126</v>
+      </c>
+      <c r="E1956" s="8" t="s">
+        <v>8127</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1957" s="5" t="s">
+        <v>8128</v>
+      </c>
+      <c r="B1957" s="13" t="s">
+        <v>8129</v>
+      </c>
+      <c r="C1957" s="73" t="s">
+        <v>8130</v>
+      </c>
+      <c r="D1957" s="8" t="s">
+        <v>8131</v>
+      </c>
+      <c r="E1957" s="8" t="s">
+        <v>8132</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1958" s="5" t="s">
+        <v>8133</v>
+      </c>
+      <c r="B1958" s="13" t="s">
+        <v>8134</v>
+      </c>
+      <c r="C1958" s="73" t="s">
+        <v>8135</v>
+      </c>
+      <c r="D1958" s="8" t="s">
+        <v>8136</v>
+      </c>
+      <c r="E1958" s="8" t="s">
+        <v>8137</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1959" s="5" t="s">
+        <v>8138</v>
+      </c>
+      <c r="B1959" s="13" t="s">
+        <v>8139</v>
+      </c>
+      <c r="C1959" s="73" t="s">
+        <v>8140</v>
+      </c>
+      <c r="D1959" s="8" t="s">
+        <v>8141</v>
+      </c>
+      <c r="E1959" s="8" t="s">
+        <v>8142</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1960" s="5" t="s">
+        <v>8143</v>
+      </c>
+      <c r="B1960" s="13" t="s">
+        <v>8144</v>
+      </c>
+      <c r="C1960" s="73" t="s">
+        <v>8145</v>
+      </c>
+      <c r="D1960" s="8" t="s">
+        <v>8146</v>
+      </c>
+      <c r="E1960" s="8" t="s">
+        <v>8147</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1961" s="5" t="s">
+        <v>8148</v>
+      </c>
+      <c r="B1961" s="13" t="s">
+        <v>8149</v>
+      </c>
+      <c r="C1961" s="73" t="s">
+        <v>8150</v>
+      </c>
+      <c r="D1961" s="8" t="s">
+        <v>8151</v>
+      </c>
+      <c r="E1961" s="8" t="s">
+        <v>8152</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1962" s="5" t="s">
+        <v>8153</v>
+      </c>
+      <c r="B1962" s="13" t="s">
+        <v>8154</v>
+      </c>
+      <c r="C1962" s="73" t="s">
+        <v>8155</v>
+      </c>
+      <c r="D1962" s="8" t="s">
+        <v>8156</v>
+      </c>
+      <c r="E1962" s="8" t="s">
+        <v>8157</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1963" s="5" t="s">
+        <v>8158</v>
+      </c>
+      <c r="B1963" s="13" t="s">
+        <v>8159</v>
+      </c>
+      <c r="C1963" s="73" t="s">
+        <v>8160</v>
+      </c>
+      <c r="D1963" s="8" t="s">
+        <v>8161</v>
+      </c>
+      <c r="E1963" s="8" t="s">
+        <v>8162</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1964" s="5" t="s">
+        <v>8163</v>
+      </c>
+      <c r="B1964" s="13" t="s">
+        <v>8164</v>
+      </c>
+      <c r="C1964" s="73" t="s">
+        <v>8165</v>
+      </c>
+      <c r="D1964" s="8" t="s">
+        <v>8166</v>
+      </c>
+      <c r="E1964" s="8" t="s">
+        <v>8167</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1965" s="5" t="s">
+        <v>8168</v>
+      </c>
+      <c r="B1965" s="13" t="s">
+        <v>8169</v>
+      </c>
+      <c r="C1965" s="73" t="s">
+        <v>8170</v>
+      </c>
+      <c r="D1965" s="8" t="s">
+        <v>8171</v>
+      </c>
+      <c r="E1965" s="8" t="s">
+        <v>8172</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1966" s="5" t="s">
+        <v>8173</v>
+      </c>
+      <c r="B1966" s="13" t="s">
+        <v>8174</v>
+      </c>
+      <c r="C1966" s="73" t="s">
+        <v>8175</v>
+      </c>
+      <c r="D1966" s="8" t="s">
+        <v>8176</v>
+      </c>
+      <c r="E1966" s="8" t="s">
+        <v>8177</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:5" ht="39" x14ac:dyDescent="0.25">
+      <c r="A1967" s="5" t="s">
+        <v>8178</v>
+      </c>
+      <c r="B1967" s="13" t="s">
+        <v>8179</v>
+      </c>
+      <c r="C1967" s="73" t="s">
+        <v>8180</v>
+      </c>
+      <c r="D1967" s="8" t="s">
+        <v>8181</v>
+      </c>
+      <c r="E1967" s="8" t="s">
+        <v>8182</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1968" s="5" t="s">
+        <v>8183</v>
+      </c>
+      <c r="B1968" s="13" t="s">
+        <v>8184</v>
+      </c>
+      <c r="C1968" s="73" t="s">
+        <v>8185</v>
+      </c>
+      <c r="D1968" s="8" t="s">
+        <v>8186</v>
+      </c>
+      <c r="E1968" s="8" t="s">
+        <v>8187</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1969" s="5" t="s">
+        <v>8188</v>
+      </c>
+      <c r="B1969" s="13" t="s">
+        <v>8189</v>
+      </c>
+      <c r="C1969" s="73" t="s">
+        <v>8190</v>
+      </c>
+      <c r="D1969" s="8" t="s">
+        <v>8191</v>
+      </c>
+      <c r="E1969" s="8" t="s">
+        <v>8192</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1970" s="5" t="s">
+        <v>8193</v>
+      </c>
+      <c r="B1970" s="13" t="s">
+        <v>8194</v>
+      </c>
+      <c r="C1970" s="73" t="s">
+        <v>8195</v>
+      </c>
+      <c r="D1970" s="8" t="s">
+        <v>8196</v>
+      </c>
+      <c r="E1970" s="8" t="s">
+        <v>8197</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1971" s="5" t="s">
+        <v>8198</v>
+      </c>
+      <c r="B1971" s="13" t="s">
+        <v>8199</v>
+      </c>
+      <c r="C1971" s="73" t="s">
+        <v>8200</v>
+      </c>
+      <c r="D1971" s="8" t="s">
+        <v>8201</v>
+      </c>
+      <c r="E1971" s="8" t="s">
+        <v>8202</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1972" s="5" t="s">
+        <v>8203</v>
+      </c>
+      <c r="B1972" s="13" t="s">
+        <v>8204</v>
+      </c>
+      <c r="C1972" s="73" t="s">
+        <v>8205</v>
+      </c>
+      <c r="D1972" s="8" t="s">
+        <v>8206</v>
+      </c>
+      <c r="E1972" s="8" t="s">
+        <v>8207</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1973" s="5" t="s">
+        <v>8208</v>
+      </c>
+      <c r="B1973" s="13" t="s">
+        <v>8209</v>
+      </c>
+      <c r="C1973" s="73" t="s">
+        <v>8210</v>
+      </c>
+      <c r="D1973" s="8" t="s">
+        <v>8211</v>
+      </c>
+      <c r="E1973" s="8" t="s">
+        <v>8212</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1974" s="5" t="s">
+        <v>8213</v>
+      </c>
+      <c r="B1974" s="13" t="s">
+        <v>8214</v>
+      </c>
+      <c r="C1974" s="73" t="s">
+        <v>8215</v>
+      </c>
+      <c r="D1974" s="8" t="s">
+        <v>8216</v>
+      </c>
+      <c r="E1974" s="8" t="s">
+        <v>8217</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9E02E2-BB79-46DC-9914-0BFA0BBC6635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68524A5-8659-426F-B4A9-05D74FEFB485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2565" yWindow="2415" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="2505" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22550,9 +22550,6 @@
     <t>@fr_tbl_1</t>
   </si>
   <si>
-    <t>39.927359, 66.899398</t>
-  </si>
-  <si>
     <t>Koʻkmuyin sh., Oʻrtachirchiq tumani, Temirchi ko‘chasi, 90A uy : г. Кукмуйин, Уртачирчикский район, улица Темирчи, дом 90А</t>
   </si>
   <si>
@@ -24254,9 +24251,6 @@
     <t>@frkrl_1</t>
   </si>
   <si>
-    <t>39.101702, 65.334704</t>
-  </si>
-  <si>
     <t>Beruniy sh., Qiyichirchiq tumani, Sharof Rashidov koʻchasi, 38 uy : г. Беруни, Куйичирчикский район, улица Шарофа Рашидова, дом 38</t>
   </si>
   <si>
@@ -24690,6 +24684,12 @@
   </si>
   <si>
     <t>40.234233, 68.840763</t>
+  </si>
+  <si>
+    <t>39.089234, 65.368674</t>
+  </si>
+  <si>
+    <t>39.927109, 66.895948</t>
   </si>
 </sst>
 </file>
@@ -55236,7 +55236,7 @@
         <v>7092</v>
       </c>
       <c r="D1748" s="8" t="s">
-        <v>7515</v>
+        <v>7514</v>
       </c>
       <c r="E1748" s="8" t="s">
         <v>7093</v>
@@ -56650,2436 +56650,2436 @@
         <v>7503</v>
       </c>
       <c r="E1831" s="8" t="s">
-        <v>7504</v>
+        <v>8217</v>
       </c>
     </row>
     <row r="1832" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1832" s="10" t="s">
+        <v>7504</v>
+      </c>
+      <c r="B1832" s="20" t="s">
         <v>7505</v>
       </c>
-      <c r="B1832" s="20" t="s">
+      <c r="C1832" s="49" t="s">
         <v>7506</v>
       </c>
-      <c r="C1832" s="49" t="s">
+      <c r="D1832" s="11" t="s">
         <v>7507</v>
       </c>
-      <c r="D1832" s="11" t="s">
+      <c r="E1832" s="11" t="s">
         <v>7508</v>
-      </c>
-      <c r="E1832" s="11" t="s">
-        <v>7509</v>
       </c>
     </row>
     <row r="1833" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1833" s="5" t="s">
+        <v>7509</v>
+      </c>
+      <c r="B1833" s="13" t="s">
         <v>7510</v>
       </c>
-      <c r="B1833" s="13" t="s">
+      <c r="C1833" s="50" t="s">
         <v>7511</v>
       </c>
-      <c r="C1833" s="50" t="s">
+      <c r="D1833" s="8" t="s">
         <v>7512</v>
       </c>
-      <c r="D1833" s="8" t="s">
+      <c r="E1833" s="8" t="s">
         <v>7513</v>
-      </c>
-      <c r="E1833" s="8" t="s">
-        <v>7514</v>
       </c>
     </row>
     <row r="1834" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1834" s="5" t="s">
+        <v>7515</v>
+      </c>
+      <c r="B1834" s="13" t="s">
         <v>7516</v>
       </c>
-      <c r="B1834" s="13" t="s">
+      <c r="C1834" s="50" t="s">
         <v>7517</v>
       </c>
-      <c r="C1834" s="50" t="s">
+      <c r="D1834" s="8" t="s">
         <v>7518</v>
       </c>
-      <c r="D1834" s="8" t="s">
+      <c r="E1834" s="8" t="s">
         <v>7519</v>
-      </c>
-      <c r="E1834" s="8" t="s">
-        <v>7520</v>
       </c>
     </row>
     <row r="1835" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1835" s="15" t="s">
+        <v>7520</v>
+      </c>
+      <c r="B1835" s="13" t="s">
         <v>7521</v>
       </c>
-      <c r="B1835" s="13" t="s">
+      <c r="C1835" s="51" t="s">
         <v>7522</v>
       </c>
-      <c r="C1835" s="51" t="s">
+      <c r="D1835" s="13" t="s">
         <v>7523</v>
       </c>
-      <c r="D1835" s="13" t="s">
+      <c r="E1835" s="13" t="s">
         <v>7524</v>
-      </c>
-      <c r="E1835" s="13" t="s">
-        <v>7525</v>
       </c>
     </row>
     <row r="1836" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1836" s="5" t="s">
+        <v>7525</v>
+      </c>
+      <c r="B1836" s="13" t="s">
         <v>7526</v>
       </c>
-      <c r="B1836" s="13" t="s">
+      <c r="C1836" s="50" t="s">
         <v>7527</v>
       </c>
-      <c r="C1836" s="50" t="s">
+      <c r="D1836" s="8" t="s">
         <v>7528</v>
       </c>
-      <c r="D1836" s="8" t="s">
+      <c r="E1836" s="8" t="s">
         <v>7529</v>
-      </c>
-      <c r="E1836" s="8" t="s">
-        <v>7530</v>
       </c>
     </row>
     <row r="1837" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1837" s="5" t="s">
+        <v>7530</v>
+      </c>
+      <c r="B1837" s="13" t="s">
         <v>7531</v>
       </c>
-      <c r="B1837" s="13" t="s">
+      <c r="C1837" s="50" t="s">
         <v>7532</v>
       </c>
-      <c r="C1837" s="50" t="s">
+      <c r="D1837" s="8" t="s">
         <v>7533</v>
       </c>
-      <c r="D1837" s="8" t="s">
+      <c r="E1837" s="8" t="s">
         <v>7534</v>
-      </c>
-      <c r="E1837" s="8" t="s">
-        <v>7535</v>
       </c>
     </row>
     <row r="1838" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1838" s="5" t="s">
+        <v>7535</v>
+      </c>
+      <c r="B1838" s="13" t="s">
         <v>7536</v>
       </c>
-      <c r="B1838" s="13" t="s">
+      <c r="C1838" s="50" t="s">
         <v>7537</v>
       </c>
-      <c r="C1838" s="50" t="s">
+      <c r="D1838" s="8" t="s">
         <v>7538</v>
       </c>
-      <c r="D1838" s="8" t="s">
+      <c r="E1838" s="8" t="s">
         <v>7539</v>
-      </c>
-      <c r="E1838" s="8" t="s">
-        <v>7540</v>
       </c>
     </row>
     <row r="1839" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1839" s="10" t="s">
+        <v>7540</v>
+      </c>
+      <c r="B1839" s="17" t="s">
         <v>7541</v>
       </c>
-      <c r="B1839" s="17" t="s">
+      <c r="C1839" s="52" t="s">
         <v>7542</v>
       </c>
-      <c r="C1839" s="52" t="s">
+      <c r="D1839" s="11" t="s">
         <v>7543</v>
       </c>
-      <c r="D1839" s="11" t="s">
+      <c r="E1839" s="11" t="s">
         <v>7544</v>
-      </c>
-      <c r="E1839" s="11" t="s">
-        <v>7545</v>
       </c>
     </row>
     <row r="1840" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1840" s="5" t="s">
+        <v>7545</v>
+      </c>
+      <c r="B1840" s="13" t="s">
         <v>7546</v>
       </c>
-      <c r="B1840" s="13" t="s">
+      <c r="C1840" s="53" t="s">
         <v>7547</v>
       </c>
-      <c r="C1840" s="53" t="s">
+      <c r="D1840" s="8" t="s">
         <v>7548</v>
       </c>
-      <c r="D1840" s="8" t="s">
+      <c r="E1840" s="8" t="s">
         <v>7549</v>
-      </c>
-      <c r="E1840" s="8" t="s">
-        <v>7550</v>
       </c>
     </row>
     <row r="1841" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1841" s="5" t="s">
+        <v>7550</v>
+      </c>
+      <c r="B1841" s="13" t="s">
         <v>7551</v>
       </c>
-      <c r="B1841" s="13" t="s">
+      <c r="C1841" s="53" t="s">
         <v>7552</v>
       </c>
-      <c r="C1841" s="53" t="s">
+      <c r="D1841" s="8" t="s">
         <v>7553</v>
       </c>
-      <c r="D1841" s="8" t="s">
+      <c r="E1841" s="8" t="s">
         <v>7554</v>
-      </c>
-      <c r="E1841" s="8" t="s">
-        <v>7555</v>
       </c>
     </row>
     <row r="1842" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1842" s="5" t="s">
+        <v>7555</v>
+      </c>
+      <c r="B1842" s="13" t="s">
         <v>7556</v>
       </c>
-      <c r="B1842" s="13" t="s">
+      <c r="C1842" s="53" t="s">
         <v>7557</v>
       </c>
-      <c r="C1842" s="53" t="s">
+      <c r="D1842" s="8" t="s">
         <v>7558</v>
       </c>
-      <c r="D1842" s="8" t="s">
+      <c r="E1842" s="8" t="s">
         <v>7559</v>
-      </c>
-      <c r="E1842" s="8" t="s">
-        <v>7560</v>
       </c>
     </row>
     <row r="1843" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1843" s="5" t="s">
+        <v>7560</v>
+      </c>
+      <c r="B1843" s="13" t="s">
         <v>7561</v>
       </c>
-      <c r="B1843" s="13" t="s">
+      <c r="C1843" s="53" t="s">
         <v>7562</v>
       </c>
-      <c r="C1843" s="53" t="s">
+      <c r="D1843" s="8" t="s">
         <v>7563</v>
       </c>
-      <c r="D1843" s="8" t="s">
+      <c r="E1843" s="8" t="s">
         <v>7564</v>
-      </c>
-      <c r="E1843" s="8" t="s">
-        <v>7565</v>
       </c>
     </row>
     <row r="1844" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1844" s="5" t="s">
+        <v>7565</v>
+      </c>
+      <c r="B1844" s="13" t="s">
         <v>7566</v>
       </c>
-      <c r="B1844" s="13" t="s">
+      <c r="C1844" s="53" t="s">
         <v>7567</v>
       </c>
-      <c r="C1844" s="53" t="s">
+      <c r="D1844" s="8" t="s">
         <v>7568</v>
       </c>
-      <c r="D1844" s="8" t="s">
+      <c r="E1844" s="8" t="s">
         <v>7569</v>
-      </c>
-      <c r="E1844" s="8" t="s">
-        <v>7570</v>
       </c>
     </row>
     <row r="1845" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1845" s="5" t="s">
+        <v>7570</v>
+      </c>
+      <c r="B1845" s="13" t="s">
         <v>7571</v>
       </c>
-      <c r="B1845" s="13" t="s">
+      <c r="C1845" s="53" t="s">
         <v>7572</v>
       </c>
-      <c r="C1845" s="53" t="s">
+      <c r="D1845" s="8" t="s">
         <v>7573</v>
       </c>
-      <c r="D1845" s="8" t="s">
+      <c r="E1845" s="8" t="s">
         <v>7574</v>
-      </c>
-      <c r="E1845" s="8" t="s">
-        <v>7575</v>
       </c>
     </row>
     <row r="1846" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1846" s="5" t="s">
+        <v>7575</v>
+      </c>
+      <c r="B1846" s="13" t="s">
         <v>7576</v>
       </c>
-      <c r="B1846" s="13" t="s">
+      <c r="C1846" s="53" t="s">
         <v>7577</v>
       </c>
-      <c r="C1846" s="53" t="s">
+      <c r="D1846" s="8" t="s">
         <v>7578</v>
       </c>
-      <c r="D1846" s="8" t="s">
+      <c r="E1846" s="8" t="s">
         <v>7579</v>
-      </c>
-      <c r="E1846" s="8" t="s">
-        <v>7580</v>
       </c>
     </row>
     <row r="1847" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1847" s="5" t="s">
+        <v>7580</v>
+      </c>
+      <c r="B1847" s="13" t="s">
         <v>7581</v>
       </c>
-      <c r="B1847" s="13" t="s">
+      <c r="C1847" s="53" t="s">
         <v>7582</v>
       </c>
-      <c r="C1847" s="53" t="s">
+      <c r="D1847" s="8" t="s">
         <v>7583</v>
       </c>
-      <c r="D1847" s="8" t="s">
+      <c r="E1847" s="8" t="s">
         <v>7584</v>
-      </c>
-      <c r="E1847" s="8" t="s">
-        <v>7585</v>
       </c>
     </row>
     <row r="1848" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1848" s="5" t="s">
+        <v>7585</v>
+      </c>
+      <c r="B1848" s="13" t="s">
         <v>7586</v>
       </c>
-      <c r="B1848" s="13" t="s">
+      <c r="C1848" s="53" t="s">
         <v>7587</v>
       </c>
-      <c r="C1848" s="53" t="s">
+      <c r="D1848" s="8" t="s">
         <v>7588</v>
       </c>
-      <c r="D1848" s="8" t="s">
+      <c r="E1848" s="8" t="s">
         <v>7589</v>
-      </c>
-      <c r="E1848" s="8" t="s">
-        <v>7590</v>
       </c>
     </row>
     <row r="1849" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1849" s="5" t="s">
+        <v>7590</v>
+      </c>
+      <c r="B1849" s="13" t="s">
         <v>7591</v>
       </c>
-      <c r="B1849" s="13" t="s">
+      <c r="C1849" s="53" t="s">
         <v>7592</v>
       </c>
-      <c r="C1849" s="53" t="s">
+      <c r="D1849" s="8" t="s">
         <v>7593</v>
       </c>
-      <c r="D1849" s="8" t="s">
+      <c r="E1849" s="8" t="s">
         <v>7594</v>
-      </c>
-      <c r="E1849" s="8" t="s">
-        <v>7595</v>
       </c>
     </row>
     <row r="1850" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1850" s="5" t="s">
+        <v>7595</v>
+      </c>
+      <c r="B1850" s="13" t="s">
         <v>7596</v>
       </c>
-      <c r="B1850" s="13" t="s">
+      <c r="C1850" s="53" t="s">
         <v>7597</v>
       </c>
-      <c r="C1850" s="53" t="s">
+      <c r="D1850" s="8" t="s">
         <v>7598</v>
       </c>
-      <c r="D1850" s="8" t="s">
+      <c r="E1850" s="8" t="s">
         <v>7599</v>
-      </c>
-      <c r="E1850" s="8" t="s">
-        <v>7600</v>
       </c>
     </row>
     <row r="1851" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1851" s="5" t="s">
+        <v>7600</v>
+      </c>
+      <c r="B1851" s="13" t="s">
         <v>7601</v>
       </c>
-      <c r="B1851" s="13" t="s">
+      <c r="C1851" s="53" t="s">
         <v>7602</v>
       </c>
-      <c r="C1851" s="53" t="s">
+      <c r="D1851" s="8" t="s">
         <v>7603</v>
       </c>
-      <c r="D1851" s="8" t="s">
+      <c r="E1851" s="8" t="s">
         <v>7604</v>
-      </c>
-      <c r="E1851" s="8" t="s">
-        <v>7605</v>
       </c>
     </row>
     <row r="1852" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1852" s="5" t="s">
+        <v>7605</v>
+      </c>
+      <c r="B1852" s="13" t="s">
         <v>7606</v>
       </c>
-      <c r="B1852" s="13" t="s">
+      <c r="C1852" s="53" t="s">
         <v>7607</v>
       </c>
-      <c r="C1852" s="53" t="s">
+      <c r="D1852" s="8" t="s">
         <v>7608</v>
       </c>
-      <c r="D1852" s="8" t="s">
+      <c r="E1852" s="8" t="s">
         <v>7609</v>
-      </c>
-      <c r="E1852" s="8" t="s">
-        <v>7610</v>
       </c>
     </row>
     <row r="1853" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1853" s="10" t="s">
+        <v>7610</v>
+      </c>
+      <c r="B1853" s="17" t="s">
         <v>7611</v>
       </c>
-      <c r="B1853" s="17" t="s">
+      <c r="C1853" s="54" t="s">
         <v>7612</v>
       </c>
-      <c r="C1853" s="54" t="s">
+      <c r="D1853" s="11" t="s">
         <v>7613</v>
       </c>
-      <c r="D1853" s="11" t="s">
+      <c r="E1853" s="11" t="s">
         <v>7614</v>
-      </c>
-      <c r="E1853" s="11" t="s">
-        <v>7615</v>
       </c>
     </row>
     <row r="1854" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1854" s="5" t="s">
+        <v>7615</v>
+      </c>
+      <c r="B1854" s="6" t="s">
         <v>7616</v>
       </c>
-      <c r="B1854" s="6" t="s">
+      <c r="C1854" s="55" t="s">
         <v>7617</v>
       </c>
-      <c r="C1854" s="55" t="s">
+      <c r="D1854" s="8" t="s">
         <v>7618</v>
       </c>
-      <c r="D1854" s="8" t="s">
+      <c r="E1854" s="8" t="s">
         <v>7619</v>
-      </c>
-      <c r="E1854" s="8" t="s">
-        <v>7620</v>
       </c>
     </row>
     <row r="1855" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1855" s="5" t="s">
+        <v>7620</v>
+      </c>
+      <c r="B1855" s="6" t="s">
         <v>7621</v>
       </c>
-      <c r="B1855" s="6" t="s">
+      <c r="C1855" s="55" t="s">
         <v>7622</v>
       </c>
-      <c r="C1855" s="55" t="s">
+      <c r="D1855" s="8" t="s">
         <v>7623</v>
       </c>
-      <c r="D1855" s="8" t="s">
+      <c r="E1855" s="8" t="s">
         <v>7624</v>
-      </c>
-      <c r="E1855" s="8" t="s">
-        <v>7625</v>
       </c>
     </row>
     <row r="1856" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1856" s="5" t="s">
+        <v>7625</v>
+      </c>
+      <c r="B1856" s="6" t="s">
         <v>7626</v>
       </c>
-      <c r="B1856" s="6" t="s">
+      <c r="C1856" s="55" t="s">
         <v>7627</v>
       </c>
-      <c r="C1856" s="55" t="s">
+      <c r="D1856" s="8" t="s">
         <v>7628</v>
       </c>
-      <c r="D1856" s="8" t="s">
+      <c r="E1856" s="8" t="s">
         <v>7629</v>
-      </c>
-      <c r="E1856" s="8" t="s">
-        <v>7630</v>
       </c>
     </row>
     <row r="1857" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1857" s="5" t="s">
+        <v>7630</v>
+      </c>
+      <c r="B1857" s="6" t="s">
         <v>7631</v>
       </c>
-      <c r="B1857" s="6" t="s">
+      <c r="C1857" s="55" t="s">
         <v>7632</v>
       </c>
-      <c r="C1857" s="55" t="s">
+      <c r="D1857" s="8" t="s">
         <v>7633</v>
       </c>
-      <c r="D1857" s="8" t="s">
+      <c r="E1857" s="8" t="s">
         <v>7634</v>
-      </c>
-      <c r="E1857" s="8" t="s">
-        <v>7635</v>
       </c>
     </row>
     <row r="1858" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1858" s="5" t="s">
+        <v>7635</v>
+      </c>
+      <c r="B1858" s="6" t="s">
         <v>7636</v>
       </c>
-      <c r="B1858" s="6" t="s">
+      <c r="C1858" s="55" t="s">
         <v>7637</v>
       </c>
-      <c r="C1858" s="55" t="s">
+      <c r="D1858" s="8" t="s">
         <v>7638</v>
       </c>
-      <c r="D1858" s="8" t="s">
+      <c r="E1858" s="8" t="s">
         <v>7639</v>
-      </c>
-      <c r="E1858" s="8" t="s">
-        <v>7640</v>
       </c>
     </row>
     <row r="1859" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1859" s="5" t="s">
+        <v>7640</v>
+      </c>
+      <c r="B1859" s="6" t="s">
         <v>7641</v>
       </c>
-      <c r="B1859" s="6" t="s">
+      <c r="C1859" s="55" t="s">
         <v>7642</v>
       </c>
-      <c r="C1859" s="55" t="s">
+      <c r="D1859" s="8" t="s">
         <v>7643</v>
       </c>
-      <c r="D1859" s="8" t="s">
+      <c r="E1859" s="8" t="s">
         <v>7644</v>
-      </c>
-      <c r="E1859" s="8" t="s">
-        <v>7645</v>
       </c>
     </row>
     <row r="1860" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1860" s="5" t="s">
+        <v>7645</v>
+      </c>
+      <c r="B1860" s="6" t="s">
         <v>7646</v>
       </c>
-      <c r="B1860" s="6" t="s">
+      <c r="C1860" s="55" t="s">
         <v>7647</v>
       </c>
-      <c r="C1860" s="55" t="s">
+      <c r="D1860" s="8" t="s">
         <v>7648</v>
       </c>
-      <c r="D1860" s="8" t="s">
+      <c r="E1860" s="8" t="s">
         <v>7649</v>
-      </c>
-      <c r="E1860" s="8" t="s">
-        <v>7650</v>
       </c>
     </row>
     <row r="1861" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1861" s="5" t="s">
+        <v>7650</v>
+      </c>
+      <c r="B1861" s="6" t="s">
         <v>7651</v>
       </c>
-      <c r="B1861" s="6" t="s">
+      <c r="C1861" s="55" t="s">
         <v>7652</v>
       </c>
-      <c r="C1861" s="55" t="s">
+      <c r="D1861" s="8" t="s">
         <v>7653</v>
       </c>
-      <c r="D1861" s="8" t="s">
+      <c r="E1861" s="8" t="s">
         <v>7654</v>
-      </c>
-      <c r="E1861" s="8" t="s">
-        <v>7655</v>
       </c>
     </row>
     <row r="1862" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1862" s="5" t="s">
+        <v>7655</v>
+      </c>
+      <c r="B1862" s="6" t="s">
         <v>7656</v>
       </c>
-      <c r="B1862" s="6" t="s">
+      <c r="C1862" s="55" t="s">
         <v>7657</v>
       </c>
-      <c r="C1862" s="55" t="s">
+      <c r="D1862" s="8" t="s">
         <v>7658</v>
       </c>
-      <c r="D1862" s="8" t="s">
+      <c r="E1862" s="8" t="s">
         <v>7659</v>
-      </c>
-      <c r="E1862" s="8" t="s">
-        <v>7660</v>
       </c>
     </row>
     <row r="1863" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1863" s="5" t="s">
+        <v>7660</v>
+      </c>
+      <c r="B1863" s="6" t="s">
         <v>7661</v>
       </c>
-      <c r="B1863" s="6" t="s">
+      <c r="C1863" s="55" t="s">
         <v>7662</v>
       </c>
-      <c r="C1863" s="55" t="s">
+      <c r="D1863" s="8" t="s">
         <v>7663</v>
       </c>
-      <c r="D1863" s="8" t="s">
+      <c r="E1863" s="8" t="s">
         <v>7664</v>
-      </c>
-      <c r="E1863" s="8" t="s">
-        <v>7665</v>
       </c>
     </row>
     <row r="1864" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1864" s="5" t="s">
+        <v>7665</v>
+      </c>
+      <c r="B1864" s="8" t="s">
         <v>7666</v>
       </c>
-      <c r="B1864" s="8" t="s">
+      <c r="C1864" s="55" t="s">
         <v>7667</v>
       </c>
-      <c r="C1864" s="55" t="s">
+      <c r="D1864" s="8" t="s">
         <v>7668</v>
       </c>
-      <c r="D1864" s="8" t="s">
+      <c r="E1864" s="8" t="s">
         <v>7669</v>
-      </c>
-      <c r="E1864" s="8" t="s">
-        <v>7670</v>
       </c>
     </row>
     <row r="1865" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1865" s="5" t="s">
+        <v>7670</v>
+      </c>
+      <c r="B1865" s="8" t="s">
         <v>7671</v>
       </c>
-      <c r="B1865" s="8" t="s">
+      <c r="C1865" s="55" t="s">
         <v>7672</v>
       </c>
-      <c r="C1865" s="55" t="s">
+      <c r="D1865" s="8" t="s">
         <v>7673</v>
       </c>
-      <c r="D1865" s="8" t="s">
+      <c r="E1865" s="8" t="s">
         <v>7674</v>
-      </c>
-      <c r="E1865" s="8" t="s">
-        <v>7675</v>
       </c>
     </row>
     <row r="1866" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1866" s="5" t="s">
+        <v>7675</v>
+      </c>
+      <c r="B1866" s="8" t="s">
         <v>7676</v>
-      </c>
-      <c r="B1866" s="8" t="s">
-        <v>7677</v>
       </c>
       <c r="C1866" s="5"/>
       <c r="D1866" s="8" t="s">
+        <v>7677</v>
+      </c>
+      <c r="E1866" s="8" t="s">
         <v>7678</v>
-      </c>
-      <c r="E1866" s="8" t="s">
-        <v>7679</v>
       </c>
     </row>
     <row r="1867" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1867" s="10" t="s">
+        <v>7679</v>
+      </c>
+      <c r="B1867" s="11" t="s">
         <v>7680</v>
       </c>
-      <c r="B1867" s="11" t="s">
+      <c r="C1867" s="56" t="s">
         <v>7681</v>
       </c>
-      <c r="C1867" s="56" t="s">
+      <c r="D1867" s="11" t="s">
         <v>7682</v>
       </c>
-      <c r="D1867" s="11" t="s">
+      <c r="E1867" s="11" t="s">
         <v>7683</v>
-      </c>
-      <c r="E1867" s="11" t="s">
-        <v>7684</v>
       </c>
     </row>
     <row r="1868" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1868" s="5" t="s">
+        <v>7684</v>
+      </c>
+      <c r="B1868" s="13" t="s">
         <v>7685</v>
       </c>
-      <c r="B1868" s="13" t="s">
+      <c r="C1868" s="57" t="s">
         <v>7686</v>
       </c>
-      <c r="C1868" s="57" t="s">
+      <c r="D1868" s="8" t="s">
         <v>7687</v>
       </c>
-      <c r="D1868" s="8" t="s">
+      <c r="E1868" s="8" t="s">
         <v>7688</v>
-      </c>
-      <c r="E1868" s="8" t="s">
-        <v>7689</v>
       </c>
     </row>
     <row r="1869" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1869" s="10" t="s">
+        <v>7689</v>
+      </c>
+      <c r="B1869" s="17" t="s">
         <v>7690</v>
       </c>
-      <c r="B1869" s="17" t="s">
+      <c r="C1869" s="58" t="s">
         <v>7691</v>
       </c>
-      <c r="C1869" s="58" t="s">
+      <c r="D1869" s="11" t="s">
         <v>7692</v>
       </c>
-      <c r="D1869" s="11" t="s">
+      <c r="E1869" s="11" t="s">
         <v>7693</v>
-      </c>
-      <c r="E1869" s="11" t="s">
-        <v>7694</v>
       </c>
     </row>
     <row r="1870" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1870" s="5" t="s">
+        <v>7694</v>
+      </c>
+      <c r="B1870" s="13" t="s">
         <v>7695</v>
       </c>
-      <c r="B1870" s="13" t="s">
+      <c r="C1870" s="59" t="s">
         <v>7696</v>
       </c>
-      <c r="C1870" s="59" t="s">
+      <c r="D1870" s="8" t="s">
         <v>7697</v>
       </c>
-      <c r="D1870" s="8" t="s">
+      <c r="E1870" s="8" t="s">
         <v>7698</v>
-      </c>
-      <c r="E1870" s="8" t="s">
-        <v>7699</v>
       </c>
     </row>
     <row r="1871" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1871" s="5" t="s">
+        <v>7699</v>
+      </c>
+      <c r="B1871" s="13" t="s">
         <v>7700</v>
       </c>
-      <c r="B1871" s="13" t="s">
+      <c r="C1871" s="59" t="s">
         <v>7701</v>
       </c>
-      <c r="C1871" s="59" t="s">
+      <c r="D1871" s="8" t="s">
         <v>7702</v>
       </c>
-      <c r="D1871" s="8" t="s">
+      <c r="E1871" s="8" t="s">
         <v>7703</v>
-      </c>
-      <c r="E1871" s="8" t="s">
-        <v>7704</v>
       </c>
     </row>
     <row r="1872" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1872" s="5" t="s">
+        <v>7704</v>
+      </c>
+      <c r="B1872" s="13" t="s">
         <v>7705</v>
       </c>
-      <c r="B1872" s="13" t="s">
+      <c r="C1872" s="59" t="s">
         <v>7706</v>
       </c>
-      <c r="C1872" s="59" t="s">
+      <c r="D1872" s="8" t="s">
         <v>7707</v>
       </c>
-      <c r="D1872" s="8" t="s">
+      <c r="E1872" s="8" t="s">
         <v>7708</v>
-      </c>
-      <c r="E1872" s="8" t="s">
-        <v>7709</v>
       </c>
     </row>
     <row r="1873" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1873" s="10" t="s">
+        <v>7709</v>
+      </c>
+      <c r="B1873" s="17" t="s">
         <v>7710</v>
       </c>
-      <c r="B1873" s="17" t="s">
+      <c r="C1873" s="60" t="s">
         <v>7711</v>
       </c>
-      <c r="C1873" s="60" t="s">
+      <c r="D1873" s="11" t="s">
         <v>7712</v>
       </c>
-      <c r="D1873" s="11" t="s">
+      <c r="E1873" s="11" t="s">
         <v>7713</v>
-      </c>
-      <c r="E1873" s="11" t="s">
-        <v>7714</v>
       </c>
     </row>
     <row r="1874" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1874" s="5" t="s">
+        <v>7714</v>
+      </c>
+      <c r="B1874" s="13" t="s">
         <v>7715</v>
       </c>
-      <c r="B1874" s="13" t="s">
+      <c r="C1874" s="61" t="s">
         <v>7716</v>
       </c>
-      <c r="C1874" s="61" t="s">
+      <c r="D1874" s="8" t="s">
         <v>7717</v>
       </c>
-      <c r="D1874" s="8" t="s">
+      <c r="E1874" s="8" t="s">
         <v>7718</v>
-      </c>
-      <c r="E1874" s="8" t="s">
-        <v>7719</v>
       </c>
     </row>
     <row r="1875" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1875" s="5" t="s">
+        <v>7719</v>
+      </c>
+      <c r="B1875" s="13" t="s">
         <v>7720</v>
       </c>
-      <c r="B1875" s="13" t="s">
+      <c r="C1875" s="61" t="s">
         <v>7721</v>
       </c>
-      <c r="C1875" s="61" t="s">
+      <c r="D1875" s="8" t="s">
         <v>7722</v>
       </c>
-      <c r="D1875" s="8" t="s">
+      <c r="E1875" s="8" t="s">
         <v>7723</v>
-      </c>
-      <c r="E1875" s="8" t="s">
-        <v>7724</v>
       </c>
     </row>
     <row r="1876" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1876" s="5" t="s">
+        <v>7724</v>
+      </c>
+      <c r="B1876" s="13" t="s">
         <v>7725</v>
       </c>
-      <c r="B1876" s="13" t="s">
+      <c r="C1876" s="61" t="s">
         <v>7726</v>
       </c>
-      <c r="C1876" s="61" t="s">
+      <c r="D1876" s="8" t="s">
         <v>7727</v>
       </c>
-      <c r="D1876" s="8" t="s">
+      <c r="E1876" s="8" t="s">
         <v>7728</v>
-      </c>
-      <c r="E1876" s="8" t="s">
-        <v>7729</v>
       </c>
     </row>
     <row r="1877" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1877" s="5" t="s">
+        <v>7729</v>
+      </c>
+      <c r="B1877" s="13" t="s">
         <v>7730</v>
       </c>
-      <c r="B1877" s="13" t="s">
+      <c r="C1877" s="61" t="s">
         <v>7731</v>
       </c>
-      <c r="C1877" s="61" t="s">
+      <c r="D1877" s="8" t="s">
         <v>7732</v>
       </c>
-      <c r="D1877" s="8" t="s">
+      <c r="E1877" s="8" t="s">
         <v>7733</v>
-      </c>
-      <c r="E1877" s="8" t="s">
-        <v>7734</v>
       </c>
     </row>
     <row r="1878" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1878" s="5" t="s">
+        <v>7734</v>
+      </c>
+      <c r="B1878" s="13" t="s">
         <v>7735</v>
       </c>
-      <c r="B1878" s="13" t="s">
+      <c r="C1878" s="61" t="s">
         <v>7736</v>
       </c>
-      <c r="C1878" s="61" t="s">
+      <c r="D1878" s="8" t="s">
         <v>7737</v>
       </c>
-      <c r="D1878" s="8" t="s">
+      <c r="E1878" s="8" t="s">
         <v>7738</v>
-      </c>
-      <c r="E1878" s="8" t="s">
-        <v>7739</v>
       </c>
     </row>
     <row r="1879" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1879" s="5" t="s">
+        <v>7739</v>
+      </c>
+      <c r="B1879" s="13" t="s">
         <v>7740</v>
       </c>
-      <c r="B1879" s="13" t="s">
+      <c r="C1879" s="61" t="s">
         <v>7741</v>
       </c>
-      <c r="C1879" s="61" t="s">
+      <c r="D1879" s="8" t="s">
         <v>7742</v>
       </c>
-      <c r="D1879" s="8" t="s">
+      <c r="E1879" s="8" t="s">
         <v>7743</v>
-      </c>
-      <c r="E1879" s="8" t="s">
-        <v>7744</v>
       </c>
     </row>
     <row r="1880" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1880" s="5" t="s">
+        <v>7744</v>
+      </c>
+      <c r="B1880" s="13" t="s">
         <v>7745</v>
       </c>
-      <c r="B1880" s="13" t="s">
+      <c r="C1880" s="61" t="s">
         <v>7746</v>
       </c>
-      <c r="C1880" s="61" t="s">
+      <c r="D1880" s="8" t="s">
         <v>7747</v>
       </c>
-      <c r="D1880" s="8" t="s">
+      <c r="E1880" s="8" t="s">
         <v>7748</v>
-      </c>
-      <c r="E1880" s="8" t="s">
-        <v>7749</v>
       </c>
     </row>
     <row r="1881" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1881" s="5" t="s">
+        <v>7749</v>
+      </c>
+      <c r="B1881" s="13" t="s">
         <v>7750</v>
       </c>
-      <c r="B1881" s="13" t="s">
+      <c r="C1881" s="61" t="s">
         <v>7751</v>
       </c>
-      <c r="C1881" s="61" t="s">
+      <c r="D1881" s="8" t="s">
         <v>7752</v>
       </c>
-      <c r="D1881" s="8" t="s">
+      <c r="E1881" s="8" t="s">
         <v>7753</v>
-      </c>
-      <c r="E1881" s="8" t="s">
-        <v>7754</v>
       </c>
     </row>
     <row r="1882" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1882" s="5" t="s">
+        <v>7754</v>
+      </c>
+      <c r="B1882" s="13" t="s">
         <v>7755</v>
       </c>
-      <c r="B1882" s="13" t="s">
+      <c r="C1882" s="61" t="s">
         <v>7756</v>
       </c>
-      <c r="C1882" s="61" t="s">
+      <c r="D1882" s="8" t="s">
         <v>7757</v>
       </c>
-      <c r="D1882" s="8" t="s">
+      <c r="E1882" s="8" t="s">
         <v>7758</v>
-      </c>
-      <c r="E1882" s="8" t="s">
-        <v>7759</v>
       </c>
     </row>
     <row r="1883" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1883" s="5" t="s">
+        <v>7759</v>
+      </c>
+      <c r="B1883" s="13" t="s">
         <v>7760</v>
       </c>
-      <c r="B1883" s="13" t="s">
+      <c r="C1883" s="61" t="s">
         <v>7761</v>
       </c>
-      <c r="C1883" s="61" t="s">
+      <c r="D1883" s="8" t="s">
         <v>7762</v>
       </c>
-      <c r="D1883" s="8" t="s">
+      <c r="E1883" s="8" t="s">
         <v>7763</v>
-      </c>
-      <c r="E1883" s="8" t="s">
-        <v>7764</v>
       </c>
     </row>
     <row r="1884" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1884" s="5" t="s">
+        <v>7764</v>
+      </c>
+      <c r="B1884" s="13" t="s">
         <v>7765</v>
       </c>
-      <c r="B1884" s="13" t="s">
+      <c r="C1884" s="61" t="s">
         <v>7766</v>
       </c>
-      <c r="C1884" s="61" t="s">
+      <c r="D1884" s="8" t="s">
         <v>7767</v>
       </c>
-      <c r="D1884" s="8" t="s">
+      <c r="E1884" s="8" t="s">
         <v>7768</v>
-      </c>
-      <c r="E1884" s="8" t="s">
-        <v>7769</v>
       </c>
     </row>
     <row r="1885" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1885" s="5" t="s">
+        <v>7769</v>
+      </c>
+      <c r="B1885" s="13" t="s">
         <v>7770</v>
       </c>
-      <c r="B1885" s="13" t="s">
+      <c r="C1885" s="61" t="s">
         <v>7771</v>
       </c>
-      <c r="C1885" s="61" t="s">
+      <c r="D1885" s="8" t="s">
         <v>7772</v>
       </c>
-      <c r="D1885" s="8" t="s">
+      <c r="E1885" s="8" t="s">
         <v>7773</v>
-      </c>
-      <c r="E1885" s="8" t="s">
-        <v>7774</v>
       </c>
     </row>
     <row r="1886" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1886" s="5" t="s">
+        <v>7774</v>
+      </c>
+      <c r="B1886" s="13" t="s">
         <v>7775</v>
       </c>
-      <c r="B1886" s="13" t="s">
+      <c r="C1886" s="61" t="s">
         <v>7776</v>
       </c>
-      <c r="C1886" s="61" t="s">
+      <c r="D1886" s="8" t="s">
         <v>7777</v>
       </c>
-      <c r="D1886" s="8" t="s">
+      <c r="E1886" s="8" t="s">
         <v>7778</v>
-      </c>
-      <c r="E1886" s="8" t="s">
-        <v>7779</v>
       </c>
     </row>
     <row r="1887" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1887" s="5" t="s">
+        <v>7779</v>
+      </c>
+      <c r="B1887" s="13" t="s">
         <v>7780</v>
       </c>
-      <c r="B1887" s="13" t="s">
+      <c r="C1887" s="61" t="s">
         <v>7781</v>
       </c>
-      <c r="C1887" s="61" t="s">
+      <c r="D1887" s="8" t="s">
         <v>7782</v>
       </c>
-      <c r="D1887" s="8" t="s">
+      <c r="E1887" s="8" t="s">
         <v>7783</v>
-      </c>
-      <c r="E1887" s="8" t="s">
-        <v>7784</v>
       </c>
     </row>
     <row r="1888" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1888" s="5" t="s">
+        <v>7784</v>
+      </c>
+      <c r="B1888" s="13" t="s">
         <v>7785</v>
       </c>
-      <c r="B1888" s="13" t="s">
+      <c r="C1888" s="61" t="s">
         <v>7786</v>
       </c>
-      <c r="C1888" s="61" t="s">
+      <c r="D1888" s="8" t="s">
         <v>7787</v>
       </c>
-      <c r="D1888" s="8" t="s">
+      <c r="E1888" s="8" t="s">
         <v>7788</v>
-      </c>
-      <c r="E1888" s="8" t="s">
-        <v>7789</v>
       </c>
     </row>
     <row r="1889" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1889" s="5" t="s">
+        <v>7789</v>
+      </c>
+      <c r="B1889" s="13" t="s">
         <v>7790</v>
       </c>
-      <c r="B1889" s="13" t="s">
+      <c r="C1889" s="61" t="s">
         <v>7791</v>
       </c>
-      <c r="C1889" s="61" t="s">
+      <c r="D1889" s="8" t="s">
         <v>7792</v>
       </c>
-      <c r="D1889" s="8" t="s">
+      <c r="E1889" s="8" t="s">
         <v>7793</v>
-      </c>
-      <c r="E1889" s="8" t="s">
-        <v>7794</v>
       </c>
     </row>
     <row r="1890" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1890" s="5" t="s">
+        <v>7794</v>
+      </c>
+      <c r="B1890" s="13" t="s">
         <v>7795</v>
       </c>
-      <c r="B1890" s="13" t="s">
+      <c r="C1890" s="61" t="s">
         <v>7796</v>
       </c>
-      <c r="C1890" s="61" t="s">
+      <c r="D1890" s="8" t="s">
         <v>7797</v>
       </c>
-      <c r="D1890" s="8" t="s">
+      <c r="E1890" s="8" t="s">
         <v>7798</v>
-      </c>
-      <c r="E1890" s="8" t="s">
-        <v>7799</v>
       </c>
     </row>
     <row r="1891" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1891" s="5" t="s">
+        <v>7799</v>
+      </c>
+      <c r="B1891" s="13" t="s">
         <v>7800</v>
       </c>
-      <c r="B1891" s="13" t="s">
+      <c r="C1891" s="61" t="s">
         <v>7801</v>
       </c>
-      <c r="C1891" s="61" t="s">
+      <c r="D1891" s="8" t="s">
         <v>7802</v>
       </c>
-      <c r="D1891" s="8" t="s">
+      <c r="E1891" s="8" t="s">
         <v>7803</v>
-      </c>
-      <c r="E1891" s="8" t="s">
-        <v>7804</v>
       </c>
     </row>
     <row r="1892" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1892" s="5" t="s">
+        <v>7804</v>
+      </c>
+      <c r="B1892" s="13" t="s">
         <v>7805</v>
       </c>
-      <c r="B1892" s="13" t="s">
+      <c r="C1892" s="61" t="s">
         <v>7806</v>
       </c>
-      <c r="C1892" s="61" t="s">
+      <c r="D1892" s="8" t="s">
         <v>7807</v>
       </c>
-      <c r="D1892" s="8" t="s">
+      <c r="E1892" s="8" t="s">
         <v>7808</v>
-      </c>
-      <c r="E1892" s="8" t="s">
-        <v>7809</v>
       </c>
     </row>
     <row r="1893" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1893" s="5" t="s">
+        <v>7809</v>
+      </c>
+      <c r="B1893" s="13" t="s">
         <v>7810</v>
       </c>
-      <c r="B1893" s="13" t="s">
+      <c r="C1893" s="61" t="s">
         <v>7811</v>
       </c>
-      <c r="C1893" s="61" t="s">
+      <c r="D1893" s="8" t="s">
         <v>7812</v>
       </c>
-      <c r="D1893" s="8" t="s">
+      <c r="E1893" s="8" t="s">
         <v>7813</v>
-      </c>
-      <c r="E1893" s="8" t="s">
-        <v>7814</v>
       </c>
     </row>
     <row r="1894" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1894" s="5" t="s">
+        <v>7814</v>
+      </c>
+      <c r="B1894" s="13" t="s">
         <v>7815</v>
       </c>
-      <c r="B1894" s="13" t="s">
+      <c r="C1894" s="61" t="s">
         <v>7816</v>
       </c>
-      <c r="C1894" s="61" t="s">
+      <c r="D1894" s="8" t="s">
         <v>7817</v>
       </c>
-      <c r="D1894" s="8" t="s">
+      <c r="E1894" s="8" t="s">
         <v>7818</v>
-      </c>
-      <c r="E1894" s="8" t="s">
-        <v>7819</v>
       </c>
     </row>
     <row r="1895" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1895" s="5" t="s">
+        <v>7819</v>
+      </c>
+      <c r="B1895" s="13" t="s">
         <v>7820</v>
       </c>
-      <c r="B1895" s="13" t="s">
+      <c r="C1895" s="61" t="s">
         <v>7821</v>
       </c>
-      <c r="C1895" s="61" t="s">
+      <c r="D1895" s="8" t="s">
         <v>7822</v>
       </c>
-      <c r="D1895" s="8" t="s">
+      <c r="E1895" s="8" t="s">
         <v>7823</v>
-      </c>
-      <c r="E1895" s="8" t="s">
-        <v>7824</v>
       </c>
     </row>
     <row r="1896" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1896" s="5" t="s">
+        <v>7824</v>
+      </c>
+      <c r="B1896" s="13" t="s">
         <v>7825</v>
       </c>
-      <c r="B1896" s="13" t="s">
+      <c r="C1896" s="61" t="s">
         <v>7826</v>
       </c>
-      <c r="C1896" s="61" t="s">
+      <c r="D1896" s="8" t="s">
         <v>7827</v>
       </c>
-      <c r="D1896" s="8" t="s">
+      <c r="E1896" s="8" t="s">
         <v>7828</v>
-      </c>
-      <c r="E1896" s="8" t="s">
-        <v>7829</v>
       </c>
     </row>
     <row r="1897" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1897" s="5" t="s">
+        <v>7829</v>
+      </c>
+      <c r="B1897" s="13" t="s">
         <v>7830</v>
       </c>
-      <c r="B1897" s="13" t="s">
+      <c r="C1897" s="61" t="s">
         <v>7831</v>
       </c>
-      <c r="C1897" s="61" t="s">
+      <c r="D1897" s="8" t="s">
         <v>7832</v>
       </c>
-      <c r="D1897" s="8" t="s">
+      <c r="E1897" s="8" t="s">
         <v>7833</v>
-      </c>
-      <c r="E1897" s="8" t="s">
-        <v>7834</v>
       </c>
     </row>
     <row r="1898" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1898" s="5" t="s">
+        <v>7834</v>
+      </c>
+      <c r="B1898" s="13" t="s">
         <v>7835</v>
       </c>
-      <c r="B1898" s="13" t="s">
+      <c r="C1898" s="61" t="s">
         <v>7836</v>
       </c>
-      <c r="C1898" s="61" t="s">
+      <c r="D1898" s="8" t="s">
         <v>7837</v>
       </c>
-      <c r="D1898" s="8" t="s">
+      <c r="E1898" s="8" t="s">
         <v>7838</v>
-      </c>
-      <c r="E1898" s="8" t="s">
-        <v>7839</v>
       </c>
     </row>
     <row r="1899" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1899" s="5" t="s">
+        <v>7839</v>
+      </c>
+      <c r="B1899" s="13" t="s">
         <v>7840</v>
       </c>
-      <c r="B1899" s="13" t="s">
+      <c r="C1899" s="61" t="s">
         <v>7841</v>
       </c>
-      <c r="C1899" s="61" t="s">
+      <c r="D1899" s="8" t="s">
         <v>7842</v>
       </c>
-      <c r="D1899" s="8" t="s">
+      <c r="E1899" s="8" t="s">
         <v>7843</v>
-      </c>
-      <c r="E1899" s="8" t="s">
-        <v>7844</v>
       </c>
     </row>
     <row r="1900" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1900" s="5" t="s">
+        <v>7844</v>
+      </c>
+      <c r="B1900" s="13" t="s">
         <v>7845</v>
       </c>
-      <c r="B1900" s="13" t="s">
+      <c r="C1900" s="61" t="s">
         <v>7846</v>
       </c>
-      <c r="C1900" s="61" t="s">
+      <c r="D1900" s="8" t="s">
         <v>7847</v>
       </c>
-      <c r="D1900" s="8" t="s">
+      <c r="E1900" s="8" t="s">
         <v>7848</v>
-      </c>
-      <c r="E1900" s="8" t="s">
-        <v>7849</v>
       </c>
     </row>
     <row r="1901" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1901" s="5" t="s">
+        <v>7849</v>
+      </c>
+      <c r="B1901" s="13" t="s">
         <v>7850</v>
       </c>
-      <c r="B1901" s="13" t="s">
+      <c r="C1901" s="61" t="s">
         <v>7851</v>
       </c>
-      <c r="C1901" s="61" t="s">
+      <c r="D1901" s="8" t="s">
         <v>7852</v>
       </c>
-      <c r="D1901" s="8" t="s">
+      <c r="E1901" s="8" t="s">
         <v>7853</v>
-      </c>
-      <c r="E1901" s="8" t="s">
-        <v>7854</v>
       </c>
     </row>
     <row r="1902" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1902" s="5" t="s">
+        <v>7854</v>
+      </c>
+      <c r="B1902" s="13" t="s">
         <v>7855</v>
       </c>
-      <c r="B1902" s="13" t="s">
+      <c r="C1902" s="61" t="s">
         <v>7856</v>
       </c>
-      <c r="C1902" s="61" t="s">
+      <c r="D1902" s="8" t="s">
         <v>7857</v>
       </c>
-      <c r="D1902" s="8" t="s">
+      <c r="E1902" s="8" t="s">
         <v>7858</v>
-      </c>
-      <c r="E1902" s="8" t="s">
-        <v>7859</v>
       </c>
     </row>
     <row r="1903" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1903" s="5" t="s">
+        <v>7859</v>
+      </c>
+      <c r="B1903" s="13" t="s">
         <v>7860</v>
       </c>
-      <c r="B1903" s="13" t="s">
+      <c r="C1903" s="61" t="s">
         <v>7861</v>
       </c>
-      <c r="C1903" s="61" t="s">
+      <c r="D1903" s="8" t="s">
         <v>7862</v>
       </c>
-      <c r="D1903" s="8" t="s">
+      <c r="E1903" s="8" t="s">
         <v>7863</v>
-      </c>
-      <c r="E1903" s="8" t="s">
-        <v>7864</v>
       </c>
     </row>
     <row r="1904" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1904" s="10" t="s">
+        <v>7864</v>
+      </c>
+      <c r="B1904" s="17" t="s">
         <v>7865</v>
       </c>
-      <c r="B1904" s="17" t="s">
+      <c r="C1904" s="62" t="s">
         <v>7866</v>
       </c>
-      <c r="C1904" s="62" t="s">
+      <c r="D1904" s="11" t="s">
         <v>7867</v>
       </c>
-      <c r="D1904" s="11" t="s">
+      <c r="E1904" s="11" t="s">
         <v>7868</v>
-      </c>
-      <c r="E1904" s="11" t="s">
-        <v>7869</v>
       </c>
     </row>
     <row r="1905" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1905" s="5" t="s">
+        <v>7869</v>
+      </c>
+      <c r="B1905" s="13" t="s">
         <v>7870</v>
       </c>
-      <c r="B1905" s="13" t="s">
+      <c r="C1905" s="63" t="s">
         <v>7871</v>
       </c>
-      <c r="C1905" s="63" t="s">
+      <c r="D1905" s="8" t="s">
         <v>7872</v>
       </c>
-      <c r="D1905" s="8" t="s">
+      <c r="E1905" s="8" t="s">
         <v>7873</v>
-      </c>
-      <c r="E1905" s="8" t="s">
-        <v>7874</v>
       </c>
     </row>
     <row r="1906" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1906" s="5" t="s">
+        <v>7874</v>
+      </c>
+      <c r="B1906" s="13" t="s">
         <v>7875</v>
       </c>
-      <c r="B1906" s="13" t="s">
+      <c r="C1906" s="63" t="s">
+        <v>7602</v>
+      </c>
+      <c r="D1906" s="8" t="s">
+        <v>7603</v>
+      </c>
+      <c r="E1906" s="8" t="s">
         <v>7876</v>
-      </c>
-      <c r="C1906" s="63" t="s">
-        <v>7603</v>
-      </c>
-      <c r="D1906" s="8" t="s">
-        <v>7604</v>
-      </c>
-      <c r="E1906" s="8" t="s">
-        <v>7877</v>
       </c>
     </row>
     <row r="1907" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1907" s="5" t="s">
+        <v>7877</v>
+      </c>
+      <c r="B1907" s="13" t="s">
         <v>7878</v>
       </c>
-      <c r="B1907" s="13" t="s">
+      <c r="C1907" s="63" t="s">
         <v>7879</v>
       </c>
-      <c r="C1907" s="63" t="s">
+      <c r="D1907" s="8" t="s">
         <v>7880</v>
       </c>
-      <c r="D1907" s="8" t="s">
+      <c r="E1907" s="8" t="s">
         <v>7881</v>
-      </c>
-      <c r="E1907" s="8" t="s">
-        <v>7882</v>
       </c>
     </row>
     <row r="1908" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1908" s="5" t="s">
+        <v>7882</v>
+      </c>
+      <c r="B1908" s="13" t="s">
         <v>7883</v>
       </c>
-      <c r="B1908" s="13" t="s">
+      <c r="C1908" s="63" t="s">
         <v>7884</v>
       </c>
-      <c r="C1908" s="63" t="s">
+      <c r="D1908" s="8" t="s">
         <v>7885</v>
       </c>
-      <c r="D1908" s="8" t="s">
+      <c r="E1908" s="8" t="s">
         <v>7886</v>
-      </c>
-      <c r="E1908" s="8" t="s">
-        <v>7887</v>
       </c>
     </row>
     <row r="1909" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1909" s="5" t="s">
+        <v>7887</v>
+      </c>
+      <c r="B1909" s="13" t="s">
         <v>7888</v>
       </c>
-      <c r="B1909" s="13" t="s">
+      <c r="C1909" s="63" t="s">
         <v>7889</v>
       </c>
-      <c r="C1909" s="63" t="s">
+      <c r="D1909" s="8" t="s">
         <v>7890</v>
       </c>
-      <c r="D1909" s="8" t="s">
+      <c r="E1909" s="8" t="s">
         <v>7891</v>
-      </c>
-      <c r="E1909" s="8" t="s">
-        <v>7892</v>
       </c>
     </row>
     <row r="1910" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1910" s="5" t="s">
+        <v>7892</v>
+      </c>
+      <c r="B1910" s="13" t="s">
         <v>7893</v>
       </c>
-      <c r="B1910" s="13" t="s">
+      <c r="C1910" s="63" t="s">
         <v>7894</v>
       </c>
-      <c r="C1910" s="63" t="s">
+      <c r="D1910" s="8" t="s">
         <v>7895</v>
       </c>
-      <c r="D1910" s="8" t="s">
+      <c r="E1910" s="8" t="s">
         <v>7896</v>
-      </c>
-      <c r="E1910" s="8" t="s">
-        <v>7897</v>
       </c>
     </row>
     <row r="1911" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1911" s="5" t="s">
+        <v>7897</v>
+      </c>
+      <c r="B1911" s="13" t="s">
         <v>7898</v>
       </c>
-      <c r="B1911" s="13" t="s">
+      <c r="C1911" s="63" t="s">
         <v>7899</v>
       </c>
-      <c r="C1911" s="63" t="s">
+      <c r="D1911" s="8" t="s">
         <v>7900</v>
       </c>
-      <c r="D1911" s="8" t="s">
+      <c r="E1911" s="8" t="s">
         <v>7901</v>
-      </c>
-      <c r="E1911" s="8" t="s">
-        <v>7902</v>
       </c>
     </row>
     <row r="1912" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1912" s="5" t="s">
+        <v>7902</v>
+      </c>
+      <c r="B1912" s="13" t="s">
         <v>7903</v>
       </c>
-      <c r="B1912" s="13" t="s">
+      <c r="C1912" s="63" t="s">
         <v>7904</v>
       </c>
-      <c r="C1912" s="63" t="s">
+      <c r="D1912" s="8" t="s">
         <v>7905</v>
       </c>
-      <c r="D1912" s="8" t="s">
+      <c r="E1912" s="8" t="s">
         <v>7906</v>
-      </c>
-      <c r="E1912" s="8" t="s">
-        <v>7907</v>
       </c>
     </row>
     <row r="1913" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1913" s="5" t="s">
+        <v>7907</v>
+      </c>
+      <c r="B1913" s="13" t="s">
         <v>7908</v>
       </c>
-      <c r="B1913" s="13" t="s">
+      <c r="C1913" s="63" t="s">
         <v>7909</v>
       </c>
-      <c r="C1913" s="63" t="s">
+      <c r="D1913" s="8" t="s">
         <v>7910</v>
       </c>
-      <c r="D1913" s="8" t="s">
+      <c r="E1913" s="8" t="s">
         <v>7911</v>
-      </c>
-      <c r="E1913" s="8" t="s">
-        <v>7912</v>
       </c>
     </row>
     <row r="1914" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1914" s="5" t="s">
+        <v>7912</v>
+      </c>
+      <c r="B1914" s="13" t="s">
         <v>7913</v>
       </c>
-      <c r="B1914" s="13" t="s">
+      <c r="C1914" s="63" t="s">
         <v>7914</v>
       </c>
-      <c r="C1914" s="63" t="s">
+      <c r="D1914" s="8" t="s">
         <v>7915</v>
       </c>
-      <c r="D1914" s="8" t="s">
+      <c r="E1914" s="8" t="s">
         <v>7916</v>
-      </c>
-      <c r="E1914" s="8" t="s">
-        <v>7917</v>
       </c>
     </row>
     <row r="1915" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1915" s="5" t="s">
+        <v>7917</v>
+      </c>
+      <c r="B1915" s="13" t="s">
         <v>7918</v>
       </c>
-      <c r="B1915" s="13" t="s">
+      <c r="C1915" s="63" t="s">
         <v>7919</v>
       </c>
-      <c r="C1915" s="63" t="s">
+      <c r="D1915" s="8" t="s">
         <v>7920</v>
       </c>
-      <c r="D1915" s="8" t="s">
+      <c r="E1915" s="8" t="s">
         <v>7921</v>
-      </c>
-      <c r="E1915" s="8" t="s">
-        <v>7922</v>
       </c>
     </row>
     <row r="1916" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1916" s="5" t="s">
+        <v>7922</v>
+      </c>
+      <c r="B1916" s="13" t="s">
         <v>7923</v>
       </c>
-      <c r="B1916" s="13" t="s">
+      <c r="C1916" s="63" t="s">
         <v>7924</v>
       </c>
-      <c r="C1916" s="63" t="s">
+      <c r="D1916" s="8" t="s">
         <v>7925</v>
       </c>
-      <c r="D1916" s="8" t="s">
+      <c r="E1916" s="8" t="s">
         <v>7926</v>
-      </c>
-      <c r="E1916" s="8" t="s">
-        <v>7927</v>
       </c>
     </row>
     <row r="1917" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1917" s="10" t="s">
+        <v>7927</v>
+      </c>
+      <c r="B1917" s="17" t="s">
         <v>7928</v>
       </c>
-      <c r="B1917" s="17" t="s">
+      <c r="C1917" s="64" t="s">
         <v>7929</v>
       </c>
-      <c r="C1917" s="64" t="s">
+      <c r="D1917" s="11" t="s">
         <v>7930</v>
       </c>
-      <c r="D1917" s="11" t="s">
+      <c r="E1917" s="11" t="s">
         <v>7931</v>
-      </c>
-      <c r="E1917" s="11" t="s">
-        <v>7932</v>
       </c>
     </row>
     <row r="1918" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1918" s="65" t="s">
+        <v>7932</v>
+      </c>
+      <c r="B1918" s="66" t="s">
         <v>7933</v>
       </c>
-      <c r="B1918" s="66" t="s">
+      <c r="C1918" s="67" t="s">
         <v>7934</v>
       </c>
-      <c r="C1918" s="67" t="s">
+      <c r="D1918" s="66" t="s">
         <v>7935</v>
       </c>
-      <c r="D1918" s="66" t="s">
+      <c r="E1918" s="66" t="s">
         <v>7936</v>
-      </c>
-      <c r="E1918" s="66" t="s">
-        <v>7937</v>
       </c>
     </row>
     <row r="1919" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1919" s="65" t="s">
+        <v>7937</v>
+      </c>
+      <c r="B1919" s="66" t="s">
         <v>7938</v>
       </c>
-      <c r="B1919" s="66" t="s">
+      <c r="C1919" s="67" t="s">
         <v>7939</v>
       </c>
-      <c r="C1919" s="67" t="s">
+      <c r="D1919" s="66" t="s">
         <v>7940</v>
       </c>
-      <c r="D1919" s="66" t="s">
+      <c r="E1919" s="66" t="s">
         <v>7941</v>
-      </c>
-      <c r="E1919" s="66" t="s">
-        <v>7942</v>
       </c>
     </row>
     <row r="1920" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1920" s="65" t="s">
+        <v>7942</v>
+      </c>
+      <c r="B1920" s="66" t="s">
         <v>7943</v>
       </c>
-      <c r="B1920" s="66" t="s">
+      <c r="C1920" s="67" t="s">
         <v>7944</v>
       </c>
-      <c r="C1920" s="67" t="s">
+      <c r="D1920" s="66" t="s">
         <v>7945</v>
       </c>
-      <c r="D1920" s="66" t="s">
+      <c r="E1920" s="66" t="s">
         <v>7946</v>
-      </c>
-      <c r="E1920" s="66" t="s">
-        <v>7947</v>
       </c>
     </row>
     <row r="1921" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1921" s="65" t="s">
+        <v>7947</v>
+      </c>
+      <c r="B1921" s="66" t="s">
         <v>7948</v>
       </c>
-      <c r="B1921" s="66" t="s">
+      <c r="C1921" s="67" t="s">
         <v>7949</v>
       </c>
-      <c r="C1921" s="67" t="s">
+      <c r="D1921" s="66" t="s">
         <v>7950</v>
       </c>
-      <c r="D1921" s="66" t="s">
+      <c r="E1921" s="66" t="s">
         <v>7951</v>
-      </c>
-      <c r="E1921" s="66" t="s">
-        <v>7952</v>
       </c>
     </row>
     <row r="1922" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1922" s="65" t="s">
+        <v>7952</v>
+      </c>
+      <c r="B1922" s="66" t="s">
         <v>7953</v>
       </c>
-      <c r="B1922" s="66" t="s">
+      <c r="C1922" s="67" t="s">
         <v>7954</v>
       </c>
-      <c r="C1922" s="67" t="s">
+      <c r="D1922" s="66" t="s">
         <v>7955</v>
       </c>
-      <c r="D1922" s="66" t="s">
+      <c r="E1922" s="66" t="s">
         <v>7956</v>
-      </c>
-      <c r="E1922" s="66" t="s">
-        <v>7957</v>
       </c>
     </row>
     <row r="1923" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1923" s="65" t="s">
+        <v>7957</v>
+      </c>
+      <c r="B1923" s="66" t="s">
         <v>7958</v>
       </c>
-      <c r="B1923" s="66" t="s">
+      <c r="C1923" s="67" t="s">
         <v>7959</v>
       </c>
-      <c r="C1923" s="67" t="s">
+      <c r="D1923" s="66" t="s">
         <v>7960</v>
       </c>
-      <c r="D1923" s="66" t="s">
+      <c r="E1923" s="66" t="s">
         <v>7961</v>
-      </c>
-      <c r="E1923" s="66" t="s">
-        <v>7962</v>
       </c>
     </row>
     <row r="1924" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1924" s="65" t="s">
+        <v>7962</v>
+      </c>
+      <c r="B1924" s="66" t="s">
         <v>7963</v>
       </c>
-      <c r="B1924" s="66" t="s">
+      <c r="C1924" s="67" t="s">
         <v>7964</v>
       </c>
-      <c r="C1924" s="67" t="s">
+      <c r="D1924" s="66" t="s">
         <v>7965</v>
       </c>
-      <c r="D1924" s="66" t="s">
+      <c r="E1924" s="66" t="s">
         <v>7966</v>
-      </c>
-      <c r="E1924" s="66" t="s">
-        <v>7967</v>
       </c>
     </row>
     <row r="1925" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1925" s="65" t="s">
+        <v>7967</v>
+      </c>
+      <c r="B1925" s="66" t="s">
         <v>7968</v>
       </c>
-      <c r="B1925" s="66" t="s">
+      <c r="C1925" s="67" t="s">
         <v>7969</v>
       </c>
-      <c r="C1925" s="67" t="s">
+      <c r="D1925" s="66" t="s">
         <v>7970</v>
       </c>
-      <c r="D1925" s="66" t="s">
+      <c r="E1925" s="66" t="s">
         <v>7971</v>
-      </c>
-      <c r="E1925" s="66" t="s">
-        <v>7972</v>
       </c>
     </row>
     <row r="1926" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1926" s="65" t="s">
+        <v>7972</v>
+      </c>
+      <c r="B1926" s="66" t="s">
         <v>7973</v>
       </c>
-      <c r="B1926" s="66" t="s">
+      <c r="C1926" s="67" t="s">
         <v>7974</v>
       </c>
-      <c r="C1926" s="67" t="s">
+      <c r="D1926" s="66" t="s">
         <v>7975</v>
       </c>
-      <c r="D1926" s="66" t="s">
+      <c r="E1926" s="66" t="s">
         <v>7976</v>
-      </c>
-      <c r="E1926" s="66" t="s">
-        <v>7977</v>
       </c>
     </row>
     <row r="1927" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1927" s="65" t="s">
+        <v>7977</v>
+      </c>
+      <c r="B1927" s="66" t="s">
         <v>7978</v>
       </c>
-      <c r="B1927" s="66" t="s">
+      <c r="C1927" s="67" t="s">
         <v>7979</v>
       </c>
-      <c r="C1927" s="67" t="s">
+      <c r="D1927" s="66" t="s">
         <v>7980</v>
       </c>
-      <c r="D1927" s="66" t="s">
+      <c r="E1927" s="66" t="s">
         <v>7981</v>
-      </c>
-      <c r="E1927" s="66" t="s">
-        <v>7982</v>
       </c>
     </row>
     <row r="1928" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1928" s="65" t="s">
+        <v>7982</v>
+      </c>
+      <c r="B1928" s="66" t="s">
         <v>7983</v>
       </c>
-      <c r="B1928" s="66" t="s">
+      <c r="C1928" s="67" t="s">
         <v>7984</v>
       </c>
-      <c r="C1928" s="67" t="s">
+      <c r="D1928" s="66" t="s">
         <v>7985</v>
       </c>
-      <c r="D1928" s="66" t="s">
+      <c r="E1928" s="66" t="s">
         <v>7986</v>
-      </c>
-      <c r="E1928" s="66" t="s">
-        <v>7987</v>
       </c>
     </row>
     <row r="1929" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1929" s="65" t="s">
+        <v>7987</v>
+      </c>
+      <c r="B1929" s="66" t="s">
         <v>7988</v>
       </c>
-      <c r="B1929" s="66" t="s">
+      <c r="C1929" s="67" t="s">
         <v>7989</v>
       </c>
-      <c r="C1929" s="67" t="s">
+      <c r="D1929" s="66" t="s">
         <v>7990</v>
       </c>
-      <c r="D1929" s="66" t="s">
+      <c r="E1929" s="66" t="s">
         <v>7991</v>
-      </c>
-      <c r="E1929" s="66" t="s">
-        <v>7992</v>
       </c>
     </row>
     <row r="1930" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1930" s="65" t="s">
+        <v>7992</v>
+      </c>
+      <c r="B1930" s="66" t="s">
         <v>7993</v>
       </c>
-      <c r="B1930" s="66" t="s">
+      <c r="C1930" s="67" t="s">
         <v>7994</v>
       </c>
-      <c r="C1930" s="67" t="s">
+      <c r="D1930" s="66" t="s">
         <v>7995</v>
       </c>
-      <c r="D1930" s="66" t="s">
+      <c r="E1930" s="66" t="s">
         <v>7996</v>
-      </c>
-      <c r="E1930" s="66" t="s">
-        <v>7997</v>
       </c>
     </row>
     <row r="1931" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1931" s="65" t="s">
+        <v>7997</v>
+      </c>
+      <c r="B1931" s="66" t="s">
         <v>7998</v>
       </c>
-      <c r="B1931" s="66" t="s">
+      <c r="C1931" s="67" t="s">
         <v>7999</v>
       </c>
-      <c r="C1931" s="67" t="s">
+      <c r="D1931" s="66" t="s">
         <v>8000</v>
       </c>
-      <c r="D1931" s="66" t="s">
+      <c r="E1931" s="66" t="s">
         <v>8001</v>
-      </c>
-      <c r="E1931" s="66" t="s">
-        <v>8002</v>
       </c>
     </row>
     <row r="1932" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1932" s="65" t="s">
+        <v>8002</v>
+      </c>
+      <c r="B1932" s="66" t="s">
         <v>8003</v>
       </c>
-      <c r="B1932" s="66" t="s">
+      <c r="C1932" s="67" t="s">
         <v>8004</v>
       </c>
-      <c r="C1932" s="67" t="s">
+      <c r="D1932" s="66" t="s">
         <v>8005</v>
       </c>
-      <c r="D1932" s="66" t="s">
+      <c r="E1932" s="66" t="s">
         <v>8006</v>
-      </c>
-      <c r="E1932" s="66" t="s">
-        <v>8007</v>
       </c>
     </row>
     <row r="1933" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1933" s="65" t="s">
+        <v>8007</v>
+      </c>
+      <c r="B1933" s="66" t="s">
         <v>8008</v>
       </c>
-      <c r="B1933" s="66" t="s">
+      <c r="C1933" s="67" t="s">
         <v>8009</v>
       </c>
-      <c r="C1933" s="67" t="s">
+      <c r="D1933" s="66" t="s">
         <v>8010</v>
       </c>
-      <c r="D1933" s="66" t="s">
+      <c r="E1933" s="66" t="s">
         <v>8011</v>
-      </c>
-      <c r="E1933" s="66" t="s">
-        <v>8012</v>
       </c>
     </row>
     <row r="1934" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1934" s="65" t="s">
+        <v>8012</v>
+      </c>
+      <c r="B1934" s="66" t="s">
         <v>8013</v>
       </c>
-      <c r="B1934" s="66" t="s">
+      <c r="C1934" s="67" t="s">
         <v>8014</v>
       </c>
-      <c r="C1934" s="67" t="s">
+      <c r="D1934" s="66" t="s">
         <v>8015</v>
       </c>
-      <c r="D1934" s="66" t="s">
+      <c r="E1934" s="66" t="s">
         <v>8016</v>
-      </c>
-      <c r="E1934" s="66" t="s">
-        <v>8017</v>
       </c>
     </row>
     <row r="1935" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1935" s="65" t="s">
+        <v>8017</v>
+      </c>
+      <c r="B1935" s="66" t="s">
         <v>8018</v>
       </c>
-      <c r="B1935" s="66" t="s">
+      <c r="C1935" s="67" t="s">
         <v>8019</v>
       </c>
-      <c r="C1935" s="67" t="s">
+      <c r="D1935" s="66" t="s">
         <v>8020</v>
       </c>
-      <c r="D1935" s="66" t="s">
+      <c r="E1935" s="66" t="s">
         <v>8021</v>
-      </c>
-      <c r="E1935" s="66" t="s">
-        <v>8022</v>
       </c>
     </row>
     <row r="1936" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1936" s="65" t="s">
+        <v>8022</v>
+      </c>
+      <c r="B1936" s="66" t="s">
         <v>8023</v>
       </c>
-      <c r="B1936" s="66" t="s">
+      <c r="C1936" s="67" t="s">
         <v>8024</v>
       </c>
-      <c r="C1936" s="67" t="s">
+      <c r="D1936" s="66" t="s">
         <v>8025</v>
       </c>
-      <c r="D1936" s="66" t="s">
+      <c r="E1936" s="66" t="s">
         <v>8026</v>
-      </c>
-      <c r="E1936" s="66" t="s">
-        <v>8027</v>
       </c>
     </row>
     <row r="1937" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1937" s="65" t="s">
+        <v>8027</v>
+      </c>
+      <c r="B1937" s="66" t="s">
         <v>8028</v>
       </c>
-      <c r="B1937" s="66" t="s">
+      <c r="C1937" s="67" t="s">
         <v>8029</v>
       </c>
-      <c r="C1937" s="67" t="s">
+      <c r="D1937" s="66" t="s">
         <v>8030</v>
       </c>
-      <c r="D1937" s="66" t="s">
+      <c r="E1937" s="66" t="s">
         <v>8031</v>
-      </c>
-      <c r="E1937" s="66" t="s">
-        <v>8032</v>
       </c>
     </row>
     <row r="1938" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1938" s="65" t="s">
+        <v>8032</v>
+      </c>
+      <c r="B1938" s="66" t="s">
         <v>8033</v>
       </c>
-      <c r="B1938" s="66" t="s">
+      <c r="C1938" s="67" t="s">
         <v>8034</v>
       </c>
-      <c r="C1938" s="67" t="s">
+      <c r="D1938" s="66" t="s">
         <v>8035</v>
       </c>
-      <c r="D1938" s="66" t="s">
+      <c r="E1938" s="66" t="s">
         <v>8036</v>
-      </c>
-      <c r="E1938" s="66" t="s">
-        <v>8037</v>
       </c>
     </row>
     <row r="1939" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1939" s="65" t="s">
+        <v>8037</v>
+      </c>
+      <c r="B1939" s="66" t="s">
         <v>8038</v>
       </c>
-      <c r="B1939" s="66" t="s">
+      <c r="C1939" s="67" t="s">
         <v>8039</v>
       </c>
-      <c r="C1939" s="67" t="s">
+      <c r="D1939" s="66" t="s">
         <v>8040</v>
       </c>
-      <c r="D1939" s="66" t="s">
+      <c r="E1939" s="66" t="s">
         <v>8041</v>
-      </c>
-      <c r="E1939" s="66" t="s">
-        <v>8042</v>
       </c>
     </row>
     <row r="1940" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1940" s="65" t="s">
+        <v>8042</v>
+      </c>
+      <c r="B1940" s="66" t="s">
         <v>8043</v>
       </c>
-      <c r="B1940" s="66" t="s">
+      <c r="C1940" s="67" t="s">
         <v>8044</v>
       </c>
-      <c r="C1940" s="67" t="s">
+      <c r="D1940" s="66" t="s">
         <v>8045</v>
       </c>
-      <c r="D1940" s="66" t="s">
+      <c r="E1940" s="66" t="s">
         <v>8046</v>
-      </c>
-      <c r="E1940" s="66" t="s">
-        <v>8047</v>
       </c>
     </row>
     <row r="1941" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1941" s="65" t="s">
+        <v>8047</v>
+      </c>
+      <c r="B1941" s="66" t="s">
         <v>8048</v>
       </c>
-      <c r="B1941" s="66" t="s">
+      <c r="C1941" s="67" t="s">
         <v>8049</v>
       </c>
-      <c r="C1941" s="67" t="s">
+      <c r="D1941" s="66" t="s">
         <v>8050</v>
       </c>
-      <c r="D1941" s="66" t="s">
+      <c r="E1941" s="66" t="s">
         <v>8051</v>
-      </c>
-      <c r="E1941" s="66" t="s">
-        <v>8052</v>
       </c>
     </row>
     <row r="1942" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1942" s="65" t="s">
+        <v>8052</v>
+      </c>
+      <c r="B1942" s="66" t="s">
         <v>8053</v>
       </c>
-      <c r="B1942" s="66" t="s">
+      <c r="C1942" s="67" t="s">
         <v>8054</v>
       </c>
-      <c r="C1942" s="67" t="s">
+      <c r="D1942" s="66" t="s">
         <v>8055</v>
       </c>
-      <c r="D1942" s="66" t="s">
+      <c r="E1942" s="66" t="s">
         <v>8056</v>
-      </c>
-      <c r="E1942" s="66" t="s">
-        <v>8057</v>
       </c>
     </row>
     <row r="1943" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1943" s="65" t="s">
+        <v>8057</v>
+      </c>
+      <c r="B1943" s="66" t="s">
         <v>8058</v>
       </c>
-      <c r="B1943" s="66" t="s">
+      <c r="C1943" s="67" t="s">
         <v>8059</v>
       </c>
-      <c r="C1943" s="67" t="s">
+      <c r="D1943" s="66" t="s">
         <v>8060</v>
       </c>
-      <c r="D1943" s="66" t="s">
+      <c r="E1943" s="66" t="s">
         <v>8061</v>
-      </c>
-      <c r="E1943" s="66" t="s">
-        <v>8062</v>
       </c>
     </row>
     <row r="1944" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1944" s="65" t="s">
+        <v>8062</v>
+      </c>
+      <c r="B1944" s="66" t="s">
         <v>8063</v>
       </c>
-      <c r="B1944" s="66" t="s">
+      <c r="C1944" s="67" t="s">
         <v>8064</v>
       </c>
-      <c r="C1944" s="67" t="s">
+      <c r="D1944" s="66" t="s">
         <v>8065</v>
       </c>
-      <c r="D1944" s="66" t="s">
+      <c r="E1944" s="66" t="s">
         <v>8066</v>
-      </c>
-      <c r="E1944" s="66" t="s">
-        <v>8067</v>
       </c>
     </row>
     <row r="1945" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1945" s="65" t="s">
+        <v>8067</v>
+      </c>
+      <c r="B1945" s="66" t="s">
         <v>8068</v>
       </c>
-      <c r="B1945" s="66" t="s">
+      <c r="C1945" s="67" t="s">
         <v>8069</v>
       </c>
-      <c r="C1945" s="67" t="s">
+      <c r="D1945" s="66" t="s">
         <v>8070</v>
       </c>
-      <c r="D1945" s="66" t="s">
-        <v>8071</v>
-      </c>
       <c r="E1945" s="66" t="s">
-        <v>8072</v>
+        <v>8216</v>
       </c>
     </row>
     <row r="1946" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1946" s="65" t="s">
+        <v>8071</v>
+      </c>
+      <c r="B1946" s="66" t="s">
+        <v>8072</v>
+      </c>
+      <c r="C1946" s="67" t="s">
         <v>8073</v>
       </c>
-      <c r="B1946" s="66" t="s">
+      <c r="D1946" s="66" t="s">
         <v>8074</v>
       </c>
-      <c r="C1946" s="67" t="s">
+      <c r="E1946" s="66" t="s">
         <v>8075</v>
-      </c>
-      <c r="D1946" s="66" t="s">
-        <v>8076</v>
-      </c>
-      <c r="E1946" s="66" t="s">
-        <v>8077</v>
       </c>
     </row>
     <row r="1947" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1947" s="68" t="s">
+        <v>8076</v>
+      </c>
+      <c r="B1947" s="69" t="s">
+        <v>8077</v>
+      </c>
+      <c r="C1947" s="70" t="s">
         <v>8078</v>
       </c>
-      <c r="B1947" s="69" t="s">
+      <c r="D1947" s="69" t="s">
         <v>8079</v>
       </c>
-      <c r="C1947" s="70" t="s">
+      <c r="E1947" s="69" t="s">
         <v>8080</v>
-      </c>
-      <c r="D1947" s="69" t="s">
-        <v>8081</v>
-      </c>
-      <c r="E1947" s="69" t="s">
-        <v>8082</v>
       </c>
     </row>
     <row r="1948" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1948" s="15" t="s">
+        <v>8081</v>
+      </c>
+      <c r="B1948" s="13" t="s">
+        <v>8082</v>
+      </c>
+      <c r="C1948" s="71" t="s">
         <v>8083</v>
       </c>
-      <c r="B1948" s="13" t="s">
+      <c r="D1948" s="13" t="s">
         <v>8084</v>
       </c>
-      <c r="C1948" s="71" t="s">
+      <c r="E1948" s="13" t="s">
         <v>8085</v>
-      </c>
-      <c r="D1948" s="13" t="s">
-        <v>8086</v>
-      </c>
-      <c r="E1948" s="13" t="s">
-        <v>8087</v>
       </c>
     </row>
     <row r="1949" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1949" s="15" t="s">
+        <v>8086</v>
+      </c>
+      <c r="B1949" s="13" t="s">
+        <v>8087</v>
+      </c>
+      <c r="C1949" s="71" t="s">
         <v>8088</v>
       </c>
-      <c r="B1949" s="13" t="s">
+      <c r="D1949" s="13" t="s">
         <v>8089</v>
       </c>
-      <c r="C1949" s="71" t="s">
+      <c r="E1949" s="13" t="s">
         <v>8090</v>
-      </c>
-      <c r="D1949" s="13" t="s">
-        <v>8091</v>
-      </c>
-      <c r="E1949" s="13" t="s">
-        <v>8092</v>
       </c>
     </row>
     <row r="1950" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1950" s="10" t="s">
+        <v>8091</v>
+      </c>
+      <c r="B1950" s="11" t="s">
+        <v>8092</v>
+      </c>
+      <c r="C1950" s="72" t="s">
         <v>8093</v>
       </c>
-      <c r="B1950" s="11" t="s">
+      <c r="D1950" s="11" t="s">
         <v>8094</v>
       </c>
-      <c r="C1950" s="72" t="s">
+      <c r="E1950" s="11" t="s">
         <v>8095</v>
-      </c>
-      <c r="D1950" s="11" t="s">
-        <v>8096</v>
-      </c>
-      <c r="E1950" s="11" t="s">
-        <v>8097</v>
       </c>
     </row>
     <row r="1951" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1951" s="5" t="s">
+        <v>8096</v>
+      </c>
+      <c r="B1951" s="13" t="s">
+        <v>8097</v>
+      </c>
+      <c r="C1951" s="73" t="s">
         <v>8098</v>
       </c>
-      <c r="B1951" s="13" t="s">
+      <c r="D1951" s="8" t="s">
         <v>8099</v>
       </c>
-      <c r="C1951" s="73" t="s">
+      <c r="E1951" s="8" t="s">
         <v>8100</v>
-      </c>
-      <c r="D1951" s="8" t="s">
-        <v>8101</v>
-      </c>
-      <c r="E1951" s="8" t="s">
-        <v>8102</v>
       </c>
     </row>
     <row r="1952" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1952" s="5" t="s">
+        <v>8101</v>
+      </c>
+      <c r="B1952" s="13" t="s">
+        <v>8102</v>
+      </c>
+      <c r="C1952" s="73" t="s">
         <v>8103</v>
       </c>
-      <c r="B1952" s="13" t="s">
+      <c r="D1952" s="8" t="s">
         <v>8104</v>
       </c>
-      <c r="C1952" s="73" t="s">
+      <c r="E1952" s="8" t="s">
         <v>8105</v>
-      </c>
-      <c r="D1952" s="8" t="s">
-        <v>8106</v>
-      </c>
-      <c r="E1952" s="8" t="s">
-        <v>8107</v>
       </c>
     </row>
     <row r="1953" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1953" s="5" t="s">
+        <v>8106</v>
+      </c>
+      <c r="B1953" s="13" t="s">
+        <v>8107</v>
+      </c>
+      <c r="C1953" s="73" t="s">
         <v>8108</v>
       </c>
-      <c r="B1953" s="13" t="s">
+      <c r="D1953" s="8" t="s">
         <v>8109</v>
       </c>
-      <c r="C1953" s="73" t="s">
+      <c r="E1953" s="8" t="s">
         <v>8110</v>
-      </c>
-      <c r="D1953" s="8" t="s">
-        <v>8111</v>
-      </c>
-      <c r="E1953" s="8" t="s">
-        <v>8112</v>
       </c>
     </row>
     <row r="1954" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1954" s="5" t="s">
+        <v>8111</v>
+      </c>
+      <c r="B1954" s="13" t="s">
+        <v>8112</v>
+      </c>
+      <c r="C1954" s="73" t="s">
         <v>8113</v>
       </c>
-      <c r="B1954" s="13" t="s">
+      <c r="D1954" s="8" t="s">
         <v>8114</v>
       </c>
-      <c r="C1954" s="73" t="s">
+      <c r="E1954" s="8" t="s">
         <v>8115</v>
-      </c>
-      <c r="D1954" s="8" t="s">
-        <v>8116</v>
-      </c>
-      <c r="E1954" s="8" t="s">
-        <v>8117</v>
       </c>
     </row>
     <row r="1955" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1955" s="5" t="s">
+        <v>8116</v>
+      </c>
+      <c r="B1955" s="13" t="s">
+        <v>8117</v>
+      </c>
+      <c r="C1955" s="73" t="s">
         <v>8118</v>
       </c>
-      <c r="B1955" s="13" t="s">
+      <c r="D1955" s="8" t="s">
         <v>8119</v>
       </c>
-      <c r="C1955" s="73" t="s">
+      <c r="E1955" s="8" t="s">
         <v>8120</v>
-      </c>
-      <c r="D1955" s="8" t="s">
-        <v>8121</v>
-      </c>
-      <c r="E1955" s="8" t="s">
-        <v>8122</v>
       </c>
     </row>
     <row r="1956" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1956" s="5" t="s">
+        <v>8121</v>
+      </c>
+      <c r="B1956" s="13" t="s">
+        <v>8122</v>
+      </c>
+      <c r="C1956" s="73" t="s">
         <v>8123</v>
       </c>
-      <c r="B1956" s="13" t="s">
+      <c r="D1956" s="8" t="s">
         <v>8124</v>
       </c>
-      <c r="C1956" s="73" t="s">
+      <c r="E1956" s="8" t="s">
         <v>8125</v>
-      </c>
-      <c r="D1956" s="8" t="s">
-        <v>8126</v>
-      </c>
-      <c r="E1956" s="8" t="s">
-        <v>8127</v>
       </c>
     </row>
     <row r="1957" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1957" s="5" t="s">
+        <v>8126</v>
+      </c>
+      <c r="B1957" s="13" t="s">
+        <v>8127</v>
+      </c>
+      <c r="C1957" s="73" t="s">
         <v>8128</v>
       </c>
-      <c r="B1957" s="13" t="s">
+      <c r="D1957" s="8" t="s">
         <v>8129</v>
       </c>
-      <c r="C1957" s="73" t="s">
+      <c r="E1957" s="8" t="s">
         <v>8130</v>
-      </c>
-      <c r="D1957" s="8" t="s">
-        <v>8131</v>
-      </c>
-      <c r="E1957" s="8" t="s">
-        <v>8132</v>
       </c>
     </row>
     <row r="1958" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1958" s="5" t="s">
+        <v>8131</v>
+      </c>
+      <c r="B1958" s="13" t="s">
+        <v>8132</v>
+      </c>
+      <c r="C1958" s="73" t="s">
         <v>8133</v>
       </c>
-      <c r="B1958" s="13" t="s">
+      <c r="D1958" s="8" t="s">
         <v>8134</v>
       </c>
-      <c r="C1958" s="73" t="s">
+      <c r="E1958" s="8" t="s">
         <v>8135</v>
-      </c>
-      <c r="D1958" s="8" t="s">
-        <v>8136</v>
-      </c>
-      <c r="E1958" s="8" t="s">
-        <v>8137</v>
       </c>
     </row>
     <row r="1959" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1959" s="5" t="s">
+        <v>8136</v>
+      </c>
+      <c r="B1959" s="13" t="s">
+        <v>8137</v>
+      </c>
+      <c r="C1959" s="73" t="s">
         <v>8138</v>
       </c>
-      <c r="B1959" s="13" t="s">
+      <c r="D1959" s="8" t="s">
         <v>8139</v>
       </c>
-      <c r="C1959" s="73" t="s">
+      <c r="E1959" s="8" t="s">
         <v>8140</v>
-      </c>
-      <c r="D1959" s="8" t="s">
-        <v>8141</v>
-      </c>
-      <c r="E1959" s="8" t="s">
-        <v>8142</v>
       </c>
     </row>
     <row r="1960" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1960" s="5" t="s">
+        <v>8141</v>
+      </c>
+      <c r="B1960" s="13" t="s">
+        <v>8142</v>
+      </c>
+      <c r="C1960" s="73" t="s">
         <v>8143</v>
       </c>
-      <c r="B1960" s="13" t="s">
+      <c r="D1960" s="8" t="s">
         <v>8144</v>
       </c>
-      <c r="C1960" s="73" t="s">
+      <c r="E1960" s="8" t="s">
         <v>8145</v>
-      </c>
-      <c r="D1960" s="8" t="s">
-        <v>8146</v>
-      </c>
-      <c r="E1960" s="8" t="s">
-        <v>8147</v>
       </c>
     </row>
     <row r="1961" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1961" s="5" t="s">
+        <v>8146</v>
+      </c>
+      <c r="B1961" s="13" t="s">
+        <v>8147</v>
+      </c>
+      <c r="C1961" s="73" t="s">
         <v>8148</v>
       </c>
-      <c r="B1961" s="13" t="s">
+      <c r="D1961" s="8" t="s">
         <v>8149</v>
       </c>
-      <c r="C1961" s="73" t="s">
+      <c r="E1961" s="8" t="s">
         <v>8150</v>
-      </c>
-      <c r="D1961" s="8" t="s">
-        <v>8151</v>
-      </c>
-      <c r="E1961" s="8" t="s">
-        <v>8152</v>
       </c>
     </row>
     <row r="1962" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1962" s="5" t="s">
+        <v>8151</v>
+      </c>
+      <c r="B1962" s="13" t="s">
+        <v>8152</v>
+      </c>
+      <c r="C1962" s="73" t="s">
         <v>8153</v>
       </c>
-      <c r="B1962" s="13" t="s">
+      <c r="D1962" s="8" t="s">
         <v>8154</v>
       </c>
-      <c r="C1962" s="73" t="s">
+      <c r="E1962" s="8" t="s">
         <v>8155</v>
-      </c>
-      <c r="D1962" s="8" t="s">
-        <v>8156</v>
-      </c>
-      <c r="E1962" s="8" t="s">
-        <v>8157</v>
       </c>
     </row>
     <row r="1963" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1963" s="5" t="s">
+        <v>8156</v>
+      </c>
+      <c r="B1963" s="13" t="s">
+        <v>8157</v>
+      </c>
+      <c r="C1963" s="73" t="s">
         <v>8158</v>
       </c>
-      <c r="B1963" s="13" t="s">
+      <c r="D1963" s="8" t="s">
         <v>8159</v>
       </c>
-      <c r="C1963" s="73" t="s">
+      <c r="E1963" s="8" t="s">
         <v>8160</v>
-      </c>
-      <c r="D1963" s="8" t="s">
-        <v>8161</v>
-      </c>
-      <c r="E1963" s="8" t="s">
-        <v>8162</v>
       </c>
     </row>
     <row r="1964" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1964" s="5" t="s">
+        <v>8161</v>
+      </c>
+      <c r="B1964" s="13" t="s">
+        <v>8162</v>
+      </c>
+      <c r="C1964" s="73" t="s">
         <v>8163</v>
       </c>
-      <c r="B1964" s="13" t="s">
+      <c r="D1964" s="8" t="s">
         <v>8164</v>
       </c>
-      <c r="C1964" s="73" t="s">
+      <c r="E1964" s="8" t="s">
         <v>8165</v>
-      </c>
-      <c r="D1964" s="8" t="s">
-        <v>8166</v>
-      </c>
-      <c r="E1964" s="8" t="s">
-        <v>8167</v>
       </c>
     </row>
     <row r="1965" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1965" s="5" t="s">
+        <v>8166</v>
+      </c>
+      <c r="B1965" s="13" t="s">
+        <v>8167</v>
+      </c>
+      <c r="C1965" s="73" t="s">
         <v>8168</v>
       </c>
-      <c r="B1965" s="13" t="s">
+      <c r="D1965" s="8" t="s">
         <v>8169</v>
       </c>
-      <c r="C1965" s="73" t="s">
+      <c r="E1965" s="8" t="s">
         <v>8170</v>
-      </c>
-      <c r="D1965" s="8" t="s">
-        <v>8171</v>
-      </c>
-      <c r="E1965" s="8" t="s">
-        <v>8172</v>
       </c>
     </row>
     <row r="1966" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1966" s="5" t="s">
+        <v>8171</v>
+      </c>
+      <c r="B1966" s="13" t="s">
+        <v>8172</v>
+      </c>
+      <c r="C1966" s="73" t="s">
         <v>8173</v>
       </c>
-      <c r="B1966" s="13" t="s">
+      <c r="D1966" s="8" t="s">
         <v>8174</v>
       </c>
-      <c r="C1966" s="73" t="s">
+      <c r="E1966" s="8" t="s">
         <v>8175</v>
-      </c>
-      <c r="D1966" s="8" t="s">
-        <v>8176</v>
-      </c>
-      <c r="E1966" s="8" t="s">
-        <v>8177</v>
       </c>
     </row>
     <row r="1967" spans="1:5" ht="39" x14ac:dyDescent="0.25">
       <c r="A1967" s="5" t="s">
+        <v>8176</v>
+      </c>
+      <c r="B1967" s="13" t="s">
+        <v>8177</v>
+      </c>
+      <c r="C1967" s="73" t="s">
         <v>8178</v>
       </c>
-      <c r="B1967" s="13" t="s">
+      <c r="D1967" s="8" t="s">
         <v>8179</v>
       </c>
-      <c r="C1967" s="73" t="s">
+      <c r="E1967" s="8" t="s">
         <v>8180</v>
-      </c>
-      <c r="D1967" s="8" t="s">
-        <v>8181</v>
-      </c>
-      <c r="E1967" s="8" t="s">
-        <v>8182</v>
       </c>
     </row>
     <row r="1968" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1968" s="5" t="s">
+        <v>8181</v>
+      </c>
+      <c r="B1968" s="13" t="s">
+        <v>8182</v>
+      </c>
+      <c r="C1968" s="73" t="s">
         <v>8183</v>
       </c>
-      <c r="B1968" s="13" t="s">
+      <c r="D1968" s="8" t="s">
         <v>8184</v>
       </c>
-      <c r="C1968" s="73" t="s">
+      <c r="E1968" s="8" t="s">
         <v>8185</v>
-      </c>
-      <c r="D1968" s="8" t="s">
-        <v>8186</v>
-      </c>
-      <c r="E1968" s="8" t="s">
-        <v>8187</v>
       </c>
     </row>
     <row r="1969" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1969" s="5" t="s">
+        <v>8186</v>
+      </c>
+      <c r="B1969" s="13" t="s">
+        <v>8187</v>
+      </c>
+      <c r="C1969" s="73" t="s">
         <v>8188</v>
       </c>
-      <c r="B1969" s="13" t="s">
+      <c r="D1969" s="8" t="s">
         <v>8189</v>
       </c>
-      <c r="C1969" s="73" t="s">
+      <c r="E1969" s="8" t="s">
         <v>8190</v>
-      </c>
-      <c r="D1969" s="8" t="s">
-        <v>8191</v>
-      </c>
-      <c r="E1969" s="8" t="s">
-        <v>8192</v>
       </c>
     </row>
     <row r="1970" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1970" s="5" t="s">
+        <v>8191</v>
+      </c>
+      <c r="B1970" s="13" t="s">
+        <v>8192</v>
+      </c>
+      <c r="C1970" s="73" t="s">
         <v>8193</v>
       </c>
-      <c r="B1970" s="13" t="s">
+      <c r="D1970" s="8" t="s">
         <v>8194</v>
       </c>
-      <c r="C1970" s="73" t="s">
+      <c r="E1970" s="8" t="s">
         <v>8195</v>
-      </c>
-      <c r="D1970" s="8" t="s">
-        <v>8196</v>
-      </c>
-      <c r="E1970" s="8" t="s">
-        <v>8197</v>
       </c>
     </row>
     <row r="1971" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1971" s="5" t="s">
+        <v>8196</v>
+      </c>
+      <c r="B1971" s="13" t="s">
+        <v>8197</v>
+      </c>
+      <c r="C1971" s="73" t="s">
         <v>8198</v>
       </c>
-      <c r="B1971" s="13" t="s">
+      <c r="D1971" s="8" t="s">
         <v>8199</v>
       </c>
-      <c r="C1971" s="73" t="s">
+      <c r="E1971" s="8" t="s">
         <v>8200</v>
-      </c>
-      <c r="D1971" s="8" t="s">
-        <v>8201</v>
-      </c>
-      <c r="E1971" s="8" t="s">
-        <v>8202</v>
       </c>
     </row>
     <row r="1972" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1972" s="5" t="s">
+        <v>8201</v>
+      </c>
+      <c r="B1972" s="13" t="s">
+        <v>8202</v>
+      </c>
+      <c r="C1972" s="73" t="s">
         <v>8203</v>
       </c>
-      <c r="B1972" s="13" t="s">
+      <c r="D1972" s="8" t="s">
         <v>8204</v>
       </c>
-      <c r="C1972" s="73" t="s">
+      <c r="E1972" s="8" t="s">
         <v>8205</v>
-      </c>
-      <c r="D1972" s="8" t="s">
-        <v>8206</v>
-      </c>
-      <c r="E1972" s="8" t="s">
-        <v>8207</v>
       </c>
     </row>
     <row r="1973" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1973" s="5" t="s">
+        <v>8206</v>
+      </c>
+      <c r="B1973" s="13" t="s">
+        <v>8207</v>
+      </c>
+      <c r="C1973" s="73" t="s">
         <v>8208</v>
       </c>
-      <c r="B1973" s="13" t="s">
+      <c r="D1973" s="8" t="s">
         <v>8209</v>
       </c>
-      <c r="C1973" s="73" t="s">
+      <c r="E1973" s="8" t="s">
         <v>8210</v>
-      </c>
-      <c r="D1973" s="8" t="s">
-        <v>8211</v>
-      </c>
-      <c r="E1973" s="8" t="s">
-        <v>8212</v>
       </c>
     </row>
     <row r="1974" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A1974" s="5" t="s">
+        <v>8211</v>
+      </c>
+      <c r="B1974" s="13" t="s">
+        <v>8212</v>
+      </c>
+      <c r="C1974" s="73" t="s">
         <v>8213</v>
       </c>
-      <c r="B1974" s="13" t="s">
+      <c r="D1974" s="8" t="s">
         <v>8214</v>
       </c>
-      <c r="C1974" s="73" t="s">
+      <c r="E1974" s="8" t="s">
         <v>8215</v>
-      </c>
-      <c r="D1974" s="8" t="s">
-        <v>8216</v>
-      </c>
-      <c r="E1974" s="8" t="s">
-        <v>8217</v>
       </c>
     </row>
   </sheetData>

--- a/pvz.xlsx
+++ b/pvz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\taziz\Desktop\PVZ_BOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68524A5-8659-426F-B4A9-05D74FEFB485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B332B5C-83A2-4580-A46D-8E72D3D1C417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1620" yWindow="2505" windowWidth="21600" windowHeight="11325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8232" uniqueCount="8218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8272" uniqueCount="8258">
   <si>
     <t>Toshkent sh., Chilonzor tumani, 7-mavze, 45b-uy (Qatortol): г. Ташкент, Чиланзарский район, квартал-7, д 45б (Катартал)</t>
   </si>
@@ -24690,18 +24690,146 @@
   </si>
   <si>
     <t>39.927109, 66.895948</t>
+  </si>
+  <si>
+    <t>Toshkent sh., Chilonzor tumani, 3 kvartal, 53 uy: г. Ташкент, Чиланзарский район, 3 квартал , 53 дом</t>
+  </si>
+  <si>
+    <t>FrТАШ-426</t>
+  </si>
+  <si>
+    <t>998 92 182 06 49</t>
+  </si>
+  <si>
+    <t>@uzumfrtash_426</t>
+  </si>
+  <si>
+    <t>41.283308, 69.221966</t>
+  </si>
+  <si>
+    <t>Kuyi Abran sh., Koson tumani, Buyuk Ipak yo‘li ko'chasi, 164 uy : г. Куйи Абран, Касанский район, улица Буюк Ипак Йули, дом 164</t>
+  </si>
+  <si>
+    <t>FrКУА-1</t>
+  </si>
+  <si>
+    <t>998 50 502 19 92</t>
+  </si>
+  <si>
+    <t>@FrKUA1</t>
+  </si>
+  <si>
+    <t>38.994226, 65.651009</t>
+  </si>
+  <si>
+    <t>Urganch sh., Yog'du ko'chasi, 4 uy: г. Ургенч, улица Ёгду, дом 4</t>
+  </si>
+  <si>
+    <t>FrУРГ-31</t>
+  </si>
+  <si>
+    <t>998 90 640 47 23</t>
+  </si>
+  <si>
+    <t>@frurg31</t>
+  </si>
+  <si>
+    <t>41.551258, 60.617236</t>
+  </si>
+  <si>
+    <t>Kattaqo‘rg‘on sh., Oʻzbekiston koʻchasi, 7/12 uy : г. Каттакурган, улица Узбекистон, дом 7/12</t>
+  </si>
+  <si>
+    <t>FrКТГ-12</t>
+  </si>
+  <si>
+    <t>998 33 423 71 97</t>
+  </si>
+  <si>
+    <t>@frktg_12</t>
+  </si>
+  <si>
+    <t>39.914290, 66.255511</t>
+  </si>
+  <si>
+    <t>Denov sh., Qoʻzichoqli 1-koʻchasi, 71A uy : г. Денау, 1-я улица Кузичогли, дом 71А</t>
+  </si>
+  <si>
+    <t>FrДЕН-13</t>
+  </si>
+  <si>
+    <t>998 97 945 42 76</t>
+  </si>
+  <si>
+    <t>@FrDEN_13</t>
+  </si>
+  <si>
+    <t>38.244920, 67.876278</t>
+  </si>
+  <si>
+    <t>Bogot sh., Dexkonobod MFY, Mingmehmon ko'chasi, 1024 uy: г. Багат, Дексконобод МФИ, улица Мингмехмон, дом 1024</t>
+  </si>
+  <si>
+    <t>FrБГТ-4</t>
+  </si>
+  <si>
+    <t>998 90 004 93 30</t>
+  </si>
+  <si>
+    <t>@FRBGT4</t>
+  </si>
+  <si>
+    <t>41.335708, 60.911367</t>
+  </si>
+  <si>
+    <t>Denov sh., Yashil Diyor koʻchasi, 8 uy : г. Денау, улица Яшил Диёр, дом 8</t>
+  </si>
+  <si>
+    <t>FrДЕН-12</t>
+  </si>
+  <si>
+    <t>998 95 931 18 99</t>
+  </si>
+  <si>
+    <t>@Frden12</t>
+  </si>
+  <si>
+    <t>38.322719, 67.826044</t>
+  </si>
+  <si>
+    <t>Chirchiq sh., Amir Temur shohkoʻchasi, 9 kichik noxiya mavzesi, 17 uy : г. Чирчик, проспект Амира Темура, 9-й кичик нохия массив, дом 17</t>
+  </si>
+  <si>
+    <t>FrЧИР-24</t>
+  </si>
+  <si>
+    <t>998 33 919 63 62</t>
+  </si>
+  <si>
+    <t>@FrCHIR24</t>
+  </si>
+  <si>
+    <t>41.459610, 69.562934</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -24992,57 +25120,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25051,7 +25188,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25060,16 +25197,19 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25078,16 +25218,10 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25096,13 +25230,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25111,40 +25248,37 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25180,31 +25314,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -25517,7 +25651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1974"/>
+  <dimension ref="A1:E1982"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="58.28515625" style="1" customWidth="1"/>
@@ -59066,20 +59200,156 @@
       </c>
     </row>
     <row r="1974" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A1974" s="5" t="s">
+      <c r="A1974" s="10" t="s">
         <v>8211</v>
       </c>
-      <c r="B1974" s="13" t="s">
+      <c r="B1974" s="17" t="s">
         <v>8212</v>
       </c>
-      <c r="C1974" s="73" t="s">
+      <c r="C1974" s="74" t="s">
         <v>8213</v>
       </c>
-      <c r="D1974" s="8" t="s">
+      <c r="D1974" s="11" t="s">
         <v>8214</v>
       </c>
-      <c r="E1974" s="8" t="s">
+      <c r="E1974" s="11" t="s">
         <v>8215</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1975" s="5" t="s">
+        <v>8218</v>
+      </c>
+      <c r="B1975" s="13" t="s">
+        <v>8219</v>
+      </c>
+      <c r="C1975" s="75" t="s">
+        <v>8220</v>
+      </c>
+      <c r="D1975" s="8" t="s">
+        <v>8221</v>
+      </c>
+      <c r="E1975" s="8" t="s">
+        <v>8222</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1976" s="5" t="s">
+        <v>8223</v>
+      </c>
+      <c r="B1976" s="13" t="s">
+        <v>8224</v>
+      </c>
+      <c r="C1976" s="75" t="s">
+        <v>8225</v>
+      </c>
+      <c r="D1976" s="8" t="s">
+        <v>8226</v>
+      </c>
+      <c r="E1976" s="8" t="s">
+        <v>8227</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1977" s="5" t="s">
+        <v>8228</v>
+      </c>
+      <c r="B1977" s="13" t="s">
+        <v>8229</v>
+      </c>
+      <c r="C1977" s="75" t="s">
+        <v>8230</v>
+      </c>
+      <c r="D1977" s="8" t="s">
+        <v>8231</v>
+      </c>
+      <c r="E1977" s="8" t="s">
+        <v>8232</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1978" s="5" t="s">
+        <v>8233</v>
+      </c>
+      <c r="B1978" s="13" t="s">
+        <v>8234</v>
+      </c>
+      <c r="C1978" s="75" t="s">
+        <v>8235</v>
+      </c>
+      <c r="D1978" s="8" t="s">
+        <v>8236</v>
+      </c>
+      <c r="E1978" s="8" t="s">
+        <v>8237</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1979" s="5" t="s">
+        <v>8238</v>
+      </c>
+      <c r="B1979" s="13" t="s">
+        <v>8239</v>
+      </c>
+      <c r="C1979" s="75" t="s">
+        <v>8240</v>
+      </c>
+      <c r="D1979" s="8" t="s">
+        <v>8241</v>
+      </c>
+      <c r="E1979" s="8" t="s">
+        <v>8242</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1980" s="5" t="s">
+        <v>8243</v>
+      </c>
+      <c r="B1980" s="13" t="s">
+        <v>8244</v>
+      </c>
+      <c r="C1980" s="75" t="s">
+        <v>8245</v>
+      </c>
+      <c r="D1980" s="8" t="s">
+        <v>8246</v>
+      </c>
+      <c r="E1980" s="8" t="s">
+        <v>8247</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1981" s="5" t="s">
+        <v>8248</v>
+      </c>
+      <c r="B1981" s="13" t="s">
+        <v>8249</v>
+      </c>
+      <c r="C1981" s="75" t="s">
+        <v>8250</v>
+      </c>
+      <c r="D1981" s="8" t="s">
+        <v>8251</v>
+      </c>
+      <c r="E1981" s="8" t="s">
+        <v>8252</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:5" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A1982" s="5" t="s">
+        <v>8253</v>
+      </c>
+      <c r="B1982" s="13" t="s">
+        <v>8254</v>
+      </c>
+      <c r="C1982" s="75" t="s">
+        <v>8255</v>
+      </c>
+      <c r="D1982" s="8" t="s">
+        <v>8256</v>
+      </c>
+      <c r="E1982" s="8" t="s">
+        <v>8257</v>
       </c>
     </row>
   </sheetData>
